--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5009,6 +5009,12 @@
       <c r="AI54" t="n">
         <v>235</v>
       </c>
+      <c r="AK54" t="n">
+        <v>135.61</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0.4</v>
+      </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
@@ -5022,6 +5028,24 @@
     <row r="55">
       <c r="A55" s="1" t="n">
         <v>46243</v>
+      </c>
+      <c r="B55" t="n">
+        <v>146.3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>9</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>22.9</v>
       </c>
+      <c r="V2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y2" t="n">
         <v>7</v>
       </c>
@@ -686,6 +695,15 @@
       </c>
       <c r="AA2" t="n">
         <v>12.8</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.4</v>
       </c>
       <c r="AF2" t="n">
         <v>221.34</v>
@@ -785,6 +803,15 @@
       <c r="T3" t="n">
         <v>22.3</v>
       </c>
+      <c r="V3" t="n">
+        <v>11</v>
+      </c>
+      <c r="W3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y3" t="n">
         <v>10</v>
       </c>
@@ -793,6 +820,15 @@
       </c>
       <c r="AA3" t="n">
         <v>11.8</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5</v>
       </c>
       <c r="AF3" t="n">
         <v>219.56</v>
@@ -865,6 +901,15 @@
       <c r="O4" t="n">
         <v>39.1</v>
       </c>
+      <c r="V4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>13.9</v>
+      </c>
       <c r="Y4" t="n">
         <v>8</v>
       </c>
@@ -873,6 +918,15 @@
       </c>
       <c r="AA4" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF4" t="n">
         <v>220.8</v>
@@ -939,6 +993,15 @@
       <c r="O5" t="n">
         <v>40.7</v>
       </c>
+      <c r="V5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y5" t="n">
         <v>4</v>
       </c>
@@ -947,6 +1010,15 @@
       </c>
       <c r="AA5" t="n">
         <v>9.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.1</v>
       </c>
       <c r="AF5" t="n">
         <v>225.5</v>
@@ -1040,6 +1112,15 @@
       <c r="T6" t="n">
         <v>21.9</v>
       </c>
+      <c r="V6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>12.5</v>
+      </c>
       <c r="Y6" t="n">
         <v>9</v>
       </c>
@@ -1048,6 +1129,15 @@
       </c>
       <c r="AA6" t="n">
         <v>11.1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.4</v>
       </c>
       <c r="AF6" t="n">
         <v>231.46</v>
@@ -1147,6 +1237,15 @@
       <c r="T7" t="n">
         <v>20.7</v>
       </c>
+      <c r="V7" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X7" t="n">
+        <v>12.3</v>
+      </c>
       <c r="Y7" t="n">
         <v>7</v>
       </c>
@@ -1155,6 +1254,15 @@
       </c>
       <c r="AA7" t="n">
         <v>10.9</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3</v>
       </c>
       <c r="AF7" t="n">
         <v>231.82</v>
@@ -1254,6 +1362,15 @@
       <c r="T8" t="n">
         <v>21.6</v>
       </c>
+      <c r="V8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X8" t="n">
+        <v>11</v>
+      </c>
       <c r="Y8" t="n">
         <v>4</v>
       </c>
@@ -1262,6 +1379,15 @@
       </c>
       <c r="AA8" t="n">
         <v>9.199999999999999</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.9</v>
       </c>
       <c r="AF8" t="n">
         <v>230.65</v>
@@ -1361,6 +1487,15 @@
       <c r="T9" t="n">
         <v>21.6</v>
       </c>
+      <c r="V9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11.3</v>
+      </c>
       <c r="Y9" t="n">
         <v>4</v>
       </c>
@@ -1369,6 +1504,15 @@
       </c>
       <c r="AA9" t="n">
         <v>8.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>5.3</v>
       </c>
       <c r="AF9" t="n">
         <v>227.74</v>
@@ -1468,6 +1612,15 @@
       <c r="T10" t="n">
         <v>22.1</v>
       </c>
+      <c r="V10" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>13.5</v>
+      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1476,6 +1629,15 @@
       </c>
       <c r="AA10" t="n">
         <v>9.1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5</v>
       </c>
       <c r="AF10" t="n">
         <v>226.8</v>
@@ -1548,6 +1710,15 @@
       <c r="O11" t="n">
         <v>40.1</v>
       </c>
+      <c r="V11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12</v>
+      </c>
       <c r="Y11" t="n">
         <v>3</v>
       </c>
@@ -1556,6 +1727,15 @@
       </c>
       <c r="AA11" t="n">
         <v>8.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4.1</v>
       </c>
       <c r="AF11" t="n">
         <v>226.39</v>
@@ -1610,6 +1790,15 @@
       <c r="O12" t="n">
         <v>40.8</v>
       </c>
+      <c r="V12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y12" t="n">
         <v>7</v>
       </c>
@@ -1618,6 +1807,15 @@
       </c>
       <c r="AA12" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.4</v>
       </c>
       <c r="AF12" t="n">
         <v>229.98</v>
@@ -1699,6 +1897,15 @@
       <c r="T13" t="n">
         <v>22</v>
       </c>
+      <c r="V13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y13" t="n">
         <v>8</v>
       </c>
@@ -1707,6 +1914,15 @@
       </c>
       <c r="AA13" t="n">
         <v>13</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.8</v>
       </c>
       <c r="AF13" t="n">
         <v>236.38</v>
@@ -1794,6 +2010,15 @@
       <c r="T14" t="n">
         <v>20.9</v>
       </c>
+      <c r="V14" t="n">
+        <v>6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>10.4</v>
+      </c>
       <c r="Y14" t="n">
         <v>5</v>
       </c>
@@ -1802,6 +2027,15 @@
       </c>
       <c r="AA14" t="n">
         <v>9.9</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
         <v>236.23</v>
@@ -1889,6 +2123,15 @@
       <c r="T15" t="n">
         <v>22</v>
       </c>
+      <c r="V15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y15" t="n">
         <v>3</v>
       </c>
@@ -1897,6 +2140,15 @@
       </c>
       <c r="AA15" t="n">
         <v>9.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-2.9</v>
       </c>
       <c r="AF15" t="n">
         <v>236.72</v>
@@ -1984,6 +2236,15 @@
       <c r="T16" t="n">
         <v>21.8</v>
       </c>
+      <c r="V16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.2</v>
+      </c>
       <c r="Y16" t="n">
         <v>4</v>
       </c>
@@ -1992,6 +2253,15 @@
       </c>
       <c r="AA16" t="n">
         <v>9.699999999999999</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-6.5</v>
       </c>
       <c r="AF16" t="n">
         <v>229.92</v>
@@ -2079,6 +2349,15 @@
       <c r="T17" t="n">
         <v>22.7</v>
       </c>
+      <c r="V17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>10</v>
+      </c>
+      <c r="X17" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="Y17" t="n">
         <v>1</v>
       </c>
@@ -2087,6 +2366,15 @@
       </c>
       <c r="AA17" t="n">
         <v>6.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-3.3</v>
       </c>
       <c r="AF17" t="n">
         <v>223</v>
@@ -2147,6 +2435,15 @@
       <c r="O18" t="n">
         <v>39.4</v>
       </c>
+      <c r="V18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="X18" t="n">
+        <v>7.6</v>
+      </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
@@ -2155,6 +2452,15 @@
       </c>
       <c r="AA18" t="n">
         <v>4.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-2.8</v>
       </c>
       <c r="AF18" t="n">
         <v>221.08</v>
@@ -2209,6 +2515,15 @@
       <c r="O19" t="n">
         <v>39.5</v>
       </c>
+      <c r="V19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>7.5</v>
+      </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
@@ -2217,6 +2532,15 @@
       </c>
       <c r="AA19" t="n">
         <v>5.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-1.3</v>
       </c>
       <c r="AF19" t="n">
         <v>221.24</v>
@@ -2298,6 +2622,15 @@
       <c r="T20" t="n">
         <v>22.7</v>
       </c>
+      <c r="V20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W20" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="Y20" t="n">
         <v>5</v>
       </c>
@@ -2306,6 +2639,15 @@
       </c>
       <c r="AA20" t="n">
         <v>6.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1.2</v>
       </c>
       <c r="AF20" t="n">
         <v>223.94</v>
@@ -2393,6 +2735,15 @@
       <c r="T21" t="n">
         <v>23</v>
       </c>
+      <c r="V21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>9.5</v>
+      </c>
       <c r="Y21" t="n">
         <v>5</v>
       </c>
@@ -2401,6 +2752,15 @@
       </c>
       <c r="AA21" t="n">
         <v>7.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>224.33</v>
@@ -2488,6 +2848,15 @@
       <c r="T22" t="n">
         <v>23</v>
       </c>
+      <c r="V22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>10.2</v>
+      </c>
       <c r="Y22" t="n">
         <v>2.4</v>
       </c>
@@ -2496,6 +2865,15 @@
       </c>
       <c r="AA22" t="n">
         <v>10.3</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF22" t="n">
         <v>224.34</v>
@@ -2556,6 +2934,15 @@
       <c r="O23" t="n">
         <v>40.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X23" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y23" t="n">
         <v>8</v>
       </c>
@@ -2564,6 +2951,15 @@
       </c>
       <c r="AA23" t="n">
         <v>14</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.6</v>
       </c>
       <c r="AF23" t="n">
         <v>231.46</v>
@@ -2618,6 +3014,15 @@
       <c r="O24" t="n">
         <v>40.6</v>
       </c>
+      <c r="V24" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>15.2</v>
+      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -2626,6 +3031,15 @@
       </c>
       <c r="AA24" t="n">
         <v>12.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-0.2</v>
       </c>
       <c r="AF24" t="n">
         <v>229.92</v>
@@ -2680,6 +3094,15 @@
       <c r="O25" t="n">
         <v>38</v>
       </c>
+      <c r="V25" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W25" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X25" t="n">
+        <v>13.8</v>
+      </c>
       <c r="Y25" t="n">
         <v>10</v>
       </c>
@@ -2688,6 +3111,15 @@
       </c>
       <c r="AA25" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AF25" t="n">
         <v>226.95</v>
@@ -2742,6 +3174,15 @@
       <c r="O26" t="n">
         <v>39.8</v>
       </c>
+      <c r="V26" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y26" t="n">
         <v>7</v>
       </c>
@@ -2750,6 +3191,15 @@
       </c>
       <c r="AA26" t="n">
         <v>11</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.6</v>
       </c>
       <c r="AF26" t="n">
         <v>223.11</v>
@@ -2804,6 +3254,15 @@
       <c r="O27" t="n">
         <v>40.2</v>
       </c>
+      <c r="V27" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X27" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y27" t="n">
         <v>7</v>
       </c>
@@ -2812,6 +3271,15 @@
       </c>
       <c r="AA27" t="n">
         <v>10</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4.8</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -2887,6 +3355,15 @@
       <c r="T28" t="n">
         <v>23</v>
       </c>
+      <c r="V28" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W28" t="n">
+        <v>20</v>
+      </c>
+      <c r="X28" t="n">
+        <v>14.4</v>
+      </c>
       <c r="Y28" t="n">
         <v>4</v>
       </c>
@@ -2895,6 +3372,15 @@
       </c>
       <c r="AA28" t="n">
         <v>7.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>6.2</v>
       </c>
       <c r="AF28" t="n">
         <v>220.36</v>
@@ -2982,6 +3468,15 @@
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
+      <c r="V29" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X29" t="n">
+        <v>14.9</v>
+      </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
@@ -2990,6 +3485,15 @@
       </c>
       <c r="AA29" t="n">
         <v>11.9</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>5.2</v>
       </c>
       <c r="AF29" t="n">
         <v>219.64</v>
@@ -3077,6 +3581,15 @@
       <c r="T30" t="n">
         <v>22.6</v>
       </c>
+      <c r="V30" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W30" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X30" t="n">
+        <v>17</v>
+      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3085,6 +3598,15 @@
       </c>
       <c r="AA30" t="n">
         <v>14.9</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF30" t="n">
         <v>224.93</v>
@@ -3172,6 +3694,15 @@
       <c r="T31" t="n">
         <v>21.5</v>
       </c>
+      <c r="V31" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>26</v>
+      </c>
+      <c r="X31" t="n">
+        <v>18.1</v>
+      </c>
       <c r="Y31" t="n">
         <v>17</v>
       </c>
@@ -3180,6 +3711,15 @@
       </c>
       <c r="AA31" t="n">
         <v>19.3</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF31" t="n">
         <v>232.31</v>
@@ -3234,6 +3774,15 @@
       <c r="O32" t="n">
         <v>39.2</v>
       </c>
+      <c r="V32" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>26.6</v>
+      </c>
       <c r="Y32" t="n">
         <v>18</v>
       </c>
@@ -3242,6 +3791,15 @@
       </c>
       <c r="AA32" t="n">
         <v>20.5</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.7</v>
       </c>
       <c r="AF32" t="n">
         <v>235.4</v>
@@ -3290,6 +3848,15 @@
       <c r="O33" t="n">
         <v>37.8</v>
       </c>
+      <c r="V33" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X33" t="n">
+        <v>17.9</v>
+      </c>
       <c r="Y33" t="n">
         <v>14</v>
       </c>
@@ -3298,6 +3865,15 @@
       </c>
       <c r="AA33" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.7</v>
       </c>
       <c r="AF33" t="n">
         <v>231.99</v>
@@ -3379,6 +3955,15 @@
       <c r="T34" t="n">
         <v>20.5</v>
       </c>
+      <c r="V34" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X34" t="n">
+        <v>16.7</v>
+      </c>
       <c r="Y34" t="n">
         <v>9</v>
       </c>
@@ -3387,6 +3972,15 @@
       </c>
       <c r="AA34" t="n">
         <v>11.1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AF34" t="n">
         <v>225.51</v>
@@ -3474,6 +4068,15 @@
       <c r="T35" t="n">
         <v>22.3</v>
       </c>
+      <c r="V35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X35" t="n">
+        <v>13.5</v>
+      </c>
       <c r="Y35" t="n">
         <v>9</v>
       </c>
@@ -3482,6 +4085,15 @@
       </c>
       <c r="AA35" t="n">
         <v>11.6</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>-1.3</v>
       </c>
       <c r="AF35" t="n">
         <v>220.92</v>
@@ -3569,6 +4181,15 @@
       <c r="T36" t="n">
         <v>22.5</v>
       </c>
+      <c r="V36" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W36" t="n">
+        <v>13</v>
+      </c>
+      <c r="X36" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -3577,6 +4198,15 @@
       </c>
       <c r="AA36" t="n">
         <v>11.4</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>-0.9</v>
       </c>
       <c r="AF36" t="n">
         <v>220.92</v>
@@ -3664,6 +4294,15 @@
       <c r="T37" t="n">
         <v>22.6</v>
       </c>
+      <c r="V37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X37" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y37" t="n">
         <v>9</v>
       </c>
@@ -3672,6 +4311,15 @@
       </c>
       <c r="AA37" t="n">
         <v>11.1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.5</v>
       </c>
       <c r="AF37" t="n">
         <v>216.02</v>
@@ -3759,6 +4407,15 @@
       <c r="T38" t="n">
         <v>23.3</v>
       </c>
+      <c r="V38" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X38" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y38" t="n">
         <v>8</v>
       </c>
@@ -3767,6 +4424,15 @@
       </c>
       <c r="AA38" t="n">
         <v>12.7</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4.7</v>
       </c>
       <c r="AF38" t="n">
         <v>216.02</v>
@@ -3821,6 +4487,15 @@
       <c r="O39" t="n">
         <v>39.2</v>
       </c>
+      <c r="V39" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X39" t="n">
+        <v>14</v>
+      </c>
       <c r="Y39" t="n">
         <v>12</v>
       </c>
@@ -3829,6 +4504,15 @@
       </c>
       <c r="AA39" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.4</v>
       </c>
       <c r="AF39" t="n">
         <v>224.53</v>
@@ -3877,6 +4561,15 @@
       <c r="O40" t="n">
         <v>39.3</v>
       </c>
+      <c r="V40" t="n">
+        <v>8</v>
+      </c>
+      <c r="W40" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X40" t="n">
+        <v>15.2</v>
+      </c>
       <c r="Y40" t="n">
         <v>11</v>
       </c>
@@ -3885,6 +4578,15 @@
       </c>
       <c r="AA40" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.1</v>
       </c>
       <c r="AF40" t="n">
         <v>230.27</v>
@@ -3966,6 +4668,15 @@
       <c r="T41" t="n">
         <v>21.7</v>
       </c>
+      <c r="V41" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W41" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X41" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y41" t="n">
         <v>12</v>
       </c>
@@ -3974,6 +4685,15 @@
       </c>
       <c r="AA41" t="n">
         <v>15.7</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AF41" t="n">
         <v>237.43</v>
@@ -4028,6 +4748,15 @@
       <c r="O42" t="n">
         <v>37.9</v>
       </c>
+      <c r="V42" t="n">
+        <v>10</v>
+      </c>
+      <c r="W42" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="X42" t="n">
+        <v>17.8</v>
+      </c>
       <c r="Y42" t="n">
         <v>13</v>
       </c>
@@ -4036,6 +4765,15 @@
       </c>
       <c r="AA42" t="n">
         <v>16</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9</v>
       </c>
       <c r="AF42" t="n">
         <v>236.14</v>
@@ -4117,6 +4855,15 @@
       <c r="T43" t="n">
         <v>20.3</v>
       </c>
+      <c r="V43" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W43" t="n">
+        <v>27</v>
+      </c>
+      <c r="X43" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y43" t="n">
         <v>11</v>
       </c>
@@ -4125,6 +4872,15 @@
       </c>
       <c r="AA43" t="n">
         <v>14.4</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>-0.4</v>
       </c>
       <c r="AF43" t="n">
         <v>236.13</v>
@@ -4212,6 +4968,15 @@
       <c r="T44" t="n">
         <v>19</v>
       </c>
+      <c r="V44" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W44" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X44" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y44" t="n">
         <v>9</v>
       </c>
@@ -4220,6 +4985,15 @@
       </c>
       <c r="AA44" t="n">
         <v>12.5</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>-0.7</v>
       </c>
       <c r="AF44" t="n">
         <v>218.6</v>
@@ -4307,6 +5081,15 @@
       <c r="T45" t="n">
         <v>21.6</v>
       </c>
+      <c r="V45" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y45" t="n">
         <v>11</v>
       </c>
@@ -4315,6 +5098,15 @@
       </c>
       <c r="AA45" t="n">
         <v>13.6</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.5</v>
       </c>
       <c r="AF45" t="n">
         <v>218.84</v>
@@ -4369,6 +5161,15 @@
       <c r="O46" t="n">
         <v>35.1</v>
       </c>
+      <c r="V46" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W46" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X46" t="n">
+        <v>19</v>
+      </c>
       <c r="Y46" t="n">
         <v>14</v>
       </c>
@@ -4377,6 +5178,15 @@
       </c>
       <c r="AA46" t="n">
         <v>17.5</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF46" t="n">
         <v>221.78</v>
@@ -4425,6 +5235,15 @@
       <c r="O47" t="n">
         <v>31.6</v>
       </c>
+      <c r="V47" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W47" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X47" t="n">
+        <v>19.8</v>
+      </c>
       <c r="Y47" t="n">
         <v>14</v>
       </c>
@@ -4433,6 +5252,15 @@
       </c>
       <c r="AA47" t="n">
         <v>16.5</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.1</v>
       </c>
       <c r="AF47" t="n">
         <v>224.78</v>
@@ -4514,6 +5342,15 @@
       <c r="T48" t="n">
         <v>21.6</v>
       </c>
+      <c r="V48" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W48" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X48" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y48" t="n">
         <v>12</v>
       </c>
@@ -4522,6 +5359,15 @@
       </c>
       <c r="AA48" t="n">
         <v>15.4</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>3.2</v>
       </c>
       <c r="AF48" t="n">
         <v>232.22</v>
@@ -4609,6 +5455,15 @@
       <c r="T49" t="n">
         <v>21.1</v>
       </c>
+      <c r="V49" t="n">
+        <v>13</v>
+      </c>
+      <c r="W49" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X49" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y49" t="n">
         <v>13</v>
       </c>
@@ -4617,6 +5472,15 @@
       </c>
       <c r="AA49" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2</v>
       </c>
       <c r="AF49" t="n">
         <v>229.69</v>
@@ -4959,6 +5823,12 @@
       <c r="AA53" t="n">
         <v>9</v>
       </c>
+      <c r="AF53" t="n">
+        <v>221.37</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0.05</v>
+      </c>
       <c r="AH53" t="n">
         <v>215</v>
       </c>
@@ -5003,6 +5873,12 @@
       <c r="AA54" t="n">
         <v>10</v>
       </c>
+      <c r="AF54" t="n">
+        <v>224.37</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3</v>
+      </c>
       <c r="AH54" t="n">
         <v>215</v>
       </c>
@@ -5053,6 +5929,12 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
+      <c r="AK55" t="n">
+        <v>135.28</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>-0.33</v>
+      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
@@ -5066,6 +5948,24 @@
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>46244</v>
+      </c>
+      <c r="B56" t="n">
+        <v>169.3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>36</v>
+      </c>
+      <c r="F56" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>8</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -696,15 +696,6 @@
       <c r="AA2" t="n">
         <v>12.8</v>
       </c>
-      <c r="AB2" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AF2" t="n">
         <v>221.34</v>
       </c>
@@ -821,15 +812,6 @@
       <c r="AA3" t="n">
         <v>11.8</v>
       </c>
-      <c r="AB3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>5</v>
-      </c>
       <c r="AF3" t="n">
         <v>219.56</v>
       </c>
@@ -919,15 +901,6 @@
       <c r="AA4" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF4" t="n">
         <v>220.8</v>
       </c>
@@ -1011,15 +984,6 @@
       <c r="AA5" t="n">
         <v>9.5</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AF5" t="n">
         <v>225.5</v>
       </c>
@@ -1130,15 +1094,6 @@
       <c r="AA6" t="n">
         <v>11.1</v>
       </c>
-      <c r="AB6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AF6" t="n">
         <v>231.46</v>
       </c>
@@ -1255,15 +1210,6 @@
       <c r="AA7" t="n">
         <v>10.9</v>
       </c>
-      <c r="AB7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3</v>
-      </c>
       <c r="AF7" t="n">
         <v>231.82</v>
       </c>
@@ -1380,15 +1326,6 @@
       <c r="AA8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AB8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AF8" t="n">
         <v>230.65</v>
       </c>
@@ -1505,15 +1442,6 @@
       <c r="AA9" t="n">
         <v>8.5</v>
       </c>
-      <c r="AB9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AF9" t="n">
         <v>227.74</v>
       </c>
@@ -1630,15 +1558,6 @@
       <c r="AA10" t="n">
         <v>9.1</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5</v>
-      </c>
       <c r="AF10" t="n">
         <v>226.8</v>
       </c>
@@ -1728,15 +1647,6 @@
       <c r="AA11" t="n">
         <v>8.5</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AF11" t="n">
         <v>226.39</v>
       </c>
@@ -1808,15 +1718,6 @@
       <c r="AA12" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AF12" t="n">
         <v>229.98</v>
       </c>
@@ -1915,15 +1816,6 @@
       <c r="AA13" t="n">
         <v>13</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AF13" t="n">
         <v>236.38</v>
       </c>
@@ -2028,15 +1920,6 @@
       <c r="AA14" t="n">
         <v>9.9</v>
       </c>
-      <c r="AB14" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AF14" t="n">
         <v>236.23</v>
       </c>
@@ -2141,15 +2024,6 @@
       <c r="AA15" t="n">
         <v>9.5</v>
       </c>
-      <c r="AB15" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>-2.9</v>
-      </c>
       <c r="AF15" t="n">
         <v>236.72</v>
       </c>
@@ -2254,15 +2128,6 @@
       <c r="AA16" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="AB16" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>-6.5</v>
-      </c>
       <c r="AF16" t="n">
         <v>229.92</v>
       </c>
@@ -2367,15 +2232,6 @@
       <c r="AA17" t="n">
         <v>6.1</v>
       </c>
-      <c r="AB17" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-3.3</v>
-      </c>
       <c r="AF17" t="n">
         <v>223</v>
       </c>
@@ -2453,15 +2309,6 @@
       <c r="AA18" t="n">
         <v>4.5</v>
       </c>
-      <c r="AB18" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-2.8</v>
-      </c>
       <c r="AF18" t="n">
         <v>221.08</v>
       </c>
@@ -2533,15 +2380,6 @@
       <c r="AA19" t="n">
         <v>5.5</v>
       </c>
-      <c r="AB19" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>-1.3</v>
-      </c>
       <c r="AF19" t="n">
         <v>221.24</v>
       </c>
@@ -2640,15 +2478,6 @@
       <c r="AA20" t="n">
         <v>6.1</v>
       </c>
-      <c r="AB20" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-1.2</v>
-      </c>
       <c r="AF20" t="n">
         <v>223.94</v>
       </c>
@@ -2753,15 +2582,6 @@
       <c r="AA21" t="n">
         <v>7.5</v>
       </c>
-      <c r="AB21" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF21" t="n">
         <v>224.33</v>
       </c>
@@ -2866,15 +2686,6 @@
       <c r="AA22" t="n">
         <v>10.3</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF22" t="n">
         <v>224.34</v>
       </c>
@@ -2952,15 +2763,6 @@
       <c r="AA23" t="n">
         <v>14</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AF23" t="n">
         <v>231.46</v>
       </c>
@@ -3032,15 +2834,6 @@
       <c r="AA24" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB24" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="AF24" t="n">
         <v>229.92</v>
       </c>
@@ -3112,15 +2905,6 @@
       <c r="AA25" t="n">
         <v>11.5</v>
       </c>
-      <c r="AB25" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="AF25" t="n">
         <v>226.95</v>
       </c>
@@ -3192,15 +2976,6 @@
       <c r="AA26" t="n">
         <v>11</v>
       </c>
-      <c r="AB26" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AF26" t="n">
         <v>223.11</v>
       </c>
@@ -3272,15 +3047,6 @@
       <c r="AA27" t="n">
         <v>10</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AH27" t="n">
         <v>215</v>
       </c>
@@ -3373,15 +3139,6 @@
       <c r="AA28" t="n">
         <v>7.7</v>
       </c>
-      <c r="AB28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AF28" t="n">
         <v>220.36</v>
       </c>
@@ -3486,15 +3243,6 @@
       <c r="AA29" t="n">
         <v>11.9</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AF29" t="n">
         <v>219.64</v>
       </c>
@@ -3599,15 +3347,6 @@
       <c r="AA30" t="n">
         <v>14.9</v>
       </c>
-      <c r="AB30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AF30" t="n">
         <v>224.93</v>
       </c>
@@ -3712,15 +3451,6 @@
       <c r="AA31" t="n">
         <v>19.3</v>
       </c>
-      <c r="AB31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AF31" t="n">
         <v>232.31</v>
       </c>
@@ -3792,15 +3522,6 @@
       <c r="AA32" t="n">
         <v>20.5</v>
       </c>
-      <c r="AB32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AF32" t="n">
         <v>235.4</v>
       </c>
@@ -3866,15 +3587,6 @@
       <c r="AA33" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB33" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF33" t="n">
         <v>231.99</v>
       </c>
@@ -3973,15 +3685,6 @@
       <c r="AA34" t="n">
         <v>11.1</v>
       </c>
-      <c r="AB34" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="AF34" t="n">
         <v>225.51</v>
       </c>
@@ -4086,15 +3789,6 @@
       <c r="AA35" t="n">
         <v>11.6</v>
       </c>
-      <c r="AB35" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>-1.3</v>
-      </c>
       <c r="AF35" t="n">
         <v>220.92</v>
       </c>
@@ -4199,15 +3893,6 @@
       <c r="AA36" t="n">
         <v>11.4</v>
       </c>
-      <c r="AB36" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF36" t="n">
         <v>220.92</v>
       </c>
@@ -4312,15 +3997,6 @@
       <c r="AA37" t="n">
         <v>11.1</v>
       </c>
-      <c r="AB37" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AF37" t="n">
         <v>216.02</v>
       </c>
@@ -4425,15 +4101,6 @@
       <c r="AA38" t="n">
         <v>12.7</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AF38" t="n">
         <v>216.02</v>
       </c>
@@ -4505,15 +4172,6 @@
       <c r="AA39" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB39" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AF39" t="n">
         <v>224.53</v>
       </c>
@@ -4579,15 +4237,6 @@
       <c r="AA40" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB40" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF40" t="n">
         <v>230.27</v>
       </c>
@@ -4686,15 +4335,6 @@
       <c r="AA41" t="n">
         <v>15.7</v>
       </c>
-      <c r="AB41" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="AF41" t="n">
         <v>237.43</v>
       </c>
@@ -4766,15 +4406,6 @@
       <c r="AA42" t="n">
         <v>16</v>
       </c>
-      <c r="AB42" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.9</v>
-      </c>
       <c r="AF42" t="n">
         <v>236.14</v>
       </c>
@@ -4873,15 +4504,6 @@
       <c r="AA43" t="n">
         <v>14.4</v>
       </c>
-      <c r="AB43" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>-0.4</v>
-      </c>
       <c r="AF43" t="n">
         <v>236.13</v>
       </c>
@@ -4986,15 +4608,6 @@
       <c r="AA44" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB44" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>-0.7</v>
-      </c>
       <c r="AF44" t="n">
         <v>218.6</v>
       </c>
@@ -5099,15 +4712,6 @@
       <c r="AA45" t="n">
         <v>13.6</v>
       </c>
-      <c r="AB45" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF45" t="n">
         <v>218.84</v>
       </c>
@@ -5179,15 +4783,6 @@
       <c r="AA46" t="n">
         <v>17.5</v>
       </c>
-      <c r="AB46" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AF46" t="n">
         <v>221.78</v>
       </c>
@@ -5253,15 +4848,6 @@
       <c r="AA47" t="n">
         <v>16.5</v>
       </c>
-      <c r="AB47" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF47" t="n">
         <v>224.78</v>
       </c>
@@ -5360,15 +4946,6 @@
       <c r="AA48" t="n">
         <v>15.4</v>
       </c>
-      <c r="AB48" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AF48" t="n">
         <v>232.22</v>
       </c>
@@ -5473,15 +5050,6 @@
       <c r="AA49" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB49" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2</v>
-      </c>
       <c r="AF49" t="n">
         <v>229.69</v>
       </c>
@@ -5568,6 +5136,15 @@
       <c r="T50" t="n">
         <v>21.3</v>
       </c>
+      <c r="V50" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W50" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X50" t="n">
+        <v>20</v>
+      </c>
       <c r="Y50" t="n">
         <v>11</v>
       </c>
@@ -5923,6 +5500,12 @@
       <c r="AA55" t="n">
         <v>9</v>
       </c>
+      <c r="AF55" t="n">
+        <v>225.93</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.56</v>
+      </c>
       <c r="AH55" t="n">
         <v>215</v>
       </c>
@@ -5967,11 +5550,23 @@
       <c r="AA56" t="n">
         <v>8</v>
       </c>
+      <c r="AF56" t="n">
+        <v>218.63</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>-7.3</v>
+      </c>
       <c r="AH56" t="n">
         <v>215</v>
       </c>
       <c r="AI56" t="n">
         <v>235</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>126.27</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>-9.01</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5986,6 +5581,24 @@
     <row r="57">
       <c r="A57" s="1" t="n">
         <v>46245</v>
+      </c>
+      <c r="B57" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>9</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -696,6 +696,15 @@
       <c r="AA2" t="n">
         <v>12.8</v>
       </c>
+      <c r="AB2" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="AF2" t="n">
         <v>221.34</v>
       </c>
@@ -812,6 +821,15 @@
       <c r="AA3" t="n">
         <v>11.8</v>
       </c>
+      <c r="AB3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5</v>
+      </c>
       <c r="AF3" t="n">
         <v>219.56</v>
       </c>
@@ -901,6 +919,15 @@
       <c r="AA4" t="n">
         <v>11.5</v>
       </c>
+      <c r="AB4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AF4" t="n">
         <v>220.8</v>
       </c>
@@ -984,6 +1011,15 @@
       <c r="AA5" t="n">
         <v>9.5</v>
       </c>
+      <c r="AB5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.1</v>
+      </c>
       <c r="AF5" t="n">
         <v>225.5</v>
       </c>
@@ -1094,6 +1130,15 @@
       <c r="AA6" t="n">
         <v>11.1</v>
       </c>
+      <c r="AB6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.4</v>
+      </c>
       <c r="AF6" t="n">
         <v>231.46</v>
       </c>
@@ -1210,6 +1255,15 @@
       <c r="AA7" t="n">
         <v>10.9</v>
       </c>
+      <c r="AB7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3</v>
+      </c>
       <c r="AF7" t="n">
         <v>231.82</v>
       </c>
@@ -1326,6 +1380,15 @@
       <c r="AA8" t="n">
         <v>9.199999999999999</v>
       </c>
+      <c r="AB8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AF8" t="n">
         <v>230.65</v>
       </c>
@@ -1442,6 +1505,15 @@
       <c r="AA9" t="n">
         <v>8.5</v>
       </c>
+      <c r="AB9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>5.3</v>
+      </c>
       <c r="AF9" t="n">
         <v>227.74</v>
       </c>
@@ -1558,6 +1630,15 @@
       <c r="AA10" t="n">
         <v>9.1</v>
       </c>
+      <c r="AB10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5</v>
+      </c>
       <c r="AF10" t="n">
         <v>226.8</v>
       </c>
@@ -1647,6 +1728,15 @@
       <c r="AA11" t="n">
         <v>8.5</v>
       </c>
+      <c r="AB11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4.1</v>
+      </c>
       <c r="AF11" t="n">
         <v>226.39</v>
       </c>
@@ -1718,6 +1808,15 @@
       <c r="AA12" t="n">
         <v>11.5</v>
       </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.4</v>
+      </c>
       <c r="AF12" t="n">
         <v>229.98</v>
       </c>
@@ -1816,6 +1915,15 @@
       <c r="AA13" t="n">
         <v>13</v>
       </c>
+      <c r="AB13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AF13" t="n">
         <v>236.38</v>
       </c>
@@ -1920,6 +2028,15 @@
       <c r="AA14" t="n">
         <v>9.9</v>
       </c>
+      <c r="AB14" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.5</v>
+      </c>
       <c r="AF14" t="n">
         <v>236.23</v>
       </c>
@@ -2024,6 +2141,15 @@
       <c r="AA15" t="n">
         <v>9.5</v>
       </c>
+      <c r="AB15" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-2.9</v>
+      </c>
       <c r="AF15" t="n">
         <v>236.72</v>
       </c>
@@ -2128,6 +2254,15 @@
       <c r="AA16" t="n">
         <v>9.699999999999999</v>
       </c>
+      <c r="AB16" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-6.5</v>
+      </c>
       <c r="AF16" t="n">
         <v>229.92</v>
       </c>
@@ -2232,6 +2367,15 @@
       <c r="AA17" t="n">
         <v>6.1</v>
       </c>
+      <c r="AB17" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-3.3</v>
+      </c>
       <c r="AF17" t="n">
         <v>223</v>
       </c>
@@ -2309,6 +2453,15 @@
       <c r="AA18" t="n">
         <v>4.5</v>
       </c>
+      <c r="AB18" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-2.8</v>
+      </c>
       <c r="AF18" t="n">
         <v>221.08</v>
       </c>
@@ -2380,6 +2533,15 @@
       <c r="AA19" t="n">
         <v>5.5</v>
       </c>
+      <c r="AB19" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-1.3</v>
+      </c>
       <c r="AF19" t="n">
         <v>221.24</v>
       </c>
@@ -2478,6 +2640,15 @@
       <c r="AA20" t="n">
         <v>6.1</v>
       </c>
+      <c r="AB20" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1.2</v>
+      </c>
       <c r="AF20" t="n">
         <v>223.94</v>
       </c>
@@ -2582,6 +2753,15 @@
       <c r="AA21" t="n">
         <v>7.5</v>
       </c>
+      <c r="AB21" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AF21" t="n">
         <v>224.33</v>
       </c>
@@ -2686,6 +2866,15 @@
       <c r="AA22" t="n">
         <v>10.3</v>
       </c>
+      <c r="AB22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4.3</v>
+      </c>
       <c r="AF22" t="n">
         <v>224.34</v>
       </c>
@@ -2763,6 +2952,15 @@
       <c r="AA23" t="n">
         <v>14</v>
       </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.6</v>
+      </c>
       <c r="AF23" t="n">
         <v>231.46</v>
       </c>
@@ -2834,6 +3032,15 @@
       <c r="AA24" t="n">
         <v>12.5</v>
       </c>
+      <c r="AB24" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="AF24" t="n">
         <v>229.92</v>
       </c>
@@ -2905,6 +3112,15 @@
       <c r="AA25" t="n">
         <v>11.5</v>
       </c>
+      <c r="AB25" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="AF25" t="n">
         <v>226.95</v>
       </c>
@@ -2976,6 +3192,15 @@
       <c r="AA26" t="n">
         <v>11</v>
       </c>
+      <c r="AB26" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AF26" t="n">
         <v>223.11</v>
       </c>
@@ -3047,6 +3272,15 @@
       <c r="AA27" t="n">
         <v>10</v>
       </c>
+      <c r="AB27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AH27" t="n">
         <v>215</v>
       </c>
@@ -3139,6 +3373,15 @@
       <c r="AA28" t="n">
         <v>7.7</v>
       </c>
+      <c r="AB28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>6.2</v>
+      </c>
       <c r="AF28" t="n">
         <v>220.36</v>
       </c>
@@ -3243,6 +3486,15 @@
       <c r="AA29" t="n">
         <v>11.9</v>
       </c>
+      <c r="AB29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>5.2</v>
+      </c>
       <c r="AF29" t="n">
         <v>219.64</v>
       </c>
@@ -3347,6 +3599,15 @@
       <c r="AA30" t="n">
         <v>14.9</v>
       </c>
+      <c r="AB30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>5.7</v>
+      </c>
       <c r="AF30" t="n">
         <v>224.93</v>
       </c>
@@ -3451,6 +3712,15 @@
       <c r="AA31" t="n">
         <v>19.3</v>
       </c>
+      <c r="AB31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AF31" t="n">
         <v>232.31</v>
       </c>
@@ -3522,6 +3792,15 @@
       <c r="AA32" t="n">
         <v>20.5</v>
       </c>
+      <c r="AB32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.7</v>
+      </c>
       <c r="AF32" t="n">
         <v>235.4</v>
       </c>
@@ -3587,6 +3866,15 @@
       <c r="AA33" t="n">
         <v>15.5</v>
       </c>
+      <c r="AB33" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.7</v>
+      </c>
       <c r="AF33" t="n">
         <v>231.99</v>
       </c>
@@ -3685,6 +3973,15 @@
       <c r="AA34" t="n">
         <v>11.1</v>
       </c>
+      <c r="AB34" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="AF34" t="n">
         <v>225.51</v>
       </c>
@@ -3789,6 +4086,15 @@
       <c r="AA35" t="n">
         <v>11.6</v>
       </c>
+      <c r="AB35" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>-1.3</v>
+      </c>
       <c r="AF35" t="n">
         <v>220.92</v>
       </c>
@@ -3893,6 +4199,15 @@
       <c r="AA36" t="n">
         <v>11.4</v>
       </c>
+      <c r="AB36" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>-0.9</v>
+      </c>
       <c r="AF36" t="n">
         <v>220.92</v>
       </c>
@@ -3997,6 +4312,15 @@
       <c r="AA37" t="n">
         <v>11.1</v>
       </c>
+      <c r="AB37" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AF37" t="n">
         <v>216.02</v>
       </c>
@@ -4101,6 +4425,15 @@
       <c r="AA38" t="n">
         <v>12.7</v>
       </c>
+      <c r="AB38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4.7</v>
+      </c>
       <c r="AF38" t="n">
         <v>216.02</v>
       </c>
@@ -4172,6 +4505,15 @@
       <c r="AA39" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB39" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.4</v>
+      </c>
       <c r="AF39" t="n">
         <v>224.53</v>
       </c>
@@ -4237,6 +4579,15 @@
       <c r="AA40" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB40" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.1</v>
+      </c>
       <c r="AF40" t="n">
         <v>230.27</v>
       </c>
@@ -4335,6 +4686,15 @@
       <c r="AA41" t="n">
         <v>15.7</v>
       </c>
+      <c r="AB41" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="AF41" t="n">
         <v>237.43</v>
       </c>
@@ -4406,6 +4766,15 @@
       <c r="AA42" t="n">
         <v>16</v>
       </c>
+      <c r="AB42" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AF42" t="n">
         <v>236.14</v>
       </c>
@@ -4504,6 +4873,15 @@
       <c r="AA43" t="n">
         <v>14.4</v>
       </c>
+      <c r="AB43" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="AF43" t="n">
         <v>236.13</v>
       </c>
@@ -4608,6 +4986,15 @@
       <c r="AA44" t="n">
         <v>12.5</v>
       </c>
+      <c r="AB44" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>-0.7</v>
+      </c>
       <c r="AF44" t="n">
         <v>218.6</v>
       </c>
@@ -4712,6 +5099,15 @@
       <c r="AA45" t="n">
         <v>13.6</v>
       </c>
+      <c r="AB45" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AF45" t="n">
         <v>218.84</v>
       </c>
@@ -4783,6 +5179,15 @@
       <c r="AA46" t="n">
         <v>17.5</v>
       </c>
+      <c r="AB46" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AF46" t="n">
         <v>221.78</v>
       </c>
@@ -4848,6 +5253,15 @@
       <c r="AA47" t="n">
         <v>16.5</v>
       </c>
+      <c r="AB47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.1</v>
+      </c>
       <c r="AF47" t="n">
         <v>224.78</v>
       </c>
@@ -4946,6 +5360,15 @@
       <c r="AA48" t="n">
         <v>15.4</v>
       </c>
+      <c r="AB48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>3.2</v>
+      </c>
       <c r="AF48" t="n">
         <v>232.22</v>
       </c>
@@ -5050,6 +5473,15 @@
       <c r="AA49" t="n">
         <v>15.5</v>
       </c>
+      <c r="AB49" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2</v>
+      </c>
       <c r="AF49" t="n">
         <v>229.69</v>
       </c>
@@ -5154,6 +5586,15 @@
       <c r="AA50" t="n">
         <v>13.5</v>
       </c>
+      <c r="AB50" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.2</v>
+      </c>
       <c r="AF50" t="n">
         <v>228.57</v>
       </c>
@@ -5240,6 +5681,15 @@
       <c r="T51" t="n">
         <v>20.9</v>
       </c>
+      <c r="V51" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W51" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X51" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y51" t="n">
         <v>13</v>
       </c>
@@ -5248,6 +5698,15 @@
       </c>
       <c r="AA51" t="n">
         <v>14.1</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.6</v>
       </c>
       <c r="AF51" t="n">
         <v>225.08</v>
@@ -5391,6 +5850,12 @@
       <c r="F53" t="n">
         <v>5.4</v>
       </c>
+      <c r="K53" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="O53" t="n">
+        <v>36.8</v>
+      </c>
       <c r="Y53" t="n">
         <v>5</v>
       </c>
@@ -5441,6 +5906,12 @@
       <c r="F54" t="n">
         <v>5</v>
       </c>
+      <c r="K54" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O54" t="n">
+        <v>35.5</v>
+      </c>
       <c r="Y54" t="n">
         <v>7</v>
       </c>
@@ -5491,6 +5962,12 @@
       <c r="F55" t="n">
         <v>5.5</v>
       </c>
+      <c r="K55" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="O55" t="n">
+        <v>35.1</v>
+      </c>
       <c r="Y55" t="n">
         <v>3</v>
       </c>
@@ -5533,13 +6010,52 @@
         <v>46244</v>
       </c>
       <c r="B56" t="n">
-        <v>169.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C56" t="n">
+        <v>86.8</v>
       </c>
       <c r="D56" t="n">
-        <v>36</v>
+        <v>31.8</v>
+      </c>
+      <c r="E56" t="n">
+        <v>33</v>
       </c>
       <c r="F56" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H56" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N56" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O56" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="n">
+        <v>22.4</v>
       </c>
       <c r="Y56" t="n">
         <v>4</v>
@@ -5548,7 +6064,7 @@
         <v>12</v>
       </c>
       <c r="AA56" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF56" t="n">
         <v>218.63</v>
@@ -5573,6 +6089,12 @@
       </c>
       <c r="AN56" t="n">
         <v>142</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>14.7</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46244</v>
@@ -5600,11 +6122,23 @@
       <c r="AA57" t="n">
         <v>9</v>
       </c>
+      <c r="AF57" t="n">
+        <v>216.39</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>-2.23</v>
+      </c>
       <c r="AH57" t="n">
         <v>215</v>
       </c>
       <c r="AI57" t="n">
         <v>235</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>123.32</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>-2.95</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -5619,6 +6153,24 @@
     <row r="58">
       <c r="A58" s="1" t="n">
         <v>46246</v>
+      </c>
+      <c r="B58" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>28</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>10.5</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5794,6 +5794,15 @@
       <c r="T52" t="n">
         <v>21</v>
       </c>
+      <c r="V52" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W52" t="n">
+        <v>27</v>
+      </c>
+      <c r="X52" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y52" t="n">
         <v>9</v>
       </c>
@@ -5802,6 +5811,15 @@
       </c>
       <c r="AA52" t="n">
         <v>11.4</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AF52" t="n">
         <v>225</v>
@@ -6105,13 +6123,52 @@
         <v>46245</v>
       </c>
       <c r="B57" t="n">
-        <v>159.1</v>
+        <v>181.8</v>
+      </c>
+      <c r="C57" t="n">
+        <v>86.5</v>
       </c>
       <c r="D57" t="n">
-        <v>28.6</v>
+        <v>31.4</v>
+      </c>
+      <c r="E57" t="n">
+        <v>34.2</v>
       </c>
       <c r="F57" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
+      </c>
+      <c r="H57" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K57" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O57" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>23</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S57" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>23</v>
       </c>
       <c r="Y57" t="n">
         <v>6</v>
@@ -6120,7 +6177,7 @@
         <v>12</v>
       </c>
       <c r="AA57" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF57" t="n">
         <v>216.39</v>
@@ -6145,6 +6202,12 @@
       </c>
       <c r="AN57" t="n">
         <v>142</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>13.91</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46245</v>
@@ -6172,11 +6235,23 @@
       <c r="AA58" t="n">
         <v>10.5</v>
       </c>
+      <c r="AF58" t="n">
+        <v>217.16</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0.76</v>
+      </c>
       <c r="AH58" t="n">
         <v>215</v>
       </c>
       <c r="AI58" t="n">
         <v>235</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>117.87</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-5.45</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6191,6 +6266,24 @@
     <row r="59">
       <c r="A59" s="1" t="n">
         <v>46247</v>
+      </c>
+      <c r="B59" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>29</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>10</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -678,15 +678,6 @@
       <c r="T2" t="n">
         <v>22.9</v>
       </c>
-      <c r="V2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W2" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X2" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y2" t="n">
         <v>7</v>
       </c>
@@ -695,15 +686,6 @@
       </c>
       <c r="AA2" t="n">
         <v>12.8</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.4</v>
       </c>
       <c r="AF2" t="n">
         <v>221.34</v>
@@ -803,15 +785,6 @@
       <c r="T3" t="n">
         <v>22.3</v>
       </c>
-      <c r="V3" t="n">
-        <v>11</v>
-      </c>
-      <c r="W3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>14.1</v>
-      </c>
       <c r="Y3" t="n">
         <v>10</v>
       </c>
@@ -820,15 +793,6 @@
       </c>
       <c r="AA3" t="n">
         <v>11.8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>5</v>
       </c>
       <c r="AF3" t="n">
         <v>219.56</v>
@@ -901,15 +865,6 @@
       <c r="O4" t="n">
         <v>39.1</v>
       </c>
-      <c r="V4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>13.9</v>
-      </c>
       <c r="Y4" t="n">
         <v>8</v>
       </c>
@@ -918,15 +873,6 @@
       </c>
       <c r="AA4" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4.5</v>
       </c>
       <c r="AF4" t="n">
         <v>220.8</v>
@@ -993,15 +939,6 @@
       <c r="O5" t="n">
         <v>40.7</v>
       </c>
-      <c r="V5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W5" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X5" t="n">
-        <v>12.4</v>
-      </c>
       <c r="Y5" t="n">
         <v>4</v>
       </c>
@@ -1010,15 +947,6 @@
       </c>
       <c r="AA5" t="n">
         <v>9.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.1</v>
       </c>
       <c r="AF5" t="n">
         <v>225.5</v>
@@ -1112,15 +1040,6 @@
       <c r="T6" t="n">
         <v>21.9</v>
       </c>
-      <c r="V6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>12.5</v>
-      </c>
       <c r="Y6" t="n">
         <v>9</v>
       </c>
@@ -1129,15 +1048,6 @@
       </c>
       <c r="AA6" t="n">
         <v>11.1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.4</v>
       </c>
       <c r="AF6" t="n">
         <v>231.46</v>
@@ -1237,15 +1147,6 @@
       <c r="T7" t="n">
         <v>20.7</v>
       </c>
-      <c r="V7" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.3</v>
-      </c>
       <c r="Y7" t="n">
         <v>7</v>
       </c>
@@ -1254,15 +1155,6 @@
       </c>
       <c r="AA7" t="n">
         <v>10.9</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3</v>
       </c>
       <c r="AF7" t="n">
         <v>231.82</v>
@@ -1362,15 +1254,6 @@
       <c r="T8" t="n">
         <v>21.6</v>
       </c>
-      <c r="V8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X8" t="n">
-        <v>11</v>
-      </c>
       <c r="Y8" t="n">
         <v>4</v>
       </c>
@@ -1379,15 +1262,6 @@
       </c>
       <c r="AA8" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.9</v>
       </c>
       <c r="AF8" t="n">
         <v>230.65</v>
@@ -1487,15 +1361,6 @@
       <c r="T9" t="n">
         <v>21.6</v>
       </c>
-      <c r="V9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X9" t="n">
-        <v>11.3</v>
-      </c>
       <c r="Y9" t="n">
         <v>4</v>
       </c>
@@ -1504,15 +1369,6 @@
       </c>
       <c r="AA9" t="n">
         <v>8.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>5.3</v>
       </c>
       <c r="AF9" t="n">
         <v>227.74</v>
@@ -1612,15 +1468,6 @@
       <c r="T10" t="n">
         <v>22.1</v>
       </c>
-      <c r="V10" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W10" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>13.5</v>
-      </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
@@ -1629,15 +1476,6 @@
       </c>
       <c r="AA10" t="n">
         <v>9.1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5</v>
       </c>
       <c r="AF10" t="n">
         <v>226.8</v>
@@ -1710,15 +1548,6 @@
       <c r="O11" t="n">
         <v>40.1</v>
       </c>
-      <c r="V11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>12</v>
-      </c>
       <c r="Y11" t="n">
         <v>3</v>
       </c>
@@ -1727,15 +1556,6 @@
       </c>
       <c r="AA11" t="n">
         <v>8.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.1</v>
       </c>
       <c r="AF11" t="n">
         <v>226.39</v>
@@ -1790,15 +1610,6 @@
       <c r="O12" t="n">
         <v>40.8</v>
       </c>
-      <c r="V12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X12" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y12" t="n">
         <v>7</v>
       </c>
@@ -1807,15 +1618,6 @@
       </c>
       <c r="AA12" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.4</v>
       </c>
       <c r="AF12" t="n">
         <v>229.98</v>
@@ -1897,15 +1699,6 @@
       <c r="T13" t="n">
         <v>22</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>14.2</v>
-      </c>
       <c r="Y13" t="n">
         <v>8</v>
       </c>
@@ -1914,15 +1707,6 @@
       </c>
       <c r="AA13" t="n">
         <v>13</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.8</v>
       </c>
       <c r="AF13" t="n">
         <v>236.38</v>
@@ -2010,15 +1794,6 @@
       <c r="T14" t="n">
         <v>20.9</v>
       </c>
-      <c r="V14" t="n">
-        <v>6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X14" t="n">
-        <v>10.4</v>
-      </c>
       <c r="Y14" t="n">
         <v>5</v>
       </c>
@@ -2027,15 +1802,6 @@
       </c>
       <c r="AA14" t="n">
         <v>9.9</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
         <v>236.23</v>
@@ -2123,15 +1889,6 @@
       <c r="T15" t="n">
         <v>22</v>
       </c>
-      <c r="V15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W15" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X15" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y15" t="n">
         <v>3</v>
       </c>
@@ -2140,15 +1897,6 @@
       </c>
       <c r="AA15" t="n">
         <v>9.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>-2.9</v>
       </c>
       <c r="AF15" t="n">
         <v>236.72</v>
@@ -2236,15 +1984,6 @@
       <c r="T16" t="n">
         <v>21.8</v>
       </c>
-      <c r="V16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>10.2</v>
-      </c>
       <c r="Y16" t="n">
         <v>4</v>
       </c>
@@ -2253,15 +1992,6 @@
       </c>
       <c r="AA16" t="n">
         <v>9.699999999999999</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>-6.5</v>
       </c>
       <c r="AF16" t="n">
         <v>229.92</v>
@@ -2349,15 +2079,6 @@
       <c r="T17" t="n">
         <v>22.7</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>10</v>
-      </c>
-      <c r="X17" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="Y17" t="n">
         <v>1</v>
       </c>
@@ -2366,15 +2087,6 @@
       </c>
       <c r="AA17" t="n">
         <v>6.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-3.3</v>
       </c>
       <c r="AF17" t="n">
         <v>223</v>
@@ -2435,15 +2147,6 @@
       <c r="O18" t="n">
         <v>39.4</v>
       </c>
-      <c r="V18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="X18" t="n">
-        <v>7.6</v>
-      </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
@@ -2452,15 +2155,6 @@
       </c>
       <c r="AA18" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-2.8</v>
       </c>
       <c r="AF18" t="n">
         <v>221.08</v>
@@ -2515,15 +2209,6 @@
       <c r="O19" t="n">
         <v>39.5</v>
       </c>
-      <c r="V19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="X19" t="n">
-        <v>7.5</v>
-      </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
@@ -2532,15 +2217,6 @@
       </c>
       <c r="AA19" t="n">
         <v>5.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>-1.3</v>
       </c>
       <c r="AF19" t="n">
         <v>221.24</v>
@@ -2622,15 +2298,6 @@
       <c r="T20" t="n">
         <v>22.7</v>
       </c>
-      <c r="V20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W20" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="X20" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="Y20" t="n">
         <v>5</v>
       </c>
@@ -2639,15 +2306,6 @@
       </c>
       <c r="AA20" t="n">
         <v>6.1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-1.2</v>
       </c>
       <c r="AF20" t="n">
         <v>223.94</v>
@@ -2735,15 +2393,6 @@
       <c r="T21" t="n">
         <v>23</v>
       </c>
-      <c r="V21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X21" t="n">
-        <v>9.5</v>
-      </c>
       <c r="Y21" t="n">
         <v>5</v>
       </c>
@@ -2752,15 +2401,6 @@
       </c>
       <c r="AA21" t="n">
         <v>7.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
         <v>224.33</v>
@@ -2848,15 +2488,6 @@
       <c r="T22" t="n">
         <v>23</v>
       </c>
-      <c r="V22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W22" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>10.2</v>
-      </c>
       <c r="Y22" t="n">
         <v>2.4</v>
       </c>
@@ -2865,15 +2496,6 @@
       </c>
       <c r="AA22" t="n">
         <v>10.3</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.3</v>
       </c>
       <c r="AF22" t="n">
         <v>224.34</v>
@@ -2934,15 +2556,6 @@
       <c r="O23" t="n">
         <v>40.5</v>
       </c>
-      <c r="V23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="X23" t="n">
-        <v>12.1</v>
-      </c>
       <c r="Y23" t="n">
         <v>8</v>
       </c>
@@ -2951,15 +2564,6 @@
       </c>
       <c r="AA23" t="n">
         <v>14</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.6</v>
       </c>
       <c r="AF23" t="n">
         <v>231.46</v>
@@ -3014,15 +2618,6 @@
       <c r="O24" t="n">
         <v>40.6</v>
       </c>
-      <c r="V24" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="X24" t="n">
-        <v>15.2</v>
-      </c>
       <c r="Y24" t="n">
         <v>8</v>
       </c>
@@ -3031,15 +2626,6 @@
       </c>
       <c r="AA24" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>-0.2</v>
       </c>
       <c r="AF24" t="n">
         <v>229.92</v>
@@ -3094,15 +2680,6 @@
       <c r="O25" t="n">
         <v>38</v>
       </c>
-      <c r="V25" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W25" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X25" t="n">
-        <v>13.8</v>
-      </c>
       <c r="Y25" t="n">
         <v>10</v>
       </c>
@@ -3111,15 +2688,6 @@
       </c>
       <c r="AA25" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>-0.1</v>
       </c>
       <c r="AF25" t="n">
         <v>226.95</v>
@@ -3174,15 +2742,6 @@
       <c r="O26" t="n">
         <v>39.8</v>
       </c>
-      <c r="V26" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W26" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="X26" t="n">
-        <v>16.4</v>
-      </c>
       <c r="Y26" t="n">
         <v>7</v>
       </c>
@@ -3191,15 +2750,6 @@
       </c>
       <c r="AA26" t="n">
         <v>11</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.6</v>
       </c>
       <c r="AF26" t="n">
         <v>223.11</v>
@@ -3254,15 +2804,6 @@
       <c r="O27" t="n">
         <v>40.2</v>
       </c>
-      <c r="V27" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X27" t="n">
-        <v>13.6</v>
-      </c>
       <c r="Y27" t="n">
         <v>7</v>
       </c>
@@ -3271,15 +2812,6 @@
       </c>
       <c r="AA27" t="n">
         <v>10</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4.8</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3355,15 +2887,6 @@
       <c r="T28" t="n">
         <v>23</v>
       </c>
-      <c r="V28" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W28" t="n">
-        <v>20</v>
-      </c>
-      <c r="X28" t="n">
-        <v>14.4</v>
-      </c>
       <c r="Y28" t="n">
         <v>4</v>
       </c>
@@ -3372,15 +2895,6 @@
       </c>
       <c r="AA28" t="n">
         <v>7.7</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>6.2</v>
       </c>
       <c r="AF28" t="n">
         <v>220.36</v>
@@ -3468,15 +2982,6 @@
       <c r="T29" t="n">
         <v>23.1</v>
       </c>
-      <c r="V29" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X29" t="n">
-        <v>14.9</v>
-      </c>
       <c r="Y29" t="n">
         <v>8</v>
       </c>
@@ -3485,15 +2990,6 @@
       </c>
       <c r="AA29" t="n">
         <v>11.9</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>5.2</v>
       </c>
       <c r="AF29" t="n">
         <v>219.64</v>
@@ -3581,15 +3077,6 @@
       <c r="T30" t="n">
         <v>22.6</v>
       </c>
-      <c r="V30" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W30" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X30" t="n">
-        <v>17</v>
-      </c>
       <c r="Y30" t="n">
         <v>11</v>
       </c>
@@ -3598,15 +3085,6 @@
       </c>
       <c r="AA30" t="n">
         <v>14.9</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>5.7</v>
       </c>
       <c r="AF30" t="n">
         <v>224.93</v>
@@ -3694,15 +3172,6 @@
       <c r="T31" t="n">
         <v>21.5</v>
       </c>
-      <c r="V31" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>26</v>
-      </c>
-      <c r="X31" t="n">
-        <v>18.1</v>
-      </c>
       <c r="Y31" t="n">
         <v>17</v>
       </c>
@@ -3711,15 +3180,6 @@
       </c>
       <c r="AA31" t="n">
         <v>19.3</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4.5</v>
       </c>
       <c r="AF31" t="n">
         <v>232.31</v>
@@ -3774,15 +3234,6 @@
       <c r="O32" t="n">
         <v>39.2</v>
       </c>
-      <c r="V32" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>26.6</v>
-      </c>
       <c r="Y32" t="n">
         <v>18</v>
       </c>
@@ -3791,15 +3242,6 @@
       </c>
       <c r="AA32" t="n">
         <v>20.5</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.7</v>
       </c>
       <c r="AF32" t="n">
         <v>235.4</v>
@@ -3848,15 +3290,6 @@
       <c r="O33" t="n">
         <v>37.8</v>
       </c>
-      <c r="V33" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="W33" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X33" t="n">
-        <v>17.9</v>
-      </c>
       <c r="Y33" t="n">
         <v>14</v>
       </c>
@@ -3865,15 +3298,6 @@
       </c>
       <c r="AA33" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.7</v>
       </c>
       <c r="AF33" t="n">
         <v>231.99</v>
@@ -3955,15 +3379,6 @@
       <c r="T34" t="n">
         <v>20.5</v>
       </c>
-      <c r="V34" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X34" t="n">
-        <v>16.7</v>
-      </c>
       <c r="Y34" t="n">
         <v>9</v>
       </c>
@@ -3972,15 +3387,6 @@
       </c>
       <c r="AA34" t="n">
         <v>11.1</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>-0.3</v>
       </c>
       <c r="AF34" t="n">
         <v>225.51</v>
@@ -4068,15 +3474,6 @@
       <c r="T35" t="n">
         <v>22.3</v>
       </c>
-      <c r="V35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X35" t="n">
-        <v>13.5</v>
-      </c>
       <c r="Y35" t="n">
         <v>9</v>
       </c>
@@ -4085,15 +3482,6 @@
       </c>
       <c r="AA35" t="n">
         <v>11.6</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>-1.3</v>
       </c>
       <c r="AF35" t="n">
         <v>220.92</v>
@@ -4181,15 +3569,6 @@
       <c r="T36" t="n">
         <v>22.5</v>
       </c>
-      <c r="V36" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W36" t="n">
-        <v>13</v>
-      </c>
-      <c r="X36" t="n">
-        <v>11.8</v>
-      </c>
       <c r="Y36" t="n">
         <v>10</v>
       </c>
@@ -4198,15 +3577,6 @@
       </c>
       <c r="AA36" t="n">
         <v>11.4</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>-0.9</v>
       </c>
       <c r="AF36" t="n">
         <v>220.92</v>
@@ -4294,15 +3664,6 @@
       <c r="T37" t="n">
         <v>22.6</v>
       </c>
-      <c r="V37" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W37" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X37" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y37" t="n">
         <v>9</v>
       </c>
@@ -4311,15 +3672,6 @@
       </c>
       <c r="AA37" t="n">
         <v>11.1</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.5</v>
       </c>
       <c r="AF37" t="n">
         <v>216.02</v>
@@ -4407,15 +3759,6 @@
       <c r="T38" t="n">
         <v>23.3</v>
       </c>
-      <c r="V38" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X38" t="n">
-        <v>12.6</v>
-      </c>
       <c r="Y38" t="n">
         <v>8</v>
       </c>
@@ -4424,15 +3767,6 @@
       </c>
       <c r="AA38" t="n">
         <v>12.7</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.7</v>
       </c>
       <c r="AF38" t="n">
         <v>216.02</v>
@@ -4487,15 +3821,6 @@
       <c r="O39" t="n">
         <v>39.2</v>
       </c>
-      <c r="V39" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="X39" t="n">
-        <v>14</v>
-      </c>
       <c r="Y39" t="n">
         <v>12</v>
       </c>
@@ -4504,15 +3829,6 @@
       </c>
       <c r="AA39" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.4</v>
       </c>
       <c r="AF39" t="n">
         <v>224.53</v>
@@ -4561,15 +3877,6 @@
       <c r="O40" t="n">
         <v>39.3</v>
       </c>
-      <c r="V40" t="n">
-        <v>8</v>
-      </c>
-      <c r="W40" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X40" t="n">
-        <v>15.2</v>
-      </c>
       <c r="Y40" t="n">
         <v>11</v>
       </c>
@@ -4578,15 +3885,6 @@
       </c>
       <c r="AA40" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.1</v>
       </c>
       <c r="AF40" t="n">
         <v>230.27</v>
@@ -4668,15 +3966,6 @@
       <c r="T41" t="n">
         <v>21.7</v>
       </c>
-      <c r="V41" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W41" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X41" t="n">
-        <v>17.4</v>
-      </c>
       <c r="Y41" t="n">
         <v>12</v>
       </c>
@@ -4685,15 +3974,6 @@
       </c>
       <c r="AA41" t="n">
         <v>15.7</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>-0.1</v>
       </c>
       <c r="AF41" t="n">
         <v>237.43</v>
@@ -4748,15 +4028,6 @@
       <c r="O42" t="n">
         <v>37.9</v>
       </c>
-      <c r="V42" t="n">
-        <v>10</v>
-      </c>
-      <c r="W42" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X42" t="n">
-        <v>17.8</v>
-      </c>
       <c r="Y42" t="n">
         <v>13</v>
       </c>
@@ -4765,15 +4036,6 @@
       </c>
       <c r="AA42" t="n">
         <v>16</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.9</v>
       </c>
       <c r="AF42" t="n">
         <v>236.14</v>
@@ -4855,15 +4117,6 @@
       <c r="T43" t="n">
         <v>20.3</v>
       </c>
-      <c r="V43" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="W43" t="n">
-        <v>27</v>
-      </c>
-      <c r="X43" t="n">
-        <v>19.4</v>
-      </c>
       <c r="Y43" t="n">
         <v>11</v>
       </c>
@@ -4872,15 +4125,6 @@
       </c>
       <c r="AA43" t="n">
         <v>14.4</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>-0.4</v>
       </c>
       <c r="AF43" t="n">
         <v>236.13</v>
@@ -4968,15 +4212,6 @@
       <c r="T44" t="n">
         <v>19</v>
       </c>
-      <c r="V44" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W44" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X44" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y44" t="n">
         <v>9</v>
       </c>
@@ -4985,15 +4220,6 @@
       </c>
       <c r="AA44" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>-0.7</v>
       </c>
       <c r="AF44" t="n">
         <v>218.6</v>
@@ -5081,15 +4307,6 @@
       <c r="T45" t="n">
         <v>21.6</v>
       </c>
-      <c r="V45" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W45" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X45" t="n">
-        <v>19.1</v>
-      </c>
       <c r="Y45" t="n">
         <v>11</v>
       </c>
@@ -5098,15 +4315,6 @@
       </c>
       <c r="AA45" t="n">
         <v>13.6</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.5</v>
       </c>
       <c r="AF45" t="n">
         <v>218.84</v>
@@ -5161,15 +4369,6 @@
       <c r="O46" t="n">
         <v>35.1</v>
       </c>
-      <c r="V46" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="W46" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X46" t="n">
-        <v>19</v>
-      </c>
       <c r="Y46" t="n">
         <v>14</v>
       </c>
@@ -5178,15 +4377,6 @@
       </c>
       <c r="AA46" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.8</v>
       </c>
       <c r="AF46" t="n">
         <v>221.78</v>
@@ -5235,15 +4425,6 @@
       <c r="O47" t="n">
         <v>31.6</v>
       </c>
-      <c r="V47" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="W47" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X47" t="n">
-        <v>19.8</v>
-      </c>
       <c r="Y47" t="n">
         <v>14</v>
       </c>
@@ -5252,15 +4433,6 @@
       </c>
       <c r="AA47" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>2.1</v>
       </c>
       <c r="AF47" t="n">
         <v>224.78</v>
@@ -5342,15 +4514,6 @@
       <c r="T48" t="n">
         <v>21.6</v>
       </c>
-      <c r="V48" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W48" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Y48" t="n">
         <v>12</v>
       </c>
@@ -5359,15 +4522,6 @@
       </c>
       <c r="AA48" t="n">
         <v>15.4</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>3.2</v>
       </c>
       <c r="AF48" t="n">
         <v>232.22</v>
@@ -5455,15 +4609,6 @@
       <c r="T49" t="n">
         <v>21.1</v>
       </c>
-      <c r="V49" t="n">
-        <v>13</v>
-      </c>
-      <c r="W49" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X49" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y49" t="n">
         <v>13</v>
       </c>
@@ -5472,15 +4617,6 @@
       </c>
       <c r="AA49" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2</v>
       </c>
       <c r="AF49" t="n">
         <v>229.69</v>
@@ -5568,15 +4704,6 @@
       <c r="T50" t="n">
         <v>21.3</v>
       </c>
-      <c r="V50" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W50" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X50" t="n">
-        <v>20</v>
-      </c>
       <c r="Y50" t="n">
         <v>11</v>
       </c>
@@ -5585,15 +4712,6 @@
       </c>
       <c r="AA50" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.2</v>
       </c>
       <c r="AF50" t="n">
         <v>228.57</v>
@@ -5681,15 +4799,6 @@
       <c r="T51" t="n">
         <v>20.9</v>
       </c>
-      <c r="V51" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W51" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X51" t="n">
-        <v>19.6</v>
-      </c>
       <c r="Y51" t="n">
         <v>13</v>
       </c>
@@ -5698,15 +4807,6 @@
       </c>
       <c r="AA51" t="n">
         <v>14.1</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.6</v>
       </c>
       <c r="AF51" t="n">
         <v>225.08</v>
@@ -5794,15 +4894,6 @@
       <c r="T52" t="n">
         <v>21</v>
       </c>
-      <c r="V52" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W52" t="n">
-        <v>27</v>
-      </c>
-      <c r="X52" t="n">
-        <v>19.9</v>
-      </c>
       <c r="Y52" t="n">
         <v>9</v>
       </c>
@@ -5811,15 +4902,6 @@
       </c>
       <c r="AA52" t="n">
         <v>11.4</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>-0.3</v>
       </c>
       <c r="AF52" t="n">
         <v>225</v>
@@ -6218,13 +5300,52 @@
         <v>46246</v>
       </c>
       <c r="B58" t="n">
-        <v>166.5</v>
+        <v>183</v>
+      </c>
+      <c r="C58" t="n">
+        <v>84.7</v>
       </c>
       <c r="D58" t="n">
-        <v>28</v>
+        <v>30.9</v>
+      </c>
+      <c r="E58" t="n">
+        <v>33.7</v>
       </c>
       <c r="F58" t="n">
-        <v>6.5</v>
+        <v>7</v>
+      </c>
+      <c r="H58" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4</v>
+      </c>
+      <c r="N58" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="O58" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S58" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T58" t="n">
+        <v>23.6</v>
       </c>
       <c r="Y58" t="n">
         <v>8</v>
@@ -6233,7 +5354,7 @@
         <v>13</v>
       </c>
       <c r="AA58" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AF58" t="n">
         <v>217.16</v>
@@ -6258,6 +5379,12 @@
       </c>
       <c r="AN58" t="n">
         <v>142</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>78.56</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>13.45</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46246</v>
@@ -6285,11 +5412,23 @@
       <c r="AA59" t="n">
         <v>10</v>
       </c>
+      <c r="AF59" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>3.16</v>
+      </c>
       <c r="AH59" t="n">
         <v>215</v>
       </c>
       <c r="AI59" t="n">
         <v>235</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>116.52</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>-1.35</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6304,6 +5443,24 @@
     <row r="60">
       <c r="A60" s="1" t="n">
         <v>46248</v>
+      </c>
+      <c r="B60" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="D60" t="n">
+        <v>28</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>11.5</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,70 +628,70 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="B2" t="n">
-        <v>176.9</v>
+        <v>183.8</v>
       </c>
       <c r="C2" t="n">
-        <v>75.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="D2" t="n">
-        <v>31.2</v>
+        <v>27.1</v>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>5.7</v>
+        <v>7.3</v>
       </c>
       <c r="H2" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>42.5</v>
+        <v>41.3</v>
       </c>
       <c r="K2" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>34.6</v>
+        <v>38</v>
       </c>
       <c r="O2" t="n">
-        <v>37.9</v>
+        <v>41.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.9</v>
+        <v>21.6</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T2" t="n">
-        <v>22.9</v>
+        <v>21.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.8</v>
+        <v>8.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>221.34</v>
+        <v>227.74</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1.2</v>
+        <v>-3.29</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -700,10 +700,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>123.51</v>
+        <v>127.86</v>
       </c>
       <c r="AL2" t="n">
-        <v>-2.66</v>
+        <v>-3.67</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -712,93 +712,93 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>82.01000000000001</v>
+        <v>84.81</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.28</v>
+        <v>13.95</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="BM2" t="n">
-        <v>41.78</v>
+        <v>37.03</v>
       </c>
       <c r="BN2" t="n">
-        <v>4128.6</v>
+        <v>15572</v>
       </c>
       <c r="BO2" t="n">
-        <v>1204.7</v>
+        <v>2181.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>3187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="B3" t="n">
-        <v>173</v>
+        <v>178.9</v>
       </c>
       <c r="C3" t="n">
-        <v>77.5</v>
+        <v>84.2</v>
       </c>
       <c r="D3" t="n">
-        <v>31.9</v>
+        <v>28.2</v>
       </c>
       <c r="E3" t="n">
-        <v>32.1</v>
+        <v>31.1</v>
       </c>
       <c r="F3" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="H3" t="n">
-        <v>23.8</v>
+        <v>24.7</v>
       </c>
       <c r="I3" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="J3" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="K3" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>34.1</v>
+        <v>38.1</v>
       </c>
       <c r="O3" t="n">
-        <v>37.8</v>
+        <v>41.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T3" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
         <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>219.56</v>
+        <v>226.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1.79</v>
+        <v>-0.95</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -807,10 +807,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>121.5</v>
+        <v>129.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>-2.01</v>
+        <v>1.24</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -819,66 +819,66 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>81.17</v>
+        <v>81.91</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.36</v>
+        <v>15.61</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="BM3" t="n">
-        <v>38.65</v>
+        <v>38.28</v>
       </c>
       <c r="BN3" t="n">
-        <v>6526.2</v>
+        <v>14004.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>1242.5</v>
+        <v>2044.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>2960.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="B4" t="n">
-        <v>149.8</v>
+        <v>155.4</v>
       </c>
       <c r="C4" t="n">
-        <v>75.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>30.7</v>
+        <v>27.4</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="F4" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="K4" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="O4" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>220.8</v>
+        <v>226.39</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>-0.4</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -887,10 +887,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>122.48</v>
+        <v>129.78</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.98</v>
+        <v>0.68</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -899,60 +899,48 @@
         <v>142</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46192</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>35.93</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>7489.8</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1470.2</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>2894.4</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B5" t="n">
-        <v>146.2</v>
+        <v>151.1</v>
       </c>
       <c r="C5" t="n">
-        <v>71.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>29.4</v>
+        <v>26.8</v>
       </c>
       <c r="E5" t="n">
-        <v>29.7</v>
+        <v>30.9</v>
       </c>
       <c r="F5" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>98.40000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="O5" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>225.5</v>
+        <v>229.98</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.7</v>
+        <v>3.58</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -961,10 +949,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>126.49</v>
+        <v>132.56</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.01</v>
+        <v>2.78</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -973,87 +961,75 @@
         <v>142</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46193</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>34.91</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5186.1</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>561</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>2993.6</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B6" t="n">
-        <v>163</v>
+        <v>167.2</v>
       </c>
       <c r="C6" t="n">
-        <v>67.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>27.3</v>
+        <v>27.6</v>
       </c>
       <c r="E6" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="F6" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="H6" t="n">
         <v>24.6</v>
       </c>
       <c r="I6" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="J6" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="K6" t="n">
-        <v>75.8</v>
+        <v>75</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>38.7</v>
+        <v>37.2</v>
       </c>
       <c r="O6" t="n">
-        <v>42.2</v>
+        <v>39.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="S6" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="T6" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.1</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>231.46</v>
+        <v>236.38</v>
       </c>
       <c r="AG6" t="n">
-        <v>5.97</v>
+        <v>6.4</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1062,10 +1038,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>131.04</v>
+        <v>132.97</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.55</v>
+        <v>0.41</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1074,93 +1050,81 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>92.62</v>
+        <v>90.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>16.04</v>
+        <v>16.05</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>6002.2</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>518.5</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>2894.8</v>
+        <v>46201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="B7" t="n">
-        <v>170.7</v>
+        <v>176.7</v>
       </c>
       <c r="C7" t="n">
-        <v>81.5</v>
+        <v>80.8</v>
       </c>
       <c r="D7" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>31.6</v>
       </c>
       <c r="F7" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="H7" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="I7" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="J7" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="K7" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="N7" t="n">
-        <v>36.5</v>
+        <v>38.4</v>
       </c>
       <c r="O7" t="n">
-        <v>39.7</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>15.5</v>
+        <v>19.1</v>
       </c>
       <c r="T7" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>231.82</v>
+        <v>236.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1169,10 +1133,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>131.28</v>
+        <v>132.79</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.24</v>
+        <v>-0.18</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1181,93 +1145,81 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>89.87</v>
+        <v>89.64</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.86</v>
+        <v>15.89</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46195</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>11946.7</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1461</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>3090</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46196</v>
+        <v>46203</v>
       </c>
       <c r="B8" t="n">
-        <v>179.1</v>
+        <v>175.3</v>
       </c>
       <c r="C8" t="n">
-        <v>85.8</v>
+        <v>83.5</v>
       </c>
       <c r="D8" t="n">
-        <v>26.5</v>
+        <v>27.8</v>
       </c>
       <c r="E8" t="n">
         <v>30.3</v>
       </c>
       <c r="F8" t="n">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="H8" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="I8" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="J8" t="n">
-        <v>42</v>
+        <v>42.9</v>
       </c>
       <c r="K8" t="n">
-        <v>76.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="N8" t="n">
-        <v>39.3</v>
+        <v>38.6</v>
       </c>
       <c r="O8" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>230.65</v>
+        <v>236.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.17</v>
+        <v>0.49</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1276,10 +1228,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>131.53</v>
+        <v>134.11</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.25</v>
+        <v>1.32</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1288,93 +1240,81 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>87.15000000000001</v>
+        <v>88.87</v>
       </c>
       <c r="AS8" t="n">
-        <v>15.8</v>
+        <v>15.71</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46196</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>36.16</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>14456.2</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1789.4</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>2814.9</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="B9" t="n">
-        <v>183.8</v>
+        <v>181.9</v>
       </c>
       <c r="C9" t="n">
-        <v>86.7</v>
+        <v>88.7</v>
       </c>
       <c r="D9" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="F9" t="n">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
-        <v>24.4</v>
+        <v>23.2</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="J9" t="n">
-        <v>41.3</v>
+        <v>42.3</v>
       </c>
       <c r="K9" t="n">
-        <v>75.7</v>
+        <v>76.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
         <v>38</v>
       </c>
       <c r="O9" t="n">
-        <v>41.6</v>
+        <v>41.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="S9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T9" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Y9" t="n">
         <v>4</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AF9" t="n">
-        <v>227.74</v>
+        <v>229.92</v>
       </c>
       <c r="AG9" t="n">
-        <v>-3.29</v>
+        <v>-6.8</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1383,10 +1323,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>127.86</v>
+        <v>133.43</v>
       </c>
       <c r="AL9" t="n">
-        <v>-3.67</v>
+        <v>-0.68</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1395,93 +1335,81 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>84.81</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>13.95</v>
+        <v>15.36</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>37.03</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>15572</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>2181.8</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46198</v>
+        <v>46205</v>
       </c>
       <c r="B10" t="n">
-        <v>178.9</v>
+        <v>188.8</v>
       </c>
       <c r="C10" t="n">
-        <v>84.2</v>
+        <v>94.8</v>
       </c>
       <c r="D10" t="n">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="E10" t="n">
-        <v>31.1</v>
+        <v>32.4</v>
       </c>
       <c r="F10" t="n">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="H10" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="I10" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="J10" t="n">
-        <v>41.5</v>
+        <v>40.8</v>
       </c>
       <c r="K10" t="n">
-        <v>76.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>38.1</v>
+        <v>36.5</v>
       </c>
       <c r="O10" t="n">
-        <v>41.6</v>
+        <v>40.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.1</v>
+        <v>22.7</v>
       </c>
       <c r="R10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>8</v>
-      </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>226.8</v>
+        <v>223</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.95</v>
+        <v>-6.92</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1490,10 +1418,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>129.1</v>
+        <v>128.87</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.24</v>
+        <v>-4.56</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1502,66 +1430,54 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>81.91</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>15.61</v>
+        <v>14.68</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>38.28</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>14004.4</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>2044.8</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="B11" t="n">
-        <v>155.4</v>
+        <v>166.3</v>
       </c>
       <c r="C11" t="n">
-        <v>82.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>27.4</v>
+        <v>26.1</v>
       </c>
       <c r="E11" t="n">
-        <v>29.1</v>
+        <v>30.6</v>
       </c>
       <c r="F11" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="O11" t="n">
-        <v>40.1</v>
+        <v>39.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>14</v>
+        <v>9.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>226.39</v>
+        <v>221.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.4</v>
+        <v>-1.92</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1570,10 +1486,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>129.78</v>
+        <v>125.07</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.68</v>
+        <v>-3.8</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1582,48 +1498,48 @@
         <v>142</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46199</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46200</v>
+        <v>46207</v>
       </c>
       <c r="B12" t="n">
-        <v>151.1</v>
+        <v>154.6</v>
       </c>
       <c r="C12" t="n">
-        <v>76.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>26.8</v>
+        <v>25.2</v>
       </c>
       <c r="E12" t="n">
-        <v>30.9</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>97.7</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>40.8</v>
+        <v>39.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>229.98</v>
+        <v>221.24</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.58</v>
+        <v>0.16</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1632,10 +1548,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>132.56</v>
+        <v>125.99</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.78</v>
+        <v>0.92</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1644,75 +1560,75 @@
         <v>142</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46200</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46201</v>
+        <v>46208</v>
       </c>
       <c r="B13" t="n">
-        <v>167.2</v>
+        <v>175.7</v>
       </c>
       <c r="C13" t="n">
-        <v>74.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="D13" t="n">
-        <v>27.6</v>
+        <v>24</v>
       </c>
       <c r="E13" t="n">
-        <v>28.2</v>
+        <v>26.9</v>
       </c>
       <c r="F13" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="I13" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="J13" t="n">
-        <v>40.3</v>
+        <v>42.1</v>
       </c>
       <c r="K13" t="n">
-        <v>75</v>
+        <v>77.8</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
         <v>37.2</v>
       </c>
       <c r="O13" t="n">
-        <v>39.9</v>
+        <v>42.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>22</v>
+        <v>22.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="T13" t="n">
-        <v>22</v>
+        <v>22.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA13" t="n">
-        <v>13</v>
+        <v>6.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>236.38</v>
+        <v>223.94</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1721,10 +1637,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>132.97</v>
+        <v>128.11</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.41</v>
+        <v>2.12</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1733,81 +1649,81 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>90.8</v>
+        <v>88.34</v>
       </c>
       <c r="AS13" t="n">
-        <v>16.05</v>
+        <v>16.09</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46201</v>
+        <v>46208</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="B14" t="n">
-        <v>176.7</v>
+        <v>178.9</v>
       </c>
       <c r="C14" t="n">
-        <v>80.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>28.3</v>
+        <v>26.6</v>
       </c>
       <c r="E14" t="n">
-        <v>31.6</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="H14" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="I14" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="J14" t="n">
         <v>41.8</v>
       </c>
       <c r="K14" t="n">
-        <v>76.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>38.4</v>
+        <v>37.5</v>
       </c>
       <c r="O14" t="n">
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.9</v>
+        <v>23</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S14" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="T14" t="n">
-        <v>20.9</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="n">
         <v>5</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.9</v>
+        <v>7.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>236.23</v>
+        <v>224.33</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.15</v>
+        <v>0.39</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1816,10 +1732,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>132.79</v>
+        <v>128.49</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.18</v>
+        <v>0.38</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1828,81 +1744,81 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>89.64</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>15.89</v>
+        <v>16.13</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B15" t="n">
         <v>175.3</v>
       </c>
       <c r="C15" t="n">
-        <v>83.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D15" t="n">
+        <v>27</v>
+      </c>
+      <c r="E15" t="n">
         <v>27.8</v>
       </c>
-      <c r="E15" t="n">
-        <v>30.3</v>
-      </c>
       <c r="F15" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="H15" t="n">
-        <v>24.7</v>
+        <v>24.2</v>
       </c>
       <c r="I15" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="J15" t="n">
-        <v>42.9</v>
+        <v>41.4</v>
       </c>
       <c r="K15" t="n">
-        <v>77.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="O15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>18</v>
+        <v>19.9</v>
       </c>
       <c r="T15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>14</v>
+        <v>16.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>236.72</v>
+        <v>224.34</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.49</v>
+        <v>0.01</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1911,10 +1827,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>134.11</v>
+        <v>128.93</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.32</v>
+        <v>0.44</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1923,81 +1839,54 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>88.87</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>15.71</v>
+        <v>15.43</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="B16" t="n">
-        <v>181.9</v>
+        <v>157.8</v>
       </c>
       <c r="C16" t="n">
-        <v>88.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>27.2</v>
+        <v>26.5</v>
       </c>
       <c r="E16" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="F16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>42.3</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>38</v>
+        <v>98.7</v>
       </c>
       <c r="O16" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>17</v>
-      </c>
-      <c r="T16" t="n">
-        <v>21.8</v>
+        <v>40.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.699999999999999</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>229.92</v>
+        <v>231.46</v>
       </c>
       <c r="AG16" t="n">
-        <v>-6.8</v>
+        <v>3.7</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2006,10 +1895,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>133.43</v>
+        <v>129.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.68</v>
+        <v>0.87</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2017,82 +1906,49 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
-      <c r="AP16" t="n">
-        <v>85.26000000000001</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>15.36</v>
-      </c>
       <c r="BL16" s="1" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="B17" t="n">
-        <v>188.8</v>
+        <v>151.6</v>
       </c>
       <c r="C17" t="n">
-        <v>94.8</v>
+        <v>73.8</v>
       </c>
       <c r="D17" t="n">
-        <v>27.9</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>32.4</v>
+        <v>33.9</v>
       </c>
       <c r="F17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I17" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>40.8</v>
+        <v>7.4</v>
       </c>
       <c r="K17" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>36.5</v>
+        <v>97.5</v>
       </c>
       <c r="O17" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S17" t="n">
-        <v>20</v>
-      </c>
-      <c r="T17" t="n">
-        <v>22.7</v>
+        <v>40.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.1</v>
+        <v>12.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>223</v>
+        <v>229.92</v>
       </c>
       <c r="AG17" t="n">
-        <v>-6.92</v>
+        <v>-1.54</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2101,10 +1957,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>128.87</v>
+        <v>133.01</v>
       </c>
       <c r="AL17" t="n">
-        <v>-4.56</v>
+        <v>3.21</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2112,55 +1968,49 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
-      <c r="AP17" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>14.68</v>
-      </c>
       <c r="BL17" s="1" t="n">
-        <v>46205</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B18" t="n">
-        <v>166.3</v>
+        <v>157.5</v>
       </c>
       <c r="C18" t="n">
-        <v>94.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>26.1</v>
+        <v>27.1</v>
       </c>
       <c r="E18" t="n">
-        <v>30.6</v>
+        <v>36.9</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="K18" t="n">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="O18" t="n">
-        <v>39.4</v>
+        <v>38</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.1</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>221.08</v>
+        <v>226.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>-1.92</v>
+        <v>-2.97</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2169,10 +2019,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>125.07</v>
+        <v>128.4</v>
       </c>
       <c r="AL18" t="n">
-        <v>-3.8</v>
+        <v>-4.61</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2181,48 +2031,48 @@
         <v>142</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B19" t="n">
-        <v>154.6</v>
+        <v>148.5</v>
       </c>
       <c r="C19" t="n">
-        <v>89</v>
+        <v>70.5</v>
       </c>
       <c r="D19" t="n">
-        <v>25.2</v>
+        <v>26.8</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>34.3</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="K19" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="O19" t="n">
-        <v>39.5</v>
+        <v>39.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA19" t="n">
         <v>11</v>
       </c>
-      <c r="AA19" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AF19" t="n">
-        <v>221.24</v>
+        <v>223.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.16</v>
+        <v>-3.83</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2231,10 +2081,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>125.99</v>
+        <v>124.76</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.92</v>
+        <v>-3.64</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2243,75 +2093,42 @@
         <v>142</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B20" t="n">
-        <v>175.7</v>
+        <v>147.5</v>
       </c>
       <c r="C20" t="n">
-        <v>91.2</v>
+        <v>72.8</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>26.7</v>
       </c>
       <c r="E20" t="n">
-        <v>26.9</v>
+        <v>31.4</v>
       </c>
       <c r="F20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="I20" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>42.1</v>
+        <v>7.4</v>
       </c>
       <c r="K20" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>37.2</v>
+        <v>100</v>
       </c>
       <c r="O20" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>22.7</v>
+        <v>40.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>223.94</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.7</v>
+        <v>10</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2320,10 +2137,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>128.11</v>
+        <v>127.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2331,82 +2148,76 @@
       <c r="AN20" t="n">
         <v>142</v>
       </c>
-      <c r="AP20" t="n">
-        <v>88.34</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>16.09</v>
-      </c>
       <c r="BL20" s="1" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="B21" t="n">
-        <v>178.9</v>
+        <v>183.5</v>
       </c>
       <c r="C21" t="n">
-        <v>92.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="D21" t="n">
-        <v>26.6</v>
+        <v>31.5</v>
       </c>
       <c r="E21" t="n">
-        <v>24</v>
+        <v>34.6</v>
       </c>
       <c r="F21" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H21" t="n">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="I21" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="J21" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
       <c r="K21" t="n">
-        <v>77.7</v>
+        <v>76.3</v>
       </c>
       <c r="M21" t="n">
         <v>4.1</v>
       </c>
       <c r="N21" t="n">
-        <v>37.5</v>
+        <v>37.7</v>
       </c>
       <c r="O21" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="Q21" t="n">
         <v>23</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="S21" t="n">
-        <v>19.3</v>
+        <v>18</v>
       </c>
       <c r="T21" t="n">
         <v>23</v>
       </c>
       <c r="Y21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>224.33</v>
+        <v>220.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.39</v>
+        <v>-3.75</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2415,10 +2226,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>128.49</v>
+        <v>127.13</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.38</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2427,81 +2238,81 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>87.56999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>16.13</v>
+        <v>14.17</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46210</v>
+        <v>46217</v>
       </c>
       <c r="B22" t="n">
-        <v>175.3</v>
+        <v>180.5</v>
       </c>
       <c r="C22" t="n">
-        <v>85.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>30.7</v>
       </c>
       <c r="E22" t="n">
-        <v>27.8</v>
+        <v>34.6</v>
       </c>
       <c r="F22" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="H22" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="J22" t="n">
-        <v>41.4</v>
+        <v>41.9</v>
       </c>
       <c r="K22" t="n">
-        <v>76.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>38.4</v>
+        <v>37.7</v>
       </c>
       <c r="O22" t="n">
-        <v>42</v>
+        <v>42.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="S22" t="n">
-        <v>19.9</v>
+        <v>17.6</v>
       </c>
       <c r="T22" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="Z22" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="n">
-        <v>10.3</v>
+        <v>11.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>224.34</v>
+        <v>219.64</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01</v>
+        <v>-0.72</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2510,10 +2321,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>128.93</v>
+        <v>126.03</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.44</v>
+        <v>-1.1</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2522,54 +2333,81 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>89.06999999999999</v>
+        <v>82.95</v>
       </c>
       <c r="AS22" t="n">
-        <v>15.43</v>
+        <v>14.55</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46210</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="B23" t="n">
-        <v>157.8</v>
+        <v>168.1</v>
       </c>
       <c r="C23" t="n">
-        <v>85.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="D23" t="n">
-        <v>26.5</v>
+        <v>30.4</v>
       </c>
       <c r="E23" t="n">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>7.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>41.2</v>
       </c>
       <c r="K23" t="n">
-        <v>98.7</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>38.1</v>
       </c>
       <c r="O23" t="n">
-        <v>40.5</v>
+        <v>43.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA23" t="n">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>231.46</v>
+        <v>224.93</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.7</v>
+        <v>5.29</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2578,10 +2416,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>129.8</v>
+        <v>129.28</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.87</v>
+        <v>3.25</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2589,49 +2427,82 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
+      <c r="AP23" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>15.25</v>
+      </c>
       <c r="BL23" s="1" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46212</v>
+        <v>46219</v>
       </c>
       <c r="B24" t="n">
-        <v>151.6</v>
+        <v>158.9</v>
       </c>
       <c r="C24" t="n">
-        <v>73.8</v>
+        <v>58.8</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>31.1</v>
       </c>
       <c r="E24" t="n">
-        <v>33.9</v>
+        <v>30.4</v>
       </c>
       <c r="F24" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>97.5</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>37.8</v>
       </c>
       <c r="O24" t="n">
-        <v>40.6</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="n">
+        <v>21.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="n">
-        <v>12.5</v>
+        <v>19.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>229.92</v>
+        <v>232.31</v>
       </c>
       <c r="AG24" t="n">
-        <v>-1.54</v>
+        <v>9.67</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2640,10 +2511,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>133.01</v>
+        <v>134.44</v>
       </c>
       <c r="AL24" t="n">
-        <v>3.21</v>
+        <v>5.16</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2651,49 +2522,49 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
+      <c r="AP24" t="n">
+        <v>91.73999999999999</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>17.07</v>
+      </c>
       <c r="BL24" s="1" t="n">
-        <v>46212</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="B25" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C25" t="n">
-        <v>76.40000000000001</v>
+        <v>136.7</v>
       </c>
       <c r="D25" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>36.9</v>
+        <v>30.7</v>
       </c>
       <c r="F25" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="K25" t="n">
-        <v>100</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>38</v>
+        <v>39.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Z25" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AA25" t="n">
-        <v>11.5</v>
+        <v>20.5</v>
       </c>
       <c r="AF25" t="n">
-        <v>226.95</v>
+        <v>235.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>-2.97</v>
+        <v>3.09</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2702,10 +2573,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>128.4</v>
+        <v>137.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>-4.61</v>
+        <v>3.06</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2714,48 +2585,42 @@
         <v>142</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46213</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B26" t="n">
-        <v>148.5</v>
-      </c>
-      <c r="C26" t="n">
-        <v>70.5</v>
+        <v>138.5</v>
       </c>
       <c r="D26" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>34.3</v>
+        <v>31.7</v>
       </c>
       <c r="F26" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>98.2</v>
+        <v>91</v>
       </c>
       <c r="O26" t="n">
-        <v>39.8</v>
+        <v>37.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA26" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>223.11</v>
+        <v>231.99</v>
       </c>
       <c r="AG26" t="n">
-        <v>-3.83</v>
+        <v>-3.41</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -2764,10 +2629,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>124.76</v>
+        <v>136.12</v>
       </c>
       <c r="AL26" t="n">
-        <v>-3.64</v>
+        <v>-1.38</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -2776,42 +2641,75 @@
         <v>142</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B27" t="n">
-        <v>147.5</v>
+        <v>161.1</v>
       </c>
       <c r="C27" t="n">
-        <v>72.8</v>
+        <v>67</v>
       </c>
       <c r="D27" t="n">
-        <v>26.7</v>
+        <v>31.9</v>
       </c>
       <c r="E27" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="F27" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>41.1</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>35</v>
       </c>
       <c r="O27" t="n">
-        <v>40.2</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>20.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA27" t="n">
-        <v>10</v>
+        <v>11.1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>225.51</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>-6.48</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -2820,10 +2718,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>127.2</v>
+        <v>133.83</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.44</v>
+        <v>-2.29</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -2831,76 +2729,82 @@
       <c r="AN27" t="n">
         <v>142</v>
       </c>
+      <c r="AP27" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL27" s="1" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="B28" t="n">
-        <v>183.5</v>
+        <v>176.4</v>
       </c>
       <c r="C28" t="n">
-        <v>84.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>31.5</v>
+        <v>32.7</v>
       </c>
       <c r="E28" t="n">
-        <v>34.6</v>
+        <v>35</v>
       </c>
       <c r="F28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H28" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="I28" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="J28" t="n">
         <v>41.5</v>
       </c>
       <c r="K28" t="n">
-        <v>76.3</v>
+        <v>76</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="N28" t="n">
-        <v>37.7</v>
+        <v>36.4</v>
       </c>
       <c r="O28" t="n">
-        <v>41.8</v>
+        <v>39.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>22.3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T28" t="n">
-        <v>23</v>
+        <v>22.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA28" t="n">
-        <v>7.7</v>
+        <v>11.6</v>
       </c>
       <c r="AF28" t="n">
-        <v>220.36</v>
+        <v>220.92</v>
       </c>
       <c r="AG28" t="n">
-        <v>-3.75</v>
+        <v>-4.59</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -2909,10 +2813,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>127.13</v>
+        <v>131.85</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.98</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -2921,81 +2825,81 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>76.90000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS28" t="n">
-        <v>14.17</v>
+        <v>15.49</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46216</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="B29" t="n">
-        <v>180.5</v>
+        <v>181</v>
       </c>
       <c r="C29" t="n">
-        <v>79.2</v>
+        <v>80.7</v>
       </c>
       <c r="D29" t="n">
-        <v>30.7</v>
+        <v>33</v>
       </c>
       <c r="E29" t="n">
-        <v>34.6</v>
+        <v>35.1</v>
       </c>
       <c r="F29" t="n">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="H29" t="n">
-        <v>23.9</v>
+        <v>22.8</v>
       </c>
       <c r="I29" t="n">
-        <v>10.3</v>
+        <v>11.2</v>
       </c>
       <c r="J29" t="n">
         <v>41.9</v>
       </c>
       <c r="K29" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>37.7</v>
+        <v>36.9</v>
       </c>
       <c r="O29" t="n">
-        <v>42.7</v>
+        <v>39.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="R29" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="S29" t="n">
-        <v>17.6</v>
+        <v>20.5</v>
       </c>
       <c r="T29" t="n">
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA29" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>219.64</v>
+        <v>220.92</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3004,10 +2908,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>126.03</v>
+        <v>130.06</v>
       </c>
       <c r="AL29" t="n">
-        <v>-1.1</v>
+        <v>-1.79</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3016,81 +2920,81 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>82.95</v>
+        <v>79.94</v>
       </c>
       <c r="AS29" t="n">
-        <v>14.55</v>
+        <v>14.93</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46217</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46218</v>
+        <v>46225</v>
       </c>
       <c r="B30" t="n">
-        <v>168.1</v>
+        <v>179.6</v>
       </c>
       <c r="C30" t="n">
-        <v>69.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="E30" t="n">
-        <v>33.9</v>
+        <v>31.1</v>
       </c>
       <c r="F30" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="H30" t="n">
-        <v>24.1</v>
+        <v>21.5</v>
       </c>
       <c r="I30" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="J30" t="n">
-        <v>41.2</v>
+        <v>42.3</v>
       </c>
       <c r="K30" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="N30" t="n">
-        <v>38.1</v>
+        <v>37.1</v>
       </c>
       <c r="O30" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q30" t="n">
         <v>22.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>17.6</v>
+        <v>21.2</v>
       </c>
       <c r="T30" t="n">
         <v>22.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z30" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA30" t="n">
-        <v>14.9</v>
+        <v>11.1</v>
       </c>
       <c r="AF30" t="n">
-        <v>224.93</v>
+        <v>216.02</v>
       </c>
       <c r="AG30" t="n">
-        <v>5.29</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3099,10 +3003,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>129.28</v>
+        <v>127.85</v>
       </c>
       <c r="AL30" t="n">
-        <v>3.25</v>
+        <v>-2.21</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3111,81 +3015,81 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>87.43000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="AS30" t="n">
-        <v>15.25</v>
+        <v>15.16</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46218</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B31" t="n">
-        <v>158.9</v>
+        <v>170.4</v>
       </c>
       <c r="C31" t="n">
-        <v>58.8</v>
+        <v>78.5</v>
       </c>
       <c r="D31" t="n">
-        <v>31.1</v>
+        <v>29.8</v>
       </c>
       <c r="E31" t="n">
-        <v>30.4</v>
+        <v>29.7</v>
       </c>
       <c r="F31" t="n">
-        <v>7.8</v>
+        <v>6.3</v>
       </c>
       <c r="H31" t="n">
-        <v>23.7</v>
+        <v>22.5</v>
       </c>
       <c r="I31" t="n">
         <v>11.2</v>
       </c>
       <c r="J31" t="n">
-        <v>41</v>
+        <v>41.4</v>
       </c>
       <c r="K31" t="n">
-        <v>75.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="N31" t="n">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
       <c r="O31" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>21.5</v>
+        <v>23.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>21.1</v>
       </c>
       <c r="T31" t="n">
-        <v>21.5</v>
+        <v>23.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Z31" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.3</v>
+        <v>12.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>232.31</v>
+        <v>216.02</v>
       </c>
       <c r="AG31" t="n">
-        <v>9.67</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3194,10 +3098,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>134.44</v>
+        <v>128.54</v>
       </c>
       <c r="AL31" t="n">
-        <v>5.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3206,48 +3110,48 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>91.73999999999999</v>
+        <v>84.73</v>
       </c>
       <c r="AS31" t="n">
-        <v>17.07</v>
+        <v>15.34</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B32" t="n">
-        <v>136.7</v>
+        <v>156</v>
       </c>
       <c r="D32" t="n">
-        <v>30.7</v>
+        <v>30.1</v>
       </c>
       <c r="F32" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="K32" t="n">
-        <v>92.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O32" t="n">
         <v>39.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Z32" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="n">
-        <v>20.5</v>
+        <v>13.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>235.4</v>
+        <v>224.53</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.09</v>
+        <v>2.32</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3256,10 +3160,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>137.5</v>
+        <v>130.92</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.06</v>
+        <v>2.38</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3268,42 +3172,42 @@
         <v>142</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B33" t="n">
-        <v>138.5</v>
+        <v>147.8</v>
       </c>
       <c r="D33" t="n">
-        <v>31.7</v>
+        <v>32</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K33" t="n">
-        <v>91</v>
+        <v>96.5</v>
       </c>
       <c r="O33" t="n">
-        <v>37.8</v>
+        <v>39.3</v>
       </c>
       <c r="Y33" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA33" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>231.99</v>
+        <v>230.27</v>
       </c>
       <c r="AG33" t="n">
-        <v>-3.41</v>
+        <v>5.74</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3312,10 +3216,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>136.12</v>
+        <v>132.76</v>
       </c>
       <c r="AL33" t="n">
-        <v>-1.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3324,75 +3228,75 @@
         <v>142</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B34" t="n">
-        <v>161.1</v>
+        <v>149.1</v>
       </c>
       <c r="C34" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D34" t="n">
-        <v>31.9</v>
+        <v>29</v>
       </c>
       <c r="E34" t="n">
-        <v>31.5</v>
+        <v>25.9</v>
       </c>
       <c r="F34" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="H34" t="n">
-        <v>23.1</v>
+        <v>24</v>
       </c>
       <c r="I34" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="J34" t="n">
-        <v>41.1</v>
+        <v>38.8</v>
       </c>
       <c r="K34" t="n">
-        <v>75.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="M34" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>35</v>
+        <v>36.7</v>
       </c>
       <c r="O34" t="n">
-        <v>37.2</v>
+        <v>40.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>20.5</v>
+        <v>21.7</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T34" t="n">
-        <v>20.5</v>
+        <v>21.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="n">
-        <v>11.1</v>
+        <v>15.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>225.51</v>
+        <v>237.43</v>
       </c>
       <c r="AG34" t="n">
-        <v>-6.48</v>
+        <v>7.16</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3401,10 +3305,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>133.83</v>
+        <v>134.95</v>
       </c>
       <c r="AL34" t="n">
-        <v>-2.29</v>
+        <v>2.19</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3413,81 +3317,48 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>82.93000000000001</v>
+        <v>91.28</v>
       </c>
       <c r="AS34" t="n">
-        <v>15.73</v>
+        <v>16.95</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="B35" t="n">
-        <v>176.4</v>
-      </c>
-      <c r="C35" t="n">
-        <v>77.09999999999999</v>
+        <v>143.9</v>
       </c>
       <c r="D35" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E35" t="n">
-        <v>35</v>
+        <v>32.9</v>
       </c>
       <c r="F35" t="n">
         <v>6.8</v>
       </c>
-      <c r="H35" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="I35" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>41.5</v>
-      </c>
       <c r="K35" t="n">
-        <v>76</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N35" t="n">
-        <v>36.4</v>
+        <v>96.2</v>
       </c>
       <c r="O35" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>14</v>
-      </c>
-      <c r="T35" t="n">
-        <v>22.3</v>
+        <v>37.9</v>
       </c>
       <c r="Y35" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA35" t="n">
-        <v>11.6</v>
+        <v>16</v>
       </c>
       <c r="AF35" t="n">
-        <v>220.92</v>
+        <v>236.14</v>
       </c>
       <c r="AG35" t="n">
-        <v>-4.59</v>
+        <v>-1.29</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3496,10 +3367,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>131.85</v>
+        <v>136.28</v>
       </c>
       <c r="AL35" t="n">
-        <v>-1.98</v>
+        <v>1.33</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3507,82 +3378,76 @@
       <c r="AN35" t="n">
         <v>142</v>
       </c>
-      <c r="AP35" t="n">
-        <v>79.75</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>15.49</v>
-      </c>
       <c r="BL35" s="1" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46224</v>
+        <v>46231</v>
       </c>
       <c r="B36" t="n">
-        <v>181</v>
+        <v>166.4</v>
       </c>
       <c r="C36" t="n">
-        <v>80.7</v>
+        <v>63.7</v>
       </c>
       <c r="D36" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="E36" t="n">
-        <v>35.1</v>
+        <v>36.4</v>
       </c>
       <c r="F36" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="H36" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="I36" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="J36" t="n">
-        <v>41.9</v>
+        <v>39.9</v>
       </c>
       <c r="K36" t="n">
-        <v>75.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>36.9</v>
+        <v>35.9</v>
       </c>
       <c r="O36" t="n">
-        <v>39.8</v>
+        <v>39</v>
       </c>
       <c r="Q36" t="n">
-        <v>22.5</v>
+        <v>20.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S36" t="n">
-        <v>20.5</v>
+        <v>6</v>
       </c>
       <c r="T36" t="n">
-        <v>22.5</v>
+        <v>20.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z36" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA36" t="n">
-        <v>11.4</v>
+        <v>14.4</v>
       </c>
       <c r="AF36" t="n">
-        <v>220.92</v>
+        <v>236.13</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3591,10 +3456,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>130.06</v>
+        <v>134.54</v>
       </c>
       <c r="AL36" t="n">
-        <v>-1.79</v>
+        <v>-1.74</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -3603,81 +3468,81 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>79.94</v>
+        <v>82.27</v>
       </c>
       <c r="AS36" t="n">
-        <v>14.93</v>
+        <v>16.28</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46224</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B37" t="n">
-        <v>179.6</v>
+        <v>172.9</v>
       </c>
       <c r="C37" t="n">
-        <v>81.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>30.3</v>
+        <v>34.9</v>
       </c>
       <c r="E37" t="n">
-        <v>31.1</v>
+        <v>35.2</v>
       </c>
       <c r="F37" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="H37" t="n">
-        <v>21.5</v>
+        <v>23.6</v>
       </c>
       <c r="I37" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="J37" t="n">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="K37" t="n">
-        <v>74.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="M37" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="N37" t="n">
-        <v>37.1</v>
+        <v>34.8</v>
       </c>
       <c r="O37" t="n">
-        <v>41.4</v>
+        <v>37.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>22.6</v>
+        <v>19</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>21.2</v>
+        <v>10</v>
       </c>
       <c r="T37" t="n">
-        <v>22.6</v>
+        <v>19</v>
       </c>
       <c r="Y37" t="n">
         <v>9</v>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA37" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>216.02</v>
+        <v>218.6</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -3686,10 +3551,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>127.85</v>
+        <v>130.39</v>
       </c>
       <c r="AL37" t="n">
-        <v>-2.21</v>
+        <v>-4.15</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -3698,81 +3563,81 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>82.2</v>
+        <v>78.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>15.16</v>
+        <v>15.79</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46225</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46226</v>
+        <v>46233</v>
       </c>
       <c r="B38" t="n">
-        <v>170.4</v>
+        <v>157.5</v>
       </c>
       <c r="C38" t="n">
-        <v>78.5</v>
+        <v>68.5</v>
       </c>
       <c r="D38" t="n">
-        <v>29.8</v>
+        <v>33.2</v>
       </c>
       <c r="E38" t="n">
-        <v>29.7</v>
+        <v>27.7</v>
       </c>
       <c r="F38" t="n">
-        <v>6.3</v>
+        <v>3.6</v>
       </c>
       <c r="H38" t="n">
-        <v>22.5</v>
+        <v>23.4</v>
       </c>
       <c r="I38" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="J38" t="n">
         <v>41.4</v>
       </c>
       <c r="K38" t="n">
-        <v>75</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="N38" t="n">
-        <v>36.6</v>
+        <v>34.9</v>
       </c>
       <c r="O38" t="n">
-        <v>41.3</v>
+        <v>37.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.3</v>
+        <v>21.6</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>21.1</v>
+        <v>9</v>
       </c>
       <c r="T38" t="n">
-        <v>23.3</v>
+        <v>21.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z38" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA38" t="n">
-        <v>12.7</v>
+        <v>13.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>216.02</v>
+        <v>218.84</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -3781,10 +3646,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>128.54</v>
+        <v>133.09</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -3793,48 +3658,48 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>84.73</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS38" t="n">
-        <v>15.34</v>
+        <v>15.63</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46226</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B39" t="n">
-        <v>156</v>
+        <v>137.6</v>
       </c>
       <c r="D39" t="n">
-        <v>30.1</v>
+        <v>35</v>
       </c>
       <c r="F39" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="K39" t="n">
-        <v>95.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="O39" t="n">
-        <v>39.2</v>
+        <v>35.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z39" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>224.53</v>
+        <v>221.78</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.32</v>
+        <v>2.94</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -3843,10 +3708,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>130.92</v>
+        <v>138.76</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.38</v>
+        <v>5.67</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -3855,42 +3720,42 @@
         <v>142</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B40" t="n">
-        <v>147.8</v>
+        <v>132.5</v>
       </c>
       <c r="D40" t="n">
-        <v>32</v>
+        <v>33.6</v>
       </c>
       <c r="F40" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="K40" t="n">
-        <v>96.5</v>
+        <v>97.8</v>
       </c>
       <c r="O40" t="n">
-        <v>39.3</v>
+        <v>31.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z40" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA40" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF40" t="n">
-        <v>230.27</v>
+        <v>224.78</v>
       </c>
       <c r="AG40" t="n">
-        <v>5.74</v>
+        <v>3</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -3899,10 +3764,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>132.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.84</v>
+        <v>4.79</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -3911,75 +3776,75 @@
         <v>142</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B41" t="n">
-        <v>149.1</v>
+        <v>137.2</v>
       </c>
       <c r="C41" t="n">
-        <v>60</v>
+        <v>56.3</v>
       </c>
       <c r="D41" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I41" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J41" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N41" t="n">
         <v>29</v>
       </c>
-      <c r="E41" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="F41" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H41" t="n">
-        <v>24</v>
-      </c>
-      <c r="I41" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J41" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="K41" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N41" t="n">
-        <v>36.7</v>
-      </c>
       <c r="O41" t="n">
-        <v>40.1</v>
+        <v>32.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Y41" t="n">
         <v>12</v>
       </c>
       <c r="Z41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA41" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="AF41" t="n">
-        <v>237.43</v>
+        <v>232.22</v>
       </c>
       <c r="AG41" t="n">
-        <v>7.16</v>
+        <v>7.43</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -3988,10 +3853,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>134.95</v>
+        <v>143.61</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.19</v>
+        <v>0.06</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4000,48 +3865,81 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>91.28</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="AS41" t="n">
-        <v>16.95</v>
+        <v>18.02</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="B42" t="n">
-        <v>143.9</v>
+        <v>157.5</v>
+      </c>
+      <c r="C42" t="n">
+        <v>59.6</v>
       </c>
       <c r="D42" t="n">
-        <v>32.9</v>
+        <v>35</v>
+      </c>
+      <c r="E42" t="n">
+        <v>30.6</v>
       </c>
       <c r="F42" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>38.9</v>
       </c>
       <c r="K42" t="n">
-        <v>96.2</v>
+        <v>74.3</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N42" t="n">
+        <v>33.4</v>
       </c>
       <c r="O42" t="n">
-        <v>37.9</v>
+        <v>37.1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>21.1</v>
       </c>
       <c r="Y42" t="n">
         <v>13</v>
       </c>
       <c r="Z42" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA42" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF42" t="n">
-        <v>236.14</v>
+        <v>229.69</v>
       </c>
       <c r="AG42" t="n">
-        <v>-1.29</v>
+        <v>-2.53</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4050,10 +3948,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>136.28</v>
+        <v>136.96</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.33</v>
+        <v>-6.65</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4061,76 +3959,82 @@
       <c r="AN42" t="n">
         <v>142</v>
       </c>
+      <c r="AP42" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>16.96</v>
+      </c>
       <c r="BL42" s="1" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46231</v>
+        <v>46238</v>
       </c>
       <c r="B43" t="n">
-        <v>166.4</v>
+        <v>159.6</v>
       </c>
       <c r="C43" t="n">
-        <v>63.7</v>
+        <v>63</v>
       </c>
       <c r="D43" t="n">
         <v>34.5</v>
       </c>
       <c r="E43" t="n">
-        <v>36.4</v>
+        <v>31.1</v>
       </c>
       <c r="F43" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="H43" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="I43" t="n">
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="J43" t="n">
-        <v>39.9</v>
+        <v>40.5</v>
       </c>
       <c r="K43" t="n">
         <v>75.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>35.9</v>
+        <v>34.3</v>
       </c>
       <c r="O43" t="n">
-        <v>39</v>
+        <v>38.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>20.3</v>
+        <v>21.3</v>
       </c>
       <c r="R43" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>20.3</v>
+        <v>21.3</v>
       </c>
       <c r="Y43" t="n">
         <v>11</v>
       </c>
       <c r="Z43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA43" t="n">
-        <v>14.4</v>
+        <v>13.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>236.13</v>
+        <v>228.57</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.01</v>
+        <v>-1.14</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4139,10 +4043,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>134.54</v>
+        <v>133.01</v>
       </c>
       <c r="AL43" t="n">
-        <v>-1.74</v>
+        <v>-3.95</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4151,81 +4055,81 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>82.27</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS43" t="n">
-        <v>16.28</v>
+        <v>15.95</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46231</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="B44" t="n">
-        <v>172.9</v>
+        <v>160.4</v>
       </c>
       <c r="C44" t="n">
-        <v>67.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="D44" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="E44" t="n">
-        <v>35.2</v>
+        <v>32.2</v>
       </c>
       <c r="F44" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="H44" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="I44" t="n">
-        <v>11.3</v>
+        <v>10.7</v>
       </c>
       <c r="J44" t="n">
-        <v>41.7</v>
+        <v>41.1</v>
       </c>
       <c r="K44" t="n">
-        <v>76.7</v>
+        <v>75.7</v>
       </c>
       <c r="M44" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="N44" t="n">
-        <v>34.8</v>
+        <v>32.6</v>
       </c>
       <c r="O44" t="n">
-        <v>37.2</v>
+        <v>38</v>
       </c>
       <c r="Q44" t="n">
-        <v>19</v>
+        <v>20.9</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="n">
-        <v>19</v>
+        <v>20.9</v>
       </c>
       <c r="Y44" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA44" t="n">
-        <v>12.5</v>
+        <v>14.1</v>
       </c>
       <c r="AF44" t="n">
-        <v>218.6</v>
+        <v>225.08</v>
       </c>
       <c r="AG44" t="n">
-        <v>-9.380000000000001</v>
+        <v>-3.5</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4234,10 +4138,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>130.39</v>
+        <v>135.24</v>
       </c>
       <c r="AL44" t="n">
-        <v>-4.15</v>
+        <v>2.23</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4246,81 +4150,81 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>78.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS44" t="n">
-        <v>15.79</v>
+        <v>15.4</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46232</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46233</v>
+        <v>46240</v>
       </c>
       <c r="B45" t="n">
-        <v>157.5</v>
+        <v>161.7</v>
       </c>
       <c r="C45" t="n">
-        <v>68.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>33.2</v>
+        <v>34.9</v>
       </c>
       <c r="E45" t="n">
-        <v>27.7</v>
+        <v>27.3</v>
       </c>
       <c r="F45" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="H45" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="I45" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="J45" t="n">
-        <v>41.4</v>
+        <v>42.6</v>
       </c>
       <c r="K45" t="n">
-        <v>76.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="M45" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="N45" t="n">
-        <v>34.9</v>
+        <v>31.5</v>
       </c>
       <c r="O45" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S45" t="n">
+        <v>6</v>
+      </c>
+      <c r="T45" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y45" t="n">
         <v>9</v>
       </c>
-      <c r="T45" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>11</v>
-      </c>
       <c r="Z45" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA45" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="AF45" t="n">
-        <v>218.84</v>
+        <v>225</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.25</v>
+        <v>-0.08</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4329,10 +4233,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>133.09</v>
+        <v>134.62</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.7</v>
+        <v>-0.62</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4341,48 +4245,48 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>83.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS45" t="n">
-        <v>15.63</v>
+        <v>13.86</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46233</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="B46" t="n">
-        <v>137.6</v>
+        <v>151.5</v>
       </c>
       <c r="D46" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F46" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="K46" t="n">
-        <v>96.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>35.1</v>
+        <v>36.8</v>
       </c>
       <c r="Y46" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Z46" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AA46" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="AF46" t="n">
-        <v>221.78</v>
+        <v>221.37</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.94</v>
+        <v>0.05</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4391,10 +4295,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>138.76</v>
+        <v>135.21</v>
       </c>
       <c r="AL46" t="n">
-        <v>5.67</v>
+        <v>0.59</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4403,39 +4307,39 @@
         <v>142</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="B47" t="n">
-        <v>132.5</v>
+        <v>145.2</v>
       </c>
       <c r="D47" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="F47" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>97.8</v>
+        <v>100.3</v>
       </c>
       <c r="O47" t="n">
-        <v>31.6</v>
+        <v>35.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Z47" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AA47" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AF47" t="n">
-        <v>224.78</v>
+        <v>224.37</v>
       </c>
       <c r="AG47" t="n">
         <v>3</v>
@@ -4447,10 +4351,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>143.55</v>
+        <v>135.61</v>
       </c>
       <c r="AL47" t="n">
-        <v>4.79</v>
+        <v>0.4</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -4459,75 +4363,42 @@
         <v>142</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46235</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B48" t="n">
-        <v>137.2</v>
-      </c>
-      <c r="C48" t="n">
-        <v>56.3</v>
+        <v>146.3</v>
       </c>
       <c r="D48" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E48" t="n">
-        <v>21.2</v>
+        <v>33.4</v>
       </c>
       <c r="F48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H48" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I48" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J48" t="n">
-        <v>40.4</v>
+        <v>5.5</v>
       </c>
       <c r="K48" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N48" t="n">
-        <v>29</v>
+        <v>98.2</v>
       </c>
       <c r="O48" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="Y48" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Z48" t="n">
         <v>15</v>
       </c>
       <c r="AA48" t="n">
-        <v>15.4</v>
+        <v>9</v>
       </c>
       <c r="AF48" t="n">
-        <v>232.22</v>
+        <v>225.93</v>
       </c>
       <c r="AG48" t="n">
-        <v>7.43</v>
+        <v>1.56</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -4536,10 +4407,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>143.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.06</v>
+        <v>-0.33</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -4547,82 +4418,76 @@
       <c r="AN48" t="n">
         <v>142</v>
       </c>
-      <c r="AP48" t="n">
-        <v>89.31999999999999</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>18.02</v>
-      </c>
       <c r="BL48" s="1" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B49" t="n">
-        <v>157.5</v>
+        <v>182.8</v>
       </c>
       <c r="C49" t="n">
-        <v>59.6</v>
+        <v>86.8</v>
       </c>
       <c r="D49" t="n">
-        <v>35</v>
+        <v>31.8</v>
       </c>
       <c r="E49" t="n">
-        <v>30.6</v>
+        <v>33</v>
       </c>
       <c r="F49" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H49" t="n">
-        <v>24.2</v>
+        <v>23.5</v>
       </c>
       <c r="I49" t="n">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
       <c r="J49" t="n">
-        <v>38.9</v>
+        <v>41.1</v>
       </c>
       <c r="K49" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="N49" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="O49" t="n">
-        <v>37.1</v>
+        <v>38.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>21.1</v>
+        <v>22.4</v>
       </c>
       <c r="R49" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T49" t="n">
-        <v>21.1</v>
+        <v>22.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z49" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA49" t="n">
-        <v>15.5</v>
+        <v>8.5</v>
       </c>
       <c r="AF49" t="n">
-        <v>229.69</v>
+        <v>218.63</v>
       </c>
       <c r="AG49" t="n">
-        <v>-2.53</v>
+        <v>-7.3</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -4631,10 +4496,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>136.96</v>
+        <v>126.27</v>
       </c>
       <c r="AL49" t="n">
-        <v>-6.65</v>
+        <v>-9.01</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -4643,81 +4508,81 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>86.59</v>
+        <v>82.66</v>
       </c>
       <c r="AS49" t="n">
-        <v>16.96</v>
+        <v>14.7</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="B50" t="n">
-        <v>159.6</v>
+        <v>181.8</v>
       </c>
       <c r="C50" t="n">
-        <v>63</v>
+        <v>86.5</v>
       </c>
       <c r="D50" t="n">
-        <v>34.5</v>
+        <v>31.4</v>
       </c>
       <c r="E50" t="n">
-        <v>31.1</v>
+        <v>34.2</v>
       </c>
       <c r="F50" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H50" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="I50" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="J50" t="n">
-        <v>40.5</v>
+        <v>41.9</v>
       </c>
       <c r="K50" t="n">
-        <v>75.2</v>
+        <v>76.8</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N50" t="n">
-        <v>34.3</v>
+        <v>35.7</v>
       </c>
       <c r="O50" t="n">
-        <v>38.2</v>
+        <v>39.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>21.3</v>
+        <v>23</v>
       </c>
       <c r="R50" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>20.1</v>
       </c>
       <c r="T50" t="n">
-        <v>21.3</v>
+        <v>23</v>
       </c>
       <c r="Y50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z50" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA50" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF50" t="n">
-        <v>228.57</v>
+        <v>216.39</v>
       </c>
       <c r="AG50" t="n">
-        <v>-1.14</v>
+        <v>-2.23</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -4726,10 +4591,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>133.01</v>
+        <v>123.32</v>
       </c>
       <c r="AL50" t="n">
-        <v>-3.95</v>
+        <v>-2.95</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -4738,81 +4603,81 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>84.59999999999999</v>
+        <v>79.08</v>
       </c>
       <c r="AS50" t="n">
-        <v>15.95</v>
+        <v>13.91</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46238</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="B51" t="n">
-        <v>160.4</v>
+        <v>183</v>
       </c>
       <c r="C51" t="n">
-        <v>62.6</v>
+        <v>84.7</v>
       </c>
       <c r="D51" t="n">
-        <v>35</v>
+        <v>30.9</v>
       </c>
       <c r="E51" t="n">
-        <v>32.2</v>
+        <v>33.7</v>
       </c>
       <c r="F51" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="H51" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="I51" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="J51" t="n">
-        <v>41.1</v>
+        <v>42.3</v>
       </c>
       <c r="K51" t="n">
-        <v>75.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>32.6</v>
+        <v>36.7</v>
       </c>
       <c r="O51" t="n">
-        <v>38</v>
+        <v>40.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>20.9</v>
+        <v>23.6</v>
       </c>
       <c r="R51" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="S51" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T51" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="Y51" t="n">
         <v>8</v>
       </c>
-      <c r="T51" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="Y51" t="n">
+      <c r="Z51" t="n">
         <v>13</v>
       </c>
-      <c r="Z51" t="n">
-        <v>16</v>
-      </c>
       <c r="AA51" t="n">
-        <v>14.1</v>
+        <v>10</v>
       </c>
       <c r="AF51" t="n">
-        <v>225.08</v>
+        <v>217.16</v>
       </c>
       <c r="AG51" t="n">
-        <v>-3.5</v>
+        <v>0.76</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -4821,10 +4686,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>135.24</v>
+        <v>117.87</v>
       </c>
       <c r="AL51" t="n">
-        <v>2.23</v>
+        <v>-5.45</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -4833,81 +4698,42 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>84.09999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="AS51" t="n">
-        <v>15.4</v>
+        <v>13.45</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="B52" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C52" t="n">
-        <v>71.09999999999999</v>
+        <v>163.8</v>
       </c>
       <c r="D52" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E52" t="n">
-        <v>27.3</v>
+        <v>29</v>
       </c>
       <c r="F52" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H52" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I52" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J52" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K52" t="n">
-        <v>77</v>
-      </c>
-      <c r="M52" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N52" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O52" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>21</v>
-      </c>
-      <c r="R52" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S52" t="n">
-        <v>6</v>
-      </c>
-      <c r="T52" t="n">
-        <v>21</v>
+        <v>6.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z52" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA52" t="n">
-        <v>11.4</v>
+        <v>10</v>
       </c>
       <c r="AF52" t="n">
-        <v>225</v>
+        <v>220.31</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.08</v>
+        <v>3.16</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -4916,10 +4742,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>134.62</v>
+        <v>116.52</v>
       </c>
       <c r="AL52" t="n">
-        <v>-0.62</v>
+        <v>-1.35</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -4927,49 +4753,31 @@
       <c r="AN52" t="n">
         <v>142</v>
       </c>
-      <c r="AP52" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL52" s="1" t="n">
-        <v>46240</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B53" t="n">
-        <v>151.5</v>
+        <v>155.9</v>
       </c>
       <c r="D53" t="n">
-        <v>35.1</v>
+        <v>28</v>
       </c>
       <c r="F53" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K53" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="O53" t="n">
-        <v>36.8</v>
+        <v>6.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z53" t="n">
         <v>13</v>
       </c>
       <c r="AA53" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>221.37</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0.05</v>
+        <v>11.5</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -4978,10 +4786,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>135.21</v>
+        <v>116.37</v>
       </c>
       <c r="AL53" t="n">
-        <v>0.59</v>
+        <v>-0.15</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -4990,42 +4798,30 @@
         <v>142</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="B54" t="n">
-        <v>145.2</v>
+        <v>141.3</v>
       </c>
       <c r="D54" t="n">
-        <v>33.5</v>
+        <v>26.3</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
-      </c>
-      <c r="K54" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="O54" t="n">
-        <v>35.5</v>
+        <v>5.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Z54" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA54" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>224.37</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5033,12 +4829,6 @@
       <c r="AI54" t="n">
         <v>235</v>
       </c>
-      <c r="AK54" t="n">
-        <v>135.61</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
@@ -5046,42 +4836,12 @@
         <v>142</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46242</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46243</v>
-      </c>
-      <c r="B55" t="n">
-        <v>146.3</v>
-      </c>
-      <c r="D55" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="F55" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K55" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="O55" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>225.93</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.56</v>
+        <v>46250</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5089,12 +4849,6 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
-      <c r="AK55" t="n">
-        <v>135.28</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>-0.33</v>
-      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
@@ -5102,75 +4856,12 @@
         <v>142</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46243</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B56" t="n">
-        <v>182.8</v>
-      </c>
-      <c r="C56" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="D56" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E56" t="n">
-        <v>33</v>
-      </c>
-      <c r="F56" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H56" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J56" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M56" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N56" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O56" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="R56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S56" t="n">
-        <v>15</v>
-      </c>
-      <c r="T56" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>218.63</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>-7.3</v>
+        <v>46251</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5178,94 +4869,19 @@
       <c r="AI56" t="n">
         <v>235</v>
       </c>
-      <c r="AK56" t="n">
-        <v>126.27</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>-9.01</v>
-      </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
       <c r="AN56" t="n">
         <v>142</v>
       </c>
-      <c r="AP56" t="n">
-        <v>82.66</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>14.7</v>
-      </c>
       <c r="BL56" s="1" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B57" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="C57" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="D57" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E57" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="F57" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H57" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J57" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="K57" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="M57" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N57" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="O57" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>23</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S57" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T57" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>216.39</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>-2.23</v>
+        <v>46252</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5273,94 +4889,19 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
-      <c r="AK57" t="n">
-        <v>123.32</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>-2.95</v>
-      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
       </c>
-      <c r="AP57" t="n">
-        <v>79.08</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>13.91</v>
-      </c>
       <c r="BL57" s="1" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="B58" t="n">
-        <v>183</v>
-      </c>
-      <c r="C58" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="D58" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E58" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="F58" t="n">
-        <v>7</v>
-      </c>
-      <c r="H58" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I58" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J58" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="K58" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M58" t="n">
-        <v>4</v>
-      </c>
-      <c r="N58" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="O58" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S58" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T58" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>217.16</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0.76</v>
+        <v>46253</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -5368,55 +4909,19 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
-      <c r="AK58" t="n">
-        <v>117.87</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>-5.45</v>
-      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
-      <c r="AP58" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL58" s="1" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="B59" t="n">
-        <v>163.8</v>
-      </c>
-      <c r="D59" t="n">
-        <v>29</v>
-      </c>
-      <c r="F59" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>220.31</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>3.16</v>
+        <v>46254</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -5424,12 +4929,6 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
-      <c r="AK59" t="n">
-        <v>116.52</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>-1.35</v>
-      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
@@ -5437,30 +4936,12 @@
         <v>142</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="B60" t="n">
-        <v>155.9</v>
-      </c>
-      <c r="D60" t="n">
-        <v>28</v>
-      </c>
-      <c r="F60" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>11.5</v>
+        <v>46255</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -5475,12 +4956,12 @@
         <v>142</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -5495,12 +4976,12 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -5515,7 +4996,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46250</v>
+        <v>46257</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -4843,6 +4843,24 @@
       <c r="A55" s="1" t="n">
         <v>46250</v>
       </c>
+      <c r="B55" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="D55" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>15</v>
+      </c>
       <c r="AH55" t="n">
         <v>215</v>
       </c>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -678,6 +678,15 @@
       <c r="T2" t="n">
         <v>21.6</v>
       </c>
+      <c r="V2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="X2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="Y2" t="n">
         <v>4</v>
       </c>
@@ -686,6 +695,15 @@
       </c>
       <c r="AA2" t="n">
         <v>8.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>5.3</v>
       </c>
       <c r="AF2" t="n">
         <v>227.74</v>
@@ -785,6 +803,15 @@
       <c r="T3" t="n">
         <v>22.1</v>
       </c>
+      <c r="V3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
@@ -793,6 +820,15 @@
       </c>
       <c r="AA3" t="n">
         <v>9.1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5</v>
       </c>
       <c r="AF3" t="n">
         <v>226.8</v>
@@ -865,6 +901,15 @@
       <c r="O4" t="n">
         <v>40.1</v>
       </c>
+      <c r="V4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12</v>
+      </c>
       <c r="Y4" t="n">
         <v>3</v>
       </c>
@@ -873,6 +918,15 @@
       </c>
       <c r="AA4" t="n">
         <v>8.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4.1</v>
       </c>
       <c r="AF4" t="n">
         <v>226.39</v>
@@ -927,6 +981,15 @@
       <c r="O5" t="n">
         <v>40.8</v>
       </c>
+      <c r="V5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X5" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y5" t="n">
         <v>7</v>
       </c>
@@ -935,6 +998,15 @@
       </c>
       <c r="AA5" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.4</v>
       </c>
       <c r="AF5" t="n">
         <v>229.98</v>
@@ -1016,6 +1088,15 @@
       <c r="T6" t="n">
         <v>22</v>
       </c>
+      <c r="V6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y6" t="n">
         <v>8</v>
       </c>
@@ -1024,6 +1105,15 @@
       </c>
       <c r="AA6" t="n">
         <v>13</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.8</v>
       </c>
       <c r="AF6" t="n">
         <v>236.38</v>
@@ -1111,6 +1201,15 @@
       <c r="T7" t="n">
         <v>20.9</v>
       </c>
+      <c r="V7" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X7" t="n">
+        <v>10.4</v>
+      </c>
       <c r="Y7" t="n">
         <v>5</v>
       </c>
@@ -1119,6 +1218,15 @@
       </c>
       <c r="AA7" t="n">
         <v>9.9</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
         <v>236.23</v>
@@ -1206,6 +1314,15 @@
       <c r="T8" t="n">
         <v>22</v>
       </c>
+      <c r="V8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X8" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y8" t="n">
         <v>3</v>
       </c>
@@ -1214,6 +1331,15 @@
       </c>
       <c r="AA8" t="n">
         <v>9.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-2.9</v>
       </c>
       <c r="AF8" t="n">
         <v>236.72</v>
@@ -1301,6 +1427,15 @@
       <c r="T9" t="n">
         <v>21.8</v>
       </c>
+      <c r="V9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>10.2</v>
+      </c>
       <c r="Y9" t="n">
         <v>4</v>
       </c>
@@ -1309,6 +1444,15 @@
       </c>
       <c r="AA9" t="n">
         <v>9.699999999999999</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-6.5</v>
       </c>
       <c r="AF9" t="n">
         <v>229.92</v>
@@ -1396,6 +1540,15 @@
       <c r="T10" t="n">
         <v>22.7</v>
       </c>
+      <c r="V10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>10</v>
+      </c>
+      <c r="X10" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="Y10" t="n">
         <v>1</v>
       </c>
@@ -1404,6 +1557,15 @@
       </c>
       <c r="AA10" t="n">
         <v>6.1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-3.3</v>
       </c>
       <c r="AF10" t="n">
         <v>223</v>
@@ -1464,6 +1626,15 @@
       <c r="O11" t="n">
         <v>39.4</v>
       </c>
+      <c r="V11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="X11" t="n">
+        <v>7.6</v>
+      </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
@@ -1472,6 +1643,15 @@
       </c>
       <c r="AA11" t="n">
         <v>4.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-2.8</v>
       </c>
       <c r="AF11" t="n">
         <v>221.08</v>
@@ -1526,6 +1706,15 @@
       <c r="O12" t="n">
         <v>39.5</v>
       </c>
+      <c r="V12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7.5</v>
+      </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
@@ -1534,6 +1723,15 @@
       </c>
       <c r="AA12" t="n">
         <v>5.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-1.3</v>
       </c>
       <c r="AF12" t="n">
         <v>221.24</v>
@@ -1615,6 +1813,15 @@
       <c r="T13" t="n">
         <v>22.7</v>
       </c>
+      <c r="V13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="Y13" t="n">
         <v>5</v>
       </c>
@@ -1623,6 +1830,15 @@
       </c>
       <c r="AA13" t="n">
         <v>6.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-1.2</v>
       </c>
       <c r="AF13" t="n">
         <v>223.94</v>
@@ -1710,6 +1926,15 @@
       <c r="T14" t="n">
         <v>23</v>
       </c>
+      <c r="V14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X14" t="n">
+        <v>9.5</v>
+      </c>
       <c r="Y14" t="n">
         <v>5</v>
       </c>
@@ -1718,6 +1943,15 @@
       </c>
       <c r="AA14" t="n">
         <v>7.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.5</v>
       </c>
       <c r="AF14" t="n">
         <v>224.33</v>
@@ -1805,6 +2039,15 @@
       <c r="T15" t="n">
         <v>23</v>
       </c>
+      <c r="V15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>10.2</v>
+      </c>
       <c r="Y15" t="n">
         <v>2.4</v>
       </c>
@@ -1813,6 +2056,15 @@
       </c>
       <c r="AA15" t="n">
         <v>10.3</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF15" t="n">
         <v>224.34</v>
@@ -1873,6 +2125,15 @@
       <c r="O16" t="n">
         <v>40.5</v>
       </c>
+      <c r="V16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X16" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y16" t="n">
         <v>8</v>
       </c>
@@ -1881,6 +2142,15 @@
       </c>
       <c r="AA16" t="n">
         <v>14</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.6</v>
       </c>
       <c r="AF16" t="n">
         <v>231.46</v>
@@ -1935,6 +2205,15 @@
       <c r="O17" t="n">
         <v>40.6</v>
       </c>
+      <c r="V17" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15.2</v>
+      </c>
       <c r="Y17" t="n">
         <v>8</v>
       </c>
@@ -1943,6 +2222,15 @@
       </c>
       <c r="AA17" t="n">
         <v>12.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.2</v>
       </c>
       <c r="AF17" t="n">
         <v>229.92</v>
@@ -1997,6 +2285,15 @@
       <c r="O18" t="n">
         <v>38</v>
       </c>
+      <c r="V18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>13.8</v>
+      </c>
       <c r="Y18" t="n">
         <v>10</v>
       </c>
@@ -2005,6 +2302,15 @@
       </c>
       <c r="AA18" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AF18" t="n">
         <v>226.95</v>
@@ -2059,6 +2365,15 @@
       <c r="O19" t="n">
         <v>39.8</v>
       </c>
+      <c r="V19" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X19" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y19" t="n">
         <v>7</v>
       </c>
@@ -2067,6 +2382,15 @@
       </c>
       <c r="AA19" t="n">
         <v>11</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.6</v>
       </c>
       <c r="AF19" t="n">
         <v>223.11</v>
@@ -2121,6 +2445,15 @@
       <c r="O20" t="n">
         <v>40.2</v>
       </c>
+      <c r="V20" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X20" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y20" t="n">
         <v>7</v>
       </c>
@@ -2129,6 +2462,15 @@
       </c>
       <c r="AA20" t="n">
         <v>10</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.8</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2204,6 +2546,15 @@
       <c r="T21" t="n">
         <v>23</v>
       </c>
+      <c r="V21" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="n">
+        <v>14.4</v>
+      </c>
       <c r="Y21" t="n">
         <v>4</v>
       </c>
@@ -2212,6 +2563,15 @@
       </c>
       <c r="AA21" t="n">
         <v>7.7</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>6.2</v>
       </c>
       <c r="AF21" t="n">
         <v>220.36</v>
@@ -2299,6 +2659,15 @@
       <c r="T22" t="n">
         <v>23.1</v>
       </c>
+      <c r="V22" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X22" t="n">
+        <v>14.9</v>
+      </c>
       <c r="Y22" t="n">
         <v>8</v>
       </c>
@@ -2307,6 +2676,15 @@
       </c>
       <c r="AA22" t="n">
         <v>11.9</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>5.2</v>
       </c>
       <c r="AF22" t="n">
         <v>219.64</v>
@@ -2394,6 +2772,15 @@
       <c r="T23" t="n">
         <v>22.6</v>
       </c>
+      <c r="V23" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
@@ -2402,6 +2789,15 @@
       </c>
       <c r="AA23" t="n">
         <v>14.9</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF23" t="n">
         <v>224.93</v>
@@ -2489,6 +2885,15 @@
       <c r="T24" t="n">
         <v>21.5</v>
       </c>
+      <c r="V24" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>26</v>
+      </c>
+      <c r="X24" t="n">
+        <v>18.1</v>
+      </c>
       <c r="Y24" t="n">
         <v>17</v>
       </c>
@@ -2497,6 +2902,15 @@
       </c>
       <c r="AA24" t="n">
         <v>19.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>4.5</v>
       </c>
       <c r="AF24" t="n">
         <v>232.31</v>
@@ -2551,6 +2965,15 @@
       <c r="O25" t="n">
         <v>39.2</v>
       </c>
+      <c r="V25" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>26.6</v>
+      </c>
       <c r="Y25" t="n">
         <v>18</v>
       </c>
@@ -2559,6 +2982,15 @@
       </c>
       <c r="AA25" t="n">
         <v>20.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.7</v>
       </c>
       <c r="AF25" t="n">
         <v>235.4</v>
@@ -2607,6 +3039,15 @@
       <c r="O26" t="n">
         <v>37.8</v>
       </c>
+      <c r="V26" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X26" t="n">
+        <v>17.9</v>
+      </c>
       <c r="Y26" t="n">
         <v>14</v>
       </c>
@@ -2615,6 +3056,15 @@
       </c>
       <c r="AA26" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
         <v>231.99</v>
@@ -2696,6 +3146,15 @@
       <c r="T27" t="n">
         <v>20.5</v>
       </c>
+      <c r="V27" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X27" t="n">
+        <v>16.7</v>
+      </c>
       <c r="Y27" t="n">
         <v>9</v>
       </c>
@@ -2704,6 +3163,15 @@
       </c>
       <c r="AA27" t="n">
         <v>11.1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AF27" t="n">
         <v>225.51</v>
@@ -2791,6 +3259,15 @@
       <c r="T28" t="n">
         <v>22.3</v>
       </c>
+      <c r="V28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X28" t="n">
+        <v>13.5</v>
+      </c>
       <c r="Y28" t="n">
         <v>9</v>
       </c>
@@ -2799,6 +3276,15 @@
       </c>
       <c r="AA28" t="n">
         <v>11.6</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>-1.3</v>
       </c>
       <c r="AF28" t="n">
         <v>220.92</v>
@@ -2886,6 +3372,15 @@
       <c r="T29" t="n">
         <v>22.5</v>
       </c>
+      <c r="V29" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>13</v>
+      </c>
+      <c r="X29" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y29" t="n">
         <v>10</v>
       </c>
@@ -2894,6 +3389,15 @@
       </c>
       <c r="AA29" t="n">
         <v>11.4</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>-0.9</v>
       </c>
       <c r="AF29" t="n">
         <v>220.92</v>
@@ -2981,6 +3485,15 @@
       <c r="T30" t="n">
         <v>22.6</v>
       </c>
+      <c r="V30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W30" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X30" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y30" t="n">
         <v>9</v>
       </c>
@@ -2989,6 +3502,15 @@
       </c>
       <c r="AA30" t="n">
         <v>11.1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.5</v>
       </c>
       <c r="AF30" t="n">
         <v>216.02</v>
@@ -3076,6 +3598,15 @@
       <c r="T31" t="n">
         <v>23.3</v>
       </c>
+      <c r="V31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X31" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y31" t="n">
         <v>8</v>
       </c>
@@ -3084,6 +3615,15 @@
       </c>
       <c r="AA31" t="n">
         <v>12.7</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>4.7</v>
       </c>
       <c r="AF31" t="n">
         <v>216.02</v>
@@ -3138,6 +3678,15 @@
       <c r="O32" t="n">
         <v>39.2</v>
       </c>
+      <c r="V32" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X32" t="n">
+        <v>14</v>
+      </c>
       <c r="Y32" t="n">
         <v>12</v>
       </c>
@@ -3146,6 +3695,15 @@
       </c>
       <c r="AA32" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.4</v>
       </c>
       <c r="AF32" t="n">
         <v>224.53</v>
@@ -3194,6 +3752,15 @@
       <c r="O33" t="n">
         <v>39.3</v>
       </c>
+      <c r="V33" t="n">
+        <v>8</v>
+      </c>
+      <c r="W33" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X33" t="n">
+        <v>15.2</v>
+      </c>
       <c r="Y33" t="n">
         <v>11</v>
       </c>
@@ -3202,6 +3769,15 @@
       </c>
       <c r="AA33" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.1</v>
       </c>
       <c r="AF33" t="n">
         <v>230.27</v>
@@ -3283,6 +3859,15 @@
       <c r="T34" t="n">
         <v>21.7</v>
       </c>
+      <c r="V34" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X34" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y34" t="n">
         <v>12</v>
       </c>
@@ -3291,6 +3876,15 @@
       </c>
       <c r="AA34" t="n">
         <v>15.7</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AF34" t="n">
         <v>237.43</v>
@@ -3345,6 +3939,15 @@
       <c r="O35" t="n">
         <v>37.9</v>
       </c>
+      <c r="V35" t="n">
+        <v>10</v>
+      </c>
+      <c r="W35" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="X35" t="n">
+        <v>17.8</v>
+      </c>
       <c r="Y35" t="n">
         <v>13</v>
       </c>
@@ -3353,6 +3956,15 @@
       </c>
       <c r="AA35" t="n">
         <v>16</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9</v>
       </c>
       <c r="AF35" t="n">
         <v>236.14</v>
@@ -3434,6 +4046,15 @@
       <c r="T36" t="n">
         <v>20.3</v>
       </c>
+      <c r="V36" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="W36" t="n">
+        <v>27</v>
+      </c>
+      <c r="X36" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y36" t="n">
         <v>11</v>
       </c>
@@ -3442,6 +4063,15 @@
       </c>
       <c r="AA36" t="n">
         <v>14.4</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>-0.4</v>
       </c>
       <c r="AF36" t="n">
         <v>236.13</v>
@@ -3529,6 +4159,15 @@
       <c r="T37" t="n">
         <v>19</v>
       </c>
+      <c r="V37" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W37" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y37" t="n">
         <v>9</v>
       </c>
@@ -3537,6 +4176,15 @@
       </c>
       <c r="AA37" t="n">
         <v>12.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-0.7</v>
       </c>
       <c r="AF37" t="n">
         <v>218.6</v>
@@ -3624,6 +4272,15 @@
       <c r="T38" t="n">
         <v>21.6</v>
       </c>
+      <c r="V38" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="W38" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y38" t="n">
         <v>11</v>
       </c>
@@ -3632,6 +4289,15 @@
       </c>
       <c r="AA38" t="n">
         <v>13.6</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.5</v>
       </c>
       <c r="AF38" t="n">
         <v>218.84</v>
@@ -3686,6 +4352,15 @@
       <c r="O39" t="n">
         <v>35.1</v>
       </c>
+      <c r="V39" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W39" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X39" t="n">
+        <v>19</v>
+      </c>
       <c r="Y39" t="n">
         <v>14</v>
       </c>
@@ -3694,6 +4369,15 @@
       </c>
       <c r="AA39" t="n">
         <v>17.5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF39" t="n">
         <v>221.78</v>
@@ -3742,6 +4426,15 @@
       <c r="O40" t="n">
         <v>31.6</v>
       </c>
+      <c r="V40" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W40" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X40" t="n">
+        <v>19.8</v>
+      </c>
       <c r="Y40" t="n">
         <v>14</v>
       </c>
@@ -3750,6 +4443,15 @@
       </c>
       <c r="AA40" t="n">
         <v>16.5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.1</v>
       </c>
       <c r="AF40" t="n">
         <v>224.78</v>
@@ -3831,6 +4533,15 @@
       <c r="T41" t="n">
         <v>21.6</v>
       </c>
+      <c r="V41" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W41" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X41" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y41" t="n">
         <v>12</v>
       </c>
@@ -3839,6 +4550,15 @@
       </c>
       <c r="AA41" t="n">
         <v>15.4</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>3.2</v>
       </c>
       <c r="AF41" t="n">
         <v>232.22</v>
@@ -3926,6 +4646,15 @@
       <c r="T42" t="n">
         <v>21.1</v>
       </c>
+      <c r="V42" t="n">
+        <v>13</v>
+      </c>
+      <c r="W42" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X42" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y42" t="n">
         <v>13</v>
       </c>
@@ -3934,6 +4663,15 @@
       </c>
       <c r="AA42" t="n">
         <v>15.5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2</v>
       </c>
       <c r="AF42" t="n">
         <v>229.69</v>
@@ -4021,6 +4759,15 @@
       <c r="T43" t="n">
         <v>21.3</v>
       </c>
+      <c r="V43" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W43" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X43" t="n">
+        <v>20</v>
+      </c>
       <c r="Y43" t="n">
         <v>11</v>
       </c>
@@ -4029,6 +4776,15 @@
       </c>
       <c r="AA43" t="n">
         <v>13.5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.2</v>
       </c>
       <c r="AF43" t="n">
         <v>228.57</v>
@@ -4116,6 +4872,15 @@
       <c r="T44" t="n">
         <v>20.9</v>
       </c>
+      <c r="V44" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W44" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X44" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y44" t="n">
         <v>13</v>
       </c>
@@ -4124,6 +4889,15 @@
       </c>
       <c r="AA44" t="n">
         <v>14.1</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.6</v>
       </c>
       <c r="AF44" t="n">
         <v>225.08</v>
@@ -4211,6 +4985,15 @@
       <c r="T45" t="n">
         <v>21</v>
       </c>
+      <c r="V45" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W45" t="n">
+        <v>27</v>
+      </c>
+      <c r="X45" t="n">
+        <v>19.9</v>
+      </c>
       <c r="Y45" t="n">
         <v>9</v>
       </c>
@@ -4219,6 +5002,15 @@
       </c>
       <c r="AA45" t="n">
         <v>11.4</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AF45" t="n">
         <v>225</v>
@@ -4273,6 +5065,15 @@
       <c r="O46" t="n">
         <v>36.8</v>
       </c>
+      <c r="V46" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W46" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X46" t="n">
+        <v>14</v>
+      </c>
       <c r="Y46" t="n">
         <v>5</v>
       </c>
@@ -4281,6 +5082,15 @@
       </c>
       <c r="AA46" t="n">
         <v>9</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AF46" t="n">
         <v>221.37</v>
@@ -4329,6 +5139,15 @@
       <c r="O47" t="n">
         <v>35.5</v>
       </c>
+      <c r="V47" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X47" t="n">
+        <v>13.1</v>
+      </c>
       <c r="Y47" t="n">
         <v>7</v>
       </c>
@@ -4337,6 +5156,15 @@
       </c>
       <c r="AA47" t="n">
         <v>10</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>-1.5</v>
       </c>
       <c r="AF47" t="n">
         <v>224.37</v>
@@ -4385,6 +5213,15 @@
       <c r="O48" t="n">
         <v>35.1</v>
       </c>
+      <c r="V48" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W48" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X48" t="n">
+        <v>10.6</v>
+      </c>
       <c r="Y48" t="n">
         <v>3</v>
       </c>
@@ -4393,6 +5230,15 @@
       </c>
       <c r="AA48" t="n">
         <v>9</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>-3.3</v>
       </c>
       <c r="AF48" t="n">
         <v>225.93</v>
@@ -4474,6 +5320,15 @@
       <c r="T49" t="n">
         <v>22.4</v>
       </c>
+      <c r="V49" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W49" t="n">
+        <v>15</v>
+      </c>
+      <c r="X49" t="n">
+        <v>12.1</v>
+      </c>
       <c r="Y49" t="n">
         <v>4</v>
       </c>
@@ -4482,6 +5337,15 @@
       </c>
       <c r="AA49" t="n">
         <v>8.5</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>-5.1</v>
       </c>
       <c r="AF49" t="n">
         <v>218.63</v>
@@ -4880,6 +5744,24 @@
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>46251</v>
+      </c>
+      <c r="B56" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="D56" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>13</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5433,6 +5433,15 @@
       <c r="T50" t="n">
         <v>23</v>
       </c>
+      <c r="V50" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W50" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X50" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y50" t="n">
         <v>6</v>
       </c>
@@ -5441,6 +5450,15 @@
       </c>
       <c r="AA50" t="n">
         <v>9.199999999999999</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AF50" t="n">
         <v>216.39</v>
@@ -5584,6 +5602,12 @@
       <c r="F52" t="n">
         <v>6.5</v>
       </c>
+      <c r="K52" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="O52" t="n">
+        <v>40.2</v>
+      </c>
       <c r="Y52" t="n">
         <v>8</v>
       </c>
@@ -5643,6 +5667,12 @@
       <c r="AA53" t="n">
         <v>11.5</v>
       </c>
+      <c r="AF53" t="n">
+        <v>221.99</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.67</v>
+      </c>
       <c r="AH53" t="n">
         <v>215</v>
       </c>
@@ -5687,6 +5717,12 @@
       <c r="AA54" t="n">
         <v>14</v>
       </c>
+      <c r="AF54" t="n">
+        <v>225.14</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.15</v>
+      </c>
       <c r="AH54" t="n">
         <v>215</v>
       </c>
@@ -5763,6 +5799,12 @@
       <c r="AA56" t="n">
         <v>13</v>
       </c>
+      <c r="AF56" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="AH56" t="n">
         <v>215</v>
       </c>
@@ -5782,6 +5824,24 @@
     <row r="57">
       <c r="A57" s="1" t="n">
         <v>46252</v>
+      </c>
+      <c r="B57" t="n">
+        <v>145</v>
+      </c>
+      <c r="D57" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>10</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5546,6 +5546,15 @@
       <c r="T51" t="n">
         <v>23.6</v>
       </c>
+      <c r="V51" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W51" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>10.9</v>
+      </c>
       <c r="Y51" t="n">
         <v>8</v>
       </c>
@@ -5554,6 +5563,15 @@
       </c>
       <c r="AA51" t="n">
         <v>10</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.8</v>
       </c>
       <c r="AF51" t="n">
         <v>217.16</v>
@@ -5782,13 +5800,52 @@
         <v>46251</v>
       </c>
       <c r="B56" t="n">
-        <v>135.6</v>
+        <v>153</v>
+      </c>
+      <c r="C56" t="n">
+        <v>71.8</v>
       </c>
       <c r="D56" t="n">
-        <v>27.4</v>
+        <v>28.6</v>
+      </c>
+      <c r="E56" t="n">
+        <v>24.7</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="H56" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J56" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N56" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O56" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y56" t="n">
         <v>12</v>
@@ -5797,7 +5854,7 @@
         <v>14</v>
       </c>
       <c r="AA56" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AF56" t="n">
         <v>229.96</v>
@@ -5811,11 +5868,23 @@
       <c r="AI56" t="n">
         <v>235</v>
       </c>
+      <c r="AK56" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
       <c r="AN56" t="n">
         <v>142</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>14.8</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46251</v>
@@ -5843,6 +5912,12 @@
       <c r="AA57" t="n">
         <v>10</v>
       </c>
+      <c r="AF57" t="n">
+        <v>227.01</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>-2.95</v>
+      </c>
       <c r="AH57" t="n">
         <v>215</v>
       </c>
@@ -5862,6 +5937,24 @@
     <row r="58">
       <c r="A58" s="1" t="n">
         <v>46253</v>
+      </c>
+      <c r="B58" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>10.5</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5059,12 +5059,6 @@
       <c r="F46" t="n">
         <v>5.4</v>
       </c>
-      <c r="K46" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="O46" t="n">
-        <v>36.8</v>
-      </c>
       <c r="V46" t="n">
         <v>8.699999999999999</v>
       </c>
@@ -5626,6 +5620,15 @@
       <c r="O52" t="n">
         <v>40.2</v>
       </c>
+      <c r="V52" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W52" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X52" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y52" t="n">
         <v>8</v>
       </c>
@@ -5634,6 +5637,15 @@
       </c>
       <c r="AA52" t="n">
         <v>10</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>2.8</v>
       </c>
       <c r="AF52" t="n">
         <v>220.31</v>
@@ -5676,6 +5688,12 @@
       <c r="F53" t="n">
         <v>6.5</v>
       </c>
+      <c r="K53" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="O53" t="n">
+        <v>38.5</v>
+      </c>
       <c r="Y53" t="n">
         <v>10</v>
       </c>
@@ -5726,6 +5744,12 @@
       <c r="F54" t="n">
         <v>5.5</v>
       </c>
+      <c r="K54" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="O54" t="n">
+        <v>39.8</v>
+      </c>
       <c r="Y54" t="n">
         <v>13</v>
       </c>
@@ -5770,6 +5794,12 @@
       <c r="F55" t="n">
         <v>5.5</v>
       </c>
+      <c r="K55" t="n">
+        <v>97</v>
+      </c>
+      <c r="O55" t="n">
+        <v>35.7</v>
+      </c>
       <c r="Y55" t="n">
         <v>12</v>
       </c>
@@ -5895,13 +5925,52 @@
         <v>46252</v>
       </c>
       <c r="B57" t="n">
-        <v>145</v>
+        <v>165.8</v>
+      </c>
+      <c r="C57" t="n">
+        <v>77.3</v>
       </c>
       <c r="D57" t="n">
         <v>29.3</v>
       </c>
+      <c r="E57" t="n">
+        <v>27.7</v>
+      </c>
       <c r="F57" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
+      </c>
+      <c r="H57" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J57" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="K57" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N57" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S57" t="n">
+        <v>7</v>
+      </c>
+      <c r="T57" t="n">
+        <v>23.8</v>
       </c>
       <c r="Y57" t="n">
         <v>7</v>
@@ -5910,7 +5979,7 @@
         <v>13</v>
       </c>
       <c r="AA57" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="AF57" t="n">
         <v>227.01</v>
@@ -5924,11 +5993,23 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
+      <c r="AK57" t="n">
+        <v>128.15</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.01</v>
+      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>14.52</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46252</v>
@@ -5975,6 +6056,24 @@
     <row r="59">
       <c r="A59" s="1" t="n">
         <v>46254</v>
+      </c>
+      <c r="B59" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>12.5</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5694,6 +5694,15 @@
       <c r="O53" t="n">
         <v>38.5</v>
       </c>
+      <c r="V53" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X53" t="n">
+        <v>12.4</v>
+      </c>
       <c r="Y53" t="n">
         <v>10</v>
       </c>
@@ -5702,6 +5711,15 @@
       </c>
       <c r="AA53" t="n">
         <v>11.5</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3.5</v>
       </c>
       <c r="AF53" t="n">
         <v>221.99</v>
@@ -6020,13 +6038,52 @@
         <v>46253</v>
       </c>
       <c r="B58" t="n">
-        <v>142.8</v>
+        <v>158.1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>73.7</v>
       </c>
       <c r="D58" t="n">
-        <v>28.9</v>
+        <v>30.3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J58" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="K58" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="R58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S58" t="n">
+        <v>7</v>
+      </c>
+      <c r="T58" t="n">
+        <v>23.6</v>
       </c>
       <c r="Y58" t="n">
         <v>6</v>
@@ -6035,7 +6092,13 @@
         <v>15</v>
       </c>
       <c r="AA58" t="n">
-        <v>10.5</v>
+        <v>11</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>228.35</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.33</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6043,11 +6106,23 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
+      <c r="AK58" t="n">
+        <v>128.86</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0.71</v>
+      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>82.37</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>14.22</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46253</v>
@@ -6075,6 +6150,12 @@
       <c r="AA59" t="n">
         <v>12.5</v>
       </c>
+      <c r="AF59" t="n">
+        <v>231.16</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>2.81</v>
+      </c>
       <c r="AH59" t="n">
         <v>215</v>
       </c>
@@ -6094,6 +6175,24 @@
     <row r="60">
       <c r="A60" s="1" t="n">
         <v>46255</v>
+      </c>
+      <c r="B60" t="n">
+        <v>152.2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>31</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>9</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5768,6 +5768,15 @@
       <c r="O54" t="n">
         <v>39.8</v>
       </c>
+      <c r="V54" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W54" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X54" t="n">
+        <v>13.6</v>
+      </c>
       <c r="Y54" t="n">
         <v>13</v>
       </c>
@@ -5776,6 +5785,15 @@
       </c>
       <c r="AA54" t="n">
         <v>14</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>3.9</v>
       </c>
       <c r="AF54" t="n">
         <v>225.14</v>
@@ -6133,13 +6151,52 @@
         <v>46254</v>
       </c>
       <c r="B59" t="n">
-        <v>144.1</v>
+        <v>154.9</v>
+      </c>
+      <c r="C59" t="n">
+        <v>70.2</v>
       </c>
       <c r="D59" t="n">
-        <v>29.3</v>
+        <v>31.5</v>
+      </c>
+      <c r="E59" t="n">
+        <v>27.7</v>
       </c>
       <c r="F59" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="H59" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J59" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K59" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="M59" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="O59" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T59" t="n">
+        <v>23.7</v>
       </c>
       <c r="Y59" t="n">
         <v>8</v>
@@ -6148,7 +6205,7 @@
         <v>17</v>
       </c>
       <c r="AA59" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="AF59" t="n">
         <v>231.16</v>
@@ -6162,11 +6219,23 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
+      <c r="AK59" t="n">
+        <v>130.88</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>2.02</v>
+      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>13.1</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46254</v>
@@ -6213,6 +6282,24 @@
     <row r="61">
       <c r="A61" s="1" t="n">
         <v>46256</v>
+      </c>
+      <c r="B61" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="D61" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>9</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5836,6 +5836,15 @@
       <c r="O55" t="n">
         <v>35.7</v>
       </c>
+      <c r="V55" t="n">
+        <v>9</v>
+      </c>
+      <c r="W55" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="X55" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Y55" t="n">
         <v>12</v>
       </c>
@@ -5844,6 +5853,15 @@
       </c>
       <c r="AA55" t="n">
         <v>15</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>-0.4</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -6320,6 +6338,24 @@
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46257</v>
+      </c>
+      <c r="B62" t="n">
+        <v>142.3</v>
+      </c>
+      <c r="D62" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>8.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B2" t="n">
-        <v>183.8</v>
+        <v>178.9</v>
       </c>
       <c r="C2" t="n">
-        <v>86.7</v>
+        <v>84.2</v>
       </c>
       <c r="D2" t="n">
-        <v>27.1</v>
+        <v>28.2</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="F2" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="H2" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="J2" t="n">
-        <v>41.3</v>
+        <v>41.5</v>
       </c>
       <c r="K2" t="n">
-        <v>75.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="O2" t="n">
         <v>41.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>19</v>
+        <v>20.1</v>
       </c>
       <c r="T2" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="V2" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="W2" t="n">
-        <v>17.9</v>
+        <v>19.1</v>
       </c>
       <c r="X2" t="n">
-        <v>11.3</v>
+        <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AF2" t="n">
-        <v>227.74</v>
+        <v>226.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3.29</v>
+        <v>-0.95</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>127.86</v>
+        <v>129.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>-3.67</v>
+        <v>1.24</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -730,22 +730,22 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>84.81</v>
+        <v>81.91</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.95</v>
+        <v>15.61</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="BM2" t="n">
-        <v>37.03</v>
+        <v>38.28</v>
       </c>
       <c r="BN2" t="n">
-        <v>15572</v>
+        <v>14004.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>2181.8</v>
+        <v>2044.8</v>
       </c>
       <c r="BP2" t="n">
         <v>0</v>
@@ -753,88 +753,61 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B3" t="n">
-        <v>178.9</v>
+        <v>155.4</v>
       </c>
       <c r="C3" t="n">
-        <v>84.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>28.2</v>
+        <v>27.4</v>
       </c>
       <c r="E3" t="n">
-        <v>31.1</v>
+        <v>29.1</v>
       </c>
       <c r="F3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>41.5</v>
+        <v>6.6</v>
       </c>
       <c r="K3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>38.1</v>
+        <v>98.2</v>
       </c>
       <c r="O3" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>22.1</v>
+        <v>40.1</v>
       </c>
       <c r="V3" t="n">
-        <v>7.9</v>
+        <v>5.2</v>
       </c>
       <c r="W3" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>226.8</v>
+        <v>226.39</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.95</v>
+        <v>-0.4</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -843,10 +816,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>129.1</v>
+        <v>129.78</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.24</v>
+        <v>0.68</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -854,85 +827,67 @@
       <c r="AN3" t="n">
         <v>142</v>
       </c>
-      <c r="AP3" t="n">
-        <v>81.91</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>15.61</v>
-      </c>
       <c r="BL3" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>38.28</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>14004.4</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>2044.8</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B4" t="n">
-        <v>155.4</v>
+        <v>151.1</v>
       </c>
       <c r="C4" t="n">
-        <v>82.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>27.4</v>
+        <v>26.8</v>
       </c>
       <c r="E4" t="n">
-        <v>29.1</v>
+        <v>30.9</v>
       </c>
       <c r="F4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>98.2</v>
+        <v>97.7</v>
       </c>
       <c r="O4" t="n">
-        <v>40.1</v>
+        <v>40.8</v>
       </c>
       <c r="V4" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="W4" t="n">
         <v>18.8</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>-0</v>
       </c>
       <c r="AC4" t="n">
         <v>6.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>226.39</v>
+        <v>229.98</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.4</v>
+        <v>3.58</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -941,10 +896,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>129.78</v>
+        <v>132.56</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.68</v>
+        <v>2.78</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -953,66 +908,93 @@
         <v>142</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="B5" t="n">
-        <v>151.1</v>
+        <v>167.2</v>
       </c>
       <c r="C5" t="n">
-        <v>76.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>26.8</v>
+        <v>27.6</v>
       </c>
       <c r="E5" t="n">
-        <v>30.9</v>
+        <v>28.2</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>7.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40.3</v>
       </c>
       <c r="K5" t="n">
-        <v>97.7</v>
+        <v>75</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>37.2</v>
       </c>
       <c r="O5" t="n">
-        <v>40.8</v>
+        <v>39.9</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>22</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>19</v>
+      </c>
+      <c r="T5" t="n">
+        <v>22</v>
       </c>
       <c r="V5" t="n">
-        <v>6.3</v>
+        <v>9.4</v>
       </c>
       <c r="W5" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="X5" t="n">
-        <v>12.6</v>
+        <v>14.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>229.98</v>
+        <v>236.38</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.58</v>
+        <v>6.4</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1021,10 +1003,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>132.56</v>
+        <v>132.97</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.78</v>
+        <v>0.41</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1032,94 +1014,100 @@
       <c r="AN5" t="n">
         <v>142</v>
       </c>
+      <c r="AP5" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>16.05</v>
+      </c>
       <c r="BL5" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="B6" t="n">
-        <v>167.2</v>
+        <v>176.7</v>
       </c>
       <c r="C6" t="n">
-        <v>74.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="D6" t="n">
-        <v>27.6</v>
+        <v>28.3</v>
       </c>
       <c r="E6" t="n">
-        <v>28.2</v>
+        <v>31.6</v>
       </c>
       <c r="F6" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="H6" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="I6" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="J6" t="n">
-        <v>40.3</v>
+        <v>41.8</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="N6" t="n">
-        <v>37.2</v>
+        <v>38.4</v>
       </c>
       <c r="O6" t="n">
-        <v>39.9</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="T6" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>19.1</v>
+        <v>14.8</v>
       </c>
       <c r="X6" t="n">
-        <v>14.2</v>
+        <v>10.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>236.38</v>
+        <v>236.23</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1128,10 +1116,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>132.97</v>
+        <v>132.79</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.41</v>
+        <v>-0.18</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1140,99 +1128,99 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>90.8</v>
+        <v>89.64</v>
       </c>
       <c r="AS6" t="n">
-        <v>16.05</v>
+        <v>15.89</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B7" t="n">
-        <v>176.7</v>
+        <v>175.3</v>
       </c>
       <c r="C7" t="n">
-        <v>80.8</v>
+        <v>83.5</v>
       </c>
       <c r="D7" t="n">
-        <v>28.3</v>
+        <v>27.8</v>
       </c>
       <c r="E7" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="F7" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H7" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="I7" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="J7" t="n">
-        <v>41.8</v>
+        <v>42.9</v>
       </c>
       <c r="K7" t="n">
-        <v>76.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="N7" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="O7" t="n">
         <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="T7" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>14.8</v>
       </c>
       <c r="X7" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z7" t="n">
         <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.6</v>
+        <v>-7.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>236.23</v>
+        <v>236.72</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.15</v>
+        <v>0.49</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1241,10 +1229,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>132.79</v>
+        <v>134.11</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.18</v>
+        <v>1.32</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1253,99 +1241,99 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>89.64</v>
+        <v>88.87</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.89</v>
+        <v>15.71</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B8" t="n">
-        <v>175.3</v>
+        <v>181.9</v>
       </c>
       <c r="C8" t="n">
-        <v>83.5</v>
+        <v>88.7</v>
       </c>
       <c r="D8" t="n">
-        <v>27.8</v>
+        <v>27.2</v>
       </c>
       <c r="E8" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="F8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="n">
-        <v>24.7</v>
+        <v>23.2</v>
       </c>
       <c r="I8" t="n">
-        <v>10.4</v>
+        <v>11.2</v>
       </c>
       <c r="J8" t="n">
-        <v>42.9</v>
+        <v>42.3</v>
       </c>
       <c r="K8" t="n">
-        <v>77.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="O8" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T8" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="W8" t="n">
-        <v>14.8</v>
+        <v>13.1</v>
       </c>
       <c r="X8" t="n">
-        <v>11.8</v>
+        <v>10.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>-7.7</v>
+        <v>-12.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>-0.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>-2.9</v>
+        <v>-6.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>236.72</v>
+        <v>229.92</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.49</v>
+        <v>-6.8</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1354,10 +1342,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>134.11</v>
+        <v>133.43</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.32</v>
+        <v>-0.68</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1366,99 +1354,99 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>88.87</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>15.71</v>
+        <v>15.36</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B9" t="n">
-        <v>181.9</v>
+        <v>188.8</v>
       </c>
       <c r="C9" t="n">
-        <v>88.7</v>
+        <v>94.8</v>
       </c>
       <c r="D9" t="n">
-        <v>27.2</v>
+        <v>27.9</v>
       </c>
       <c r="E9" t="n">
-        <v>30.5</v>
+        <v>32.4</v>
       </c>
       <c r="F9" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="H9" t="n">
-        <v>23.2</v>
+        <v>24.4</v>
       </c>
       <c r="I9" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="J9" t="n">
-        <v>42.3</v>
+        <v>40.8</v>
       </c>
       <c r="K9" t="n">
-        <v>76.7</v>
+        <v>75.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N9" t="n">
-        <v>38</v>
+        <v>36.5</v>
       </c>
       <c r="O9" t="n">
-        <v>41.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="S9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T9" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="V9" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>13.1</v>
+        <v>10</v>
       </c>
       <c r="X9" t="n">
-        <v>10.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.699999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>-12.5</v>
+        <v>-9.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.6</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>-6.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>229.92</v>
+        <v>223</v>
       </c>
       <c r="AG9" t="n">
-        <v>-6.8</v>
+        <v>-6.92</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1467,10 +1455,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>133.43</v>
+        <v>128.87</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.68</v>
+        <v>-4.56</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1479,99 +1467,72 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>85.26000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.36</v>
+        <v>14.68</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B10" t="n">
-        <v>188.8</v>
+        <v>166.3</v>
       </c>
       <c r="C10" t="n">
-        <v>94.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>27.9</v>
+        <v>26.1</v>
       </c>
       <c r="E10" t="n">
-        <v>32.4</v>
+        <v>30.6</v>
       </c>
       <c r="F10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>40.8</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>36.5</v>
+        <v>98.8</v>
       </c>
       <c r="O10" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R10" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="X10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1.9</v>
       </c>
-      <c r="S10" t="n">
-        <v>20</v>
-      </c>
-      <c r="T10" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>10</v>
-      </c>
-      <c r="X10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AD10" t="n">
-        <v>-3.3</v>
+        <v>-2.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>223</v>
+        <v>221.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>-6.92</v>
+        <v>-1.92</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1580,10 +1541,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>128.87</v>
+        <v>125.07</v>
       </c>
       <c r="AL10" t="n">
-        <v>-4.56</v>
+        <v>-3.8</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1591,73 +1552,67 @@
       <c r="AN10" t="n">
         <v>142</v>
       </c>
-      <c r="AP10" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>14.68</v>
-      </c>
       <c r="BL10" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B11" t="n">
-        <v>166.3</v>
+        <v>154.6</v>
       </c>
       <c r="C11" t="n">
-        <v>94.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>26.1</v>
+        <v>25.2</v>
       </c>
       <c r="E11" t="n">
-        <v>30.6</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>98.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="V11" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="W11" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X11" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>-7.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>-2.8</v>
+        <v>-1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>221.08</v>
+        <v>221.24</v>
       </c>
       <c r="AG11" t="n">
-        <v>-1.92</v>
+        <v>0.16</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1666,10 +1621,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>125.07</v>
+        <v>125.99</v>
       </c>
       <c r="AL11" t="n">
-        <v>-3.8</v>
+        <v>0.92</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1678,66 +1633,93 @@
         <v>142</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B12" t="n">
-        <v>154.6</v>
+        <v>175.7</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>91.2</v>
       </c>
       <c r="D12" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>26.9</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>6.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>42.1</v>
       </c>
       <c r="K12" t="n">
-        <v>98.09999999999999</v>
+        <v>77.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>37.2</v>
       </c>
       <c r="O12" t="n">
-        <v>39.5</v>
+        <v>42.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>22.7</v>
       </c>
       <c r="V12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="W12" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="X12" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>-6.4</v>
+        <v>-5.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>221.24</v>
+        <v>223.94</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.16</v>
+        <v>2.7</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1746,10 +1728,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>125.99</v>
+        <v>128.11</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.92</v>
+        <v>2.12</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1757,94 +1739,100 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
+      <c r="AP12" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>16.09</v>
+      </c>
       <c r="BL12" s="1" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B13" t="n">
-        <v>175.7</v>
+        <v>178.9</v>
       </c>
       <c r="C13" t="n">
-        <v>91.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D13" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E13" t="n">
         <v>24</v>
       </c>
-      <c r="E13" t="n">
-        <v>26.9</v>
-      </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H13" t="n">
-        <v>24.3</v>
+        <v>25</v>
       </c>
       <c r="I13" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="J13" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="K13" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>37.2</v>
+        <v>37.5</v>
       </c>
       <c r="O13" t="n">
-        <v>42.3</v>
+        <v>41.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="S13" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="T13" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="V13" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="W13" t="n">
-        <v>10.8</v>
+        <v>16.5</v>
       </c>
       <c r="X13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Y13" t="n">
         <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>-5.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>-1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>223.94</v>
+        <v>224.33</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.7</v>
+        <v>0.39</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1853,10 +1841,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>128.11</v>
+        <v>128.49</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.12</v>
+        <v>0.38</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1865,99 +1853,99 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>88.34</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>16.09</v>
+        <v>16.13</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B14" t="n">
-        <v>178.9</v>
+        <v>175.3</v>
       </c>
       <c r="C14" t="n">
-        <v>92.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>27.8</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="H14" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="I14" t="n">
         <v>10.8</v>
       </c>
       <c r="J14" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="K14" t="n">
-        <v>77.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>37.5</v>
+        <v>38.4</v>
       </c>
       <c r="O14" t="n">
-        <v>41.6</v>
+        <v>42</v>
       </c>
       <c r="Q14" t="n">
         <v>23</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="T14" t="n">
         <v>23</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="W14" t="n">
-        <v>16.5</v>
+        <v>17.1</v>
       </c>
       <c r="X14" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>-3.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>224.33</v>
+        <v>224.34</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.39</v>
+        <v>0.01</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1966,10 +1954,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>128.49</v>
+        <v>128.93</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1978,99 +1966,72 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>87.56999999999999</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>16.13</v>
+        <v>15.43</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B15" t="n">
-        <v>175.3</v>
+        <v>157.8</v>
       </c>
       <c r="C15" t="n">
-        <v>85.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="E15" t="n">
-        <v>27.8</v>
+        <v>30.3</v>
       </c>
       <c r="F15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H15" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>41.4</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M15" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X15" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD15" t="n">
         <v>3.6</v>
       </c>
-      <c r="N15" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>23</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="T15" t="n">
-        <v>23</v>
-      </c>
-      <c r="V15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W15" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF15" t="n">
-        <v>224.34</v>
+        <v>231.46</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01</v>
+        <v>3.7</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2079,10 +2040,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>128.93</v>
+        <v>129.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2090,73 +2051,67 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
-      <c r="AP15" t="n">
-        <v>89.06999999999999</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>15.43</v>
-      </c>
       <c r="BL15" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B16" t="n">
-        <v>157.8</v>
+        <v>151.6</v>
       </c>
       <c r="C16" t="n">
-        <v>85.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="D16" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="K16" t="n">
-        <v>98.7</v>
+        <v>97.5</v>
       </c>
       <c r="O16" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>8.1</v>
       </c>
       <c r="W16" t="n">
-        <v>19.7</v>
+        <v>22.3</v>
       </c>
       <c r="X16" t="n">
-        <v>12.1</v>
+        <v>15.2</v>
       </c>
       <c r="Y16" t="n">
         <v>8</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA16" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.6</v>
+        <v>-0.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>231.46</v>
+        <v>229.92</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.7</v>
+        <v>-1.54</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2165,10 +2120,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>129.8</v>
+        <v>133.01</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.87</v>
+        <v>3.21</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2177,66 +2132,66 @@
         <v>142</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B17" t="n">
-        <v>151.6</v>
+        <v>157.5</v>
       </c>
       <c r="C17" t="n">
-        <v>73.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="E17" t="n">
-        <v>33.9</v>
+        <v>36.9</v>
       </c>
       <c r="F17" t="n">
         <v>7.4</v>
       </c>
       <c r="K17" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="O17" t="n">
-        <v>40.6</v>
+        <v>38</v>
       </c>
       <c r="V17" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="W17" t="n">
-        <v>22.3</v>
+        <v>20.8</v>
       </c>
       <c r="X17" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>-3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>229.92</v>
+        <v>226.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>-1.54</v>
+        <v>-2.97</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2245,10 +2200,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>133.01</v>
+        <v>128.4</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.21</v>
+        <v>-4.61</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2257,66 +2212,66 @@
         <v>142</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B18" t="n">
-        <v>157.5</v>
+        <v>148.5</v>
       </c>
       <c r="C18" t="n">
-        <v>76.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D18" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="E18" t="n">
-        <v>36.9</v>
+        <v>34.3</v>
       </c>
       <c r="F18" t="n">
         <v>7.4</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="O18" t="n">
-        <v>38</v>
+        <v>39.8</v>
       </c>
       <c r="V18" t="n">
-        <v>6.7</v>
+        <v>11.2</v>
       </c>
       <c r="W18" t="n">
-        <v>20.8</v>
+        <v>21.7</v>
       </c>
       <c r="X18" t="n">
-        <v>13.8</v>
+        <v>16.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AB18" t="n">
-        <v>-2.3</v>
+        <v>-1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.1</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>226.95</v>
+        <v>223.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>-2.97</v>
+        <v>-3.83</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2325,10 +2280,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>128.4</v>
+        <v>124.76</v>
       </c>
       <c r="AL18" t="n">
-        <v>-4.61</v>
+        <v>-3.64</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2337,66 +2292,60 @@
         <v>142</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B19" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="C19" t="n">
-        <v>70.5</v>
+        <v>72.8</v>
       </c>
       <c r="D19" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="E19" t="n">
-        <v>34.3</v>
+        <v>31.4</v>
       </c>
       <c r="F19" t="n">
         <v>7.4</v>
       </c>
       <c r="K19" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="O19" t="n">
-        <v>39.8</v>
+        <v>40.2</v>
       </c>
       <c r="V19" t="n">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="W19" t="n">
-        <v>21.7</v>
+        <v>16.8</v>
       </c>
       <c r="X19" t="n">
-        <v>16.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y19" t="n">
         <v>7</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB19" t="n">
-        <v>-1.9</v>
+        <v>0.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>223.11</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>-3.83</v>
+        <v>4.8</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2405,10 +2354,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>124.76</v>
+        <v>127.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>-3.64</v>
+        <v>2.44</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2417,60 +2366,93 @@
         <v>142</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B20" t="n">
-        <v>147.5</v>
+        <v>183.5</v>
       </c>
       <c r="C20" t="n">
-        <v>72.8</v>
+        <v>84.5</v>
       </c>
       <c r="D20" t="n">
-        <v>26.7</v>
+        <v>31.5</v>
       </c>
       <c r="E20" t="n">
-        <v>31.4</v>
+        <v>34.6</v>
       </c>
       <c r="F20" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>41.5</v>
       </c>
       <c r="K20" t="n">
-        <v>100</v>
+        <v>76.3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>37.7</v>
       </c>
       <c r="O20" t="n">
-        <v>40.2</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>23</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S20" t="n">
+        <v>18</v>
+      </c>
+      <c r="T20" t="n">
+        <v>23</v>
       </c>
       <c r="V20" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="W20" t="n">
-        <v>16.8</v>
+        <v>20</v>
       </c>
       <c r="X20" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>220.36</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-3.75</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2479,10 +2461,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>127.2</v>
+        <v>127.13</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2490,94 +2472,100 @@
       <c r="AN20" t="n">
         <v>142</v>
       </c>
+      <c r="AP20" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL20" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B21" t="n">
-        <v>183.5</v>
+        <v>180.5</v>
       </c>
       <c r="C21" t="n">
-        <v>84.5</v>
+        <v>79.2</v>
       </c>
       <c r="D21" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="E21" t="n">
         <v>34.6</v>
       </c>
       <c r="F21" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="H21" t="n">
         <v>23.9</v>
       </c>
       <c r="I21" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="J21" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="K21" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
         <v>37.7</v>
       </c>
       <c r="O21" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="S21" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="T21" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V21" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W21" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="X21" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA21" t="n">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>220.36</v>
+        <v>219.64</v>
       </c>
       <c r="AG21" t="n">
-        <v>-3.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2586,10 +2574,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>127.13</v>
+        <v>126.03</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2598,99 +2586,99 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>76.90000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="AS21" t="n">
-        <v>14.17</v>
+        <v>14.55</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B22" t="n">
-        <v>180.5</v>
+        <v>168.1</v>
       </c>
       <c r="C22" t="n">
-        <v>79.2</v>
+        <v>69.7</v>
       </c>
       <c r="D22" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E22" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F22" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H22" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I22" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="J22" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="K22" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O22" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S22" t="n">
         <v>17.6</v>
       </c>
       <c r="T22" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="V22" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W22" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA22" t="n">
         <v>14.9</v>
       </c>
-      <c r="Y22" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>11.9</v>
-      </c>
       <c r="AB22" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>219.64</v>
+        <v>224.93</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.72</v>
+        <v>5.29</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2699,10 +2687,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>126.03</v>
+        <v>129.28</v>
       </c>
       <c r="AL22" t="n">
-        <v>-1.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2711,99 +2699,99 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>82.95</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS22" t="n">
-        <v>14.55</v>
+        <v>15.25</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B23" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C23" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D23" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E23" t="n">
         <v>30.4</v>
       </c>
-      <c r="E23" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H23" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I23" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J23" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K23" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O23" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S23" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="V23" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="W23" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X23" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y23" t="n">
         <v>17</v>
       </c>
-      <c r="Y23" t="n">
-        <v>11</v>
-      </c>
       <c r="Z23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
-        <v>14.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG23" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2812,10 +2800,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL23" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2824,99 +2812,66 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS23" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B24" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C24" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D24" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H24" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I24" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K24" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>15</v>
-      </c>
-      <c r="T24" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
       </c>
       <c r="V24" t="n">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="W24" t="n">
-        <v>26</v>
+        <v>36.1</v>
       </c>
       <c r="X24" t="n">
-        <v>18.1</v>
+        <v>26.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA24" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC24" t="n">
         <v>6.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2925,10 +2880,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2936,67 +2891,61 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
-      <c r="AP24" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL24" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B25" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D25" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F25" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O25" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V25" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
       <c r="W25" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="X25" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3005,10 +2954,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL25" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3017,60 +2966,93 @@
         <v>142</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B26" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>67</v>
       </c>
       <c r="D26" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E26" t="n">
+        <v>31.5</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>41.1</v>
       </c>
       <c r="K26" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>35</v>
       </c>
       <c r="O26" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>20.5</v>
       </c>
       <c r="V26" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W26" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X26" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG26" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3079,10 +3061,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL26" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3090,94 +3072,100 @@
       <c r="AN26" t="n">
         <v>142</v>
       </c>
+      <c r="AP26" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL26" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B27" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C27" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E27" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I27" t="n">
         <v>11.4</v>
       </c>
       <c r="J27" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K27" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M27" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N27" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O27" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T27" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V27" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W27" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X27" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y27" t="n">
         <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA27" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3186,10 +3174,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL27" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3198,99 +3186,99 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS27" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B28" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C28" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D28" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F28" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H28" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I28" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K28" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N28" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O28" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W28" t="n">
+        <v>13</v>
+      </c>
+      <c r="X28" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA28" t="n">
         <v>11.4</v>
       </c>
-      <c r="J28" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>76</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N28" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O28" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>14</v>
-      </c>
-      <c r="T28" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB28" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF28" t="n">
         <v>220.92</v>
       </c>
       <c r="AG28" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3299,10 +3287,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL28" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3311,99 +3299,99 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS28" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B29" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C29" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E29" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F29" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H29" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I29" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J29" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K29" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O29" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X29" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD29" t="n">
         <v>0.5</v>
       </c>
-      <c r="S29" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>13</v>
-      </c>
-      <c r="X29" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF29" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3412,10 +3400,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL29" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3424,99 +3412,99 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B30" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C30" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D30" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E30" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F30" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H30" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I30" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J30" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K30" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M30" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N30" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O30" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T30" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V30" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W30" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X30" t="n">
         <v>12.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z30" t="n">
         <v>13</v>
       </c>
       <c r="AA30" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF30" t="n">
         <v>216.02</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3525,10 +3513,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL30" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3537,99 +3525,66 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS30" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B31" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C31" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D31" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E31" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F31" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H31" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I31" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K31" t="n">
-        <v>75</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N31" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V31" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W31" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X31" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA31" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3638,10 +3593,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3649,67 +3604,61 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
-      <c r="AP31" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL31" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B32" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D32" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F32" t="n">
         <v>6.8</v>
       </c>
       <c r="K32" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O32" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V32" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W32" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X32" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA32" t="n">
         <v>13.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3718,10 +3667,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3730,60 +3679,93 @@
         <v>142</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B33" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>60</v>
       </c>
       <c r="D33" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E33" t="n">
+        <v>25.9</v>
       </c>
       <c r="F33" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>24</v>
+      </c>
+      <c r="I33" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>38.8</v>
       </c>
       <c r="K33" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>36.7</v>
       </c>
       <c r="O33" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7</v>
+      </c>
+      <c r="T33" t="n">
+        <v>21.7</v>
       </c>
       <c r="V33" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W33" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X33" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z33" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF33" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3792,10 +3774,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3803,94 +3785,67 @@
       <c r="AN33" t="n">
         <v>142</v>
       </c>
+      <c r="AP33" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL33" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B34" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C34" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D34" t="n">
-        <v>29</v>
-      </c>
-      <c r="E34" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F34" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H34" t="n">
-        <v>24</v>
-      </c>
-      <c r="I34" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J34" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K34" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N34" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O34" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>7</v>
-      </c>
-      <c r="T34" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V34" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W34" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X34" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA34" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB34" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF34" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG34" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3899,10 +3854,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3910,67 +3865,94 @@
       <c r="AN34" t="n">
         <v>142</v>
       </c>
-      <c r="AP34" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL34" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B35" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>63.7</v>
       </c>
       <c r="D35" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>36.4</v>
       </c>
       <c r="F35" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I35" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>39.9</v>
       </c>
       <c r="K35" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>35.9</v>
       </c>
       <c r="O35" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6</v>
+      </c>
+      <c r="T35" t="n">
+        <v>20.3</v>
       </c>
       <c r="V35" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W35" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X35" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA35" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF35" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG35" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3979,10 +3961,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3990,94 +3972,100 @@
       <c r="AN35" t="n">
         <v>142</v>
       </c>
+      <c r="AP35" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL35" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B36" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C36" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E36" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F36" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H36" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I36" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J36" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K36" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N36" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O36" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R36" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V36" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W36" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X36" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4086,10 +4074,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL36" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4098,99 +4086,99 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B37" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C37" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D37" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E37" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F37" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H37" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I37" t="n">
         <v>11.3</v>
       </c>
       <c r="J37" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K37" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N37" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O37" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V37" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W37" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X37" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z37" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA37" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG37" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4199,10 +4187,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL37" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4211,99 +4199,66 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS37" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B38" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C38" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D38" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E38" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H38" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I38" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J38" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K38" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N38" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O38" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>9</v>
-      </c>
-      <c r="T38" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V38" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W38" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X38" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y38" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z38" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA38" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB38" t="n">
         <v>-0</v>
       </c>
       <c r="AC38" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4312,10 +4267,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4323,67 +4278,61 @@
       <c r="AN38" t="n">
         <v>142</v>
       </c>
-      <c r="AP38" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL38" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B39" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D39" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F39" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K39" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O39" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V39" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W39" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X39" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y39" t="n">
         <v>14</v>
       </c>
       <c r="Z39" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA39" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF39" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4392,10 +4341,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL39" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4404,60 +4353,93 @@
         <v>142</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B40" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>56.3</v>
       </c>
       <c r="D40" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>21.2</v>
       </c>
       <c r="F40" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I40" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J40" t="n">
+        <v>40.4</v>
       </c>
       <c r="K40" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N40" t="n">
+        <v>29</v>
       </c>
       <c r="O40" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>21.6</v>
       </c>
       <c r="V40" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W40" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X40" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z40" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA40" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF40" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG40" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4466,10 +4448,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL40" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4477,52 +4459,58 @@
       <c r="AN40" t="n">
         <v>142</v>
       </c>
+      <c r="AP40" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL40" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B41" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C41" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D41" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E41" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F41" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H41" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I41" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J41" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K41" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O41" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R41" t="n">
         <v>1.3</v>
@@ -4531,40 +4519,40 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V41" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W41" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X41" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA41" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC41" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG41" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4573,10 +4561,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4585,99 +4573,99 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS41" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B42" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C42" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D42" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E42" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F42" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H42" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I42" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J42" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K42" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O42" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V42" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W42" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X42" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y42" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z42" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA42" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF42" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG42" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4686,10 +4674,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL42" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4698,99 +4686,99 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS42" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B43" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C43" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D43" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E43" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F43" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H43" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I43" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J43" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K43" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N43" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O43" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q43" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T43" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V43" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W43" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X43" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y43" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA43" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF43" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG43" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4799,10 +4787,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL43" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4811,99 +4799,99 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS43" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B44" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C44" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E44" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F44" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H44" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I44" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J44" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K44" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M44" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N44" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O44" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R44" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T44" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V44" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W44" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X44" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z44" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA44" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG44" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4912,10 +4900,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4924,99 +4912,60 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS44" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B45" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C45" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D45" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E45" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F45" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H45" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J45" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K45" t="n">
-        <v>77</v>
-      </c>
-      <c r="M45" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N45" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O45" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>21</v>
-      </c>
-      <c r="R45" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S45" t="n">
-        <v>6</v>
-      </c>
-      <c r="T45" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V45" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W45" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X45" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y45" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA45" t="n">
         <v>9</v>
       </c>
-      <c r="Z45" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB45" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF45" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG45" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -5025,10 +4974,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL45" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -5036,61 +4985,61 @@
       <c r="AN45" t="n">
         <v>142</v>
       </c>
-      <c r="AP45" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL45" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B46" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D46" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F46" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>35.5</v>
       </c>
       <c r="V46" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W46" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X46" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z46" t="n">
         <v>13</v>
       </c>
       <c r="AA46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB46" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5099,10 +5048,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5111,60 +5060,60 @@
         <v>142</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B47" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D47" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K47" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O47" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V47" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W47" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X47" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z47" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB47" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD47" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF47" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG47" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5173,10 +5122,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5185,60 +5134,93 @@
         <v>142</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B48" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C48" t="n">
+        <v>86.8</v>
       </c>
       <c r="D48" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>33</v>
       </c>
       <c r="F48" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H48" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I48" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J48" t="n">
+        <v>41.1</v>
       </c>
       <c r="K48" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N48" t="n">
+        <v>33.5</v>
       </c>
       <c r="O48" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="n">
+        <v>22.4</v>
       </c>
       <c r="V48" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W48" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X48" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z48" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA48" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD48" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF48" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5247,10 +5229,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL48" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5258,94 +5240,100 @@
       <c r="AN48" t="n">
         <v>142</v>
       </c>
+      <c r="AP48" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL48" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B49" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C49" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D49" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E49" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F49" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H49" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I49" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J49" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K49" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M49" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O49" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R49" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T49" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V49" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W49" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X49" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z49" t="n">
         <v>12</v>
       </c>
       <c r="AA49" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB49" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF49" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG49" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5354,10 +5342,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL49" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5366,99 +5354,99 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS49" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B50" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C50" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D50" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E50" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F50" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H50" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I50" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J50" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K50" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O50" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R50" t="n">
         <v>1.8</v>
       </c>
       <c r="S50" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T50" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V50" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W50" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X50" t="n">
         <v>10.9</v>
       </c>
       <c r="Y50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA50" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB50" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD50" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD50" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF50" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG50" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5467,10 +5455,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL50" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5479,99 +5467,66 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS50" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B51" t="n">
-        <v>183</v>
-      </c>
-      <c r="C51" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D51" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E51" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
-      </c>
-      <c r="H51" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I51" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K51" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4</v>
-      </c>
-      <c r="N51" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O51" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S51" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T51" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V51" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W51" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X51" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y51" t="n">
         <v>8</v>
       </c>
       <c r="Z51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA51" t="n">
         <v>10</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF51" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5580,10 +5535,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL51" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5591,67 +5546,61 @@
       <c r="AN51" t="n">
         <v>142</v>
       </c>
-      <c r="AP51" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL51" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B52" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D52" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F52" t="n">
         <v>6.5</v>
       </c>
       <c r="K52" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O52" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V52" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W52" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X52" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA52" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC52" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF52" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG52" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5660,10 +5609,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL52" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5672,60 +5621,60 @@
         <v>142</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B53" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D53" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F53" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K53" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O53" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V53" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W53" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X53" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y53" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z53" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA53" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC53" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF53" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5733,12 +5682,6 @@
       <c r="AI53" t="n">
         <v>235</v>
       </c>
-      <c r="AK53" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
@@ -5746,60 +5689,54 @@
         <v>142</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B54" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D54" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F54" t="n">
         <v>5.5</v>
       </c>
       <c r="K54" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O54" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V54" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W54" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X54" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA54" t="n">
         <v>15</v>
       </c>
-      <c r="AA54" t="n">
-        <v>14</v>
-      </c>
       <c r="AB54" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC54" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5814,54 +5751,93 @@
         <v>142</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B55" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C55" t="n">
+        <v>71.8</v>
       </c>
       <c r="D55" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>24.7</v>
       </c>
       <c r="F55" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H55" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J55" t="n">
+        <v>41.1</v>
       </c>
       <c r="K55" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M55" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N55" t="n">
+        <v>33.5</v>
       </c>
       <c r="O55" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>23.2</v>
       </c>
       <c r="V55" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W55" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X55" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y55" t="n">
         <v>12</v>
       </c>
       <c r="Z55" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA55" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB55" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD55" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5869,82 +5845,94 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
+      <c r="AK55" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
         <v>142</v>
       </c>
+      <c r="AP55" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL55" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B56" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C56" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D56" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E56" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H56" t="n">
         <v>24.1</v>
       </c>
       <c r="I56" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J56" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K56" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N56" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O56" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R56" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T56" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="Y56" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z56" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA56" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AF56" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5953,10 +5941,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL56" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5965,81 +5953,81 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS56" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B57" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C57" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D57" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E57" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F57" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H57" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I57" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K57" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N57" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O57" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R57" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S57" t="n">
         <v>7</v>
       </c>
       <c r="T57" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="Y57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z57" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA57" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AF57" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG57" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6048,10 +6036,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL57" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6060,81 +6048,81 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS57" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B58" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C58" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D58" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E58" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F58" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H58" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I58" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J58" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K58" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N58" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O58" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R58" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T58" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Y58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z58" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA58" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6143,10 +6131,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL58" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6155,81 +6143,42 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS58" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B59" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C59" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D59" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E59" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F59" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H59" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I59" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J59" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K59" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M59" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N59" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="O59" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R59" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S59" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T59" t="n">
-        <v>23.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z59" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA59" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AF59" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG59" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6237,50 +6186,44 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
-      <c r="AK59" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
-      <c r="AP59" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL59" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B60" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D60" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F60" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z60" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA60" t="n">
         <v>9</v>
       </c>
+      <c r="AF60" t="n">
+        <v>229.16</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>1.03</v>
+      </c>
       <c r="AH60" t="n">
         <v>215</v>
       </c>
@@ -6294,18 +6237,18 @@
         <v>142</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B61" t="n">
-        <v>143.9</v>
+        <v>142.3</v>
       </c>
       <c r="D61" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="F61" t="n">
         <v>2.5</v>
@@ -6314,10 +6257,16 @@
         <v>4</v>
       </c>
       <c r="Z61" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA61" t="n">
-        <v>9</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>228.55</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>-0.61</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6332,30 +6281,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B62" t="n">
-        <v>142.3</v>
+        <v>153.9</v>
       </c>
       <c r="D62" t="n">
-        <v>30.9</v>
+        <v>33</v>
       </c>
       <c r="F62" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z62" t="n">
         <v>13</v>
       </c>
       <c r="AA62" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6370,7 +6319,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,61 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B2" t="n">
-        <v>178.9</v>
+        <v>155.4</v>
       </c>
       <c r="C2" t="n">
-        <v>84.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>28.2</v>
+        <v>27.4</v>
       </c>
       <c r="E2" t="n">
-        <v>31.1</v>
+        <v>29.1</v>
       </c>
       <c r="F2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I2" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>41.5</v>
+        <v>6.6</v>
       </c>
       <c r="K2" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>38.1</v>
+        <v>98.2</v>
       </c>
       <c r="O2" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>22.1</v>
+        <v>40.1</v>
       </c>
       <c r="V2" t="n">
-        <v>7.9</v>
+        <v>5.2</v>
       </c>
       <c r="W2" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>226.8</v>
+        <v>226.39</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.95</v>
+        <v>-0.4</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +691,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>129.1</v>
+        <v>129.78</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.24</v>
+        <v>0.68</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -729,85 +702,67 @@
       <c r="AN2" t="n">
         <v>142</v>
       </c>
-      <c r="AP2" t="n">
-        <v>81.91</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>15.61</v>
-      </c>
       <c r="BL2" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>38.28</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>14004.4</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>2044.8</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B3" t="n">
-        <v>155.4</v>
+        <v>151.1</v>
       </c>
       <c r="C3" t="n">
-        <v>82.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>27.4</v>
+        <v>26.8</v>
       </c>
       <c r="E3" t="n">
-        <v>29.1</v>
+        <v>30.9</v>
       </c>
       <c r="F3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>98.2</v>
+        <v>97.7</v>
       </c>
       <c r="O3" t="n">
-        <v>40.1</v>
+        <v>40.8</v>
       </c>
       <c r="V3" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="W3" t="n">
         <v>18.8</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>-0</v>
       </c>
       <c r="AC3" t="n">
         <v>6.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>226.39</v>
+        <v>229.98</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.4</v>
+        <v>3.58</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -816,10 +771,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>129.78</v>
+        <v>132.56</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.68</v>
+        <v>2.78</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -828,66 +783,93 @@
         <v>142</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="B4" t="n">
-        <v>151.1</v>
+        <v>167.2</v>
       </c>
       <c r="C4" t="n">
-        <v>76.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>26.8</v>
+        <v>27.6</v>
       </c>
       <c r="E4" t="n">
-        <v>30.9</v>
+        <v>28.2</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>7.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>40.3</v>
       </c>
       <c r="K4" t="n">
-        <v>97.7</v>
+        <v>75</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>37.2</v>
       </c>
       <c r="O4" t="n">
-        <v>40.8</v>
+        <v>39.9</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>19</v>
+      </c>
+      <c r="T4" t="n">
+        <v>22</v>
       </c>
       <c r="V4" t="n">
-        <v>6.3</v>
+        <v>9.4</v>
       </c>
       <c r="W4" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="X4" t="n">
-        <v>12.6</v>
+        <v>14.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>229.98</v>
+        <v>236.38</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.58</v>
+        <v>6.4</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -896,10 +878,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>132.56</v>
+        <v>132.97</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.78</v>
+        <v>0.41</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -907,94 +889,100 @@
       <c r="AN4" t="n">
         <v>142</v>
       </c>
+      <c r="AP4" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>16.05</v>
+      </c>
       <c r="BL4" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="B5" t="n">
-        <v>167.2</v>
+        <v>176.7</v>
       </c>
       <c r="C5" t="n">
-        <v>74.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="D5" t="n">
-        <v>27.6</v>
+        <v>28.3</v>
       </c>
       <c r="E5" t="n">
-        <v>28.2</v>
+        <v>31.6</v>
       </c>
       <c r="F5" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="H5" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="I5" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="J5" t="n">
-        <v>40.3</v>
+        <v>41.8</v>
       </c>
       <c r="K5" t="n">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="N5" t="n">
-        <v>37.2</v>
+        <v>38.4</v>
       </c>
       <c r="O5" t="n">
-        <v>39.9</v>
+        <v>41</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="T5" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="V5" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>19.1</v>
+        <v>14.8</v>
       </c>
       <c r="X5" t="n">
-        <v>14.2</v>
+        <v>10.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>236.38</v>
+        <v>236.23</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1003,10 +991,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>132.97</v>
+        <v>132.79</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.41</v>
+        <v>-0.18</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1015,99 +1003,99 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>90.8</v>
+        <v>89.64</v>
       </c>
       <c r="AS5" t="n">
-        <v>16.05</v>
+        <v>15.89</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B6" t="n">
-        <v>176.7</v>
+        <v>175.3</v>
       </c>
       <c r="C6" t="n">
-        <v>80.8</v>
+        <v>83.5</v>
       </c>
       <c r="D6" t="n">
-        <v>28.3</v>
+        <v>27.8</v>
       </c>
       <c r="E6" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="F6" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H6" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="I6" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="J6" t="n">
-        <v>41.8</v>
+        <v>42.9</v>
       </c>
       <c r="K6" t="n">
-        <v>76.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="N6" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="O6" t="n">
         <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="T6" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>14.8</v>
       </c>
       <c r="X6" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z6" t="n">
         <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1.6</v>
+        <v>-7.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AF6" t="n">
-        <v>236.23</v>
+        <v>236.72</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.15</v>
+        <v>0.49</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1116,10 +1104,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>132.79</v>
+        <v>134.11</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.18</v>
+        <v>1.32</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1128,99 +1116,99 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>89.64</v>
+        <v>88.87</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.89</v>
+        <v>15.71</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B7" t="n">
-        <v>175.3</v>
+        <v>181.9</v>
       </c>
       <c r="C7" t="n">
-        <v>83.5</v>
+        <v>88.7</v>
       </c>
       <c r="D7" t="n">
-        <v>27.8</v>
+        <v>27.2</v>
       </c>
       <c r="E7" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="F7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>24.7</v>
+        <v>23.2</v>
       </c>
       <c r="I7" t="n">
-        <v>10.4</v>
+        <v>11.2</v>
       </c>
       <c r="J7" t="n">
-        <v>42.9</v>
+        <v>42.3</v>
       </c>
       <c r="K7" t="n">
-        <v>77.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="O7" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T7" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="W7" t="n">
-        <v>14.8</v>
+        <v>13.1</v>
       </c>
       <c r="X7" t="n">
-        <v>11.8</v>
+        <v>10.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AB7" t="n">
-        <v>-7.7</v>
+        <v>-12.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>-0.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>-2.9</v>
+        <v>-6.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>236.72</v>
+        <v>229.92</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.49</v>
+        <v>-6.8</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1229,10 +1217,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>134.11</v>
+        <v>133.43</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.32</v>
+        <v>-0.68</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1241,99 +1229,99 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>88.87</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.71</v>
+        <v>15.36</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B8" t="n">
-        <v>181.9</v>
+        <v>188.8</v>
       </c>
       <c r="C8" t="n">
-        <v>88.7</v>
+        <v>94.8</v>
       </c>
       <c r="D8" t="n">
-        <v>27.2</v>
+        <v>27.9</v>
       </c>
       <c r="E8" t="n">
-        <v>30.5</v>
+        <v>32.4</v>
       </c>
       <c r="F8" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="H8" t="n">
-        <v>23.2</v>
+        <v>24.4</v>
       </c>
       <c r="I8" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="J8" t="n">
-        <v>42.3</v>
+        <v>40.8</v>
       </c>
       <c r="K8" t="n">
-        <v>76.7</v>
+        <v>75.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N8" t="n">
-        <v>38</v>
+        <v>36.5</v>
       </c>
       <c r="O8" t="n">
-        <v>41.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T8" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="V8" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>13.1</v>
+        <v>10</v>
       </c>
       <c r="X8" t="n">
-        <v>10.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.699999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>-12.5</v>
+        <v>-9.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.6</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>-6.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>229.92</v>
+        <v>223</v>
       </c>
       <c r="AG8" t="n">
-        <v>-6.8</v>
+        <v>-6.92</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1342,10 +1330,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>133.43</v>
+        <v>128.87</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.68</v>
+        <v>-4.56</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1354,99 +1342,72 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>85.26000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>15.36</v>
+        <v>14.68</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B9" t="n">
-        <v>188.8</v>
+        <v>166.3</v>
       </c>
       <c r="C9" t="n">
-        <v>94.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>27.9</v>
+        <v>26.1</v>
       </c>
       <c r="E9" t="n">
-        <v>32.4</v>
+        <v>30.6</v>
       </c>
       <c r="F9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>40.8</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N9" t="n">
-        <v>36.5</v>
+        <v>98.8</v>
       </c>
       <c r="O9" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R9" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="X9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.9</v>
       </c>
-      <c r="S9" t="n">
-        <v>20</v>
-      </c>
-      <c r="T9" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>10</v>
-      </c>
-      <c r="X9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AD9" t="n">
-        <v>-3.3</v>
+        <v>-2.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>223</v>
+        <v>221.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>-6.92</v>
+        <v>-1.92</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1455,10 +1416,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>128.87</v>
+        <v>125.07</v>
       </c>
       <c r="AL9" t="n">
-        <v>-4.56</v>
+        <v>-3.8</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1466,73 +1427,67 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
-      <c r="AP9" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>14.68</v>
-      </c>
       <c r="BL9" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B10" t="n">
-        <v>166.3</v>
+        <v>154.6</v>
       </c>
       <c r="C10" t="n">
-        <v>94.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1</v>
+        <v>25.2</v>
       </c>
       <c r="E10" t="n">
-        <v>30.6</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
         <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>98.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="V10" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="W10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X10" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>-7.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>-2.8</v>
+        <v>-1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>221.08</v>
+        <v>221.24</v>
       </c>
       <c r="AG10" t="n">
-        <v>-1.92</v>
+        <v>0.16</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1541,10 +1496,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>125.07</v>
+        <v>125.99</v>
       </c>
       <c r="AL10" t="n">
-        <v>-3.8</v>
+        <v>0.92</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1553,66 +1508,93 @@
         <v>142</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B11" t="n">
-        <v>154.6</v>
+        <v>175.7</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>91.2</v>
       </c>
       <c r="D11" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>26.9</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>6.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>42.1</v>
       </c>
       <c r="K11" t="n">
-        <v>98.09999999999999</v>
+        <v>77.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>37.2</v>
       </c>
       <c r="O11" t="n">
-        <v>39.5</v>
+        <v>42.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>22.7</v>
       </c>
       <c r="V11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="W11" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="X11" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>-6.4</v>
+        <v>-5.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>221.24</v>
+        <v>223.94</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.16</v>
+        <v>2.7</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1621,10 +1603,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>125.99</v>
+        <v>128.11</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.92</v>
+        <v>2.12</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1632,94 +1614,100 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
+      <c r="AP11" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>16.09</v>
+      </c>
       <c r="BL11" s="1" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="n">
-        <v>175.7</v>
+        <v>178.9</v>
       </c>
       <c r="C12" t="n">
-        <v>91.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E12" t="n">
         <v>24</v>
       </c>
-      <c r="E12" t="n">
-        <v>26.9</v>
-      </c>
       <c r="F12" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H12" t="n">
-        <v>24.3</v>
+        <v>25</v>
       </c>
       <c r="I12" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="J12" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="K12" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>37.2</v>
+        <v>37.5</v>
       </c>
       <c r="O12" t="n">
-        <v>42.3</v>
+        <v>41.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="S12" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="T12" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="V12" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="W12" t="n">
-        <v>10.8</v>
+        <v>16.5</v>
       </c>
       <c r="X12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Y12" t="n">
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>-5.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>223.94</v>
+        <v>224.33</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.7</v>
+        <v>0.39</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1728,10 +1716,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>128.11</v>
+        <v>128.49</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.12</v>
+        <v>0.38</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1740,99 +1728,99 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>88.34</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>16.09</v>
+        <v>16.13</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B13" t="n">
-        <v>178.9</v>
+        <v>175.3</v>
       </c>
       <c r="C13" t="n">
-        <v>92.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>27.8</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="H13" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="I13" t="n">
         <v>10.8</v>
       </c>
       <c r="J13" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="K13" t="n">
-        <v>77.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>37.5</v>
+        <v>38.4</v>
       </c>
       <c r="O13" t="n">
-        <v>41.6</v>
+        <v>42</v>
       </c>
       <c r="Q13" t="n">
         <v>23</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="T13" t="n">
         <v>23</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="W13" t="n">
-        <v>16.5</v>
+        <v>17.1</v>
       </c>
       <c r="X13" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>-3.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>224.33</v>
+        <v>224.34</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.39</v>
+        <v>0.01</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1841,10 +1829,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>128.49</v>
+        <v>128.93</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1853,99 +1841,72 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>87.56999999999999</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>16.13</v>
+        <v>15.43</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B14" t="n">
-        <v>175.3</v>
+        <v>157.8</v>
       </c>
       <c r="C14" t="n">
-        <v>85.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="E14" t="n">
-        <v>27.8</v>
+        <v>30.3</v>
       </c>
       <c r="F14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H14" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>41.4</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M14" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD14" t="n">
         <v>3.6</v>
       </c>
-      <c r="N14" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>23</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="T14" t="n">
-        <v>23</v>
-      </c>
-      <c r="V14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF14" t="n">
-        <v>224.34</v>
+        <v>231.46</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.01</v>
+        <v>3.7</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1954,10 +1915,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>128.93</v>
+        <v>129.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1965,73 +1926,67 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
-      <c r="AP14" t="n">
-        <v>89.06999999999999</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>15.43</v>
-      </c>
       <c r="BL14" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B15" t="n">
-        <v>157.8</v>
+        <v>151.6</v>
       </c>
       <c r="C15" t="n">
-        <v>85.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="D15" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="E15" t="n">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="K15" t="n">
-        <v>98.7</v>
+        <v>97.5</v>
       </c>
       <c r="O15" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="V15" t="n">
-        <v>4.6</v>
+        <v>8.1</v>
       </c>
       <c r="W15" t="n">
-        <v>19.7</v>
+        <v>22.3</v>
       </c>
       <c r="X15" t="n">
-        <v>12.1</v>
+        <v>15.2</v>
       </c>
       <c r="Y15" t="n">
         <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.6</v>
+        <v>-0.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>231.46</v>
+        <v>229.92</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.7</v>
+        <v>-1.54</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2040,10 +1995,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>129.8</v>
+        <v>133.01</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.87</v>
+        <v>3.21</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2052,66 +2007,66 @@
         <v>142</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B16" t="n">
-        <v>151.6</v>
+        <v>157.5</v>
       </c>
       <c r="C16" t="n">
-        <v>73.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="E16" t="n">
-        <v>33.9</v>
+        <v>36.9</v>
       </c>
       <c r="F16" t="n">
         <v>7.4</v>
       </c>
       <c r="K16" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="O16" t="n">
-        <v>40.6</v>
+        <v>38</v>
       </c>
       <c r="V16" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="W16" t="n">
-        <v>22.3</v>
+        <v>20.8</v>
       </c>
       <c r="X16" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>-3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>229.92</v>
+        <v>226.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>-1.54</v>
+        <v>-2.97</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2120,10 +2075,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>133.01</v>
+        <v>128.4</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.21</v>
+        <v>-4.61</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2132,66 +2087,66 @@
         <v>142</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B17" t="n">
-        <v>157.5</v>
+        <v>148.5</v>
       </c>
       <c r="C17" t="n">
-        <v>76.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D17" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="E17" t="n">
-        <v>36.9</v>
+        <v>34.3</v>
       </c>
       <c r="F17" t="n">
         <v>7.4</v>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="O17" t="n">
-        <v>38</v>
+        <v>39.8</v>
       </c>
       <c r="V17" t="n">
-        <v>6.7</v>
+        <v>11.2</v>
       </c>
       <c r="W17" t="n">
-        <v>20.8</v>
+        <v>21.7</v>
       </c>
       <c r="X17" t="n">
-        <v>13.8</v>
+        <v>16.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.3</v>
+        <v>-1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.1</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>226.95</v>
+        <v>223.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>-2.97</v>
+        <v>-3.83</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2200,10 +2155,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>128.4</v>
+        <v>124.76</v>
       </c>
       <c r="AL17" t="n">
-        <v>-4.61</v>
+        <v>-3.64</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2212,66 +2167,60 @@
         <v>142</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B18" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="C18" t="n">
-        <v>70.5</v>
+        <v>72.8</v>
       </c>
       <c r="D18" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="E18" t="n">
-        <v>34.3</v>
+        <v>31.4</v>
       </c>
       <c r="F18" t="n">
         <v>7.4</v>
       </c>
       <c r="K18" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="O18" t="n">
-        <v>39.8</v>
+        <v>40.2</v>
       </c>
       <c r="V18" t="n">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="W18" t="n">
-        <v>21.7</v>
+        <v>16.8</v>
       </c>
       <c r="X18" t="n">
-        <v>16.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y18" t="n">
         <v>7</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB18" t="n">
-        <v>-1.9</v>
+        <v>0.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>223.11</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>-3.83</v>
+        <v>4.8</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2280,10 +2229,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>124.76</v>
+        <v>127.2</v>
       </c>
       <c r="AL18" t="n">
-        <v>-3.64</v>
+        <v>2.44</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2292,60 +2241,93 @@
         <v>142</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B19" t="n">
-        <v>147.5</v>
+        <v>183.5</v>
       </c>
       <c r="C19" t="n">
-        <v>72.8</v>
+        <v>84.5</v>
       </c>
       <c r="D19" t="n">
-        <v>26.7</v>
+        <v>31.5</v>
       </c>
       <c r="E19" t="n">
-        <v>31.4</v>
+        <v>34.6</v>
       </c>
       <c r="F19" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I19" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>41.5</v>
       </c>
       <c r="K19" t="n">
-        <v>100</v>
+        <v>76.3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>37.7</v>
       </c>
       <c r="O19" t="n">
-        <v>40.2</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>23</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>18</v>
+      </c>
+      <c r="T19" t="n">
+        <v>23</v>
       </c>
       <c r="V19" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="W19" t="n">
-        <v>16.8</v>
+        <v>20</v>
       </c>
       <c r="X19" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>220.36</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-3.75</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2354,10 +2336,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>127.2</v>
+        <v>127.13</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2365,94 +2347,100 @@
       <c r="AN19" t="n">
         <v>142</v>
       </c>
+      <c r="AP19" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL19" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B20" t="n">
-        <v>183.5</v>
+        <v>180.5</v>
       </c>
       <c r="C20" t="n">
-        <v>84.5</v>
+        <v>79.2</v>
       </c>
       <c r="D20" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="E20" t="n">
         <v>34.6</v>
       </c>
       <c r="F20" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="H20" t="n">
         <v>23.9</v>
       </c>
       <c r="I20" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="J20" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="K20" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
         <v>37.7</v>
       </c>
       <c r="O20" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="S20" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="T20" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V20" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W20" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="X20" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>220.36</v>
+        <v>219.64</v>
       </c>
       <c r="AG20" t="n">
-        <v>-3.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2461,10 +2449,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>127.13</v>
+        <v>126.03</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2473,99 +2461,99 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>76.90000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="AS20" t="n">
-        <v>14.17</v>
+        <v>14.55</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B21" t="n">
-        <v>180.5</v>
+        <v>168.1</v>
       </c>
       <c r="C21" t="n">
-        <v>79.2</v>
+        <v>69.7</v>
       </c>
       <c r="D21" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E21" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F21" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H21" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I21" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="J21" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="K21" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M21" t="n">
         <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O21" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S21" t="n">
         <v>17.6</v>
       </c>
       <c r="T21" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="V21" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W21" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="X21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA21" t="n">
         <v>14.9</v>
       </c>
-      <c r="Y21" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>11.9</v>
-      </c>
       <c r="AB21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>219.64</v>
+        <v>224.93</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.72</v>
+        <v>5.29</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2574,10 +2562,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>126.03</v>
+        <v>129.28</v>
       </c>
       <c r="AL21" t="n">
-        <v>-1.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2586,99 +2574,99 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>82.95</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>14.55</v>
+        <v>15.25</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B22" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C22" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D22" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E22" t="n">
         <v>30.4</v>
       </c>
-      <c r="E22" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H22" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I22" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J22" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O22" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S22" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T22" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="V22" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="W22" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X22" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y22" t="n">
         <v>17</v>
       </c>
-      <c r="Y22" t="n">
-        <v>11</v>
-      </c>
       <c r="Z22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="n">
-        <v>14.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG22" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2687,10 +2675,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL22" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2699,99 +2687,66 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B23" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C23" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D23" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H23" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I23" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K23" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N23" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>15</v>
-      </c>
-      <c r="T23" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
       </c>
       <c r="V23" t="n">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="W23" t="n">
-        <v>26</v>
+        <v>36.1</v>
       </c>
       <c r="X23" t="n">
-        <v>18.1</v>
+        <v>26.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA23" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC23" t="n">
         <v>6.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2800,10 +2755,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2811,67 +2766,61 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
-      <c r="AP23" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL23" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B24" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D24" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F24" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O24" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V24" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
       <c r="W24" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="X24" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2880,10 +2829,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL24" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2892,60 +2841,93 @@
         <v>142</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B25" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>67</v>
       </c>
       <c r="D25" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>31.5</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>41.1</v>
       </c>
       <c r="K25" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>35</v>
       </c>
       <c r="O25" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>20.5</v>
       </c>
       <c r="V25" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W25" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X25" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA25" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF25" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG25" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2954,10 +2936,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL25" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2965,94 +2947,100 @@
       <c r="AN25" t="n">
         <v>142</v>
       </c>
+      <c r="AP25" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL25" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B26" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C26" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E26" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I26" t="n">
         <v>11.4</v>
       </c>
       <c r="J26" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K26" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M26" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N26" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O26" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T26" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V26" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W26" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X26" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y26" t="n">
         <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA26" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG26" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3061,10 +3049,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL26" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3073,99 +3061,99 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B27" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C27" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D27" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E27" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F27" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H27" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I27" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K27" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N27" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O27" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V27" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W27" t="n">
+        <v>13</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA27" t="n">
         <v>11.4</v>
       </c>
-      <c r="J27" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>76</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N27" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>14</v>
-      </c>
-      <c r="T27" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB27" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF27" t="n">
         <v>220.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3174,10 +3162,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL27" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3186,99 +3174,99 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS27" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B28" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C28" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E28" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F28" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H28" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I28" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J28" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K28" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O28" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W28" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD28" t="n">
         <v>0.5</v>
       </c>
-      <c r="S28" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T28" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V28" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W28" t="n">
-        <v>13</v>
-      </c>
-      <c r="X28" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF28" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3287,10 +3275,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL28" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3299,99 +3287,99 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B29" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C29" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D29" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E29" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F29" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H29" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I29" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J29" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K29" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N29" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O29" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T29" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V29" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W29" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X29" t="n">
         <v>12.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z29" t="n">
         <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF29" t="n">
         <v>216.02</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3400,10 +3388,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL29" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3412,99 +3400,66 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS29" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B30" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C30" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D30" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E30" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F30" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H30" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I30" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K30" t="n">
-        <v>75</v>
-      </c>
-      <c r="M30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N30" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V30" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W30" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X30" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA30" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF30" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3513,10 +3468,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3524,67 +3479,61 @@
       <c r="AN30" t="n">
         <v>142</v>
       </c>
-      <c r="AP30" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL30" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B31" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D31" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F31" t="n">
         <v>6.8</v>
       </c>
       <c r="K31" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O31" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V31" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W31" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA31" t="n">
         <v>13.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF31" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3593,10 +3542,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3605,60 +3554,93 @@
         <v>142</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B32" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E32" t="n">
+        <v>25.9</v>
       </c>
       <c r="F32" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>24</v>
+      </c>
+      <c r="I32" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>38.8</v>
       </c>
       <c r="K32" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>36.7</v>
       </c>
       <c r="O32" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>7</v>
+      </c>
+      <c r="T32" t="n">
+        <v>21.7</v>
       </c>
       <c r="V32" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W32" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X32" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z32" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA32" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3667,10 +3649,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3678,94 +3660,67 @@
       <c r="AN32" t="n">
         <v>142</v>
       </c>
+      <c r="AP32" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL32" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B33" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C33" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D33" t="n">
-        <v>29</v>
-      </c>
-      <c r="E33" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H33" t="n">
-        <v>24</v>
-      </c>
-      <c r="I33" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J33" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K33" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N33" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O33" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" t="n">
-        <v>7</v>
-      </c>
-      <c r="T33" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V33" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W33" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X33" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA33" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB33" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF33" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG33" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3774,10 +3729,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3785,67 +3740,94 @@
       <c r="AN33" t="n">
         <v>142</v>
       </c>
-      <c r="AP33" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL33" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B34" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>63.7</v>
       </c>
       <c r="D34" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>36.4</v>
       </c>
       <c r="F34" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H34" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I34" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>39.9</v>
       </c>
       <c r="K34" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>35.9</v>
       </c>
       <c r="O34" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>20.3</v>
       </c>
       <c r="V34" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W34" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X34" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z34" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA34" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG34" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3854,10 +3836,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3865,94 +3847,100 @@
       <c r="AN34" t="n">
         <v>142</v>
       </c>
+      <c r="AP34" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL34" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B35" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C35" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E35" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F35" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H35" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I35" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J35" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K35" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N35" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O35" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R35" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T35" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V35" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W35" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X35" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA35" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF35" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3961,10 +3949,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL35" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3973,99 +3961,99 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B36" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C36" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D36" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E36" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F36" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H36" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I36" t="n">
         <v>11.3</v>
       </c>
       <c r="J36" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K36" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N36" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O36" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V36" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W36" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X36" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z36" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA36" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG36" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4074,10 +4062,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL36" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4086,99 +4074,66 @@
         <v>142</v>
       </c>
       <c r="AP36" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS36" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B37" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C37" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D37" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H37" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I37" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J37" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K37" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N37" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O37" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>9</v>
-      </c>
-      <c r="T37" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V37" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W37" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X37" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y37" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z37" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB37" t="n">
         <v>-0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4187,10 +4142,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4198,67 +4153,61 @@
       <c r="AN37" t="n">
         <v>142</v>
       </c>
-      <c r="AP37" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL37" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B38" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F38" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K38" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O38" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V38" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W38" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X38" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y38" t="n">
         <v>14</v>
       </c>
       <c r="Z38" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA38" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF38" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4267,10 +4216,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL38" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4279,60 +4228,93 @@
         <v>142</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B39" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>56.3</v>
       </c>
       <c r="D39" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>21.2</v>
       </c>
       <c r="F39" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I39" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>40.4</v>
       </c>
       <c r="K39" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N39" t="n">
+        <v>29</v>
       </c>
       <c r="O39" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>21.6</v>
       </c>
       <c r="V39" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W39" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X39" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z39" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA39" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF39" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG39" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4341,10 +4323,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL39" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4352,52 +4334,58 @@
       <c r="AN39" t="n">
         <v>142</v>
       </c>
+      <c r="AP39" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL39" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B40" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C40" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D40" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F40" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H40" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I40" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J40" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K40" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O40" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R40" t="n">
         <v>1.3</v>
@@ -4406,40 +4394,40 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V40" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W40" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X40" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA40" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG40" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4448,10 +4436,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4460,99 +4448,99 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS40" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B41" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C41" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D41" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E41" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F41" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H41" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I41" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J41" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K41" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O41" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V41" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W41" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X41" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y41" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z41" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA41" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF41" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG41" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4561,10 +4549,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL41" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4573,99 +4561,99 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS41" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B42" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C42" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D42" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E42" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F42" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H42" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I42" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J42" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K42" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N42" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O42" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q42" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T42" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V42" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W42" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X42" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA42" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF42" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG42" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4674,10 +4662,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL42" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4686,99 +4674,99 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS42" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B43" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C43" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E43" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F43" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H43" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I43" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J43" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K43" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M43" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N43" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O43" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R43" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T43" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V43" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W43" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X43" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y43" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z43" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA43" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF43" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG43" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4787,10 +4775,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4799,99 +4787,60 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS43" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B44" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C44" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D44" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E44" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F44" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H44" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J44" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K44" t="n">
-        <v>77</v>
-      </c>
-      <c r="M44" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N44" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O44" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>21</v>
-      </c>
-      <c r="R44" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S44" t="n">
-        <v>6</v>
-      </c>
-      <c r="T44" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V44" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W44" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X44" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y44" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA44" t="n">
         <v>9</v>
       </c>
-      <c r="Z44" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB44" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF44" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG44" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4900,10 +4849,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL44" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4911,61 +4860,61 @@
       <c r="AN44" t="n">
         <v>142</v>
       </c>
-      <c r="AP44" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL44" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B45" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D45" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F45" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O45" t="n">
+        <v>35.5</v>
       </c>
       <c r="V45" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W45" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X45" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z45" t="n">
         <v>13</v>
       </c>
       <c r="AA45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB45" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD45" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4974,10 +4923,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4986,60 +4935,60 @@
         <v>142</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B46" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D46" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K46" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O46" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V46" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W46" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X46" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z46" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB46" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD46" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF46" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG46" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5048,10 +4997,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5060,60 +5009,93 @@
         <v>142</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B47" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C47" t="n">
+        <v>86.8</v>
       </c>
       <c r="D47" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E47" t="n">
+        <v>33</v>
       </c>
       <c r="F47" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H47" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J47" t="n">
+        <v>41.1</v>
       </c>
       <c r="K47" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N47" t="n">
+        <v>33.5</v>
       </c>
       <c r="O47" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="n">
+        <v>22.4</v>
       </c>
       <c r="V47" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W47" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X47" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z47" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA47" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF47" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5122,10 +5104,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL47" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5133,94 +5115,100 @@
       <c r="AN47" t="n">
         <v>142</v>
       </c>
+      <c r="AP47" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL47" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B48" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C48" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D48" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E48" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F48" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H48" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I48" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J48" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K48" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M48" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O48" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R48" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T48" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V48" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W48" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X48" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z48" t="n">
         <v>12</v>
       </c>
       <c r="AA48" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB48" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF48" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG48" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5229,10 +5217,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL48" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5241,99 +5229,99 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS48" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B49" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C49" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D49" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E49" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F49" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H49" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I49" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J49" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K49" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O49" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R49" t="n">
         <v>1.8</v>
       </c>
       <c r="S49" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T49" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V49" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W49" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X49" t="n">
         <v>10.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA49" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB49" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD49" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD49" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF49" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG49" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5342,10 +5330,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL49" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5354,99 +5342,66 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS49" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B50" t="n">
-        <v>183</v>
-      </c>
-      <c r="C50" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D50" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E50" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
-      </c>
-      <c r="H50" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I50" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J50" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K50" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M50" t="n">
-        <v>4</v>
-      </c>
-      <c r="N50" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O50" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S50" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T50" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V50" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W50" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X50" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y50" t="n">
         <v>8</v>
       </c>
       <c r="Z50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA50" t="n">
         <v>10</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF50" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5455,10 +5410,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL50" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5466,67 +5421,61 @@
       <c r="AN50" t="n">
         <v>142</v>
       </c>
-      <c r="AP50" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL50" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B51" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D51" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F51" t="n">
         <v>6.5</v>
       </c>
       <c r="K51" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O51" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V51" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W51" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X51" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA51" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF51" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG51" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5535,10 +5484,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL51" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5547,60 +5496,60 @@
         <v>142</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B52" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D52" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F52" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K52" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O52" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V52" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W52" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X52" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z52" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA52" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC52" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5608,12 +5557,6 @@
       <c r="AI52" t="n">
         <v>235</v>
       </c>
-      <c r="AK52" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM52" t="n">
         <v>110</v>
       </c>
@@ -5621,60 +5564,54 @@
         <v>142</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B53" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D53" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F53" t="n">
         <v>5.5</v>
       </c>
       <c r="K53" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O53" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V53" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W53" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X53" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y53" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z53" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA53" t="n">
         <v>15</v>
       </c>
-      <c r="AA53" t="n">
-        <v>14</v>
-      </c>
       <c r="AB53" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC53" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5689,54 +5626,93 @@
         <v>142</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B54" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C54" t="n">
+        <v>71.8</v>
       </c>
       <c r="D54" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E54" t="n">
+        <v>24.7</v>
       </c>
       <c r="F54" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H54" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J54" t="n">
+        <v>41.1</v>
       </c>
       <c r="K54" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M54" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N54" t="n">
+        <v>33.5</v>
       </c>
       <c r="O54" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>23.2</v>
       </c>
       <c r="V54" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W54" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X54" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y54" t="n">
         <v>12</v>
       </c>
       <c r="Z54" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA54" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD54" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5744,100 +5720,112 @@
       <c r="AI54" t="n">
         <v>235</v>
       </c>
+      <c r="AK54" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
       <c r="AN54" t="n">
         <v>142</v>
       </c>
+      <c r="AP54" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL54" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B55" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C55" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D55" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E55" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H55" t="n">
         <v>24.1</v>
       </c>
       <c r="I55" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J55" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K55" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N55" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O55" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R55" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T55" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V55" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W55" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X55" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z55" t="n">
         <v>13</v>
       </c>
-      <c r="X55" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>14</v>
-      </c>
       <c r="AA55" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC55" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF55" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5846,10 +5834,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL55" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5858,81 +5846,81 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS55" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B56" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C56" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D56" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E56" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F56" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H56" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I56" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K56" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O56" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R56" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S56" t="n">
         <v>7</v>
       </c>
       <c r="T56" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="Y56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA56" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AF56" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG56" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5941,10 +5929,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5953,81 +5941,81 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS56" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B57" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C57" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D57" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E57" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F57" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H57" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I57" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J57" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K57" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M57" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N57" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O57" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q57" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R57" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T57" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Y57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z57" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA57" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AF57" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6036,10 +6024,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL57" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6048,81 +6036,42 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS57" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B58" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C58" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D58" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E58" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F58" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H58" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I58" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J58" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K58" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M58" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N58" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="O58" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R58" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S58" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T58" t="n">
-        <v>23.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z58" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA58" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AF58" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6130,55 +6079,43 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
-      <c r="AK58" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
-      <c r="AP58" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL58" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B59" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D59" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F59" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z59" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA59" t="n">
         <v>9</v>
       </c>
       <c r="AF59" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG59" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6193,36 +6130,75 @@
         <v>142</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B60" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C60" t="n">
+        <v>73.7</v>
       </c>
       <c r="D60" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E60" t="n">
+        <v>28.2</v>
       </c>
       <c r="F60" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H60" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J60" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M60" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N60" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="O60" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S60" t="n">
+        <v>6</v>
+      </c>
+      <c r="T60" t="n">
+        <v>23.5</v>
       </c>
       <c r="Y60" t="n">
         <v>4</v>
       </c>
       <c r="Z60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA60" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AF60" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6230,43 +6206,55 @@
       <c r="AI60" t="n">
         <v>235</v>
       </c>
+      <c r="AK60" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM60" t="n">
         <v>110</v>
       </c>
       <c r="AN60" t="n">
         <v>142</v>
       </c>
+      <c r="AP60" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL60" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B61" t="n">
-        <v>142.3</v>
+        <v>153.9</v>
       </c>
       <c r="D61" t="n">
-        <v>30.9</v>
+        <v>33</v>
       </c>
       <c r="F61" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="Y61" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z61" t="n">
         <v>13</v>
       </c>
       <c r="AA61" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AF61" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG61" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6281,30 +6269,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B62" t="n">
-        <v>153.9</v>
+        <v>144.5</v>
       </c>
       <c r="D62" t="n">
-        <v>33</v>
+        <v>32.3</v>
       </c>
       <c r="F62" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="Y62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6319,7 +6307,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,61 +628,61 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B2" t="n">
-        <v>155.4</v>
+        <v>151.1</v>
       </c>
       <c r="C2" t="n">
-        <v>82.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>27.4</v>
+        <v>26.8</v>
       </c>
       <c r="E2" t="n">
-        <v>29.1</v>
+        <v>30.9</v>
       </c>
       <c r="F2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>98.2</v>
+        <v>97.7</v>
       </c>
       <c r="O2" t="n">
-        <v>40.1</v>
+        <v>40.8</v>
       </c>
       <c r="V2" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="W2" t="n">
         <v>18.8</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>-0</v>
       </c>
       <c r="AC2" t="n">
         <v>6.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>226.39</v>
+        <v>229.98</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.4</v>
+        <v>3.58</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -691,10 +691,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>129.78</v>
+        <v>132.56</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.68</v>
+        <v>2.78</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -703,66 +703,93 @@
         <v>142</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="B3" t="n">
-        <v>151.1</v>
+        <v>167.2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>26.8</v>
+        <v>27.6</v>
       </c>
       <c r="E3" t="n">
-        <v>30.9</v>
+        <v>28.2</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>7.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40.3</v>
       </c>
       <c r="K3" t="n">
-        <v>97.7</v>
+        <v>75</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>37.2</v>
       </c>
       <c r="O3" t="n">
-        <v>40.8</v>
+        <v>39.9</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>22</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>19</v>
+      </c>
+      <c r="T3" t="n">
+        <v>22</v>
       </c>
       <c r="V3" t="n">
-        <v>6.3</v>
+        <v>9.4</v>
       </c>
       <c r="W3" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="X3" t="n">
-        <v>12.6</v>
+        <v>14.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>229.98</v>
+        <v>236.38</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.58</v>
+        <v>6.4</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -771,10 +798,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>132.56</v>
+        <v>132.97</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.78</v>
+        <v>0.41</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -782,94 +809,100 @@
       <c r="AN3" t="n">
         <v>142</v>
       </c>
+      <c r="AP3" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>16.05</v>
+      </c>
       <c r="BL3" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="B4" t="n">
-        <v>167.2</v>
+        <v>176.7</v>
       </c>
       <c r="C4" t="n">
-        <v>74.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="D4" t="n">
-        <v>27.6</v>
+        <v>28.3</v>
       </c>
       <c r="E4" t="n">
-        <v>28.2</v>
+        <v>31.6</v>
       </c>
       <c r="F4" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="H4" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="I4" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="J4" t="n">
-        <v>40.3</v>
+        <v>41.8</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>37.2</v>
+        <v>38.4</v>
       </c>
       <c r="O4" t="n">
-        <v>39.9</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="T4" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="V4" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
-        <v>19.1</v>
+        <v>14.8</v>
       </c>
       <c r="X4" t="n">
-        <v>14.2</v>
+        <v>10.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>236.38</v>
+        <v>236.23</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -878,10 +911,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>132.97</v>
+        <v>132.79</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.41</v>
+        <v>-0.18</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -890,99 +923,99 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>90.8</v>
+        <v>89.64</v>
       </c>
       <c r="AS4" t="n">
-        <v>16.05</v>
+        <v>15.89</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B5" t="n">
-        <v>176.7</v>
+        <v>175.3</v>
       </c>
       <c r="C5" t="n">
-        <v>80.8</v>
+        <v>83.5</v>
       </c>
       <c r="D5" t="n">
-        <v>28.3</v>
+        <v>27.8</v>
       </c>
       <c r="E5" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="F5" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H5" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="I5" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="J5" t="n">
-        <v>41.8</v>
+        <v>42.9</v>
       </c>
       <c r="K5" t="n">
-        <v>76.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="N5" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="O5" t="n">
         <v>41</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="T5" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W5" t="n">
         <v>14.8</v>
       </c>
       <c r="X5" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z5" t="n">
         <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.6</v>
+        <v>-7.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>236.23</v>
+        <v>236.72</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.15</v>
+        <v>0.49</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -991,10 +1024,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>132.79</v>
+        <v>134.11</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.18</v>
+        <v>1.32</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1003,99 +1036,99 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>89.64</v>
+        <v>88.87</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.89</v>
+        <v>15.71</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B6" t="n">
-        <v>175.3</v>
+        <v>181.9</v>
       </c>
       <c r="C6" t="n">
-        <v>83.5</v>
+        <v>88.7</v>
       </c>
       <c r="D6" t="n">
-        <v>27.8</v>
+        <v>27.2</v>
       </c>
       <c r="E6" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="F6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>24.7</v>
+        <v>23.2</v>
       </c>
       <c r="I6" t="n">
-        <v>10.4</v>
+        <v>11.2</v>
       </c>
       <c r="J6" t="n">
-        <v>42.9</v>
+        <v>42.3</v>
       </c>
       <c r="K6" t="n">
-        <v>77.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="O6" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T6" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="W6" t="n">
-        <v>14.8</v>
+        <v>13.1</v>
       </c>
       <c r="X6" t="n">
-        <v>11.8</v>
+        <v>10.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>-7.7</v>
+        <v>-12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>-0.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.9</v>
+        <v>-6.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>236.72</v>
+        <v>229.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.49</v>
+        <v>-6.8</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1104,10 +1137,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>134.11</v>
+        <v>133.43</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.32</v>
+        <v>-0.68</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1116,99 +1149,99 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>88.87</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.71</v>
+        <v>15.36</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B7" t="n">
-        <v>181.9</v>
+        <v>188.8</v>
       </c>
       <c r="C7" t="n">
-        <v>88.7</v>
+        <v>94.8</v>
       </c>
       <c r="D7" t="n">
-        <v>27.2</v>
+        <v>27.9</v>
       </c>
       <c r="E7" t="n">
-        <v>30.5</v>
+        <v>32.4</v>
       </c>
       <c r="F7" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="H7" t="n">
-        <v>23.2</v>
+        <v>24.4</v>
       </c>
       <c r="I7" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="J7" t="n">
-        <v>42.3</v>
+        <v>40.8</v>
       </c>
       <c r="K7" t="n">
-        <v>76.7</v>
+        <v>75.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N7" t="n">
-        <v>38</v>
+        <v>36.5</v>
       </c>
       <c r="O7" t="n">
-        <v>41.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="S7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T7" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="V7" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W7" t="n">
-        <v>13.1</v>
+        <v>10</v>
       </c>
       <c r="X7" t="n">
-        <v>10.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.699999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>-12.5</v>
+        <v>-9.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.6</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>-6.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>229.92</v>
+        <v>223</v>
       </c>
       <c r="AG7" t="n">
-        <v>-6.8</v>
+        <v>-6.92</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1217,10 +1250,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>133.43</v>
+        <v>128.87</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.68</v>
+        <v>-4.56</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1229,99 +1262,72 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>85.26000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.36</v>
+        <v>14.68</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B8" t="n">
-        <v>188.8</v>
+        <v>166.3</v>
       </c>
       <c r="C8" t="n">
-        <v>94.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>27.9</v>
+        <v>26.1</v>
       </c>
       <c r="E8" t="n">
-        <v>32.4</v>
+        <v>30.6</v>
       </c>
       <c r="F8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>40.8</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>36.5</v>
+        <v>98.8</v>
       </c>
       <c r="O8" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R8" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="X8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.9</v>
       </c>
-      <c r="S8" t="n">
-        <v>20</v>
-      </c>
-      <c r="T8" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>10</v>
-      </c>
-      <c r="X8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AD8" t="n">
-        <v>-3.3</v>
+        <v>-2.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>223</v>
+        <v>221.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>-6.92</v>
+        <v>-1.92</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1330,10 +1336,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>128.87</v>
+        <v>125.07</v>
       </c>
       <c r="AL8" t="n">
-        <v>-4.56</v>
+        <v>-3.8</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1341,73 +1347,67 @@
       <c r="AN8" t="n">
         <v>142</v>
       </c>
-      <c r="AP8" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>14.68</v>
-      </c>
       <c r="BL8" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B9" t="n">
-        <v>166.3</v>
+        <v>154.6</v>
       </c>
       <c r="C9" t="n">
-        <v>94.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="D9" t="n">
-        <v>26.1</v>
+        <v>25.2</v>
       </c>
       <c r="E9" t="n">
-        <v>30.6</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>98.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="V9" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="W9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X9" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>-7.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>-2.8</v>
+        <v>-1.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>221.08</v>
+        <v>221.24</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.92</v>
+        <v>0.16</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1416,10 +1416,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>125.07</v>
+        <v>125.99</v>
       </c>
       <c r="AL9" t="n">
-        <v>-3.8</v>
+        <v>0.92</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1428,66 +1428,93 @@
         <v>142</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B10" t="n">
-        <v>154.6</v>
+        <v>175.7</v>
       </c>
       <c r="C10" t="n">
-        <v>89</v>
+        <v>91.2</v>
       </c>
       <c r="D10" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>26.9</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>6.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>42.1</v>
       </c>
       <c r="K10" t="n">
-        <v>98.09999999999999</v>
+        <v>77.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>37.2</v>
       </c>
       <c r="O10" t="n">
-        <v>39.5</v>
+        <v>42.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>22.7</v>
       </c>
       <c r="V10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="W10" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="X10" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6.4</v>
+        <v>-5.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>221.24</v>
+        <v>223.94</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.16</v>
+        <v>2.7</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1496,10 +1523,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>125.99</v>
+        <v>128.11</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.92</v>
+        <v>2.12</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1507,94 +1534,100 @@
       <c r="AN10" t="n">
         <v>142</v>
       </c>
+      <c r="AP10" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>16.09</v>
+      </c>
       <c r="BL10" s="1" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B11" t="n">
-        <v>175.7</v>
+        <v>178.9</v>
       </c>
       <c r="C11" t="n">
-        <v>91.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D11" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E11" t="n">
         <v>24</v>
       </c>
-      <c r="E11" t="n">
-        <v>26.9</v>
-      </c>
       <c r="F11" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H11" t="n">
-        <v>24.3</v>
+        <v>25</v>
       </c>
       <c r="I11" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="J11" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="K11" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>37.2</v>
+        <v>37.5</v>
       </c>
       <c r="O11" t="n">
-        <v>42.3</v>
+        <v>41.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="T11" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="V11" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="W11" t="n">
-        <v>10.8</v>
+        <v>16.5</v>
       </c>
       <c r="X11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Y11" t="n">
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>-5.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>223.94</v>
+        <v>224.33</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.7</v>
+        <v>0.39</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1603,10 +1636,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>128.11</v>
+        <v>128.49</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.12</v>
+        <v>0.38</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1615,99 +1648,99 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>88.34</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>16.09</v>
+        <v>16.13</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B12" t="n">
-        <v>178.9</v>
+        <v>175.3</v>
       </c>
       <c r="C12" t="n">
-        <v>92.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>27.8</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="H12" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="I12" t="n">
         <v>10.8</v>
       </c>
       <c r="J12" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="K12" t="n">
-        <v>77.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>37.5</v>
+        <v>38.4</v>
       </c>
       <c r="O12" t="n">
-        <v>41.6</v>
+        <v>42</v>
       </c>
       <c r="Q12" t="n">
         <v>23</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="T12" t="n">
         <v>23</v>
       </c>
       <c r="V12" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="W12" t="n">
-        <v>16.5</v>
+        <v>17.1</v>
       </c>
       <c r="X12" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>-3.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>224.33</v>
+        <v>224.34</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.39</v>
+        <v>0.01</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1716,10 +1749,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>128.49</v>
+        <v>128.93</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1728,99 +1761,72 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>87.56999999999999</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>16.13</v>
+        <v>15.43</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B13" t="n">
-        <v>175.3</v>
+        <v>157.8</v>
       </c>
       <c r="C13" t="n">
-        <v>85.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="E13" t="n">
-        <v>27.8</v>
+        <v>30.3</v>
       </c>
       <c r="F13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>41.4</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M13" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X13" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD13" t="n">
         <v>3.6</v>
       </c>
-      <c r="N13" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="O13" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>23</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S13" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="T13" t="n">
-        <v>23</v>
-      </c>
-      <c r="V13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF13" t="n">
-        <v>224.34</v>
+        <v>231.46</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01</v>
+        <v>3.7</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1829,10 +1835,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>128.93</v>
+        <v>129.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1840,73 +1846,67 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
-      <c r="AP13" t="n">
-        <v>89.06999999999999</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>15.43</v>
-      </c>
       <c r="BL13" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B14" t="n">
-        <v>157.8</v>
+        <v>151.6</v>
       </c>
       <c r="C14" t="n">
-        <v>85.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="D14" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="K14" t="n">
-        <v>98.7</v>
+        <v>97.5</v>
       </c>
       <c r="O14" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="V14" t="n">
-        <v>4.6</v>
+        <v>8.1</v>
       </c>
       <c r="W14" t="n">
-        <v>19.7</v>
+        <v>22.3</v>
       </c>
       <c r="X14" t="n">
-        <v>12.1</v>
+        <v>15.2</v>
       </c>
       <c r="Y14" t="n">
         <v>8</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA14" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.6</v>
+        <v>-0.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>231.46</v>
+        <v>229.92</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.7</v>
+        <v>-1.54</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1915,10 +1915,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>129.8</v>
+        <v>133.01</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.87</v>
+        <v>3.21</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1927,66 +1927,66 @@
         <v>142</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B15" t="n">
-        <v>151.6</v>
+        <v>157.5</v>
       </c>
       <c r="C15" t="n">
-        <v>73.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="E15" t="n">
-        <v>33.9</v>
+        <v>36.9</v>
       </c>
       <c r="F15" t="n">
         <v>7.4</v>
       </c>
       <c r="K15" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="O15" t="n">
-        <v>40.6</v>
+        <v>38</v>
       </c>
       <c r="V15" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="W15" t="n">
-        <v>22.3</v>
+        <v>20.8</v>
       </c>
       <c r="X15" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>-3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>229.92</v>
+        <v>226.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>-1.54</v>
+        <v>-2.97</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1995,10 +1995,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>133.01</v>
+        <v>128.4</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.21</v>
+        <v>-4.61</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2007,66 +2007,66 @@
         <v>142</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B16" t="n">
-        <v>157.5</v>
+        <v>148.5</v>
       </c>
       <c r="C16" t="n">
-        <v>76.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D16" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="E16" t="n">
-        <v>36.9</v>
+        <v>34.3</v>
       </c>
       <c r="F16" t="n">
         <v>7.4</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="O16" t="n">
-        <v>38</v>
+        <v>39.8</v>
       </c>
       <c r="V16" t="n">
-        <v>6.7</v>
+        <v>11.2</v>
       </c>
       <c r="W16" t="n">
-        <v>20.8</v>
+        <v>21.7</v>
       </c>
       <c r="X16" t="n">
-        <v>13.8</v>
+        <v>16.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AB16" t="n">
-        <v>-2.3</v>
+        <v>-1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.1</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>226.95</v>
+        <v>223.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>-2.97</v>
+        <v>-3.83</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2075,10 +2075,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>128.4</v>
+        <v>124.76</v>
       </c>
       <c r="AL16" t="n">
-        <v>-4.61</v>
+        <v>-3.64</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2087,66 +2087,60 @@
         <v>142</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B17" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="C17" t="n">
-        <v>70.5</v>
+        <v>72.8</v>
       </c>
       <c r="D17" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="E17" t="n">
-        <v>34.3</v>
+        <v>31.4</v>
       </c>
       <c r="F17" t="n">
         <v>7.4</v>
       </c>
       <c r="K17" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="O17" t="n">
-        <v>39.8</v>
+        <v>40.2</v>
       </c>
       <c r="V17" t="n">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="W17" t="n">
-        <v>21.7</v>
+        <v>16.8</v>
       </c>
       <c r="X17" t="n">
-        <v>16.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y17" t="n">
         <v>7</v>
       </c>
       <c r="Z17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB17" t="n">
-        <v>-1.9</v>
+        <v>0.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>223.11</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-3.83</v>
+        <v>4.8</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2155,10 +2149,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>124.76</v>
+        <v>127.2</v>
       </c>
       <c r="AL17" t="n">
-        <v>-3.64</v>
+        <v>2.44</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2167,60 +2161,93 @@
         <v>142</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B18" t="n">
-        <v>147.5</v>
+        <v>183.5</v>
       </c>
       <c r="C18" t="n">
-        <v>72.8</v>
+        <v>84.5</v>
       </c>
       <c r="D18" t="n">
-        <v>26.7</v>
+        <v>31.5</v>
       </c>
       <c r="E18" t="n">
-        <v>31.4</v>
+        <v>34.6</v>
       </c>
       <c r="F18" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>41.5</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>76.3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>37.7</v>
       </c>
       <c r="O18" t="n">
-        <v>40.2</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>23</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S18" t="n">
+        <v>18</v>
+      </c>
+      <c r="T18" t="n">
+        <v>23</v>
       </c>
       <c r="V18" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="W18" t="n">
-        <v>16.8</v>
+        <v>20</v>
       </c>
       <c r="X18" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA18" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>220.36</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-3.75</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2229,10 +2256,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>127.2</v>
+        <v>127.13</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2240,94 +2267,100 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
+      <c r="AP18" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL18" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B19" t="n">
-        <v>183.5</v>
+        <v>180.5</v>
       </c>
       <c r="C19" t="n">
-        <v>84.5</v>
+        <v>79.2</v>
       </c>
       <c r="D19" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="E19" t="n">
         <v>34.6</v>
       </c>
       <c r="F19" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="H19" t="n">
         <v>23.9</v>
       </c>
       <c r="I19" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="J19" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="K19" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
         <v>37.7</v>
       </c>
       <c r="O19" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="S19" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="T19" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V19" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W19" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="X19" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>220.36</v>
+        <v>219.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>-3.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2336,10 +2369,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>127.13</v>
+        <v>126.03</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2348,99 +2381,99 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>76.90000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="AS19" t="n">
-        <v>14.17</v>
+        <v>14.55</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B20" t="n">
-        <v>180.5</v>
+        <v>168.1</v>
       </c>
       <c r="C20" t="n">
-        <v>79.2</v>
+        <v>69.7</v>
       </c>
       <c r="D20" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E20" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F20" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H20" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I20" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="J20" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="K20" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O20" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S20" t="n">
         <v>17.6</v>
       </c>
       <c r="T20" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="V20" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W20" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA20" t="n">
         <v>14.9</v>
       </c>
-      <c r="Y20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>11.9</v>
-      </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>219.64</v>
+        <v>224.93</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.72</v>
+        <v>5.29</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2449,10 +2482,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>126.03</v>
+        <v>129.28</v>
       </c>
       <c r="AL20" t="n">
-        <v>-1.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2461,99 +2494,99 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>82.95</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS20" t="n">
-        <v>14.55</v>
+        <v>15.25</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B21" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C21" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D21" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E21" t="n">
         <v>30.4</v>
       </c>
-      <c r="E21" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H21" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I21" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J21" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K21" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O21" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S21" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T21" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="V21" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="W21" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X21" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y21" t="n">
         <v>17</v>
       </c>
-      <c r="Y21" t="n">
-        <v>11</v>
-      </c>
       <c r="Z21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="n">
-        <v>14.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG21" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2562,10 +2595,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2574,99 +2607,66 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B22" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C22" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D22" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H22" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I22" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K22" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N22" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>15</v>
-      </c>
-      <c r="T22" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
       </c>
       <c r="V22" t="n">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="W22" t="n">
-        <v>26</v>
+        <v>36.1</v>
       </c>
       <c r="X22" t="n">
-        <v>18.1</v>
+        <v>26.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC22" t="n">
         <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2675,10 +2675,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2686,67 +2686,61 @@
       <c r="AN22" t="n">
         <v>142</v>
       </c>
-      <c r="AP22" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL22" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B23" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D23" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F23" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O23" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V23" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
       <c r="W23" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="X23" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z23" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2755,10 +2749,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL23" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2767,60 +2761,93 @@
         <v>142</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B24" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>67</v>
       </c>
       <c r="D24" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>31.5</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>41.1</v>
       </c>
       <c r="K24" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>35</v>
       </c>
       <c r="O24" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>20.5</v>
       </c>
       <c r="V24" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W24" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X24" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2829,10 +2856,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL24" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2840,94 +2867,100 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
+      <c r="AP24" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL24" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B25" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C25" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E25" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F25" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I25" t="n">
         <v>11.4</v>
       </c>
       <c r="J25" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K25" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M25" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O25" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T25" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V25" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W25" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X25" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y25" t="n">
         <v>9</v>
       </c>
       <c r="Z25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA25" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF25" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG25" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2936,10 +2969,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2948,99 +2981,99 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS25" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B26" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C26" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D26" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E26" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F26" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H26" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I26" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N26" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O26" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>13</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA26" t="n">
         <v>11.4</v>
       </c>
-      <c r="J26" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>76</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O26" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>14</v>
-      </c>
-      <c r="T26" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB26" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF26" t="n">
         <v>220.92</v>
       </c>
       <c r="AG26" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3049,10 +3082,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL26" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3061,99 +3094,99 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B27" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C27" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E27" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F27" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I27" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J27" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K27" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N27" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O27" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W27" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD27" t="n">
         <v>0.5</v>
       </c>
-      <c r="S27" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V27" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>13</v>
-      </c>
-      <c r="X27" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF27" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3162,10 +3195,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL27" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3174,99 +3207,99 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B28" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C28" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D28" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E28" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F28" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H28" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I28" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J28" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K28" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N28" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O28" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S28" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T28" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V28" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W28" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X28" t="n">
         <v>12.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z28" t="n">
         <v>13</v>
       </c>
       <c r="AA28" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF28" t="n">
         <v>216.02</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3275,10 +3308,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL28" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3287,99 +3320,66 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS28" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B29" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C29" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D29" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E29" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F29" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I29" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K29" t="n">
-        <v>75</v>
-      </c>
-      <c r="M29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N29" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V29" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W29" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X29" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA29" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3388,10 +3388,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3399,67 +3399,61 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
-      <c r="AP29" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL29" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B30" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D30" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F30" t="n">
         <v>6.8</v>
       </c>
       <c r="K30" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O30" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V30" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W30" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X30" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA30" t="n">
         <v>13.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF30" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3468,10 +3462,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3480,60 +3474,93 @@
         <v>142</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B31" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>60</v>
       </c>
       <c r="D31" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E31" t="n">
+        <v>25.9</v>
       </c>
       <c r="F31" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>24</v>
+      </c>
+      <c r="I31" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>38.8</v>
       </c>
       <c r="K31" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>36.7</v>
       </c>
       <c r="O31" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>21.7</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W31" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X31" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z31" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF31" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3542,10 +3569,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3553,94 +3580,67 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
+      <c r="AP31" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL31" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B32" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C32" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
-      </c>
-      <c r="E32" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H32" t="n">
-        <v>24</v>
-      </c>
-      <c r="I32" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J32" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K32" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N32" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O32" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>7</v>
-      </c>
-      <c r="T32" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V32" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W32" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X32" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA32" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB32" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF32" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG32" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3649,10 +3649,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3660,67 +3660,94 @@
       <c r="AN32" t="n">
         <v>142</v>
       </c>
-      <c r="AP32" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL32" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B33" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>63.7</v>
       </c>
       <c r="D33" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>36.4</v>
       </c>
       <c r="F33" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>39.9</v>
       </c>
       <c r="K33" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>35.9</v>
       </c>
       <c r="O33" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="n">
+        <v>20.3</v>
       </c>
       <c r="V33" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W33" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X33" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA33" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG33" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3729,10 +3756,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3740,94 +3767,100 @@
       <c r="AN33" t="n">
         <v>142</v>
       </c>
+      <c r="AP33" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL33" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B34" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C34" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E34" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F34" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H34" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I34" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J34" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K34" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N34" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O34" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R34" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T34" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V34" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W34" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X34" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3836,10 +3869,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL34" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3848,99 +3881,99 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B35" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C35" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D35" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E35" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F35" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H35" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I35" t="n">
         <v>11.3</v>
       </c>
       <c r="J35" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K35" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N35" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O35" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V35" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W35" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X35" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA35" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF35" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG35" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3949,10 +3982,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL35" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3961,99 +3994,66 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS35" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B36" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C36" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D36" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E36" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F36" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H36" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I36" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J36" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K36" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N36" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O36" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>9</v>
-      </c>
-      <c r="T36" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V36" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W36" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X36" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y36" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA36" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB36" t="n">
         <v>-0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4062,10 +4062,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4073,67 +4073,61 @@
       <c r="AN36" t="n">
         <v>142</v>
       </c>
-      <c r="AP36" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL36" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B37" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F37" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K37" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O37" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V37" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W37" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X37" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y37" t="n">
         <v>14</v>
       </c>
       <c r="Z37" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA37" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF37" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4142,10 +4136,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL37" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4154,60 +4148,93 @@
         <v>142</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B38" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>56.3</v>
       </c>
       <c r="D38" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>21.2</v>
       </c>
       <c r="F38" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I38" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>40.4</v>
       </c>
       <c r="K38" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>29</v>
       </c>
       <c r="O38" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>21.6</v>
       </c>
       <c r="V38" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W38" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X38" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z38" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA38" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF38" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG38" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4216,10 +4243,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL38" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4227,52 +4254,58 @@
       <c r="AN38" t="n">
         <v>142</v>
       </c>
+      <c r="AP38" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL38" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B39" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C39" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D39" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E39" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F39" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H39" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I39" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J39" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K39" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N39" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O39" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R39" t="n">
         <v>1.3</v>
@@ -4281,40 +4314,40 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V39" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W39" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X39" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA39" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF39" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG39" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4323,10 +4356,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4335,99 +4368,99 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS39" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B40" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C40" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D40" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E40" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F40" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H40" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I40" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J40" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K40" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O40" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V40" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W40" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X40" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA40" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF40" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG40" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4436,10 +4469,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL40" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4448,99 +4481,99 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS40" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B41" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C41" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D41" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E41" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F41" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H41" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I41" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J41" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K41" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N41" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O41" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q41" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T41" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V41" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W41" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X41" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA41" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF41" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG41" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4549,10 +4582,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL41" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4561,99 +4594,99 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS41" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B42" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C42" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E42" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F42" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H42" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I42" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J42" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K42" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M42" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N42" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O42" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R42" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T42" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V42" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W42" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X42" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y42" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z42" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA42" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG42" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4662,10 +4695,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4674,99 +4707,60 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS42" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B43" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C43" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D43" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E43" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F43" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H43" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J43" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K43" t="n">
-        <v>77</v>
-      </c>
-      <c r="M43" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N43" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>21</v>
-      </c>
-      <c r="R43" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S43" t="n">
-        <v>6</v>
-      </c>
-      <c r="T43" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V43" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W43" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X43" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y43" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA43" t="n">
         <v>9</v>
       </c>
-      <c r="Z43" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB43" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF43" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4775,10 +4769,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL43" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4786,61 +4780,61 @@
       <c r="AN43" t="n">
         <v>142</v>
       </c>
-      <c r="AP43" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL43" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B44" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D44" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F44" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O44" t="n">
+        <v>35.5</v>
       </c>
       <c r="V44" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W44" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X44" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z44" t="n">
         <v>13</v>
       </c>
       <c r="AA44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB44" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD44" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4849,10 +4843,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4861,60 +4855,60 @@
         <v>142</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B45" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D45" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F45" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K45" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O45" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V45" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W45" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X45" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z45" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB45" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD45" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF45" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG45" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4923,10 +4917,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4935,60 +4929,93 @@
         <v>142</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B46" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C46" t="n">
+        <v>86.8</v>
       </c>
       <c r="D46" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>33</v>
       </c>
       <c r="F46" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H46" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J46" t="n">
+        <v>41.1</v>
       </c>
       <c r="K46" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N46" t="n">
+        <v>33.5</v>
       </c>
       <c r="O46" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="n">
+        <v>22.4</v>
       </c>
       <c r="V46" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W46" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X46" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z46" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA46" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF46" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4997,10 +5024,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL46" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5008,94 +5035,100 @@
       <c r="AN46" t="n">
         <v>142</v>
       </c>
+      <c r="AP46" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL46" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B47" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C47" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D47" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E47" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F47" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H47" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I47" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J47" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K47" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M47" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O47" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R47" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T47" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V47" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W47" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X47" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z47" t="n">
         <v>12</v>
       </c>
       <c r="AA47" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB47" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD47" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF47" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG47" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5104,10 +5137,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL47" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5116,99 +5149,99 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS47" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B48" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C48" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D48" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E48" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F48" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H48" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I48" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J48" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K48" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O48" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R48" t="n">
         <v>1.8</v>
       </c>
       <c r="S48" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T48" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V48" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W48" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X48" t="n">
         <v>10.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA48" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB48" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD48" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD48" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF48" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG48" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5217,10 +5250,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL48" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5229,99 +5262,66 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS48" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B49" t="n">
-        <v>183</v>
-      </c>
-      <c r="C49" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D49" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E49" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F49" t="n">
-        <v>7</v>
-      </c>
-      <c r="H49" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I49" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J49" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K49" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4</v>
-      </c>
-      <c r="N49" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O49" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S49" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T49" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V49" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W49" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X49" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y49" t="n">
         <v>8</v>
       </c>
       <c r="Z49" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA49" t="n">
         <v>10</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5330,10 +5330,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL49" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5341,67 +5341,61 @@
       <c r="AN49" t="n">
         <v>142</v>
       </c>
-      <c r="AP49" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL49" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B50" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F50" t="n">
         <v>6.5</v>
       </c>
       <c r="K50" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O50" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V50" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W50" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X50" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA50" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF50" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG50" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5410,10 +5404,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL50" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5422,60 +5416,60 @@
         <v>142</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B51" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D51" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F51" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K51" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O51" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V51" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W51" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X51" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y51" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z51" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA51" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC51" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5483,12 +5477,6 @@
       <c r="AI51" t="n">
         <v>235</v>
       </c>
-      <c r="AK51" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM51" t="n">
         <v>110</v>
       </c>
@@ -5496,60 +5484,54 @@
         <v>142</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B52" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D52" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F52" t="n">
         <v>5.5</v>
       </c>
       <c r="K52" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O52" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V52" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W52" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X52" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z52" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA52" t="n">
         <v>15</v>
       </c>
-      <c r="AA52" t="n">
-        <v>14</v>
-      </c>
       <c r="AB52" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC52" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5564,54 +5546,93 @@
         <v>142</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B53" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C53" t="n">
+        <v>71.8</v>
       </c>
       <c r="D53" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>24.7</v>
       </c>
       <c r="F53" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H53" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J53" t="n">
+        <v>41.1</v>
       </c>
       <c r="K53" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N53" t="n">
+        <v>33.5</v>
       </c>
       <c r="O53" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>23.2</v>
       </c>
       <c r="V53" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W53" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X53" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y53" t="n">
         <v>12</v>
       </c>
       <c r="Z53" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA53" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB53" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD53" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5619,100 +5640,112 @@
       <c r="AI53" t="n">
         <v>235</v>
       </c>
+      <c r="AK53" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
       <c r="AN53" t="n">
         <v>142</v>
       </c>
+      <c r="AP53" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL53" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B54" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C54" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D54" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E54" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H54" t="n">
         <v>24.1</v>
       </c>
       <c r="I54" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J54" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K54" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N54" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O54" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R54" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T54" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V54" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W54" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X54" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z54" t="n">
         <v>13</v>
       </c>
-      <c r="X54" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>14</v>
-      </c>
       <c r="AA54" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB54" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC54" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD54" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF54" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5721,10 +5754,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL54" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5733,99 +5766,99 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS54" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B55" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C55" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D55" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E55" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F55" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H55" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I55" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K55" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N55" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O55" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R55" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S55" t="n">
         <v>7</v>
       </c>
       <c r="T55" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V55" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W55" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X55" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z55" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA55" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB55" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC55" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF55" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG55" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5834,10 +5867,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5846,81 +5879,81 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS55" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B56" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C56" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D56" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E56" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F56" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H56" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I56" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J56" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K56" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M56" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N56" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O56" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q56" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R56" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T56" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Y56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z56" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA56" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AF56" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5929,10 +5962,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5941,81 +5974,48 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS56" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B57" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C57" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D57" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E57" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F57" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H57" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I57" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J57" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K57" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M57" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N57" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S57" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T57" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="Y57" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z57" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA57" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AF57" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG57" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6023,55 +6023,49 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
-      <c r="AK57" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
       </c>
-      <c r="AP57" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL57" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B58" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D58" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F58" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="O58" t="n">
+        <v>35.2</v>
       </c>
       <c r="Y58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z58" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA58" t="n">
         <v>9</v>
       </c>
       <c r="AF58" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG58" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6086,36 +6080,75 @@
         <v>142</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B59" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C59" t="n">
+        <v>73.7</v>
       </c>
       <c r="D59" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E59" t="n">
+        <v>28.2</v>
       </c>
       <c r="F59" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H59" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J59" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M59" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N59" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="O59" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S59" t="n">
+        <v>6</v>
+      </c>
+      <c r="T59" t="n">
+        <v>23.5</v>
       </c>
       <c r="Y59" t="n">
         <v>4</v>
       </c>
       <c r="Z59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA59" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AF59" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6123,82 +6156,94 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
+      <c r="AK59" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
+      <c r="AP59" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL59" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B60" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C60" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E60" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F60" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H60" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I60" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J60" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K60" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M60" t="n">
         <v>6.8</v>
       </c>
       <c r="N60" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O60" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R60" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T60" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="Y60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z60" t="n">
         <v>13</v>
       </c>
       <c r="AA60" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="AF60" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6207,10 +6252,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL60" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6219,42 +6264,42 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS60" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B61" t="n">
-        <v>153.9</v>
+        <v>144.5</v>
       </c>
       <c r="D61" t="n">
-        <v>33</v>
+        <v>32.3</v>
       </c>
       <c r="F61" t="n">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="Y61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF61" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG61" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6269,30 +6314,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B62" t="n">
-        <v>144.5</v>
+        <v>138.5</v>
       </c>
       <c r="D62" t="n">
-        <v>32.3</v>
+        <v>32.7</v>
       </c>
       <c r="F62" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z62" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA62" t="n">
         <v>14</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>11</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6307,7 +6352,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,61 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="B2" t="n">
-        <v>151.1</v>
+        <v>167.2</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>26.8</v>
+        <v>27.6</v>
       </c>
       <c r="E2" t="n">
-        <v>30.9</v>
+        <v>28.2</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>7.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>40.3</v>
       </c>
       <c r="K2" t="n">
-        <v>97.7</v>
+        <v>75</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N2" t="n">
+        <v>37.2</v>
       </c>
       <c r="O2" t="n">
-        <v>40.8</v>
+        <v>39.9</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>22</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>19</v>
+      </c>
+      <c r="T2" t="n">
+        <v>22</v>
       </c>
       <c r="V2" t="n">
-        <v>6.3</v>
+        <v>9.4</v>
       </c>
       <c r="W2" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="X2" t="n">
-        <v>12.6</v>
+        <v>14.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>1.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>229.98</v>
+        <v>236.38</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.58</v>
+        <v>6.4</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -691,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>132.56</v>
+        <v>132.97</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.78</v>
+        <v>0.41</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -702,94 +729,100 @@
       <c r="AN2" t="n">
         <v>142</v>
       </c>
+      <c r="AP2" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>16.05</v>
+      </c>
       <c r="BL2" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="B3" t="n">
-        <v>167.2</v>
+        <v>176.7</v>
       </c>
       <c r="C3" t="n">
-        <v>74.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="D3" t="n">
-        <v>27.6</v>
+        <v>28.3</v>
       </c>
       <c r="E3" t="n">
-        <v>28.2</v>
+        <v>31.6</v>
       </c>
       <c r="F3" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="H3" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="I3" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="J3" t="n">
-        <v>40.3</v>
+        <v>41.8</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>37.2</v>
+        <v>38.4</v>
       </c>
       <c r="O3" t="n">
-        <v>39.9</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="T3" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="V3" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>19.1</v>
+        <v>14.8</v>
       </c>
       <c r="X3" t="n">
-        <v>14.2</v>
+        <v>10.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>236.38</v>
+        <v>236.23</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.4</v>
+        <v>-0.15</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -798,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>132.97</v>
+        <v>132.79</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.41</v>
+        <v>-0.18</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -810,99 +843,99 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>90.8</v>
+        <v>89.64</v>
       </c>
       <c r="AS3" t="n">
-        <v>16.05</v>
+        <v>15.89</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B4" t="n">
-        <v>176.7</v>
+        <v>175.3</v>
       </c>
       <c r="C4" t="n">
-        <v>80.8</v>
+        <v>83.5</v>
       </c>
       <c r="D4" t="n">
-        <v>28.3</v>
+        <v>27.8</v>
       </c>
       <c r="E4" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="F4" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H4" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="I4" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="J4" t="n">
-        <v>41.8</v>
+        <v>42.9</v>
       </c>
       <c r="K4" t="n">
-        <v>76.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="N4" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="O4" t="n">
         <v>41</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="T4" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W4" t="n">
         <v>14.8</v>
       </c>
       <c r="X4" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z4" t="n">
         <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1.6</v>
+        <v>-7.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>236.23</v>
+        <v>236.72</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.15</v>
+        <v>0.49</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -911,10 +944,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>132.79</v>
+        <v>134.11</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.18</v>
+        <v>1.32</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -923,99 +956,99 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>89.64</v>
+        <v>88.87</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.89</v>
+        <v>15.71</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B5" t="n">
-        <v>175.3</v>
+        <v>181.9</v>
       </c>
       <c r="C5" t="n">
-        <v>83.5</v>
+        <v>88.7</v>
       </c>
       <c r="D5" t="n">
-        <v>27.8</v>
+        <v>27.2</v>
       </c>
       <c r="E5" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="F5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H5" t="n">
-        <v>24.7</v>
+        <v>23.2</v>
       </c>
       <c r="I5" t="n">
-        <v>10.4</v>
+        <v>11.2</v>
       </c>
       <c r="J5" t="n">
-        <v>42.9</v>
+        <v>42.3</v>
       </c>
       <c r="K5" t="n">
-        <v>77.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="M5" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="O5" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T5" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="W5" t="n">
-        <v>14.8</v>
+        <v>13.1</v>
       </c>
       <c r="X5" t="n">
-        <v>11.8</v>
+        <v>10.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>-7.7</v>
+        <v>-12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>-0.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>-2.9</v>
+        <v>-6.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>236.72</v>
+        <v>229.92</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.49</v>
+        <v>-6.8</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1024,10 +1057,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>134.11</v>
+        <v>133.43</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.32</v>
+        <v>-0.68</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1036,99 +1069,99 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>88.87</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.71</v>
+        <v>15.36</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B6" t="n">
-        <v>181.9</v>
+        <v>188.8</v>
       </c>
       <c r="C6" t="n">
-        <v>88.7</v>
+        <v>94.8</v>
       </c>
       <c r="D6" t="n">
-        <v>27.2</v>
+        <v>27.9</v>
       </c>
       <c r="E6" t="n">
-        <v>30.5</v>
+        <v>32.4</v>
       </c>
       <c r="F6" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>23.2</v>
+        <v>24.4</v>
       </c>
       <c r="I6" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="J6" t="n">
-        <v>42.3</v>
+        <v>40.8</v>
       </c>
       <c r="K6" t="n">
-        <v>76.7</v>
+        <v>75.7</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>38</v>
+        <v>36.5</v>
       </c>
       <c r="O6" t="n">
-        <v>41.2</v>
+        <v>40.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T6" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="V6" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
-        <v>13.1</v>
+        <v>10</v>
       </c>
       <c r="X6" t="n">
-        <v>10.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.699999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>-12.5</v>
+        <v>-9.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.6</v>
+        <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>-6.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>229.92</v>
+        <v>223</v>
       </c>
       <c r="AG6" t="n">
-        <v>-6.8</v>
+        <v>-6.92</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1137,10 +1170,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>133.43</v>
+        <v>128.87</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.68</v>
+        <v>-4.56</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1149,99 +1182,72 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>85.26000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.36</v>
+        <v>14.68</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B7" t="n">
-        <v>188.8</v>
+        <v>166.3</v>
       </c>
       <c r="C7" t="n">
-        <v>94.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>27.9</v>
+        <v>26.1</v>
       </c>
       <c r="E7" t="n">
-        <v>32.4</v>
+        <v>30.6</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>40.8</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N7" t="n">
-        <v>36.5</v>
+        <v>98.8</v>
       </c>
       <c r="O7" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R7" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="X7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.9</v>
       </c>
-      <c r="S7" t="n">
-        <v>20</v>
-      </c>
-      <c r="T7" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>10</v>
-      </c>
-      <c r="X7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AD7" t="n">
-        <v>-3.3</v>
+        <v>-2.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>223</v>
+        <v>221.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>-6.92</v>
+        <v>-1.92</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1250,10 +1256,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>128.87</v>
+        <v>125.07</v>
       </c>
       <c r="AL7" t="n">
-        <v>-4.56</v>
+        <v>-3.8</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1261,73 +1267,67 @@
       <c r="AN7" t="n">
         <v>142</v>
       </c>
-      <c r="AP7" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>14.68</v>
-      </c>
       <c r="BL7" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B8" t="n">
-        <v>166.3</v>
+        <v>154.6</v>
       </c>
       <c r="C8" t="n">
-        <v>94.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="D8" t="n">
-        <v>26.1</v>
+        <v>25.2</v>
       </c>
       <c r="E8" t="n">
-        <v>30.6</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>98.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="V8" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="W8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X8" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>-7.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>-2.8</v>
+        <v>-1.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>221.08</v>
+        <v>221.24</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.92</v>
+        <v>0.16</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1336,10 +1336,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>125.07</v>
+        <v>125.99</v>
       </c>
       <c r="AL8" t="n">
-        <v>-3.8</v>
+        <v>0.92</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1348,66 +1348,93 @@
         <v>142</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B9" t="n">
-        <v>154.6</v>
+        <v>175.7</v>
       </c>
       <c r="C9" t="n">
-        <v>89</v>
+        <v>91.2</v>
       </c>
       <c r="D9" t="n">
-        <v>25.2</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>26.9</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>6.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>42.1</v>
       </c>
       <c r="K9" t="n">
-        <v>98.09999999999999</v>
+        <v>77.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>37.2</v>
       </c>
       <c r="O9" t="n">
-        <v>39.5</v>
+        <v>42.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>22.7</v>
       </c>
       <c r="V9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="W9" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="X9" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>-6.4</v>
+        <v>-5.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>221.24</v>
+        <v>223.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.16</v>
+        <v>2.7</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1416,10 +1443,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>125.99</v>
+        <v>128.11</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.92</v>
+        <v>2.12</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1427,94 +1454,100 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
+      <c r="AP9" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>16.09</v>
+      </c>
       <c r="BL9" s="1" t="n">
-        <v>46207</v>
+        <v>46208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B10" t="n">
-        <v>175.7</v>
+        <v>178.9</v>
       </c>
       <c r="C10" t="n">
-        <v>91.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D10" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E10" t="n">
         <v>24</v>
       </c>
-      <c r="E10" t="n">
-        <v>26.9</v>
-      </c>
       <c r="F10" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H10" t="n">
-        <v>24.3</v>
+        <v>25</v>
       </c>
       <c r="I10" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="J10" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="K10" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>37.2</v>
+        <v>37.5</v>
       </c>
       <c r="O10" t="n">
-        <v>42.3</v>
+        <v>41.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="S10" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="T10" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="V10" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="W10" t="n">
-        <v>10.8</v>
+        <v>16.5</v>
       </c>
       <c r="X10" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Y10" t="n">
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>-5.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>223.94</v>
+        <v>224.33</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.7</v>
+        <v>0.39</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1523,10 +1556,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>128.11</v>
+        <v>128.49</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.12</v>
+        <v>0.38</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1535,99 +1568,99 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>88.34</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>16.09</v>
+        <v>16.13</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B11" t="n">
-        <v>178.9</v>
+        <v>175.3</v>
       </c>
       <c r="C11" t="n">
-        <v>92.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>27.8</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="H11" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="I11" t="n">
         <v>10.8</v>
       </c>
       <c r="J11" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="K11" t="n">
-        <v>77.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>37.5</v>
+        <v>38.4</v>
       </c>
       <c r="O11" t="n">
-        <v>41.6</v>
+        <v>42</v>
       </c>
       <c r="Q11" t="n">
         <v>23</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="T11" t="n">
         <v>23</v>
       </c>
       <c r="V11" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="W11" t="n">
-        <v>16.5</v>
+        <v>17.1</v>
       </c>
       <c r="X11" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.5</v>
+        <v>10.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>224.33</v>
+        <v>224.34</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.39</v>
+        <v>0.01</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1636,10 +1669,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>128.49</v>
+        <v>128.93</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1648,99 +1681,72 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>87.56999999999999</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>16.13</v>
+        <v>15.43</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B12" t="n">
-        <v>175.3</v>
+        <v>157.8</v>
       </c>
       <c r="C12" t="n">
-        <v>85.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="E12" t="n">
-        <v>27.8</v>
+        <v>30.3</v>
       </c>
       <c r="F12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H12" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>41.4</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M12" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD12" t="n">
         <v>3.6</v>
       </c>
-      <c r="N12" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>23</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="T12" t="n">
-        <v>23</v>
-      </c>
-      <c r="V12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W12" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AF12" t="n">
-        <v>224.34</v>
+        <v>231.46</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.01</v>
+        <v>3.7</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1749,10 +1755,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>128.93</v>
+        <v>129.8</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1760,73 +1766,67 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
-      <c r="AP12" t="n">
-        <v>89.06999999999999</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>15.43</v>
-      </c>
       <c r="BL12" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B13" t="n">
-        <v>157.8</v>
+        <v>151.6</v>
       </c>
       <c r="C13" t="n">
-        <v>85.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="D13" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="K13" t="n">
-        <v>98.7</v>
+        <v>97.5</v>
       </c>
       <c r="O13" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="V13" t="n">
-        <v>4.6</v>
+        <v>8.1</v>
       </c>
       <c r="W13" t="n">
-        <v>19.7</v>
+        <v>22.3</v>
       </c>
       <c r="X13" t="n">
-        <v>12.1</v>
+        <v>15.2</v>
       </c>
       <c r="Y13" t="n">
         <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA13" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.6</v>
+        <v>-0.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>231.46</v>
+        <v>229.92</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.7</v>
+        <v>-1.54</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1835,10 +1835,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>129.8</v>
+        <v>133.01</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.87</v>
+        <v>3.21</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1847,66 +1847,66 @@
         <v>142</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B14" t="n">
-        <v>151.6</v>
+        <v>157.5</v>
       </c>
       <c r="C14" t="n">
-        <v>73.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="E14" t="n">
-        <v>33.9</v>
+        <v>36.9</v>
       </c>
       <c r="F14" t="n">
         <v>7.4</v>
       </c>
       <c r="K14" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="O14" t="n">
-        <v>40.6</v>
+        <v>38</v>
       </c>
       <c r="V14" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="W14" t="n">
-        <v>22.3</v>
+        <v>20.8</v>
       </c>
       <c r="X14" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>-3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>229.92</v>
+        <v>226.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>-1.54</v>
+        <v>-2.97</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1915,10 +1915,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>133.01</v>
+        <v>128.4</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.21</v>
+        <v>-4.61</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1927,66 +1927,66 @@
         <v>142</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B15" t="n">
-        <v>157.5</v>
+        <v>148.5</v>
       </c>
       <c r="C15" t="n">
-        <v>76.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D15" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="E15" t="n">
-        <v>36.9</v>
+        <v>34.3</v>
       </c>
       <c r="F15" t="n">
         <v>7.4</v>
       </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="O15" t="n">
-        <v>38</v>
+        <v>39.8</v>
       </c>
       <c r="V15" t="n">
-        <v>6.7</v>
+        <v>11.2</v>
       </c>
       <c r="W15" t="n">
-        <v>20.8</v>
+        <v>21.7</v>
       </c>
       <c r="X15" t="n">
-        <v>13.8</v>
+        <v>16.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AB15" t="n">
-        <v>-2.3</v>
+        <v>-1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.1</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>226.95</v>
+        <v>223.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>-2.97</v>
+        <v>-3.83</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1995,10 +1995,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>128.4</v>
+        <v>124.76</v>
       </c>
       <c r="AL15" t="n">
-        <v>-4.61</v>
+        <v>-3.64</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2007,66 +2007,60 @@
         <v>142</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B16" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="C16" t="n">
-        <v>70.5</v>
+        <v>72.8</v>
       </c>
       <c r="D16" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="E16" t="n">
-        <v>34.3</v>
+        <v>31.4</v>
       </c>
       <c r="F16" t="n">
         <v>7.4</v>
       </c>
       <c r="K16" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="O16" t="n">
-        <v>39.8</v>
+        <v>40.2</v>
       </c>
       <c r="V16" t="n">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="W16" t="n">
-        <v>21.7</v>
+        <v>16.8</v>
       </c>
       <c r="X16" t="n">
-        <v>16.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y16" t="n">
         <v>7</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.9</v>
+        <v>0.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>223.11</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>-3.83</v>
+        <v>4.8</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2075,10 +2069,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>124.76</v>
+        <v>127.2</v>
       </c>
       <c r="AL16" t="n">
-        <v>-3.64</v>
+        <v>2.44</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2087,60 +2081,93 @@
         <v>142</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B17" t="n">
-        <v>147.5</v>
+        <v>183.5</v>
       </c>
       <c r="C17" t="n">
-        <v>72.8</v>
+        <v>84.5</v>
       </c>
       <c r="D17" t="n">
-        <v>26.7</v>
+        <v>31.5</v>
       </c>
       <c r="E17" t="n">
-        <v>31.4</v>
+        <v>34.6</v>
       </c>
       <c r="F17" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>41.5</v>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>76.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>37.7</v>
       </c>
       <c r="O17" t="n">
-        <v>40.2</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>23</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T17" t="n">
+        <v>23</v>
       </c>
       <c r="V17" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="W17" t="n">
-        <v>16.8</v>
+        <v>20</v>
       </c>
       <c r="X17" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>220.36</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-3.75</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2149,10 +2176,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>127.2</v>
+        <v>127.13</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2160,94 +2187,100 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
+      <c r="AP17" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL17" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B18" t="n">
-        <v>183.5</v>
+        <v>180.5</v>
       </c>
       <c r="C18" t="n">
-        <v>84.5</v>
+        <v>79.2</v>
       </c>
       <c r="D18" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="E18" t="n">
         <v>34.6</v>
       </c>
       <c r="F18" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="H18" t="n">
         <v>23.9</v>
       </c>
       <c r="I18" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="J18" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="K18" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
         <v>37.7</v>
       </c>
       <c r="O18" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="T18" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V18" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W18" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="X18" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>220.36</v>
+        <v>219.64</v>
       </c>
       <c r="AG18" t="n">
-        <v>-3.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2256,10 +2289,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>127.13</v>
+        <v>126.03</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2268,99 +2301,99 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>76.90000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="AS18" t="n">
-        <v>14.17</v>
+        <v>14.55</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B19" t="n">
-        <v>180.5</v>
+        <v>168.1</v>
       </c>
       <c r="C19" t="n">
-        <v>79.2</v>
+        <v>69.7</v>
       </c>
       <c r="D19" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E19" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F19" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H19" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I19" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="J19" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="K19" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M19" t="n">
         <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O19" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S19" t="n">
         <v>17.6</v>
       </c>
       <c r="T19" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="V19" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W19" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA19" t="n">
         <v>14.9</v>
       </c>
-      <c r="Y19" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>11.9</v>
-      </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>219.64</v>
+        <v>224.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.72</v>
+        <v>5.29</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2369,10 +2402,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>126.03</v>
+        <v>129.28</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2381,99 +2414,99 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>82.95</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>14.55</v>
+        <v>15.25</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B20" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C20" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D20" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E20" t="n">
         <v>30.4</v>
       </c>
-      <c r="E20" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H20" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I20" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J20" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K20" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O20" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S20" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="V20" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="W20" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X20" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y20" t="n">
         <v>17</v>
       </c>
-      <c r="Y20" t="n">
-        <v>11</v>
-      </c>
       <c r="Z20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>14.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2482,10 +2515,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2494,99 +2527,66 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B21" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C21" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D21" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H21" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I21" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K21" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N21" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>15</v>
-      </c>
-      <c r="T21" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
       </c>
       <c r="V21" t="n">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="W21" t="n">
-        <v>26</v>
+        <v>36.1</v>
       </c>
       <c r="X21" t="n">
-        <v>18.1</v>
+        <v>26.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC21" t="n">
         <v>6.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2595,10 +2595,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2606,67 +2606,61 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
-      <c r="AP21" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL21" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B22" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D22" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F22" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O22" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V22" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
       <c r="W22" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="X22" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2675,10 +2669,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL22" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2687,60 +2681,93 @@
         <v>142</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B23" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>67</v>
       </c>
       <c r="D23" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>31.5</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>41.1</v>
       </c>
       <c r="K23" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>35</v>
       </c>
       <c r="O23" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>20.5</v>
       </c>
       <c r="V23" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W23" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X23" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG23" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2749,10 +2776,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL23" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2760,94 +2787,100 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
+      <c r="AP23" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL23" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B24" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C24" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E24" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F24" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H24" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I24" t="n">
         <v>11.4</v>
       </c>
       <c r="J24" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K24" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M24" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O24" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V24" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W24" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X24" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y24" t="n">
         <v>9</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA24" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG24" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2856,10 +2889,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2868,99 +2901,99 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS24" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B25" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C25" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D25" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F25" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H25" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I25" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K25" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N25" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O25" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>13</v>
+      </c>
+      <c r="X25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA25" t="n">
         <v>11.4</v>
       </c>
-      <c r="J25" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>76</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N25" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O25" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>14</v>
-      </c>
-      <c r="T25" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB25" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF25" t="n">
         <v>220.92</v>
       </c>
       <c r="AG25" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2969,10 +3002,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL25" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2981,99 +3014,99 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS25" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B26" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C26" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E26" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F26" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I26" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J26" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K26" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N26" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O26" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X26" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD26" t="n">
         <v>0.5</v>
       </c>
-      <c r="S26" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>13</v>
-      </c>
-      <c r="X26" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF26" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3082,10 +3115,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL26" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3094,99 +3127,99 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B27" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C27" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D27" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E27" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F27" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H27" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I27" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J27" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K27" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M27" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N27" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O27" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S27" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T27" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V27" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W27" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X27" t="n">
         <v>12.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z27" t="n">
         <v>13</v>
       </c>
       <c r="AA27" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF27" t="n">
         <v>216.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3195,10 +3228,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL27" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3207,99 +3240,66 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS27" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B28" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C28" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D28" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E28" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F28" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H28" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K28" t="n">
-        <v>75</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N28" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S28" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V28" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W28" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X28" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA28" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF28" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3308,10 +3308,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3319,67 +3319,61 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
-      <c r="AP28" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL28" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B29" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D29" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F29" t="n">
         <v>6.8</v>
       </c>
       <c r="K29" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O29" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V29" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W29" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X29" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3388,10 +3382,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3400,60 +3394,93 @@
         <v>142</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B30" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>60</v>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E30" t="n">
+        <v>25.9</v>
       </c>
       <c r="F30" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>24</v>
+      </c>
+      <c r="I30" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>38.8</v>
       </c>
       <c r="K30" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>36.7</v>
       </c>
       <c r="O30" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>21.7</v>
       </c>
       <c r="V30" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W30" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X30" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA30" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF30" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG30" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3462,10 +3489,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3473,94 +3500,67 @@
       <c r="AN30" t="n">
         <v>142</v>
       </c>
+      <c r="AP30" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL30" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B31" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C31" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D31" t="n">
-        <v>29</v>
-      </c>
-      <c r="E31" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H31" t="n">
-        <v>24</v>
-      </c>
-      <c r="I31" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J31" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K31" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N31" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O31" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V31" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W31" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X31" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA31" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB31" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG31" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3569,10 +3569,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3580,67 +3580,94 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
-      <c r="AP31" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL31" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B32" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>63.7</v>
       </c>
       <c r="D32" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>36.4</v>
       </c>
       <c r="F32" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I32" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>39.9</v>
       </c>
       <c r="K32" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>35.9</v>
       </c>
       <c r="O32" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6</v>
+      </c>
+      <c r="T32" t="n">
+        <v>20.3</v>
       </c>
       <c r="V32" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W32" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X32" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z32" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA32" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG32" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3649,10 +3676,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3660,94 +3687,100 @@
       <c r="AN32" t="n">
         <v>142</v>
       </c>
+      <c r="AP32" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL32" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B33" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C33" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E33" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F33" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H33" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I33" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J33" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K33" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N33" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O33" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R33" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T33" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V33" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W33" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X33" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA33" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3756,10 +3789,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL33" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3768,99 +3801,99 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B34" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C34" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D34" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E34" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F34" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H34" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I34" t="n">
         <v>11.3</v>
       </c>
       <c r="J34" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K34" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N34" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O34" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V34" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W34" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X34" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z34" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA34" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF34" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG34" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3869,10 +3902,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL34" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3881,99 +3914,66 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS34" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B35" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C35" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D35" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E35" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H35" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I35" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J35" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K35" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N35" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O35" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>9</v>
-      </c>
-      <c r="T35" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V35" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W35" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X35" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y35" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z35" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB35" t="n">
         <v>-0</v>
       </c>
       <c r="AC35" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3982,10 +3982,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3993,67 +3993,61 @@
       <c r="AN35" t="n">
         <v>142</v>
       </c>
-      <c r="AP35" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL35" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B36" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D36" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F36" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K36" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O36" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V36" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W36" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X36" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y36" t="n">
         <v>14</v>
       </c>
       <c r="Z36" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA36" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4062,10 +4056,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL36" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4074,60 +4068,93 @@
         <v>142</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B37" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>56.3</v>
       </c>
       <c r="D37" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>21.2</v>
       </c>
       <c r="F37" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I37" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>40.4</v>
       </c>
       <c r="K37" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N37" t="n">
+        <v>29</v>
       </c>
       <c r="O37" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>21.6</v>
       </c>
       <c r="V37" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W37" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X37" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z37" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA37" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF37" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG37" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4136,10 +4163,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL37" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4147,52 +4174,58 @@
       <c r="AN37" t="n">
         <v>142</v>
       </c>
+      <c r="AP37" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL37" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B38" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C38" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D38" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E38" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F38" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H38" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I38" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J38" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K38" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O38" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R38" t="n">
         <v>1.3</v>
@@ -4201,40 +4234,40 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V38" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W38" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X38" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA38" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF38" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG38" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4243,10 +4276,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4255,99 +4288,99 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS38" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B39" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C39" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D39" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E39" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F39" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H39" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I39" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J39" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K39" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N39" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O39" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V39" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W39" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X39" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA39" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC39" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF39" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG39" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4356,10 +4389,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL39" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4368,99 +4401,99 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS39" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B40" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C40" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D40" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F40" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H40" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I40" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J40" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K40" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N40" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O40" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q40" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T40" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V40" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W40" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X40" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA40" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF40" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG40" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4469,10 +4502,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL40" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4481,99 +4514,99 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS40" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B41" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C41" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E41" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F41" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H41" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I41" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J41" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K41" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M41" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N41" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O41" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R41" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T41" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V41" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W41" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X41" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y41" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z41" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA41" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG41" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4582,10 +4615,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4594,99 +4627,60 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS41" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B42" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C42" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D42" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E42" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H42" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J42" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K42" t="n">
-        <v>77</v>
-      </c>
-      <c r="M42" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N42" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>21</v>
-      </c>
-      <c r="R42" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S42" t="n">
-        <v>6</v>
-      </c>
-      <c r="T42" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V42" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W42" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X42" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y42" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA42" t="n">
         <v>9</v>
       </c>
-      <c r="Z42" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB42" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF42" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4695,10 +4689,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL42" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4706,61 +4700,61 @@
       <c r="AN42" t="n">
         <v>142</v>
       </c>
-      <c r="AP42" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL42" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B43" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D43" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F43" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O43" t="n">
+        <v>35.5</v>
       </c>
       <c r="V43" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W43" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X43" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z43" t="n">
         <v>13</v>
       </c>
       <c r="AA43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB43" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD43" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4769,10 +4763,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4781,60 +4775,60 @@
         <v>142</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B44" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D44" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K44" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O44" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V44" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W44" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X44" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z44" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB44" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD44" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG44" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4843,10 +4837,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4855,60 +4849,93 @@
         <v>142</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B45" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C45" t="n">
+        <v>86.8</v>
       </c>
       <c r="D45" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>33</v>
       </c>
       <c r="F45" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H45" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>41.1</v>
       </c>
       <c r="K45" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N45" t="n">
+        <v>33.5</v>
       </c>
       <c r="O45" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="n">
+        <v>22.4</v>
       </c>
       <c r="V45" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W45" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X45" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z45" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA45" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF45" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4917,10 +4944,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL45" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4928,94 +4955,100 @@
       <c r="AN45" t="n">
         <v>142</v>
       </c>
+      <c r="AP45" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL45" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B46" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C46" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D46" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E46" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F46" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H46" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I46" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J46" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K46" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M46" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N46" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O46" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R46" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T46" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V46" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W46" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X46" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z46" t="n">
         <v>12</v>
       </c>
       <c r="AA46" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB46" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF46" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG46" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5024,10 +5057,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL46" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5036,99 +5069,99 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS46" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B47" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C47" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D47" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E47" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F47" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H47" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I47" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J47" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K47" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O47" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R47" t="n">
         <v>1.8</v>
       </c>
       <c r="S47" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T47" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V47" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W47" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X47" t="n">
         <v>10.9</v>
       </c>
       <c r="Y47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA47" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB47" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD47" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD47" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF47" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG47" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5137,10 +5170,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL47" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5149,99 +5182,66 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS47" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B48" t="n">
-        <v>183</v>
-      </c>
-      <c r="C48" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D48" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E48" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F48" t="n">
-        <v>7</v>
-      </c>
-      <c r="H48" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I48" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J48" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K48" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M48" t="n">
-        <v>4</v>
-      </c>
-      <c r="N48" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O48" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S48" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T48" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V48" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W48" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X48" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y48" t="n">
         <v>8</v>
       </c>
       <c r="Z48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA48" t="n">
         <v>10</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF48" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5250,10 +5250,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL48" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5261,67 +5261,61 @@
       <c r="AN48" t="n">
         <v>142</v>
       </c>
-      <c r="AP48" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL48" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B49" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D49" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F49" t="n">
         <v>6.5</v>
       </c>
       <c r="K49" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O49" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V49" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W49" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X49" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA49" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF49" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG49" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5330,10 +5324,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL49" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5342,60 +5336,60 @@
         <v>142</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B50" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D50" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F50" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K50" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O50" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V50" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W50" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X50" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y50" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z50" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA50" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC50" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5403,12 +5397,6 @@
       <c r="AI50" t="n">
         <v>235</v>
       </c>
-      <c r="AK50" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM50" t="n">
         <v>110</v>
       </c>
@@ -5416,60 +5404,54 @@
         <v>142</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B51" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D51" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F51" t="n">
         <v>5.5</v>
       </c>
       <c r="K51" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O51" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V51" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W51" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X51" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z51" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA51" t="n">
         <v>15</v>
       </c>
-      <c r="AA51" t="n">
-        <v>14</v>
-      </c>
       <c r="AB51" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC51" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5484,54 +5466,93 @@
         <v>142</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B52" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C52" t="n">
+        <v>71.8</v>
       </c>
       <c r="D52" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E52" t="n">
+        <v>24.7</v>
       </c>
       <c r="F52" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H52" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J52" t="n">
+        <v>41.1</v>
       </c>
       <c r="K52" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M52" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N52" t="n">
+        <v>33.5</v>
       </c>
       <c r="O52" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>23.2</v>
       </c>
       <c r="V52" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W52" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X52" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y52" t="n">
         <v>12</v>
       </c>
       <c r="Z52" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA52" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD52" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5539,100 +5560,112 @@
       <c r="AI52" t="n">
         <v>235</v>
       </c>
+      <c r="AK52" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM52" t="n">
         <v>110</v>
       </c>
       <c r="AN52" t="n">
         <v>142</v>
       </c>
+      <c r="AP52" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL52" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B53" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C53" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D53" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E53" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H53" t="n">
         <v>24.1</v>
       </c>
       <c r="I53" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J53" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K53" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N53" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O53" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R53" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T53" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V53" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W53" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z53" t="n">
         <v>13</v>
       </c>
-      <c r="X53" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>14</v>
-      </c>
       <c r="AA53" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB53" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC53" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF53" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5641,10 +5674,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL53" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5653,99 +5686,99 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS53" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B54" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C54" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D54" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E54" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F54" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H54" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I54" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K54" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N54" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O54" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R54" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S54" t="n">
         <v>7</v>
       </c>
       <c r="T54" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V54" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W54" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X54" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z54" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA54" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB54" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC54" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD54" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF54" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG54" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5754,10 +5787,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL54" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5766,99 +5799,99 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS54" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B55" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C55" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D55" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E55" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F55" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H55" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I55" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J55" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K55" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M55" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N55" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O55" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q55" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R55" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T55" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V55" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W55" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X55" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA55" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB55" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC55" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD55" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5867,10 +5900,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5879,81 +5912,48 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS55" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B56" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C56" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D56" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E56" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F56" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H56" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I56" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J56" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K56" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M56" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O56" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R56" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S56" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T56" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="Y56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z56" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA56" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AF56" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5961,61 +5961,49 @@
       <c r="AI56" t="n">
         <v>235</v>
       </c>
-      <c r="AK56" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
       <c r="AN56" t="n">
         <v>142</v>
       </c>
-      <c r="AP56" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL56" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B57" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D57" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F57" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K57" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O57" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="Y57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z57" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA57" t="n">
         <v>9</v>
       </c>
       <c r="AF57" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG57" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6030,42 +6018,75 @@
         <v>142</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B58" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>73.7</v>
       </c>
       <c r="D58" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E58" t="n">
+        <v>28.2</v>
       </c>
       <c r="F58" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H58" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>40.1</v>
       </c>
       <c r="K58" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M58" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N58" t="n">
+        <v>32.9</v>
       </c>
       <c r="O58" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R58" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S58" t="n">
+        <v>6</v>
+      </c>
+      <c r="T58" t="n">
+        <v>23.5</v>
       </c>
       <c r="Y58" t="n">
         <v>4</v>
       </c>
       <c r="Z58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA58" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AF58" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6073,82 +6094,94 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
+      <c r="AK58" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
+      <c r="AP58" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL58" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B59" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C59" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E59" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F59" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H59" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I59" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J59" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K59" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M59" t="n">
         <v>6.8</v>
       </c>
       <c r="N59" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O59" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R59" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T59" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="Y59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z59" t="n">
         <v>13</v>
       </c>
       <c r="AA59" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="AF59" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6157,10 +6190,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL59" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6169,81 +6202,81 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS59" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B60" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C60" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E60" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F60" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H60" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I60" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J60" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K60" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M60" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N60" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O60" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q60" t="n">
         <v>23.1</v>
       </c>
       <c r="R60" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S60" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T60" t="n">
         <v>23.1</v>
       </c>
       <c r="Y60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA60" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AF60" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG60" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6252,10 +6285,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL60" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6264,42 +6297,42 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS60" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B61" t="n">
-        <v>144.5</v>
+        <v>138.5</v>
       </c>
       <c r="D61" t="n">
-        <v>32.3</v>
+        <v>32.7</v>
       </c>
       <c r="F61" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Y61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z61" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA61" t="n">
         <v>14</v>
       </c>
-      <c r="AA61" t="n">
-        <v>11</v>
-      </c>
       <c r="AF61" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG61" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6314,21 +6347,21 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B62" t="n">
-        <v>138.5</v>
+        <v>136.8</v>
       </c>
       <c r="D62" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="F62" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y62" t="n">
         <v>10</v>
@@ -6352,7 +6385,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,61 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46201</v>
+        <v>46211</v>
       </c>
       <c r="B2" t="n">
-        <v>167.2</v>
+        <v>157.8</v>
       </c>
       <c r="C2" t="n">
-        <v>74.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>27.6</v>
+        <v>26.5</v>
       </c>
       <c r="E2" t="n">
-        <v>28.2</v>
+        <v>30.3</v>
       </c>
       <c r="F2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H2" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>40.3</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N2" t="n">
-        <v>37.2</v>
+        <v>98.7</v>
       </c>
       <c r="O2" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>22</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S2" t="n">
-        <v>19</v>
-      </c>
-      <c r="T2" t="n">
-        <v>22</v>
+        <v>40.5</v>
       </c>
       <c r="V2" t="n">
-        <v>9.4</v>
+        <v>4.6</v>
       </c>
       <c r="W2" t="n">
-        <v>19.1</v>
+        <v>19.7</v>
       </c>
       <c r="X2" t="n">
-        <v>14.2</v>
+        <v>12.1</v>
       </c>
       <c r="Y2" t="n">
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>236.38</v>
+        <v>231.46</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +691,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>132.97</v>
+        <v>129.8</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.41</v>
+        <v>0.87</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -729,100 +702,67 @@
       <c r="AN2" t="n">
         <v>142</v>
       </c>
-      <c r="AP2" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16.05</v>
-      </c>
       <c r="BL2" s="1" t="n">
-        <v>46201</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46202</v>
+        <v>46212</v>
       </c>
       <c r="B3" t="n">
-        <v>176.7</v>
+        <v>151.6</v>
       </c>
       <c r="C3" t="n">
-        <v>80.8</v>
+        <v>73.8</v>
       </c>
       <c r="D3" t="n">
-        <v>28.3</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>31.6</v>
+        <v>33.9</v>
       </c>
       <c r="F3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="I3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>41.8</v>
+        <v>7.4</v>
       </c>
       <c r="K3" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>38.4</v>
+        <v>97.5</v>
       </c>
       <c r="O3" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>20.9</v>
+        <v>40.6</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="W3" t="n">
-        <v>14.8</v>
+        <v>22.3</v>
       </c>
       <c r="X3" t="n">
-        <v>10.4</v>
+        <v>15.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.9</v>
+        <v>12.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.6</v>
+        <v>-3.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.5</v>
+        <v>-0.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>236.23</v>
+        <v>229.92</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.15</v>
+        <v>-1.54</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -831,10 +771,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>132.79</v>
+        <v>133.01</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.18</v>
+        <v>3.21</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -842,100 +782,67 @@
       <c r="AN3" t="n">
         <v>142</v>
       </c>
-      <c r="AP3" t="n">
-        <v>89.64</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>15.89</v>
-      </c>
       <c r="BL3" s="1" t="n">
-        <v>46202</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46203</v>
+        <v>46213</v>
       </c>
       <c r="B4" t="n">
-        <v>175.3</v>
+        <v>157.5</v>
       </c>
       <c r="C4" t="n">
-        <v>83.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>27.8</v>
+        <v>27.1</v>
       </c>
       <c r="E4" t="n">
-        <v>30.3</v>
+        <v>36.9</v>
       </c>
       <c r="F4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H4" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>42.9</v>
+        <v>7.4</v>
       </c>
       <c r="K4" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>38.6</v>
+        <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>22</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>18</v>
-      </c>
-      <c r="T4" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="V4" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="W4" t="n">
-        <v>14.8</v>
+        <v>20.8</v>
       </c>
       <c r="X4" t="n">
-        <v>11.8</v>
+        <v>13.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>-7.7</v>
+        <v>-2.3</v>
       </c>
       <c r="AC4" t="n">
         <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2.9</v>
+        <v>-0.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>236.72</v>
+        <v>226.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.49</v>
+        <v>-2.97</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -944,10 +851,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>134.11</v>
+        <v>128.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.32</v>
+        <v>-4.61</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -955,100 +862,67 @@
       <c r="AN4" t="n">
         <v>142</v>
       </c>
-      <c r="AP4" t="n">
-        <v>88.87</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>15.71</v>
-      </c>
       <c r="BL4" s="1" t="n">
-        <v>46203</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46204</v>
+        <v>46214</v>
       </c>
       <c r="B5" t="n">
-        <v>181.9</v>
+        <v>148.5</v>
       </c>
       <c r="C5" t="n">
-        <v>88.7</v>
+        <v>70.5</v>
       </c>
       <c r="D5" t="n">
-        <v>27.2</v>
+        <v>26.8</v>
       </c>
       <c r="E5" t="n">
-        <v>30.5</v>
+        <v>34.3</v>
       </c>
       <c r="F5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H5" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="I5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="V5" t="n">
         <v>11.2</v>
       </c>
-      <c r="J5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>38</v>
-      </c>
-      <c r="O5" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S5" t="n">
-        <v>17</v>
-      </c>
-      <c r="T5" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="V5" t="n">
-        <v>7.4</v>
-      </c>
       <c r="W5" t="n">
-        <v>13.1</v>
+        <v>21.7</v>
       </c>
       <c r="X5" t="n">
-        <v>10.2</v>
+        <v>16.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="AB5" t="n">
-        <v>-12.5</v>
+        <v>-1.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.6</v>
+        <v>5</v>
       </c>
       <c r="AD5" t="n">
-        <v>-6.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>229.92</v>
+        <v>223.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>-6.8</v>
+        <v>-3.83</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1057,10 +931,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>133.43</v>
+        <v>124.76</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.68</v>
+        <v>-3.64</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1068,100 +942,61 @@
       <c r="AN5" t="n">
         <v>142</v>
       </c>
-      <c r="AP5" t="n">
-        <v>85.26000000000001</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>15.36</v>
-      </c>
       <c r="BL5" s="1" t="n">
-        <v>46204</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46205</v>
+        <v>46215</v>
       </c>
       <c r="B6" t="n">
-        <v>188.8</v>
+        <v>147.5</v>
       </c>
       <c r="C6" t="n">
-        <v>94.8</v>
+        <v>72.8</v>
       </c>
       <c r="D6" t="n">
-        <v>27.9</v>
+        <v>26.7</v>
       </c>
       <c r="E6" t="n">
-        <v>32.4</v>
+        <v>31.4</v>
       </c>
       <c r="F6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>40.8</v>
+        <v>7.4</v>
       </c>
       <c r="K6" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>36.5</v>
+        <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S6" t="n">
-        <v>20</v>
-      </c>
-      <c r="T6" t="n">
-        <v>22.7</v>
+        <v>40.2</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>10.3</v>
       </c>
       <c r="W6" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X6" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA6" t="n">
         <v>10</v>
       </c>
-      <c r="X6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC6" t="n">
         <v>9</v>
       </c>
-      <c r="AA6" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AD6" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>223</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-6.92</v>
+        <v>4.8</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1170,10 +1005,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>128.87</v>
+        <v>127.2</v>
       </c>
       <c r="AL6" t="n">
-        <v>-4.56</v>
+        <v>2.44</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1181,73 +1016,94 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
-      <c r="AP6" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>14.68</v>
-      </c>
       <c r="BL6" s="1" t="n">
-        <v>46205</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46206</v>
+        <v>46216</v>
       </c>
       <c r="B7" t="n">
-        <v>166.3</v>
+        <v>183.5</v>
       </c>
       <c r="C7" t="n">
-        <v>94.09999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="D7" t="n">
-        <v>26.1</v>
+        <v>31.5</v>
       </c>
       <c r="E7" t="n">
-        <v>30.6</v>
+        <v>34.6</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>6.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41.5</v>
       </c>
       <c r="K7" t="n">
-        <v>98.8</v>
+        <v>76.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>37.7</v>
       </c>
       <c r="O7" t="n">
-        <v>39.4</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S7" t="n">
+        <v>18</v>
+      </c>
+      <c r="T7" t="n">
+        <v>23</v>
       </c>
       <c r="V7" t="n">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="W7" t="n">
-        <v>9.300000000000001</v>
+        <v>20</v>
       </c>
       <c r="X7" t="n">
-        <v>7.6</v>
+        <v>14.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.1</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>-7.5</v>
+        <v>3.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>8.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>-2.8</v>
+        <v>6.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>221.08</v>
+        <v>220.36</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1.92</v>
+        <v>-3.75</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1256,10 +1112,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>125.07</v>
+        <v>127.13</v>
       </c>
       <c r="AL7" t="n">
-        <v>-3.8</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1267,67 +1123,100 @@
       <c r="AN7" t="n">
         <v>142</v>
       </c>
+      <c r="AP7" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL7" s="1" t="n">
-        <v>46206</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46207</v>
+        <v>46217</v>
       </c>
       <c r="B8" t="n">
-        <v>154.6</v>
+        <v>180.5</v>
       </c>
       <c r="C8" t="n">
-        <v>89</v>
+        <v>79.2</v>
       </c>
       <c r="D8" t="n">
-        <v>25.2</v>
+        <v>30.7</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>34.6</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>7.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>41.9</v>
       </c>
       <c r="K8" t="n">
-        <v>98.09999999999999</v>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>37.7</v>
       </c>
       <c r="O8" t="n">
-        <v>39.5</v>
+        <v>42.7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>23.1</v>
       </c>
       <c r="V8" t="n">
-        <v>5.6</v>
+        <v>9.1</v>
       </c>
       <c r="W8" t="n">
-        <v>9.5</v>
+        <v>20.8</v>
       </c>
       <c r="X8" t="n">
-        <v>7.5</v>
+        <v>14.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z8" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.5</v>
+        <v>11.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>-6.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.9</v>
+        <v>7.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1.3</v>
+        <v>5.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>221.24</v>
+        <v>219.64</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.16</v>
+        <v>-0.72</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1336,10 +1225,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>125.99</v>
+        <v>126.03</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.92</v>
+        <v>-1.1</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1347,94 +1236,100 @@
       <c r="AN8" t="n">
         <v>142</v>
       </c>
+      <c r="AP8" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>14.55</v>
+      </c>
       <c r="BL8" s="1" t="n">
-        <v>46207</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46208</v>
+        <v>46218</v>
       </c>
       <c r="B9" t="n">
-        <v>175.7</v>
+        <v>168.1</v>
       </c>
       <c r="C9" t="n">
-        <v>91.2</v>
+        <v>69.7</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>30.4</v>
       </c>
       <c r="E9" t="n">
-        <v>26.9</v>
+        <v>33.9</v>
       </c>
       <c r="F9" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="I9" t="n">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
       <c r="J9" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K9" t="n">
-        <v>77.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>37.2</v>
+        <v>38.1</v>
       </c>
       <c r="O9" t="n">
-        <v>42.3</v>
+        <v>43.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>19.2</v>
+        <v>17.6</v>
       </c>
       <c r="T9" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD9" t="n">
         <v>5.7</v>
       </c>
-      <c r="W9" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="X9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-1.2</v>
-      </c>
       <c r="AF9" t="n">
-        <v>223.94</v>
+        <v>224.93</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.7</v>
+        <v>5.29</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1443,10 +1338,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>128.11</v>
+        <v>129.28</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1455,99 +1350,99 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>88.34</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>16.09</v>
+        <v>15.25</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46208</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="B10" t="n">
-        <v>178.9</v>
+        <v>158.9</v>
       </c>
       <c r="C10" t="n">
-        <v>92.59999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="D10" t="n">
-        <v>26.6</v>
+        <v>31.1</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>30.4</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="H10" t="n">
-        <v>25</v>
+        <v>23.7</v>
       </c>
       <c r="I10" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J10" t="n">
-        <v>41.8</v>
+        <v>41</v>
       </c>
       <c r="K10" t="n">
-        <v>77.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>37.5</v>
+        <v>37.8</v>
       </c>
       <c r="O10" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>26</v>
+      </c>
+      <c r="X10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA10" t="n">
         <v>19.3</v>
       </c>
-      <c r="T10" t="n">
-        <v>23</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>7.5</v>
-      </c>
       <c r="AB10" t="n">
-        <v>-3.9</v>
+        <v>2.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>224.33</v>
+        <v>232.31</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.39</v>
+        <v>9.67</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1556,10 +1451,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>128.49</v>
+        <v>134.44</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.38</v>
+        <v>5.16</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1568,99 +1463,66 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>87.56999999999999</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>16.13</v>
+        <v>17.07</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46209</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46210</v>
+        <v>46220</v>
       </c>
       <c r="B11" t="n">
-        <v>175.3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>85.09999999999999</v>
+        <v>136.7</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
-      </c>
-      <c r="E11" t="n">
-        <v>27.8</v>
+        <v>30.7</v>
       </c>
       <c r="F11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>41.4</v>
+        <v>7.5</v>
       </c>
       <c r="K11" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N11" t="n">
-        <v>38.4</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q11" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z11" t="n">
         <v>23</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="T11" t="n">
-        <v>23</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>16.1</v>
-      </c>
       <c r="AA11" t="n">
-        <v>10.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>224.34</v>
+        <v>235.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01</v>
+        <v>3.09</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1669,10 +1531,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>128.93</v>
+        <v>137.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.44</v>
+        <v>3.06</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1680,73 +1542,61 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
-      <c r="AP11" t="n">
-        <v>89.06999999999999</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>15.43</v>
-      </c>
       <c r="BL11" s="1" t="n">
-        <v>46210</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46211</v>
+        <v>46221</v>
       </c>
       <c r="B12" t="n">
-        <v>157.8</v>
-      </c>
-      <c r="C12" t="n">
-        <v>85.59999999999999</v>
+        <v>138.5</v>
       </c>
       <c r="D12" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>30.3</v>
+        <v>31.7</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>98.7</v>
+        <v>91</v>
       </c>
       <c r="O12" t="n">
-        <v>40.5</v>
+        <v>37.8</v>
       </c>
       <c r="V12" t="n">
-        <v>4.6</v>
+        <v>13.2</v>
       </c>
       <c r="W12" t="n">
-        <v>19.7</v>
+        <v>22.5</v>
       </c>
       <c r="X12" t="n">
-        <v>12.1</v>
+        <v>17.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA12" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>231.46</v>
+        <v>231.99</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.7</v>
+        <v>-3.41</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1755,10 +1605,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>129.8</v>
+        <v>136.12</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.87</v>
+        <v>-1.38</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1767,66 +1617,93 @@
         <v>142</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46211</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46212</v>
+        <v>46222</v>
       </c>
       <c r="B13" t="n">
-        <v>151.6</v>
+        <v>161.1</v>
       </c>
       <c r="C13" t="n">
-        <v>73.8</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>31.9</v>
       </c>
       <c r="E13" t="n">
-        <v>33.9</v>
+        <v>31.5</v>
       </c>
       <c r="F13" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>41.1</v>
       </c>
       <c r="K13" t="n">
-        <v>97.5</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>35</v>
       </c>
       <c r="O13" t="n">
-        <v>40.6</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>20.5</v>
       </c>
       <c r="V13" t="n">
-        <v>8.1</v>
+        <v>14.1</v>
       </c>
       <c r="W13" t="n">
-        <v>22.3</v>
+        <v>19.3</v>
       </c>
       <c r="X13" t="n">
-        <v>15.2</v>
+        <v>16.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>-3.1</v>
+        <v>-3.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>229.92</v>
+        <v>225.51</v>
       </c>
       <c r="AG13" t="n">
-        <v>-1.54</v>
+        <v>-6.48</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1835,10 +1712,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>133.01</v>
+        <v>133.83</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.21</v>
+        <v>-2.29</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1846,67 +1723,100 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
+      <c r="AP13" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL13" s="1" t="n">
-        <v>46212</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46213</v>
+        <v>46223</v>
       </c>
       <c r="B14" t="n">
-        <v>157.5</v>
+        <v>176.4</v>
       </c>
       <c r="C14" t="n">
-        <v>76.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>27.1</v>
+        <v>32.7</v>
       </c>
       <c r="E14" t="n">
-        <v>36.9</v>
+        <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>41.5</v>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>76</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>36.4</v>
       </c>
       <c r="O14" t="n">
-        <v>38</v>
+        <v>39.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>14</v>
+      </c>
+      <c r="T14" t="n">
+        <v>22.3</v>
       </c>
       <c r="V14" t="n">
-        <v>6.7</v>
+        <v>11.5</v>
       </c>
       <c r="W14" t="n">
-        <v>20.8</v>
+        <v>15.5</v>
       </c>
       <c r="X14" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
         <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>-2.3</v>
+        <v>-5.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.1</v>
+        <v>-1.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>226.95</v>
+        <v>220.92</v>
       </c>
       <c r="AG14" t="n">
-        <v>-2.97</v>
+        <v>-4.59</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1915,10 +1825,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>128.4</v>
+        <v>131.85</v>
       </c>
       <c r="AL14" t="n">
-        <v>-4.61</v>
+        <v>-1.98</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1926,67 +1836,100 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
+      <c r="AP14" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>15.49</v>
+      </c>
       <c r="BL14" s="1" t="n">
-        <v>46213</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46214</v>
+        <v>46224</v>
       </c>
       <c r="B15" t="n">
-        <v>148.5</v>
+        <v>181</v>
       </c>
       <c r="C15" t="n">
-        <v>70.5</v>
+        <v>80.7</v>
       </c>
       <c r="D15" t="n">
-        <v>26.8</v>
+        <v>33</v>
       </c>
       <c r="E15" t="n">
-        <v>34.3</v>
+        <v>35.1</v>
       </c>
       <c r="F15" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>41.9</v>
       </c>
       <c r="K15" t="n">
-        <v>98.2</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N15" t="n">
+        <v>36.9</v>
       </c>
       <c r="O15" t="n">
         <v>39.8</v>
       </c>
+      <c r="Q15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>22.5</v>
+      </c>
       <c r="V15" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="W15" t="n">
-        <v>21.7</v>
+        <v>13</v>
       </c>
       <c r="X15" t="n">
-        <v>16.4</v>
+        <v>11.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA15" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1.9</v>
+        <v>-6.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.6</v>
+        <v>-0.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>223.11</v>
+        <v>220.92</v>
       </c>
       <c r="AG15" t="n">
-        <v>-3.83</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1995,10 +1938,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>124.76</v>
+        <v>130.06</v>
       </c>
       <c r="AL15" t="n">
-        <v>-3.64</v>
+        <v>-1.79</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2006,61 +1949,100 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
+      <c r="AP15" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>14.93</v>
+      </c>
       <c r="BL15" s="1" t="n">
-        <v>46214</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46215</v>
+        <v>46225</v>
       </c>
       <c r="B16" t="n">
-        <v>147.5</v>
+        <v>179.6</v>
       </c>
       <c r="C16" t="n">
-        <v>72.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.7</v>
+        <v>30.3</v>
       </c>
       <c r="E16" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="F16" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>42.3</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>37.1</v>
       </c>
       <c r="O16" t="n">
-        <v>40.2</v>
+        <v>41.4</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>22.6</v>
       </c>
       <c r="V16" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="W16" t="n">
-        <v>16.8</v>
+        <v>15.6</v>
       </c>
       <c r="X16" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z16" t="n">
         <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.7</v>
+        <v>-3.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>216.02</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2069,10 +2051,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>127.2</v>
+        <v>127.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.44</v>
+        <v>-2.21</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2080,94 +2062,100 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
+      <c r="AP16" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>15.16</v>
+      </c>
       <c r="BL16" s="1" t="n">
-        <v>46215</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="B17" t="n">
-        <v>183.5</v>
+        <v>170.4</v>
       </c>
       <c r="C17" t="n">
-        <v>84.5</v>
+        <v>78.5</v>
       </c>
       <c r="D17" t="n">
-        <v>31.5</v>
+        <v>29.8</v>
       </c>
       <c r="E17" t="n">
-        <v>34.6</v>
+        <v>29.7</v>
       </c>
       <c r="F17" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H17" t="n">
-        <v>23.9</v>
+        <v>22.5</v>
       </c>
       <c r="I17" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="J17" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="K17" t="n">
-        <v>76.3</v>
+        <v>75</v>
       </c>
       <c r="M17" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="N17" t="n">
-        <v>37.7</v>
+        <v>36.6</v>
       </c>
       <c r="O17" t="n">
-        <v>41.8</v>
+        <v>41.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="R17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X17" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.8</v>
       </c>
-      <c r="S17" t="n">
-        <v>18</v>
-      </c>
-      <c r="T17" t="n">
-        <v>23</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W17" t="n">
-        <v>20</v>
-      </c>
-      <c r="X17" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AC17" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>220.36</v>
+        <v>216.02</v>
       </c>
       <c r="AG17" t="n">
-        <v>-3.75</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2176,10 +2164,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>127.13</v>
+        <v>128.54</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2188,99 +2176,66 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>76.90000000000001</v>
+        <v>84.73</v>
       </c>
       <c r="AS17" t="n">
-        <v>14.17</v>
+        <v>15.34</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46216</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46217</v>
+        <v>46227</v>
       </c>
       <c r="B18" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>79.2</v>
+        <v>156</v>
       </c>
       <c r="D18" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E18" t="n">
-        <v>34.6</v>
+        <v>30.1</v>
       </c>
       <c r="F18" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I18" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>41.9</v>
+        <v>6.8</v>
       </c>
       <c r="K18" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M18" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="O18" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="X18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC18" t="n">
         <v>5</v>
       </c>
-      <c r="N18" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="O18" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S18" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X18" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>7.9</v>
-      </c>
       <c r="AD18" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>219.64</v>
+        <v>224.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.72</v>
+        <v>2.32</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2289,10 +2244,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>126.03</v>
+        <v>130.92</v>
       </c>
       <c r="AL18" t="n">
-        <v>-1.1</v>
+        <v>2.38</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2300,100 +2255,61 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
-      <c r="AP18" t="n">
-        <v>82.95</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>14.55</v>
-      </c>
       <c r="BL18" s="1" t="n">
-        <v>46217</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46218</v>
+        <v>46228</v>
       </c>
       <c r="B19" t="n">
-        <v>168.1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>69.7</v>
+        <v>147.8</v>
       </c>
       <c r="D19" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>33.9</v>
+        <v>32</v>
       </c>
       <c r="F19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H19" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>41.2</v>
+        <v>6.8</v>
       </c>
       <c r="K19" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M19" t="n">
-        <v>5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>38.1</v>
+        <v>96.5</v>
       </c>
       <c r="O19" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>22.6</v>
+        <v>39.3</v>
       </c>
       <c r="V19" t="n">
-        <v>11.2</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="X19" t="n">
-        <v>17</v>
+        <v>15.2</v>
       </c>
       <c r="Y19" t="n">
         <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
-        <v>14.9</v>
+        <v>13.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>224.93</v>
+        <v>230.27</v>
       </c>
       <c r="AG19" t="n">
-        <v>5.29</v>
+        <v>5.74</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2402,10 +2318,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>129.28</v>
+        <v>132.76</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.25</v>
+        <v>1.84</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2413,100 +2329,94 @@
       <c r="AN19" t="n">
         <v>142</v>
       </c>
-      <c r="AP19" t="n">
-        <v>87.43000000000001</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>15.25</v>
-      </c>
       <c r="BL19" s="1" t="n">
-        <v>46218</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46219</v>
+        <v>46229</v>
       </c>
       <c r="B20" t="n">
-        <v>158.9</v>
+        <v>149.1</v>
       </c>
       <c r="C20" t="n">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>31.1</v>
+        <v>29</v>
       </c>
       <c r="E20" t="n">
-        <v>30.4</v>
+        <v>25.9</v>
       </c>
       <c r="F20" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="H20" t="n">
-        <v>23.7</v>
+        <v>24</v>
       </c>
       <c r="I20" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="J20" t="n">
-        <v>41</v>
+        <v>38.8</v>
       </c>
       <c r="K20" t="n">
-        <v>75.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>37.8</v>
+        <v>36.7</v>
       </c>
       <c r="O20" t="n">
-        <v>41.4</v>
+        <v>40.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="V20" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="W20" t="n">
-        <v>26</v>
+        <v>24.4</v>
       </c>
       <c r="X20" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
         <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.3</v>
+        <v>15.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.4</v>
+        <v>-2.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>6.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.5</v>
+        <v>-0.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>232.31</v>
+        <v>237.43</v>
       </c>
       <c r="AG20" t="n">
-        <v>9.67</v>
+        <v>7.16</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2515,10 +2425,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>134.44</v>
+        <v>134.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.16</v>
+        <v>2.19</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2527,66 +2437,66 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>91.73999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="AS20" t="n">
-        <v>17.07</v>
+        <v>16.95</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46219</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="B21" t="n">
-        <v>136.7</v>
+        <v>143.9</v>
       </c>
       <c r="D21" t="n">
-        <v>30.7</v>
+        <v>32.9</v>
       </c>
       <c r="F21" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="K21" t="n">
-        <v>92.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="O21" t="n">
-        <v>39.2</v>
+        <v>37.9</v>
       </c>
       <c r="V21" t="n">
-        <v>17.1</v>
+        <v>10</v>
       </c>
       <c r="W21" t="n">
-        <v>36.1</v>
+        <v>25.6</v>
       </c>
       <c r="X21" t="n">
-        <v>26.6</v>
+        <v>17.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.5</v>
+        <v>16</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.6</v>
+        <v>-1.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="AF21" t="n">
-        <v>235.4</v>
+        <v>236.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.09</v>
+        <v>-1.29</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2595,10 +2505,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>137.5</v>
+        <v>136.28</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.06</v>
+        <v>1.33</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2607,60 +2517,93 @@
         <v>142</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46220</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46221</v>
+        <v>46231</v>
       </c>
       <c r="B22" t="n">
-        <v>138.5</v>
+        <v>166.4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>63.7</v>
       </c>
       <c r="D22" t="n">
-        <v>31.7</v>
+        <v>34.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>36.4</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>7.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>39.9</v>
       </c>
       <c r="K22" t="n">
-        <v>91</v>
+        <v>75.2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>35.9</v>
       </c>
       <c r="O22" t="n">
-        <v>37.8</v>
+        <v>39</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S22" t="n">
+        <v>6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>20.3</v>
       </c>
       <c r="V22" t="n">
-        <v>13.2</v>
+        <v>11.9</v>
       </c>
       <c r="W22" t="n">
-        <v>22.5</v>
+        <v>27</v>
       </c>
       <c r="X22" t="n">
-        <v>17.9</v>
+        <v>19.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="n">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>-1.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.7</v>
+        <v>-0.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>231.99</v>
+        <v>236.13</v>
       </c>
       <c r="AG22" t="n">
-        <v>-3.41</v>
+        <v>-0.01</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2669,10 +2612,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>136.12</v>
+        <v>134.54</v>
       </c>
       <c r="AL22" t="n">
-        <v>-1.38</v>
+        <v>-1.74</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2680,70 +2623,76 @@
       <c r="AN22" t="n">
         <v>142</v>
       </c>
+      <c r="AP22" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL22" s="1" t="n">
-        <v>46221</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46222</v>
+        <v>46232</v>
       </c>
       <c r="B23" t="n">
-        <v>161.1</v>
+        <v>172.9</v>
       </c>
       <c r="C23" t="n">
-        <v>67</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>31.9</v>
+        <v>34.9</v>
       </c>
       <c r="E23" t="n">
-        <v>31.5</v>
+        <v>35.2</v>
       </c>
       <c r="F23" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="H23" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="I23" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="J23" t="n">
-        <v>41.1</v>
+        <v>41.7</v>
       </c>
       <c r="K23" t="n">
-        <v>75.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="M23" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="N23" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="O23" t="n">
         <v>37.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
       <c r="V23" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="W23" t="n">
-        <v>19.3</v>
+        <v>18.7</v>
       </c>
       <c r="X23" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="Y23" t="n">
         <v>9</v>
@@ -2752,22 +2701,22 @@
         <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>-3.8</v>
+        <v>-4.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>225.51</v>
+        <v>218.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>-6.48</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2776,10 +2725,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>133.83</v>
+        <v>130.39</v>
       </c>
       <c r="AL23" t="n">
-        <v>-2.29</v>
+        <v>-4.15</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2788,99 +2737,99 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>82.93000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>15.73</v>
+        <v>15.79</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46222</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46223</v>
+        <v>46233</v>
       </c>
       <c r="B24" t="n">
-        <v>176.4</v>
+        <v>157.5</v>
       </c>
       <c r="C24" t="n">
-        <v>77.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D24" t="n">
-        <v>32.7</v>
+        <v>33.2</v>
       </c>
       <c r="E24" t="n">
-        <v>35</v>
+        <v>27.7</v>
       </c>
       <c r="F24" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="H24" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="I24" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="J24" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="K24" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="N24" t="n">
-        <v>36.4</v>
+        <v>34.9</v>
       </c>
       <c r="O24" t="n">
-        <v>39.1</v>
+        <v>37.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T24" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="V24" t="n">
-        <v>11.5</v>
+        <v>15.1</v>
       </c>
       <c r="W24" t="n">
-        <v>15.5</v>
+        <v>23.1</v>
       </c>
       <c r="X24" t="n">
-        <v>13.5</v>
+        <v>19.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>11.6</v>
+        <v>13.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>-5.6</v>
+        <v>-0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD24" t="n">
-        <v>-1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>220.92</v>
+        <v>218.84</v>
       </c>
       <c r="AG24" t="n">
-        <v>-4.59</v>
+        <v>0.25</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2889,10 +2838,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>131.85</v>
+        <v>133.09</v>
       </c>
       <c r="AL24" t="n">
-        <v>-1.98</v>
+        <v>2.7</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2901,99 +2850,66 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>79.75</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS24" t="n">
-        <v>15.49</v>
+        <v>15.63</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46223</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46224</v>
+        <v>46234</v>
       </c>
       <c r="B25" t="n">
-        <v>181</v>
-      </c>
-      <c r="C25" t="n">
-        <v>80.7</v>
+        <v>137.6</v>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
-      </c>
-      <c r="E25" t="n">
+        <v>35</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="O25" t="n">
         <v>35.1</v>
       </c>
-      <c r="F25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I25" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="K25" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N25" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="O25" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>22.5</v>
-      </c>
       <c r="V25" t="n">
-        <v>10.6</v>
+        <v>13.6</v>
       </c>
       <c r="W25" t="n">
-        <v>13</v>
+        <v>24.4</v>
       </c>
       <c r="X25" t="n">
-        <v>11.8</v>
+        <v>19</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="n">
-        <v>11.4</v>
+        <v>17.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>-6.1</v>
+        <v>-0</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.9</v>
+        <v>2.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>220.92</v>
+        <v>221.78</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3002,10 +2918,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>130.06</v>
+        <v>138.76</v>
       </c>
       <c r="AL25" t="n">
-        <v>-1.79</v>
+        <v>5.67</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3013,100 +2929,61 @@
       <c r="AN25" t="n">
         <v>142</v>
       </c>
-      <c r="AP25" t="n">
-        <v>79.94</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>14.93</v>
-      </c>
       <c r="BL25" s="1" t="n">
-        <v>46224</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46225</v>
+        <v>46235</v>
       </c>
       <c r="B26" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="C26" t="n">
-        <v>81.90000000000001</v>
+        <v>132.5</v>
       </c>
       <c r="D26" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E26" t="n">
-        <v>31.1</v>
+        <v>33.6</v>
       </c>
       <c r="F26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H26" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I26" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>42.3</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>37.1</v>
+        <v>97.8</v>
       </c>
       <c r="O26" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2</v>
-      </c>
-      <c r="S26" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>22.6</v>
+        <v>31.6</v>
       </c>
       <c r="V26" t="n">
-        <v>9.6</v>
+        <v>14.8</v>
       </c>
       <c r="W26" t="n">
-        <v>15.6</v>
+        <v>24.7</v>
       </c>
       <c r="X26" t="n">
-        <v>12.6</v>
+        <v>19.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z26" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA26" t="n">
-        <v>11.1</v>
+        <v>16.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>-3.4</v>
+        <v>0.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>216.02</v>
+        <v>224.78</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3115,10 +2992,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>127.85</v>
+        <v>143.55</v>
       </c>
       <c r="AL26" t="n">
-        <v>-2.21</v>
+        <v>4.79</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3126,100 +3003,94 @@
       <c r="AN26" t="n">
         <v>142</v>
       </c>
-      <c r="AP26" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>15.16</v>
-      </c>
       <c r="BL26" s="1" t="n">
-        <v>46225</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46226</v>
+        <v>46236</v>
       </c>
       <c r="B27" t="n">
-        <v>170.4</v>
+        <v>137.2</v>
       </c>
       <c r="C27" t="n">
-        <v>78.5</v>
+        <v>56.3</v>
       </c>
       <c r="D27" t="n">
-        <v>29.8</v>
+        <v>32.1</v>
       </c>
       <c r="E27" t="n">
-        <v>29.7</v>
+        <v>21.2</v>
       </c>
       <c r="F27" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="H27" t="n">
-        <v>22.5</v>
+        <v>23.7</v>
       </c>
       <c r="I27" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="J27" t="n">
-        <v>41.4</v>
+        <v>40.4</v>
       </c>
       <c r="K27" t="n">
-        <v>75</v>
+        <v>75.7</v>
       </c>
       <c r="M27" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
-        <v>36.6</v>
+        <v>29</v>
       </c>
       <c r="O27" t="n">
-        <v>41.3</v>
+        <v>32.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>23.3</v>
+        <v>21.6</v>
       </c>
       <c r="R27" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>23.3</v>
+        <v>21.6</v>
       </c>
       <c r="V27" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W27" t="n">
-        <v>15.7</v>
+        <v>24.3</v>
       </c>
       <c r="X27" t="n">
-        <v>12.6</v>
+        <v>17.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA27" t="n">
-        <v>12.7</v>
+        <v>15.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>216.02</v>
+        <v>232.22</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>7.43</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3228,10 +3099,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>128.54</v>
+        <v>143.61</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3240,66 +3111,99 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>84.73</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>15.34</v>
+        <v>18.02</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46226</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="B28" t="n">
-        <v>156</v>
+        <v>157.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>59.6</v>
       </c>
       <c r="D28" t="n">
-        <v>30.1</v>
+        <v>35</v>
+      </c>
+      <c r="E28" t="n">
+        <v>30.6</v>
       </c>
       <c r="F28" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>38.9</v>
       </c>
       <c r="K28" t="n">
-        <v>95.90000000000001</v>
+        <v>74.3</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N28" t="n">
+        <v>33.4</v>
       </c>
       <c r="O28" t="n">
-        <v>39.2</v>
+        <v>37.1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>21.1</v>
       </c>
       <c r="V28" t="n">
-        <v>7.1</v>
+        <v>13</v>
       </c>
       <c r="W28" t="n">
-        <v>20.9</v>
+        <v>26.3</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>19.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA28" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>224.53</v>
+        <v>229.69</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.32</v>
+        <v>-2.53</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3308,10 +3212,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>130.92</v>
+        <v>136.96</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.38</v>
+        <v>-6.65</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3319,61 +3223,100 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
+      <c r="AP28" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>16.96</v>
+      </c>
       <c r="BL28" s="1" t="n">
-        <v>46227</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46228</v>
+        <v>46238</v>
       </c>
       <c r="B29" t="n">
-        <v>147.8</v>
+        <v>159.6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>63</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>34.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>31.1</v>
       </c>
       <c r="F29" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>40.5</v>
       </c>
       <c r="K29" t="n">
-        <v>96.5</v>
+        <v>75.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>34.3</v>
       </c>
       <c r="O29" t="n">
-        <v>39.3</v>
+        <v>38.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>21.3</v>
       </c>
       <c r="V29" t="n">
-        <v>8</v>
+        <v>17.5</v>
       </c>
       <c r="W29" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="X29" t="n">
-        <v>15.2</v>
+        <v>20</v>
       </c>
       <c r="Y29" t="n">
         <v>11</v>
       </c>
       <c r="Z29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA29" t="n">
         <v>13.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AC29" t="n">
         <v>4.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>230.27</v>
+        <v>228.57</v>
       </c>
       <c r="AG29" t="n">
-        <v>5.74</v>
+        <v>-1.14</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3382,10 +3325,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>132.76</v>
+        <v>133.01</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.84</v>
+        <v>-3.95</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3393,94 +3336,100 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
+      <c r="AP29" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>15.95</v>
+      </c>
       <c r="BL29" s="1" t="n">
-        <v>46228</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46229</v>
+        <v>46239</v>
       </c>
       <c r="B30" t="n">
-        <v>149.1</v>
+        <v>160.4</v>
       </c>
       <c r="C30" t="n">
-        <v>60</v>
+        <v>62.6</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E30" t="n">
-        <v>25.9</v>
+        <v>32.2</v>
       </c>
       <c r="F30" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="H30" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="I30" t="n">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="J30" t="n">
-        <v>38.8</v>
+        <v>41.1</v>
       </c>
       <c r="K30" t="n">
-        <v>74.5</v>
+        <v>75.7</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="N30" t="n">
-        <v>36.7</v>
+        <v>32.6</v>
       </c>
       <c r="O30" t="n">
-        <v>40.1</v>
+        <v>38</v>
       </c>
       <c r="Q30" t="n">
-        <v>21.7</v>
+        <v>20.9</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T30" t="n">
-        <v>21.7</v>
+        <v>20.9</v>
       </c>
       <c r="V30" t="n">
-        <v>10.3</v>
+        <v>16.4</v>
       </c>
       <c r="W30" t="n">
-        <v>24.4</v>
+        <v>22.8</v>
       </c>
       <c r="X30" t="n">
-        <v>17.4</v>
+        <v>19.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AA30" t="n">
-        <v>15.7</v>
+        <v>14.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>-2.4</v>
+        <v>-3.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.1</v>
+        <v>0.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>237.43</v>
+        <v>225.08</v>
       </c>
       <c r="AG30" t="n">
-        <v>7.16</v>
+        <v>-3.5</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3489,10 +3438,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>134.95</v>
+        <v>135.24</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3501,66 +3450,99 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>91.28</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS30" t="n">
-        <v>16.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46229</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46230</v>
+        <v>46240</v>
       </c>
       <c r="B31" t="n">
-        <v>143.9</v>
+        <v>161.7</v>
+      </c>
+      <c r="C31" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>32.9</v>
+        <v>34.9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>27.3</v>
       </c>
       <c r="F31" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>42.6</v>
       </c>
       <c r="K31" t="n">
-        <v>96.2</v>
+        <v>77</v>
+      </c>
+      <c r="M31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N31" t="n">
+        <v>31.5</v>
       </c>
       <c r="O31" t="n">
-        <v>37.9</v>
+        <v>37.3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>21</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="n">
+        <v>21</v>
       </c>
       <c r="V31" t="n">
-        <v>10</v>
+        <v>12.7</v>
       </c>
       <c r="W31" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X31" t="n">
-        <v>17.8</v>
+        <v>19.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z31" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA31" t="n">
-        <v>16</v>
+        <v>11.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>-1.4</v>
+        <v>-5.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>236.14</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="n">
-        <v>-1.29</v>
+        <v>-0.08</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3569,10 +3551,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>136.28</v>
+        <v>134.62</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.33</v>
+        <v>-0.62</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3580,94 +3562,61 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
+      <c r="AP31" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>13.86</v>
+      </c>
       <c r="BL31" s="1" t="n">
-        <v>46230</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46231</v>
+        <v>46241</v>
       </c>
       <c r="B32" t="n">
-        <v>166.4</v>
-      </c>
-      <c r="C32" t="n">
-        <v>63.7</v>
+        <v>151.5</v>
       </c>
       <c r="D32" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E32" t="n">
-        <v>36.4</v>
+        <v>35.1</v>
       </c>
       <c r="F32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H32" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I32" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J32" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="O32" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S32" t="n">
-        <v>6</v>
-      </c>
-      <c r="T32" t="n">
-        <v>20.3</v>
+        <v>5.4</v>
       </c>
       <c r="V32" t="n">
-        <v>11.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X32" t="n">
-        <v>19.4</v>
+        <v>14</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z32" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA32" t="n">
-        <v>14.4</v>
+        <v>9</v>
       </c>
       <c r="AB32" t="n">
-        <v>-3.5</v>
+        <v>-4.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>236.13</v>
+        <v>221.37</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3676,10 +3625,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>134.54</v>
+        <v>135.21</v>
       </c>
       <c r="AL32" t="n">
-        <v>-1.74</v>
+        <v>0.59</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3687,100 +3636,61 @@
       <c r="AN32" t="n">
         <v>142</v>
       </c>
-      <c r="AP32" t="n">
-        <v>82.27</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>16.28</v>
-      </c>
       <c r="BL32" s="1" t="n">
-        <v>46231</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46232</v>
+        <v>46242</v>
       </c>
       <c r="B33" t="n">
-        <v>172.9</v>
-      </c>
-      <c r="C33" t="n">
-        <v>67.59999999999999</v>
+        <v>145.2</v>
       </c>
       <c r="D33" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E33" t="n">
-        <v>35.2</v>
+        <v>33.5</v>
       </c>
       <c r="F33" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H33" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I33" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J33" t="n">
-        <v>41.7</v>
+        <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="M33" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="AC33" t="n">
         <v>2.4</v>
       </c>
-      <c r="N33" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>19</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="n">
-        <v>19</v>
-      </c>
-      <c r="V33" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W33" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X33" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AD33" t="n">
-        <v>-0.7</v>
+        <v>-1.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>218.6</v>
+        <v>224.37</v>
       </c>
       <c r="AG33" t="n">
-        <v>-9.380000000000001</v>
+        <v>3</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3789,10 +3699,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>130.39</v>
+        <v>135.61</v>
       </c>
       <c r="AL33" t="n">
-        <v>-4.15</v>
+        <v>0.4</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3800,100 +3710,61 @@
       <c r="AN33" t="n">
         <v>142</v>
       </c>
-      <c r="AP33" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>15.79</v>
-      </c>
       <c r="BL33" s="1" t="n">
-        <v>46232</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46233</v>
+        <v>46243</v>
       </c>
       <c r="B34" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C34" t="n">
-        <v>68.5</v>
+        <v>146.3</v>
       </c>
       <c r="D34" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>27.7</v>
+        <v>33.4</v>
       </c>
       <c r="F34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H34" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J34" t="n">
-        <v>41.4</v>
+        <v>5.5</v>
       </c>
       <c r="K34" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N34" t="n">
-        <v>34.9</v>
+        <v>98.2</v>
       </c>
       <c r="O34" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W34" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X34" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA34" t="n">
         <v>9</v>
       </c>
-      <c r="T34" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V34" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>13.6</v>
-      </c>
       <c r="AB34" t="n">
-        <v>-0</v>
+        <v>-6.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>3</v>
+        <v>-0.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF34" t="n">
-        <v>218.84</v>
+        <v>225.93</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.25</v>
+        <v>1.56</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3902,10 +3773,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>133.09</v>
+        <v>135.28</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.7</v>
+        <v>-0.33</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3913,67 +3784,94 @@
       <c r="AN34" t="n">
         <v>142</v>
       </c>
-      <c r="AP34" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL34" s="1" t="n">
-        <v>46233</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B35" t="n">
-        <v>137.6</v>
+        <v>182.8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>86.8</v>
       </c>
       <c r="D35" t="n">
-        <v>35</v>
+        <v>31.8</v>
+      </c>
+      <c r="E35" t="n">
+        <v>33</v>
       </c>
       <c r="F35" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>41.1</v>
       </c>
       <c r="K35" t="n">
-        <v>96.7</v>
+        <v>74.2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N35" t="n">
+        <v>33.5</v>
       </c>
       <c r="O35" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="n">
+        <v>22.4</v>
       </c>
       <c r="V35" t="n">
-        <v>13.6</v>
+        <v>9.1</v>
       </c>
       <c r="W35" t="n">
-        <v>24.4</v>
+        <v>15</v>
       </c>
       <c r="X35" t="n">
-        <v>19</v>
+        <v>12.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Z35" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AA35" t="n">
-        <v>17.5</v>
+        <v>8.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0</v>
+        <v>-10.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.5</v>
+        <v>0.3</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.8</v>
+        <v>-5.1</v>
       </c>
       <c r="AF35" t="n">
-        <v>221.78</v>
+        <v>218.63</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.94</v>
+        <v>-7.3</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3982,10 +3880,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>138.76</v>
+        <v>126.27</v>
       </c>
       <c r="AL35" t="n">
-        <v>5.67</v>
+        <v>-9.01</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3993,61 +3891,100 @@
       <c r="AN35" t="n">
         <v>142</v>
       </c>
+      <c r="AP35" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL35" s="1" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46235</v>
+        <v>46245</v>
       </c>
       <c r="B36" t="n">
-        <v>132.5</v>
+        <v>181.8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>86.5</v>
       </c>
       <c r="D36" t="n">
-        <v>33.6</v>
+        <v>31.4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>34.2</v>
       </c>
       <c r="F36" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>41.9</v>
       </c>
       <c r="K36" t="n">
-        <v>97.8</v>
+        <v>76.8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>35.7</v>
       </c>
       <c r="O36" t="n">
-        <v>31.6</v>
+        <v>39.8</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>23</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>23</v>
       </c>
       <c r="V36" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W36" t="n">
         <v>14.8</v>
       </c>
-      <c r="W36" t="n">
-        <v>24.7</v>
-      </c>
       <c r="X36" t="n">
-        <v>19.8</v>
+        <v>10.9</v>
       </c>
       <c r="Y36" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Z36" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AA36" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.6</v>
+        <v>-4.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF36" t="n">
-        <v>224.78</v>
+        <v>216.39</v>
       </c>
       <c r="AG36" t="n">
-        <v>3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4056,10 +3993,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>143.55</v>
+        <v>123.32</v>
       </c>
       <c r="AL36" t="n">
-        <v>4.79</v>
+        <v>-2.95</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4067,94 +4004,100 @@
       <c r="AN36" t="n">
         <v>142</v>
       </c>
+      <c r="AP36" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>13.91</v>
+      </c>
       <c r="BL36" s="1" t="n">
-        <v>46235</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46236</v>
+        <v>46246</v>
       </c>
       <c r="B37" t="n">
-        <v>137.2</v>
+        <v>183</v>
       </c>
       <c r="C37" t="n">
-        <v>56.3</v>
+        <v>84.7</v>
       </c>
       <c r="D37" t="n">
-        <v>32.1</v>
+        <v>30.9</v>
       </c>
       <c r="E37" t="n">
-        <v>21.2</v>
+        <v>33.7</v>
       </c>
       <c r="F37" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="H37" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="I37" t="n">
-        <v>11.6</v>
+        <v>10.6</v>
       </c>
       <c r="J37" t="n">
-        <v>40.4</v>
+        <v>42.3</v>
       </c>
       <c r="K37" t="n">
-        <v>75.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>29</v>
+        <v>36.7</v>
       </c>
       <c r="O37" t="n">
-        <v>32.6</v>
+        <v>40.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>21.6</v>
+        <v>23.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="T37" t="n">
-        <v>21.6</v>
+        <v>23.6</v>
       </c>
       <c r="V37" t="n">
-        <v>10.7</v>
+        <v>5.7</v>
       </c>
       <c r="W37" t="n">
-        <v>24.3</v>
+        <v>16.1</v>
       </c>
       <c r="X37" t="n">
-        <v>17.5</v>
+        <v>10.9</v>
       </c>
       <c r="Y37" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z37" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA37" t="n">
-        <v>15.4</v>
+        <v>10</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>232.22</v>
+        <v>217.16</v>
       </c>
       <c r="AG37" t="n">
-        <v>7.43</v>
+        <v>0.76</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4163,10 +4106,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>143.61</v>
+        <v>117.87</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.06</v>
+        <v>-5.45</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4175,99 +4118,66 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>89.31999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="AS37" t="n">
-        <v>18.02</v>
+        <v>13.45</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46236</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="B38" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C38" t="n">
-        <v>59.6</v>
+        <v>163.8</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
-      </c>
-      <c r="E38" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F38" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H38" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I38" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J38" t="n">
-        <v>38.9</v>
+        <v>6.5</v>
       </c>
       <c r="K38" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N38" t="n">
-        <v>33.4</v>
+        <v>101.2</v>
       </c>
       <c r="O38" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>21.1</v>
+        <v>40.2</v>
       </c>
       <c r="V38" t="n">
-        <v>13</v>
+        <v>6.3</v>
       </c>
       <c r="W38" t="n">
-        <v>26.3</v>
+        <v>17.2</v>
       </c>
       <c r="X38" t="n">
-        <v>19.6</v>
+        <v>11.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Z38" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA38" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AB38" t="n">
-        <v>-2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AC38" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD38" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>229.69</v>
+        <v>220.31</v>
       </c>
       <c r="AG38" t="n">
-        <v>-2.53</v>
+        <v>3.16</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4276,10 +4186,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>136.96</v>
+        <v>116.52</v>
       </c>
       <c r="AL38" t="n">
-        <v>-6.65</v>
+        <v>-1.35</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4287,100 +4197,61 @@
       <c r="AN38" t="n">
         <v>142</v>
       </c>
-      <c r="AP38" t="n">
-        <v>86.59</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>16.96</v>
-      </c>
       <c r="BL38" s="1" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="B39" t="n">
-        <v>159.6</v>
-      </c>
-      <c r="C39" t="n">
-        <v>63</v>
+        <v>155.9</v>
       </c>
       <c r="D39" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>31.1</v>
+        <v>28</v>
       </c>
       <c r="F39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="V39" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W39" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X39" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC39" t="n">
         <v>5.7</v>
       </c>
-      <c r="H39" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I39" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J39" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="K39" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="M39" t="n">
-        <v>4</v>
-      </c>
-      <c r="N39" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O39" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="V39" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X39" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AD39" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>228.57</v>
+        <v>221.99</v>
       </c>
       <c r="AG39" t="n">
-        <v>-1.14</v>
+        <v>1.67</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4389,10 +4260,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>133.01</v>
+        <v>116.37</v>
       </c>
       <c r="AL39" t="n">
-        <v>-3.95</v>
+        <v>-0.15</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4400,100 +4271,61 @@
       <c r="AN39" t="n">
         <v>142</v>
       </c>
-      <c r="AP39" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>15.95</v>
-      </c>
       <c r="BL39" s="1" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46239</v>
+        <v>46249</v>
       </c>
       <c r="B40" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="C40" t="n">
-        <v>62.6</v>
+        <v>141.3</v>
       </c>
       <c r="D40" t="n">
-        <v>35</v>
-      </c>
-      <c r="E40" t="n">
-        <v>32.2</v>
+        <v>26.3</v>
       </c>
       <c r="F40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H40" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I40" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J40" t="n">
-        <v>41.1</v>
+        <v>5.5</v>
       </c>
       <c r="K40" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M40" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N40" t="n">
-        <v>32.6</v>
+        <v>97.8</v>
       </c>
       <c r="O40" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R40" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S40" t="n">
-        <v>8</v>
-      </c>
-      <c r="T40" t="n">
-        <v>20.9</v>
+        <v>39.8</v>
       </c>
       <c r="V40" t="n">
-        <v>16.4</v>
+        <v>9.5</v>
       </c>
       <c r="W40" t="n">
-        <v>22.8</v>
+        <v>17.7</v>
       </c>
       <c r="X40" t="n">
-        <v>19.6</v>
+        <v>13.6</v>
       </c>
       <c r="Y40" t="n">
         <v>13</v>
       </c>
       <c r="Z40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA40" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="AB40" t="n">
-        <v>-3.1</v>
+        <v>0.2</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="AF40" t="n">
-        <v>225.08</v>
+        <v>225.14</v>
       </c>
       <c r="AG40" t="n">
-        <v>-3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4501,112 +4333,61 @@
       <c r="AI40" t="n">
         <v>235</v>
       </c>
-      <c r="AK40" t="n">
-        <v>135.24</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AM40" t="n">
         <v>110</v>
       </c>
       <c r="AN40" t="n">
         <v>142</v>
       </c>
-      <c r="AP40" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>15.4</v>
-      </c>
       <c r="BL40" s="1" t="n">
-        <v>46239</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46240</v>
+        <v>46250</v>
       </c>
       <c r="B41" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C41" t="n">
-        <v>71.09999999999999</v>
+        <v>131.5</v>
       </c>
       <c r="D41" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E41" t="n">
         <v>27.3</v>
       </c>
       <c r="F41" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H41" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J41" t="n">
-        <v>42.6</v>
+        <v>5.5</v>
       </c>
       <c r="K41" t="n">
-        <v>77</v>
-      </c>
-      <c r="M41" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N41" t="n">
-        <v>31.5</v>
+        <v>97</v>
       </c>
       <c r="O41" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>21</v>
-      </c>
-      <c r="R41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S41" t="n">
-        <v>6</v>
-      </c>
-      <c r="T41" t="n">
-        <v>21</v>
+        <v>35.7</v>
       </c>
       <c r="V41" t="n">
-        <v>12.7</v>
+        <v>9</v>
       </c>
       <c r="W41" t="n">
-        <v>27</v>
+        <v>13.9</v>
       </c>
       <c r="X41" t="n">
-        <v>19.9</v>
+        <v>11.4</v>
       </c>
       <c r="Y41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z41" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA41" t="n">
-        <v>11.4</v>
+        <v>15</v>
       </c>
       <c r="AB41" t="n">
-        <v>-5.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>225</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>-0.08</v>
+        <v>-0.4</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4614,73 +4395,100 @@
       <c r="AI41" t="n">
         <v>235</v>
       </c>
-      <c r="AK41" t="n">
-        <v>134.62</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>-0.62</v>
-      </c>
       <c r="AM41" t="n">
         <v>110</v>
       </c>
       <c r="AN41" t="n">
         <v>142</v>
       </c>
-      <c r="AP41" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL41" s="1" t="n">
-        <v>46240</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="B42" t="n">
-        <v>151.5</v>
+        <v>153</v>
+      </c>
+      <c r="C42" t="n">
+        <v>71.8</v>
       </c>
       <c r="D42" t="n">
-        <v>35.1</v>
+        <v>28.6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>24.7</v>
       </c>
       <c r="F42" t="n">
-        <v>5.4</v>
+        <v>4</v>
+      </c>
+      <c r="H42" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J42" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N42" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>23.2</v>
       </c>
       <c r="V42" t="n">
-        <v>8.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="W42" t="n">
-        <v>19.4</v>
+        <v>13</v>
       </c>
       <c r="X42" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z42" t="n">
         <v>14</v>
       </c>
-      <c r="Y42" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>13</v>
-      </c>
       <c r="AA42" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>-4.7</v>
+        <v>-6.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>-1.4</v>
+        <v>-0.6</v>
       </c>
       <c r="AF42" t="n">
-        <v>221.37</v>
+        <v>229.96</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4689,10 +4497,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>135.21</v>
+        <v>128.14</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.59</v>
+        <v>11.77</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4700,37 +4508,76 @@
       <c r="AN42" t="n">
         <v>142</v>
       </c>
+      <c r="AP42" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL42" s="1" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46242</v>
+        <v>46252</v>
       </c>
       <c r="B43" t="n">
-        <v>145.2</v>
+        <v>165.8</v>
+      </c>
+      <c r="C43" t="n">
+        <v>77.3</v>
       </c>
       <c r="D43" t="n">
-        <v>33.5</v>
+        <v>29.3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>27.7</v>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>3.6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J43" t="n">
+        <v>41.6</v>
       </c>
       <c r="K43" t="n">
-        <v>100.3</v>
+        <v>76.59999999999999</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>35.1</v>
       </c>
       <c r="O43" t="n">
-        <v>35.5</v>
+        <v>39.8</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S43" t="n">
+        <v>7</v>
+      </c>
+      <c r="T43" t="n">
+        <v>23.8</v>
       </c>
       <c r="V43" t="n">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="W43" t="n">
-        <v>19.2</v>
+        <v>17.4</v>
       </c>
       <c r="X43" t="n">
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="Y43" t="n">
         <v>7</v>
@@ -4739,22 +4586,22 @@
         <v>13</v>
       </c>
       <c r="AA43" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>-5.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>-1.5</v>
+        <v>4.4</v>
       </c>
       <c r="AF43" t="n">
-        <v>224.37</v>
+        <v>227.01</v>
       </c>
       <c r="AG43" t="n">
-        <v>3</v>
+        <v>-2.95</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4763,10 +4610,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>135.61</v>
+        <v>128.15</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4774,61 +4621,100 @@
       <c r="AN43" t="n">
         <v>142</v>
       </c>
+      <c r="AP43" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>14.52</v>
+      </c>
       <c r="BL43" s="1" t="n">
-        <v>46242</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46243</v>
+        <v>46253</v>
       </c>
       <c r="B44" t="n">
-        <v>146.3</v>
+        <v>158.1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>73.7</v>
       </c>
       <c r="D44" t="n">
-        <v>33.4</v>
+        <v>30.3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>26</v>
       </c>
       <c r="F44" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J44" t="n">
+        <v>40.9</v>
       </c>
       <c r="K44" t="n">
-        <v>98.2</v>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M44" t="n">
+        <v>5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>35.3</v>
       </c>
       <c r="O44" t="n">
-        <v>35.1</v>
+        <v>40.3</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>7</v>
+      </c>
+      <c r="T44" t="n">
+        <v>23.6</v>
       </c>
       <c r="V44" t="n">
-        <v>4.9</v>
+        <v>8.9</v>
       </c>
       <c r="W44" t="n">
-        <v>16.4</v>
+        <v>19.3</v>
       </c>
       <c r="X44" t="n">
-        <v>10.6</v>
+        <v>14.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z44" t="n">
         <v>15</v>
       </c>
       <c r="AA44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AB44" t="n">
-        <v>-6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>-0.2</v>
+        <v>8.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>-3.3</v>
+        <v>6.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>225.93</v>
+        <v>228.35</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4837,10 +4723,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>135.28</v>
+        <v>128.86</v>
       </c>
       <c r="AL44" t="n">
-        <v>-0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4848,94 +4734,100 @@
       <c r="AN44" t="n">
         <v>142</v>
       </c>
+      <c r="AP44" t="n">
+        <v>82.37</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>14.22</v>
+      </c>
       <c r="BL44" s="1" t="n">
-        <v>46243</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="B45" t="n">
-        <v>182.8</v>
+        <v>154.9</v>
       </c>
       <c r="C45" t="n">
-        <v>86.8</v>
+        <v>70.2</v>
       </c>
       <c r="D45" t="n">
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
       <c r="E45" t="n">
-        <v>33</v>
+        <v>27.7</v>
       </c>
       <c r="F45" t="n">
-        <v>5.7</v>
+        <v>2.7</v>
       </c>
       <c r="H45" t="n">
-        <v>23.5</v>
+        <v>24.1</v>
       </c>
       <c r="I45" t="n">
-        <v>9.6</v>
+        <v>11.3</v>
       </c>
       <c r="J45" t="n">
-        <v>41.1</v>
+        <v>40.3</v>
       </c>
       <c r="K45" t="n">
-        <v>74.2</v>
+        <v>75.8</v>
       </c>
       <c r="M45" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
       <c r="N45" t="n">
-        <v>33.5</v>
+        <v>32.9</v>
       </c>
       <c r="O45" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="Q45" t="n">
-        <v>22.4</v>
+        <v>23.7</v>
       </c>
       <c r="R45" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>5.6</v>
       </c>
       <c r="T45" t="n">
-        <v>22.4</v>
+        <v>23.7</v>
       </c>
       <c r="V45" t="n">
-        <v>9.1</v>
+        <v>6.3</v>
       </c>
       <c r="W45" t="n">
-        <v>15</v>
+        <v>25.2</v>
       </c>
       <c r="X45" t="n">
-        <v>12.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z45" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA45" t="n">
-        <v>8.5</v>
+        <v>12.6</v>
       </c>
       <c r="AB45" t="n">
-        <v>-10.5</v>
+        <v>2.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.3</v>
+        <v>8.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>-5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AF45" t="n">
-        <v>218.63</v>
+        <v>231.16</v>
       </c>
       <c r="AG45" t="n">
-        <v>-7.3</v>
+        <v>2.81</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4944,10 +4836,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>126.27</v>
+        <v>130.88</v>
       </c>
       <c r="AL45" t="n">
-        <v>-9.01</v>
+        <v>2.02</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4956,75 +4848,42 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>82.66</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS45" t="n">
-        <v>14.7</v>
+        <v>13.1</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="B46" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="C46" t="n">
-        <v>86.5</v>
+        <v>152.2</v>
       </c>
       <c r="D46" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E46" t="n">
-        <v>34.2</v>
+        <v>31</v>
       </c>
       <c r="F46" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H46" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J46" t="n">
-        <v>41.9</v>
+        <v>3.5</v>
       </c>
       <c r="K46" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="M46" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N46" t="n">
-        <v>35.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>23</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S46" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T46" t="n">
-        <v>23</v>
+        <v>34.4</v>
       </c>
       <c r="V46" t="n">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="W46" t="n">
-        <v>14.8</v>
+        <v>25.5</v>
       </c>
       <c r="X46" t="n">
-        <v>10.9</v>
+        <v>17.5</v>
       </c>
       <c r="Y46" t="n">
         <v>6</v>
@@ -5033,22 +4892,22 @@
         <v>12</v>
       </c>
       <c r="AA46" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB46" t="n">
-        <v>-4.5</v>
+        <v>-1.1</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>-1.4</v>
+        <v>3.8</v>
       </c>
       <c r="AF46" t="n">
-        <v>216.39</v>
+        <v>228.13</v>
       </c>
       <c r="AG46" t="n">
-        <v>-2.23</v>
+        <v>-3.03</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5056,112 +4915,49 @@
       <c r="AI46" t="n">
         <v>235</v>
       </c>
-      <c r="AK46" t="n">
-        <v>123.32</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>-2.95</v>
-      </c>
       <c r="AM46" t="n">
         <v>110</v>
       </c>
       <c r="AN46" t="n">
         <v>142</v>
       </c>
-      <c r="AP46" t="n">
-        <v>79.08</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>13.91</v>
-      </c>
       <c r="BL46" s="1" t="n">
-        <v>46245</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46246</v>
+        <v>46256</v>
       </c>
       <c r="B47" t="n">
-        <v>183</v>
-      </c>
-      <c r="C47" t="n">
-        <v>84.7</v>
+        <v>143.9</v>
       </c>
       <c r="D47" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E47" t="n">
-        <v>33.7</v>
+        <v>30.8</v>
       </c>
       <c r="F47" t="n">
-        <v>7</v>
-      </c>
-      <c r="H47" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I47" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J47" t="n">
-        <v>42.3</v>
+        <v>2.5</v>
       </c>
       <c r="K47" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M47" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="Y47" t="n">
         <v>4</v>
       </c>
-      <c r="N47" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="O47" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S47" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T47" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="V47" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W47" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X47" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>8</v>
-      </c>
       <c r="Z47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA47" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.8</v>
+        <v>9</v>
       </c>
       <c r="AF47" t="n">
-        <v>217.16</v>
+        <v>229.16</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.76</v>
+        <v>1.03</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5169,79 +4965,82 @@
       <c r="AI47" t="n">
         <v>235</v>
       </c>
-      <c r="AK47" t="n">
-        <v>117.87</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>-5.45</v>
-      </c>
       <c r="AM47" t="n">
         <v>110</v>
       </c>
       <c r="AN47" t="n">
         <v>142</v>
       </c>
-      <c r="AP47" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL47" s="1" t="n">
-        <v>46246</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46247</v>
+        <v>46257</v>
       </c>
       <c r="B48" t="n">
-        <v>163.8</v>
+        <v>163.2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>73.7</v>
       </c>
       <c r="D48" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="E48" t="n">
+        <v>28.2</v>
       </c>
       <c r="F48" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H48" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>40.1</v>
       </c>
       <c r="K48" t="n">
-        <v>101.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N48" t="n">
+        <v>32.9</v>
       </c>
       <c r="O48" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="V48" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W48" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X48" t="n">
-        <v>11.8</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S48" t="n">
+        <v>6</v>
+      </c>
+      <c r="T48" t="n">
+        <v>23.5</v>
       </c>
       <c r="Y48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA48" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AF48" t="n">
-        <v>220.31</v>
+        <v>228.55</v>
       </c>
       <c r="AG48" t="n">
-        <v>3.16</v>
+        <v>-0.61</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5250,10 +5049,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>116.52</v>
+        <v>127.06</v>
       </c>
       <c r="AL48" t="n">
-        <v>-1.35</v>
+        <v>-3.82</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5261,61 +5060,82 @@
       <c r="AN48" t="n">
         <v>142</v>
       </c>
+      <c r="AP48" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL48" s="1" t="n">
-        <v>46247</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46248</v>
+        <v>46258</v>
       </c>
       <c r="B49" t="n">
-        <v>155.9</v>
+        <v>174.4</v>
+      </c>
+      <c r="C49" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>28</v>
+        <v>32.1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>30.8</v>
       </c>
       <c r="F49" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>24</v>
+      </c>
+      <c r="I49" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>39.5</v>
       </c>
       <c r="K49" t="n">
-        <v>99.3</v>
+        <v>74</v>
+      </c>
+      <c r="M49" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N49" t="n">
+        <v>35.8</v>
       </c>
       <c r="O49" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="V49" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W49" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X49" t="n">
-        <v>12.4</v>
+        <v>42.6</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S49" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T49" t="n">
+        <v>23.1</v>
       </c>
       <c r="Y49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z49" t="n">
         <v>13</v>
       </c>
       <c r="AA49" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>3.5</v>
+        <v>10.1</v>
       </c>
       <c r="AF49" t="n">
-        <v>221.99</v>
+        <v>219.99</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.67</v>
+        <v>-8.56</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5324,10 +5144,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>116.37</v>
+        <v>125.61</v>
       </c>
       <c r="AL49" t="n">
-        <v>-0.15</v>
+        <v>-1.45</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5335,61 +5155,82 @@
       <c r="AN49" t="n">
         <v>142</v>
       </c>
+      <c r="AP49" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>12.96</v>
+      </c>
       <c r="BL49" s="1" t="n">
-        <v>46248</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46249</v>
+        <v>46259</v>
       </c>
       <c r="B50" t="n">
-        <v>141.3</v>
+        <v>163.2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>70.90000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>26.3</v>
+        <v>32.9</v>
+      </c>
+      <c r="E50" t="n">
+        <v>26</v>
       </c>
       <c r="F50" t="n">
-        <v>5.5</v>
+        <v>6.9</v>
+      </c>
+      <c r="H50" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I50" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>40.1</v>
       </c>
       <c r="K50" t="n">
-        <v>97.8</v>
+        <v>71.3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N50" t="n">
+        <v>34.3</v>
       </c>
       <c r="O50" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="V50" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W50" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X50" t="n">
-        <v>13.6</v>
+        <v>41.5</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>5</v>
+      </c>
+      <c r="S50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T50" t="n">
+        <v>23.1</v>
       </c>
       <c r="Y50" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Z50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA50" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>3.9</v>
+        <v>12.2</v>
       </c>
       <c r="AF50" t="n">
-        <v>225.14</v>
+        <v>219.22</v>
       </c>
       <c r="AG50" t="n">
-        <v>3.15</v>
+        <v>-0.77</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5397,61 +5238,94 @@
       <c r="AI50" t="n">
         <v>235</v>
       </c>
+      <c r="AK50" t="n">
+        <v>124.36</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>-1.25</v>
+      </c>
       <c r="AM50" t="n">
         <v>110</v>
       </c>
       <c r="AN50" t="n">
         <v>142</v>
       </c>
+      <c r="AP50" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>12.38</v>
+      </c>
       <c r="BL50" s="1" t="n">
-        <v>46249</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46250</v>
+        <v>46260</v>
       </c>
       <c r="B51" t="n">
-        <v>131.5</v>
+        <v>152.7</v>
+      </c>
+      <c r="C51" t="n">
+        <v>62.6</v>
       </c>
       <c r="D51" t="n">
-        <v>27.3</v>
+        <v>32.7</v>
+      </c>
+      <c r="E51" t="n">
+        <v>24.6</v>
       </c>
       <c r="F51" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I51" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>38.9</v>
       </c>
       <c r="K51" t="n">
-        <v>97</v>
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M51" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N51" t="n">
+        <v>33.5</v>
       </c>
       <c r="O51" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="V51" t="n">
-        <v>9</v>
-      </c>
-      <c r="W51" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="X51" t="n">
-        <v>11.4</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S51" t="n">
+        <v>4</v>
+      </c>
+      <c r="T51" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y51" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z51" t="n">
         <v>18</v>
       </c>
       <c r="AA51" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>-0.4</v>
+        <v>14</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>220.73</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.5</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5459,100 +5333,55 @@
       <c r="AI51" t="n">
         <v>235</v>
       </c>
+      <c r="AK51" t="n">
+        <v>120.93</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>-3.43</v>
+      </c>
       <c r="AM51" t="n">
         <v>110</v>
       </c>
       <c r="AN51" t="n">
         <v>142</v>
       </c>
+      <c r="AP51" t="n">
+        <v>77.87</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>13.26</v>
+      </c>
       <c r="BL51" s="1" t="n">
-        <v>46250</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46251</v>
+        <v>46261</v>
       </c>
       <c r="B52" t="n">
-        <v>153</v>
-      </c>
-      <c r="C52" t="n">
-        <v>71.8</v>
+        <v>136.8</v>
       </c>
       <c r="D52" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E52" t="n">
-        <v>24.7</v>
+        <v>33</v>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
-      </c>
-      <c r="H52" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I52" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J52" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M52" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N52" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O52" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V52" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W52" t="n">
-        <v>13</v>
-      </c>
-      <c r="X52" t="n">
-        <v>12.1</v>
+        <v>6.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z52" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA52" t="n">
         <v>14</v>
       </c>
-      <c r="AA52" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="AF52" t="n">
-        <v>229.96</v>
+        <v>220.58</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5560,225 +5389,57 @@
       <c r="AI52" t="n">
         <v>235</v>
       </c>
-      <c r="AK52" t="n">
-        <v>128.14</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>11.77</v>
-      </c>
       <c r="AM52" t="n">
         <v>110</v>
       </c>
       <c r="AN52" t="n">
         <v>142</v>
       </c>
-      <c r="AP52" t="n">
-        <v>87.47</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>14.8</v>
-      </c>
       <c r="BL52" s="1" t="n">
-        <v>46251</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46252</v>
+        <v>46262</v>
       </c>
       <c r="B53" t="n">
-        <v>165.8</v>
-      </c>
-      <c r="C53" t="n">
-        <v>77.3</v>
+        <v>138.2</v>
       </c>
       <c r="D53" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E53" t="n">
-        <v>27.7</v>
+        <v>33.6</v>
       </c>
       <c r="F53" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H53" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I53" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J53" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="K53" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="M53" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N53" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="O53" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R53" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S53" t="n">
-        <v>7</v>
-      </c>
-      <c r="T53" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V53" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W53" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="X53" t="n">
-        <v>13.4</v>
+        <v>6.1</v>
       </c>
       <c r="Y53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z53" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA53" t="n">
         <v>13</v>
       </c>
-      <c r="AA53" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>227.01</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>-2.95</v>
-      </c>
       <c r="AH53" t="n">
         <v>215</v>
       </c>
       <c r="AI53" t="n">
         <v>235</v>
       </c>
-      <c r="AK53" t="n">
-        <v>128.15</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0.01</v>
-      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
       <c r="AN53" t="n">
         <v>142</v>
       </c>
-      <c r="AP53" t="n">
-        <v>83.41</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>14.52</v>
-      </c>
       <c r="BL53" s="1" t="n">
-        <v>46252</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="B54" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="C54" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="D54" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E54" t="n">
-        <v>26</v>
-      </c>
-      <c r="F54" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H54" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I54" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J54" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="K54" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M54" t="n">
-        <v>5</v>
-      </c>
-      <c r="N54" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="O54" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S54" t="n">
-        <v>7</v>
-      </c>
-      <c r="T54" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="V54" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W54" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X54" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>228.35</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.33</v>
+        <v>46263</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5786,112 +5447,19 @@
       <c r="AI54" t="n">
         <v>235</v>
       </c>
-      <c r="AK54" t="n">
-        <v>128.86</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0.71</v>
-      </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
       <c r="AN54" t="n">
         <v>142</v>
       </c>
-      <c r="AP54" t="n">
-        <v>82.37</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>14.22</v>
-      </c>
       <c r="BL54" s="1" t="n">
-        <v>46253</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="B55" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C55" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="D55" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E55" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="F55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H55" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J55" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K55" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M55" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="O55" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S55" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T55" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="V55" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W55" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="X55" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>231.16</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>2.81</v>
+        <v>46264</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5899,61 +5467,19 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
-      <c r="AK55" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
         <v>142</v>
       </c>
-      <c r="AP55" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL55" s="1" t="n">
-        <v>46254</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B56" t="n">
-        <v>152.2</v>
-      </c>
-      <c r="D56" t="n">
-        <v>31</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K56" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="O56" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>228.13</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>-3.03</v>
+        <v>46265</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5968,42 +5494,12 @@
         <v>142</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46255</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46256</v>
-      </c>
-      <c r="B57" t="n">
-        <v>143.9</v>
-      </c>
-      <c r="D57" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="F57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K57" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="O57" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>229.16</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.03</v>
+        <v>46266</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6018,75 +5514,12 @@
         <v>142</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46256</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46257</v>
-      </c>
-      <c r="B58" t="n">
-        <v>163.2</v>
-      </c>
-      <c r="C58" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="D58" t="n">
-        <v>30</v>
-      </c>
-      <c r="E58" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H58" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I58" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J58" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M58" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N58" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="O58" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="R58" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S58" t="n">
-        <v>6</v>
-      </c>
-      <c r="T58" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>228.55</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>-0.61</v>
+        <v>46267</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6094,94 +5527,19 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
-      <c r="AK58" t="n">
-        <v>127.06</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>-3.82</v>
-      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
-      <c r="AP58" t="n">
-        <v>82.81</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>12.9</v>
-      </c>
       <c r="BL58" s="1" t="n">
-        <v>46257</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B59" t="n">
-        <v>174.4</v>
-      </c>
-      <c r="C59" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="D59" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E59" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="F59" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H59" t="n">
-        <v>24</v>
-      </c>
-      <c r="I59" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J59" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="K59" t="n">
-        <v>74</v>
-      </c>
-      <c r="M59" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N59" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="O59" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S59" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T59" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>219.99</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>-8.56</v>
+        <v>46268</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6189,94 +5547,19 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
-      <c r="AK59" t="n">
-        <v>125.61</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>-1.45</v>
-      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
-      <c r="AP59" t="n">
-        <v>77.83</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>12.96</v>
-      </c>
       <c r="BL59" s="1" t="n">
-        <v>46258</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B60" t="n">
-        <v>163.2</v>
-      </c>
-      <c r="C60" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="D60" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E60" t="n">
-        <v>26</v>
-      </c>
-      <c r="F60" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H60" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I60" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J60" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M60" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N60" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O60" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>5</v>
-      </c>
-      <c r="S60" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T60" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>219.22</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>-0.77</v>
+        <v>46269</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6284,55 +5567,19 @@
       <c r="AI60" t="n">
         <v>235</v>
       </c>
-      <c r="AK60" t="n">
-        <v>124.36</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>-1.25</v>
-      </c>
       <c r="AM60" t="n">
         <v>110</v>
       </c>
       <c r="AN60" t="n">
         <v>142</v>
       </c>
-      <c r="AP60" t="n">
-        <v>76.81</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>12.38</v>
-      </c>
       <c r="BL60" s="1" t="n">
-        <v>46259</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B61" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="D61" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="F61" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>220.73</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>1.5</v>
+        <v>46270</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6347,30 +5594,12 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46260</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B62" t="n">
-        <v>136.8</v>
-      </c>
-      <c r="D62" t="n">
-        <v>33</v>
-      </c>
-      <c r="F62" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>14</v>
+        <v>46271</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6385,7 +5614,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46261</v>
+        <v>46271</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -4944,6 +4944,15 @@
       <c r="O47" t="n">
         <v>35.2</v>
       </c>
+      <c r="V47" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="W47" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="X47" t="n">
+        <v>14.2</v>
+      </c>
       <c r="Y47" t="n">
         <v>4</v>
       </c>
@@ -4952,6 +4961,15 @@
       </c>
       <c r="AA47" t="n">
         <v>9</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>4</v>
       </c>
       <c r="AF47" t="n">
         <v>229.16</v>
@@ -5027,6 +5045,15 @@
       <c r="T48" t="n">
         <v>23.5</v>
       </c>
+      <c r="V48" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W48" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y48" t="n">
         <v>4</v>
       </c>
@@ -5035,6 +5062,15 @@
       </c>
       <c r="AA48" t="n">
         <v>9.300000000000001</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>4.3</v>
       </c>
       <c r="AF48" t="n">
         <v>228.55</v>
@@ -5360,13 +5396,52 @@
         <v>46261</v>
       </c>
       <c r="B52" t="n">
-        <v>136.8</v>
+        <v>150.7</v>
+      </c>
+      <c r="C52" t="n">
+        <v>64.8</v>
       </c>
       <c r="D52" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E52" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H52" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I52" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J52" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K52" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="M52" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N52" t="n">
         <v>33</v>
       </c>
-      <c r="F52" t="n">
-        <v>6.4</v>
+      <c r="O52" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y52" t="n">
         <v>10</v>
@@ -5375,7 +5450,7 @@
         <v>18</v>
       </c>
       <c r="AA52" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AF52" t="n">
         <v>220.58</v>
@@ -5389,11 +5464,23 @@
       <c r="AI52" t="n">
         <v>235</v>
       </c>
+      <c r="AK52" t="n">
+        <v>120.28</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>-0.65</v>
+      </c>
       <c r="AM52" t="n">
         <v>110</v>
       </c>
       <c r="AN52" t="n">
         <v>142</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>13.79</v>
       </c>
       <c r="BL52" s="1" t="n">
         <v>46261</v>
@@ -5440,6 +5527,30 @@
     <row r="54">
       <c r="A54" s="1" t="n">
         <v>46263</v>
+      </c>
+      <c r="B54" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5158,6 +5158,15 @@
       <c r="T49" t="n">
         <v>23.1</v>
       </c>
+      <c r="V49" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W49" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>17.5</v>
+      </c>
       <c r="Y49" t="n">
         <v>7</v>
       </c>
@@ -5166,6 +5175,15 @@
       </c>
       <c r="AA49" t="n">
         <v>10.1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>4.8</v>
       </c>
       <c r="AF49" t="n">
         <v>219.99</v>
@@ -5572,6 +5590,24 @@
       <c r="A55" s="1" t="n">
         <v>46264</v>
       </c>
+      <c r="B55" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>14</v>
+      </c>
       <c r="AH55" t="n">
         <v>215</v>
       </c>
@@ -5591,6 +5627,24 @@
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>46265</v>
+      </c>
+      <c r="B56" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>15.5</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5271,6 +5271,15 @@
       <c r="T50" t="n">
         <v>23.1</v>
       </c>
+      <c r="V50" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W50" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X50" t="n">
+        <v>16.4</v>
+      </c>
       <c r="Y50" t="n">
         <v>8</v>
       </c>
@@ -5279,6 +5288,15 @@
       </c>
       <c r="AA50" t="n">
         <v>12.2</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>5.5</v>
       </c>
       <c r="AF50" t="n">
         <v>219.22</v>
@@ -5591,13 +5609,52 @@
         <v>46264</v>
       </c>
       <c r="B55" t="n">
-        <v>117.4</v>
+        <v>129.4</v>
+      </c>
+      <c r="C55" t="n">
+        <v>50.6</v>
       </c>
       <c r="D55" t="n">
-        <v>32.3</v>
+        <v>31.5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>19.4</v>
       </c>
       <c r="F55" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H55" t="n">
+        <v>24</v>
+      </c>
+      <c r="I55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K55" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N55" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O55" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>21.4</v>
       </c>
       <c r="Y55" t="n">
         <v>8</v>
@@ -5606,7 +5663,13 @@
         <v>20</v>
       </c>
       <c r="AA55" t="n">
-        <v>14</v>
+        <v>16.1</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0.02</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5614,11 +5677,23 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
+      <c r="AK55" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
         <v>142</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>15.97</v>
       </c>
       <c r="BL55" s="1" t="n">
         <v>46264</v>
@@ -5646,6 +5721,12 @@
       <c r="AA56" t="n">
         <v>15.5</v>
       </c>
+      <c r="AF56" t="n">
+        <v>238.69</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>-2.8</v>
+      </c>
       <c r="AH56" t="n">
         <v>215</v>
       </c>
@@ -5665,6 +5746,24 @@
     <row r="57">
       <c r="A57" s="1" t="n">
         <v>46266</v>
+      </c>
+      <c r="B57" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="D57" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>13.5</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5384,6 +5384,15 @@
       <c r="T51" t="n">
         <v>23.2</v>
       </c>
+      <c r="V51" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y51" t="n">
         <v>10</v>
       </c>
@@ -5392,6 +5401,15 @@
       </c>
       <c r="AA51" t="n">
         <v>14</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>5.7</v>
       </c>
       <c r="AF51" t="n">
         <v>220.73</v>
@@ -5704,13 +5722,52 @@
         <v>46265</v>
       </c>
       <c r="B56" t="n">
-        <v>128.1</v>
+        <v>142.9</v>
+      </c>
+      <c r="C56" t="n">
+        <v>52.7</v>
       </c>
       <c r="D56" t="n">
-        <v>34.3</v>
+        <v>34.7</v>
+      </c>
+      <c r="E56" t="n">
+        <v>24.8</v>
       </c>
       <c r="F56" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>22</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J56" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="K56" t="n">
+        <v>70</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N56" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O56" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>19.7</v>
       </c>
       <c r="Y56" t="n">
         <v>12</v>
@@ -5719,7 +5776,7 @@
         <v>19</v>
       </c>
       <c r="AA56" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF56" t="n">
         <v>238.69</v>
@@ -5733,11 +5790,23 @@
       <c r="AI56" t="n">
         <v>235</v>
       </c>
+      <c r="AK56" t="n">
+        <v>134.59</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>6.22</v>
+      </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
       <c r="AN56" t="n">
         <v>142</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>89.05</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>17.06</v>
       </c>
       <c r="BL56" s="1" t="n">
         <v>46265</v>
@@ -5784,6 +5853,24 @@
     <row r="58">
       <c r="A58" s="1" t="n">
         <v>46267</v>
+      </c>
+      <c r="B58" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="D58" t="n">
+        <v>35</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>17</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5497,6 +5497,15 @@
       <c r="T52" t="n">
         <v>23.2</v>
       </c>
+      <c r="V52" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W52" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X52" t="n">
+        <v>21.7</v>
+      </c>
       <c r="Y52" t="n">
         <v>10</v>
       </c>
@@ -5505,6 +5514,15 @@
       </c>
       <c r="AA52" t="n">
         <v>13.1</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>6.7</v>
       </c>
       <c r="AF52" t="n">
         <v>220.58</v>
@@ -5817,13 +5835,52 @@
         <v>46266</v>
       </c>
       <c r="B57" t="n">
-        <v>132.3</v>
+        <v>148.1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>51.9</v>
       </c>
       <c r="D57" t="n">
-        <v>35.1</v>
+        <v>35.4</v>
+      </c>
+      <c r="E57" t="n">
+        <v>31.5</v>
       </c>
       <c r="F57" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
+      </c>
+      <c r="H57" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J57" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K57" t="n">
+        <v>71</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N57" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="O57" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>20.7</v>
       </c>
       <c r="Y57" t="n">
         <v>10</v>
@@ -5832,7 +5889,13 @@
         <v>17</v>
       </c>
       <c r="AA57" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>233.48</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>-4.86</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5840,11 +5903,23 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
+      <c r="AK57" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2.01</v>
+      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>17.13</v>
       </c>
       <c r="BL57" s="1" t="n">
         <v>46266</v>
@@ -5872,6 +5947,12 @@
       <c r="AA58" t="n">
         <v>17</v>
       </c>
+      <c r="AF58" t="n">
+        <v>235.13</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.66</v>
+      </c>
       <c r="AH58" t="n">
         <v>215</v>
       </c>
@@ -5891,6 +5972,24 @@
     <row r="59">
       <c r="A59" s="1" t="n">
         <v>46268</v>
+      </c>
+      <c r="B59" t="n">
+        <v>131</v>
+      </c>
+      <c r="D59" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>15.5</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5571,6 +5571,15 @@
       <c r="F53" t="n">
         <v>6.1</v>
       </c>
+      <c r="V53" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W53" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X53" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y53" t="n">
         <v>9</v>
       </c>
@@ -5579,6 +5588,15 @@
       </c>
       <c r="AA53" t="n">
         <v>13</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>4.5</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5930,13 +5948,52 @@
         <v>46267</v>
       </c>
       <c r="B58" t="n">
-        <v>128.4</v>
+        <v>143.4</v>
+      </c>
+      <c r="C58" t="n">
+        <v>50.9</v>
       </c>
       <c r="D58" t="n">
-        <v>35</v>
+        <v>35.7</v>
+      </c>
+      <c r="E58" t="n">
+        <v>26.2</v>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>4.3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J58" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="K58" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="O58" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>21.6</v>
       </c>
       <c r="Y58" t="n">
         <v>11</v>
@@ -5945,7 +6002,7 @@
         <v>23</v>
       </c>
       <c r="AA58" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="AF58" t="n">
         <v>235.13</v>
@@ -5959,11 +6016,23 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
+      <c r="AK58" t="n">
+        <v>135.66</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>17.6</v>
       </c>
       <c r="BL58" s="1" t="n">
         <v>46267</v>
@@ -5991,6 +6060,12 @@
       <c r="AA59" t="n">
         <v>15.5</v>
       </c>
+      <c r="AF59" t="n">
+        <v>234.87</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>-0.26</v>
+      </c>
       <c r="AH59" t="n">
         <v>215</v>
       </c>
@@ -6010,6 +6085,24 @@
     <row r="60">
       <c r="A60" s="1" t="n">
         <v>46269</v>
+      </c>
+      <c r="B60" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>13</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5627,6 +5627,15 @@
       <c r="F54" t="n">
         <v>3.4</v>
       </c>
+      <c r="V54" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="W54" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X54" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y54" t="n">
         <v>8</v>
       </c>
@@ -5635,6 +5644,15 @@
       </c>
       <c r="AA54" t="n">
         <v>13</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>3.4</v>
       </c>
       <c r="AF54" t="n">
         <v>229.48</v>
@@ -6043,13 +6061,52 @@
         <v>46268</v>
       </c>
       <c r="B59" t="n">
-        <v>131</v>
+        <v>144.9</v>
+      </c>
+      <c r="C59" t="n">
+        <v>53</v>
       </c>
       <c r="D59" t="n">
-        <v>36.4</v>
+        <v>35.6</v>
+      </c>
+      <c r="E59" t="n">
+        <v>26</v>
       </c>
       <c r="F59" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
+      </c>
+      <c r="H59" t="n">
+        <v>24</v>
+      </c>
+      <c r="I59" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J59" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K59" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N59" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="O59" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>21</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>21</v>
       </c>
       <c r="Y59" t="n">
         <v>12</v>
@@ -6058,7 +6115,7 @@
         <v>19</v>
       </c>
       <c r="AA59" t="n">
-        <v>15.5</v>
+        <v>16.3</v>
       </c>
       <c r="AF59" t="n">
         <v>234.87</v>
@@ -6072,11 +6129,23 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
+      <c r="AK59" t="n">
+        <v>136.33</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0.67</v>
+      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>87.09</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>17.31</v>
       </c>
       <c r="BL59" s="1" t="n">
         <v>46268</v>
@@ -6123,6 +6192,24 @@
     <row r="61">
       <c r="A61" s="1" t="n">
         <v>46270</v>
+      </c>
+      <c r="B61" t="n">
+        <v>137.1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>10.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5728,6 +5728,15 @@
       <c r="T55" t="n">
         <v>21.4</v>
       </c>
+      <c r="V55" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W55" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="X55" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y55" t="n">
         <v>8</v>
       </c>
@@ -5736,6 +5745,15 @@
       </c>
       <c r="AA55" t="n">
         <v>16.1</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>4</v>
       </c>
       <c r="AF55" t="n">
         <v>229.5</v>
@@ -6173,6 +6191,12 @@
       <c r="AA60" t="n">
         <v>13</v>
       </c>
+      <c r="AF60" t="n">
+        <v>234.78</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>-0.09</v>
+      </c>
       <c r="AH60" t="n">
         <v>215</v>
       </c>
@@ -6211,6 +6235,12 @@
       <c r="AA61" t="n">
         <v>10.5</v>
       </c>
+      <c r="AF61" t="n">
+        <v>229.75</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>-5.03</v>
+      </c>
       <c r="AH61" t="n">
         <v>215</v>
       </c>
@@ -6230,6 +6260,24 @@
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46271</v>
+      </c>
+      <c r="B62" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="D62" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>6.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -5841,6 +5841,15 @@
       <c r="T56" t="n">
         <v>19.7</v>
       </c>
+      <c r="V56" t="n">
+        <v>12</v>
+      </c>
+      <c r="W56" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="X56" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y56" t="n">
         <v>12</v>
       </c>
@@ -5849,6 +5858,15 @@
       </c>
       <c r="AA56" t="n">
         <v>15</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>2.9</v>
       </c>
       <c r="AF56" t="n">
         <v>238.69</v>
@@ -6278,6 +6296,12 @@
       </c>
       <c r="AA62" t="n">
         <v>6.5</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>222.86</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>-6.9</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,61 +628,61 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B2" t="n">
-        <v>157.8</v>
+        <v>157.5</v>
       </c>
       <c r="C2" t="n">
-        <v>85.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>26.5</v>
+        <v>27.1</v>
       </c>
       <c r="E2" t="n">
-        <v>30.3</v>
+        <v>36.9</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="K2" t="n">
-        <v>98.7</v>
+        <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>40.5</v>
+        <v>38</v>
       </c>
       <c r="V2" t="n">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="W2" t="n">
-        <v>19.7</v>
+        <v>20.8</v>
       </c>
       <c r="X2" t="n">
-        <v>12.1</v>
+        <v>13.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>-2.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.6</v>
+        <v>-0.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>231.46</v>
+        <v>226.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.7</v>
+        <v>-2.97</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -691,10 +691,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>129.8</v>
+        <v>128.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.87</v>
+        <v>-4.61</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -703,66 +703,66 @@
         <v>142</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46212</v>
+        <v>46214</v>
       </c>
       <c r="B3" t="n">
-        <v>151.6</v>
+        <v>148.5</v>
       </c>
       <c r="C3" t="n">
-        <v>73.8</v>
+        <v>70.5</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="E3" t="n">
-        <v>33.9</v>
+        <v>34.3</v>
       </c>
       <c r="F3" t="n">
         <v>7.4</v>
       </c>
       <c r="K3" t="n">
-        <v>97.5</v>
+        <v>98.2</v>
       </c>
       <c r="O3" t="n">
-        <v>40.6</v>
+        <v>39.8</v>
       </c>
       <c r="V3" t="n">
-        <v>8.1</v>
+        <v>11.2</v>
       </c>
       <c r="W3" t="n">
-        <v>22.3</v>
+        <v>21.7</v>
       </c>
       <c r="X3" t="n">
-        <v>15.2</v>
+        <v>16.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AB3" t="n">
-        <v>-3.1</v>
+        <v>-1.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.2</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>229.92</v>
+        <v>223.11</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1.54</v>
+        <v>-3.83</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -771,10 +771,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>133.01</v>
+        <v>124.76</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.21</v>
+        <v>-3.64</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -783,24 +783,24 @@
         <v>142</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46212</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="B4" t="n">
-        <v>157.5</v>
+        <v>147.5</v>
       </c>
       <c r="C4" t="n">
-        <v>76.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D4" t="n">
-        <v>27.1</v>
+        <v>26.7</v>
       </c>
       <c r="E4" t="n">
-        <v>36.9</v>
+        <v>31.4</v>
       </c>
       <c r="F4" t="n">
         <v>7.4</v>
@@ -809,40 +809,34 @@
         <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>38</v>
+        <v>40.2</v>
       </c>
       <c r="V4" t="n">
-        <v>6.7</v>
+        <v>10.3</v>
       </c>
       <c r="W4" t="n">
-        <v>20.8</v>
+        <v>16.8</v>
       </c>
       <c r="X4" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z4" t="n">
         <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2.3</v>
+        <v>0.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>226.95</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-2.97</v>
+        <v>4.8</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -851,10 +845,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>128.4</v>
+        <v>127.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>-4.61</v>
+        <v>2.44</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -863,66 +857,93 @@
         <v>142</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46214</v>
+        <v>46216</v>
       </c>
       <c r="B5" t="n">
-        <v>148.5</v>
+        <v>183.5</v>
       </c>
       <c r="C5" t="n">
-        <v>70.5</v>
+        <v>84.5</v>
       </c>
       <c r="D5" t="n">
-        <v>26.8</v>
+        <v>31.5</v>
       </c>
       <c r="E5" t="n">
-        <v>34.3</v>
+        <v>34.6</v>
       </c>
       <c r="F5" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41.5</v>
       </c>
       <c r="K5" t="n">
-        <v>98.2</v>
+        <v>76.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>37.7</v>
       </c>
       <c r="O5" t="n">
-        <v>39.8</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>23</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S5" t="n">
+        <v>18</v>
+      </c>
+      <c r="T5" t="n">
+        <v>23</v>
       </c>
       <c r="V5" t="n">
-        <v>11.2</v>
+        <v>8.9</v>
       </c>
       <c r="W5" t="n">
-        <v>21.7</v>
+        <v>20</v>
       </c>
       <c r="X5" t="n">
-        <v>16.4</v>
+        <v>14.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>11</v>
+        <v>7.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.9</v>
+        <v>3.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>5</v>
+        <v>8.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>223.11</v>
+        <v>220.36</v>
       </c>
       <c r="AG5" t="n">
-        <v>-3.83</v>
+        <v>-3.75</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -931,10 +952,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>124.76</v>
+        <v>127.13</v>
       </c>
       <c r="AL5" t="n">
-        <v>-3.64</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -942,61 +963,100 @@
       <c r="AN5" t="n">
         <v>142</v>
       </c>
+      <c r="AP5" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL5" s="1" t="n">
-        <v>46214</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="B6" t="n">
-        <v>147.5</v>
+        <v>180.5</v>
       </c>
       <c r="C6" t="n">
-        <v>72.8</v>
+        <v>79.2</v>
       </c>
       <c r="D6" t="n">
-        <v>26.7</v>
+        <v>30.7</v>
       </c>
       <c r="E6" t="n">
-        <v>31.4</v>
+        <v>34.6</v>
       </c>
       <c r="F6" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>41.9</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>37.7</v>
       </c>
       <c r="O6" t="n">
-        <v>40.2</v>
+        <v>42.7</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>23.1</v>
       </c>
       <c r="V6" t="n">
-        <v>10.3</v>
+        <v>9.1</v>
       </c>
       <c r="W6" t="n">
-        <v>16.8</v>
+        <v>20.8</v>
       </c>
       <c r="X6" t="n">
-        <v>13.6</v>
+        <v>14.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA6" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>219.64</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.72</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1005,10 +1065,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>127.2</v>
+        <v>126.03</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.44</v>
+        <v>-1.1</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1016,94 +1076,100 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
+      <c r="AP6" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>14.55</v>
+      </c>
       <c r="BL6" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B7" t="n">
-        <v>183.5</v>
+        <v>168.1</v>
       </c>
       <c r="C7" t="n">
-        <v>84.5</v>
+        <v>69.7</v>
       </c>
       <c r="D7" t="n">
-        <v>31.5</v>
+        <v>30.4</v>
       </c>
       <c r="E7" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F7" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="H7" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I7" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="J7" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="K7" t="n">
-        <v>76.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O7" t="n">
-        <v>41.8</v>
+        <v>43.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="T7" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="V7" t="n">
-        <v>8.9</v>
+        <v>11.2</v>
       </c>
       <c r="W7" t="n">
-        <v>20</v>
+        <v>22.9</v>
       </c>
       <c r="X7" t="n">
-        <v>14.4</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.7</v>
+        <v>14.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>220.36</v>
+        <v>224.93</v>
       </c>
       <c r="AG7" t="n">
-        <v>-3.75</v>
+        <v>5.29</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1112,10 +1178,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>127.13</v>
+        <v>129.28</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1124,99 +1190,99 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>76.90000000000001</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>14.17</v>
+        <v>15.25</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B8" t="n">
-        <v>180.5</v>
+        <v>158.9</v>
       </c>
       <c r="C8" t="n">
-        <v>79.2</v>
+        <v>58.8</v>
       </c>
       <c r="D8" t="n">
-        <v>30.7</v>
+        <v>31.1</v>
       </c>
       <c r="E8" t="n">
-        <v>34.6</v>
+        <v>30.4</v>
       </c>
       <c r="F8" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="H8" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="I8" t="n">
-        <v>10.3</v>
+        <v>11.2</v>
       </c>
       <c r="J8" t="n">
-        <v>41.9</v>
+        <v>41</v>
       </c>
       <c r="K8" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="O8" t="n">
-        <v>42.7</v>
+        <v>41.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="S8" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T8" t="n">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="V8" t="n">
-        <v>9.1</v>
+        <v>10.1</v>
       </c>
       <c r="W8" t="n">
-        <v>20.8</v>
+        <v>26</v>
       </c>
       <c r="X8" t="n">
-        <v>14.9</v>
+        <v>18.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>219.64</v>
+        <v>232.31</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.72</v>
+        <v>9.67</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1225,10 +1291,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>126.03</v>
+        <v>134.44</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1.1</v>
+        <v>5.16</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1237,99 +1303,66 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>82.95</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>14.55</v>
+        <v>17.07</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B9" t="n">
-        <v>168.1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>69.7</v>
+        <v>136.7</v>
       </c>
       <c r="D9" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>33.9</v>
+        <v>30.7</v>
       </c>
       <c r="F9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>41.2</v>
+        <v>7.5</v>
       </c>
       <c r="K9" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>38.1</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T9" t="n">
-        <v>22.6</v>
+        <v>39.2</v>
       </c>
       <c r="V9" t="n">
-        <v>11.2</v>
+        <v>17.1</v>
       </c>
       <c r="W9" t="n">
-        <v>22.9</v>
+        <v>36.1</v>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>26.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.9</v>
+        <v>20.5</v>
       </c>
       <c r="AB9" t="n">
         <v>2.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>224.93</v>
+        <v>235.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.29</v>
+        <v>3.09</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1338,10 +1371,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>129.28</v>
+        <v>137.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1349,100 +1382,61 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
-      <c r="AP9" t="n">
-        <v>87.43000000000001</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>15.25</v>
-      </c>
       <c r="BL9" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="B10" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C10" t="n">
-        <v>58.8</v>
+        <v>138.5</v>
       </c>
       <c r="D10" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>30.4</v>
+        <v>31.7</v>
       </c>
       <c r="F10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H10" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I10" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N10" t="n">
+        <v>91</v>
+      </c>
+      <c r="O10" t="n">
         <v>37.8</v>
       </c>
-      <c r="O10" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>15</v>
-      </c>
-      <c r="T10" t="n">
-        <v>21.5</v>
-      </c>
       <c r="V10" t="n">
-        <v>10.1</v>
+        <v>13.2</v>
       </c>
       <c r="W10" t="n">
-        <v>26</v>
+        <v>22.5</v>
       </c>
       <c r="X10" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="Y10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z10" t="n">
         <v>17</v>
       </c>
-      <c r="Z10" t="n">
-        <v>20</v>
-      </c>
       <c r="AA10" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.4</v>
+        <v>-1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>232.31</v>
+        <v>231.99</v>
       </c>
       <c r="AG10" t="n">
-        <v>9.67</v>
+        <v>-3.41</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1451,10 +1445,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>134.44</v>
+        <v>136.12</v>
       </c>
       <c r="AL10" t="n">
-        <v>5.16</v>
+        <v>-1.38</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1462,67 +1456,94 @@
       <c r="AN10" t="n">
         <v>142</v>
       </c>
-      <c r="AP10" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL10" s="1" t="n">
-        <v>46219</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46220</v>
+        <v>46222</v>
       </c>
       <c r="B11" t="n">
-        <v>136.7</v>
+        <v>161.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>30.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>31.5</v>
       </c>
       <c r="F11" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41.1</v>
       </c>
       <c r="K11" t="n">
-        <v>92.59999999999999</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>35</v>
       </c>
       <c r="O11" t="n">
-        <v>39.2</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>20.5</v>
       </c>
       <c r="V11" t="n">
-        <v>17.1</v>
+        <v>14.1</v>
       </c>
       <c r="W11" t="n">
-        <v>36.1</v>
+        <v>19.3</v>
       </c>
       <c r="X11" t="n">
-        <v>26.6</v>
+        <v>16.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.6</v>
+        <v>-3.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>235.4</v>
+        <v>225.51</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.09</v>
+        <v>-6.48</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1531,10 +1552,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>137.5</v>
+        <v>133.83</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.06</v>
+        <v>-2.29</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1542,61 +1563,100 @@
       <c r="AN11" t="n">
         <v>142</v>
       </c>
+      <c r="AP11" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL11" s="1" t="n">
-        <v>46220</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="B12" t="n">
-        <v>138.5</v>
+        <v>176.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>77.09999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>31.7</v>
+        <v>32.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>6.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>41.5</v>
       </c>
       <c r="K12" t="n">
-        <v>91</v>
+        <v>76</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>36.4</v>
       </c>
       <c r="O12" t="n">
-        <v>37.8</v>
+        <v>39.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="n">
+        <v>22.3</v>
       </c>
       <c r="V12" t="n">
-        <v>13.2</v>
+        <v>11.5</v>
       </c>
       <c r="W12" t="n">
-        <v>22.5</v>
+        <v>15.5</v>
       </c>
       <c r="X12" t="n">
-        <v>17.9</v>
+        <v>13.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.9</v>
+        <v>-5.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>-1.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>231.99</v>
+        <v>220.92</v>
       </c>
       <c r="AG12" t="n">
-        <v>-3.41</v>
+        <v>-4.59</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1605,10 +1665,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>136.12</v>
+        <v>131.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.38</v>
+        <v>-1.98</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1616,94 +1676,100 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
+      <c r="AP12" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>15.49</v>
+      </c>
       <c r="BL12" s="1" t="n">
-        <v>46221</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="B13" t="n">
-        <v>161.1</v>
+        <v>181</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>80.7</v>
       </c>
       <c r="D13" t="n">
-        <v>31.9</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
-        <v>31.5</v>
+        <v>35.1</v>
       </c>
       <c r="F13" t="n">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
       <c r="H13" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="I13" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>13</v>
+      </c>
+      <c r="X13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA13" t="n">
         <v>11.4</v>
       </c>
-      <c r="J13" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>35</v>
-      </c>
-      <c r="O13" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="AB13" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>220.92</v>
+      </c>
+      <c r="AG13" t="n">
         <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>225.51</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-6.48</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1712,10 +1778,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>133.83</v>
+        <v>130.06</v>
       </c>
       <c r="AL13" t="n">
-        <v>-2.29</v>
+        <v>-1.79</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1724,75 +1790,75 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>82.93000000000001</v>
+        <v>79.94</v>
       </c>
       <c r="AS13" t="n">
-        <v>15.73</v>
+        <v>14.93</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B14" t="n">
-        <v>176.4</v>
+        <v>179.6</v>
       </c>
       <c r="C14" t="n">
-        <v>77.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>32.7</v>
+        <v>30.3</v>
       </c>
       <c r="E14" t="n">
-        <v>35</v>
+        <v>31.1</v>
       </c>
       <c r="F14" t="n">
         <v>6.8</v>
       </c>
       <c r="H14" t="n">
-        <v>23.2</v>
+        <v>21.5</v>
       </c>
       <c r="I14" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="J14" t="n">
-        <v>41.5</v>
+        <v>42.3</v>
       </c>
       <c r="K14" t="n">
-        <v>76</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>36.4</v>
+        <v>37.1</v>
       </c>
       <c r="O14" t="n">
-        <v>39.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>14</v>
+        <v>21.2</v>
       </c>
       <c r="T14" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="V14" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="W14" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>12.6</v>
       </c>
       <c r="Y14" t="n">
         <v>9</v>
@@ -1801,22 +1867,22 @@
         <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>-5.6</v>
+        <v>-3.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>-1.3</v>
+        <v>0.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>-4.59</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1825,10 +1891,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>131.85</v>
+        <v>127.85</v>
       </c>
       <c r="AL14" t="n">
-        <v>-1.98</v>
+        <v>-2.21</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1837,96 +1903,96 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>79.75</v>
+        <v>82.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>15.49</v>
+        <v>15.16</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B15" t="n">
-        <v>181</v>
+        <v>170.4</v>
       </c>
       <c r="C15" t="n">
-        <v>80.7</v>
+        <v>78.5</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>29.8</v>
       </c>
       <c r="E15" t="n">
-        <v>35.1</v>
+        <v>29.7</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="H15" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="I15" t="n">
         <v>11.2</v>
       </c>
       <c r="J15" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="K15" t="n">
-        <v>75.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>36.9</v>
+        <v>36.6</v>
       </c>
       <c r="O15" t="n">
-        <v>39.8</v>
+        <v>41.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="S15" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="T15" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="V15" t="n">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="W15" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X15" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z15" t="n">
         <v>13</v>
       </c>
-      <c r="X15" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>14</v>
-      </c>
       <c r="AA15" t="n">
-        <v>11.4</v>
+        <v>12.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>-6.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.9</v>
+        <v>4.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -1938,10 +2004,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>130.06</v>
+        <v>128.54</v>
       </c>
       <c r="AL15" t="n">
-        <v>-1.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -1950,99 +2016,66 @@
         <v>142</v>
       </c>
       <c r="AP15" t="n">
-        <v>79.94</v>
+        <v>84.73</v>
       </c>
       <c r="AS15" t="n">
-        <v>14.93</v>
+        <v>15.34</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B16" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>81.90000000000001</v>
+        <v>156</v>
       </c>
       <c r="D16" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>31.1</v>
+        <v>30.1</v>
       </c>
       <c r="F16" t="n">
         <v>6.8</v>
       </c>
-      <c r="H16" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>42.3</v>
-      </c>
       <c r="K16" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N16" t="n">
-        <v>37.1</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>22.6</v>
+        <v>39.2</v>
       </c>
       <c r="V16" t="n">
-        <v>9.6</v>
+        <v>7.1</v>
       </c>
       <c r="W16" t="n">
-        <v>15.6</v>
+        <v>20.9</v>
       </c>
       <c r="X16" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.1</v>
+        <v>13.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>-3.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.9399999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2051,10 +2084,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>127.85</v>
+        <v>130.92</v>
       </c>
       <c r="AL16" t="n">
-        <v>-2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2062,100 +2095,61 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
-      <c r="AP16" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>15.16</v>
-      </c>
       <c r="BL16" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="B17" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C17" t="n">
-        <v>78.5</v>
+        <v>147.8</v>
       </c>
       <c r="D17" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E17" t="n">
-        <v>29.7</v>
+        <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H17" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K17" t="n">
-        <v>75</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N17" t="n">
-        <v>36.6</v>
+        <v>96.5</v>
       </c>
       <c r="O17" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>23.3</v>
+        <v>39.3</v>
       </c>
       <c r="V17" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>15.7</v>
+        <v>22.4</v>
       </c>
       <c r="X17" t="n">
-        <v>12.6</v>
+        <v>15.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>-0.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>216.02</v>
+        <v>230.27</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2164,10 +2158,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>128.54</v>
+        <v>132.76</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.84</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2175,67 +2169,94 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
-      <c r="AP17" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL17" s="1" t="n">
-        <v>46226</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46227</v>
+        <v>46229</v>
       </c>
       <c r="B18" t="n">
-        <v>156</v>
+        <v>149.1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>30.1</v>
+        <v>29</v>
+      </c>
+      <c r="E18" t="n">
+        <v>25.9</v>
       </c>
       <c r="F18" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>24</v>
+      </c>
+      <c r="I18" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>38.8</v>
       </c>
       <c r="K18" t="n">
-        <v>95.90000000000001</v>
+        <v>74.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>36.7</v>
       </c>
       <c r="O18" t="n">
-        <v>39.2</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>21.7</v>
       </c>
       <c r="V18" t="n">
-        <v>7.1</v>
+        <v>10.3</v>
       </c>
       <c r="W18" t="n">
-        <v>20.9</v>
+        <v>24.4</v>
       </c>
       <c r="X18" t="n">
-        <v>14</v>
+        <v>17.4</v>
       </c>
       <c r="Y18" t="n">
         <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>224.53</v>
+        <v>237.43</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.32</v>
+        <v>7.16</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2244,10 +2265,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>130.92</v>
+        <v>134.95</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2255,61 +2276,67 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
+      <c r="AP18" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL18" s="1" t="n">
-        <v>46227</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B19" t="n">
-        <v>147.8</v>
+        <v>143.9</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>32.9</v>
       </c>
       <c r="F19" t="n">
         <v>6.8</v>
       </c>
       <c r="K19" t="n">
-        <v>96.5</v>
+        <v>96.2</v>
       </c>
       <c r="O19" t="n">
-        <v>39.3</v>
+        <v>37.9</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W19" t="n">
-        <v>22.4</v>
+        <v>25.6</v>
       </c>
       <c r="X19" t="n">
-        <v>15.2</v>
+        <v>17.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA19" t="n">
         <v>16</v>
       </c>
-      <c r="AA19" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AB19" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>230.27</v>
+        <v>236.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>5.74</v>
+        <v>-1.29</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2318,10 +2345,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>132.76</v>
+        <v>136.28</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.84</v>
+        <v>1.33</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2330,93 +2357,93 @@
         <v>142</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46228</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46229</v>
+        <v>46231</v>
       </c>
       <c r="B20" t="n">
-        <v>149.1</v>
+        <v>166.4</v>
       </c>
       <c r="C20" t="n">
-        <v>60</v>
+        <v>63.7</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>34.5</v>
       </c>
       <c r="E20" t="n">
-        <v>25.9</v>
+        <v>36.4</v>
       </c>
       <c r="F20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H20" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="I20" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="J20" t="n">
-        <v>38.8</v>
+        <v>39.9</v>
       </c>
       <c r="K20" t="n">
-        <v>74.5</v>
+        <v>75.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>36.7</v>
+        <v>35.9</v>
       </c>
       <c r="O20" t="n">
-        <v>40.1</v>
+        <v>39</v>
       </c>
       <c r="Q20" t="n">
-        <v>21.7</v>
+        <v>20.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>21.7</v>
+        <v>20.3</v>
       </c>
       <c r="V20" t="n">
-        <v>10.3</v>
+        <v>11.9</v>
       </c>
       <c r="W20" t="n">
-        <v>24.4</v>
+        <v>27</v>
       </c>
       <c r="X20" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AA20" t="n">
-        <v>15.7</v>
+        <v>14.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>-2.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="AF20" t="n">
-        <v>237.43</v>
+        <v>236.13</v>
       </c>
       <c r="AG20" t="n">
-        <v>7.16</v>
+        <v>-0.01</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2425,10 +2452,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>134.95</v>
+        <v>134.54</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.19</v>
+        <v>-1.74</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2437,66 +2464,99 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>91.28</v>
+        <v>82.27</v>
       </c>
       <c r="AS20" t="n">
-        <v>16.95</v>
+        <v>16.28</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46229</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B21" t="n">
-        <v>143.9</v>
+        <v>172.9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>32.9</v>
+        <v>34.9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>35.2</v>
       </c>
       <c r="F21" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>41.7</v>
       </c>
       <c r="K21" t="n">
-        <v>96.2</v>
+        <v>76.7</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>34.8</v>
       </c>
       <c r="O21" t="n">
-        <v>37.9</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>19</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="n">
+        <v>19</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="W21" t="n">
-        <v>25.6</v>
+        <v>18.7</v>
       </c>
       <c r="X21" t="n">
-        <v>17.8</v>
+        <v>16.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA21" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>-1.4</v>
+        <v>-4.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>236.14</v>
+        <v>218.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>-1.29</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2505,10 +2565,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>136.28</v>
+        <v>130.39</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.33</v>
+        <v>-4.15</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2516,94 +2576,100 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
+      <c r="AP21" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>15.79</v>
+      </c>
       <c r="BL21" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B22" t="n">
-        <v>166.4</v>
+        <v>157.5</v>
       </c>
       <c r="C22" t="n">
-        <v>63.7</v>
+        <v>68.5</v>
       </c>
       <c r="D22" t="n">
-        <v>34.5</v>
+        <v>33.2</v>
       </c>
       <c r="E22" t="n">
-        <v>36.4</v>
+        <v>27.7</v>
       </c>
       <c r="F22" t="n">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="H22" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="I22" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J22" t="n">
-        <v>39.9</v>
+        <v>41.4</v>
       </c>
       <c r="K22" t="n">
-        <v>75.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="N22" t="n">
-        <v>35.9</v>
+        <v>34.9</v>
       </c>
       <c r="O22" t="n">
-        <v>39</v>
+        <v>37.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>20.3</v>
+        <v>21.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>20.3</v>
+        <v>21.6</v>
       </c>
       <c r="V22" t="n">
-        <v>11.9</v>
+        <v>15.1</v>
       </c>
       <c r="W22" t="n">
-        <v>27</v>
+        <v>23.1</v>
       </c>
       <c r="X22" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y22" t="n">
         <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA22" t="n">
-        <v>14.4</v>
+        <v>13.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>-3.5</v>
+        <v>-0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>236.13</v>
+        <v>218.84</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.01</v>
+        <v>0.25</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2612,10 +2678,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>134.54</v>
+        <v>133.09</v>
       </c>
       <c r="AL22" t="n">
-        <v>-1.74</v>
+        <v>2.7</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2624,99 +2690,66 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>82.27</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>16.28</v>
+        <v>15.63</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B23" t="n">
-        <v>172.9</v>
-      </c>
-      <c r="C23" t="n">
-        <v>67.59999999999999</v>
+        <v>137.6</v>
       </c>
       <c r="D23" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E23" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="F23" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I23" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>41.7</v>
+        <v>6.5</v>
       </c>
       <c r="K23" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>34.8</v>
+        <v>96.7</v>
       </c>
       <c r="O23" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="Q23" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X23" t="n">
         <v>19</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="n">
-        <v>19</v>
-      </c>
-      <c r="V23" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W23" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X23" t="n">
-        <v>16.6</v>
-      </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>218.6</v>
+        <v>221.78</v>
       </c>
       <c r="AG23" t="n">
-        <v>-9.380000000000001</v>
+        <v>2.94</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2725,10 +2758,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>130.39</v>
+        <v>138.76</v>
       </c>
       <c r="AL23" t="n">
-        <v>-4.15</v>
+        <v>5.67</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2736,100 +2769,61 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
-      <c r="AP23" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>15.79</v>
-      </c>
       <c r="BL23" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="B24" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C24" t="n">
-        <v>68.5</v>
+        <v>132.5</v>
       </c>
       <c r="D24" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>27.7</v>
+        <v>33.6</v>
       </c>
       <c r="F24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="V24" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X24" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC24" t="n">
         <v>3.6</v>
       </c>
-      <c r="H24" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I24" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="K24" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="O24" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>9</v>
-      </c>
-      <c r="T24" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V24" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X24" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>224.78</v>
+      </c>
+      <c r="AG24" t="n">
         <v>3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>218.84</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.25</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2838,10 +2832,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>133.09</v>
+        <v>143.55</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.7</v>
+        <v>4.79</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2849,67 +2843,94 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
-      <c r="AP24" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL24" s="1" t="n">
-        <v>46233</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B25" t="n">
-        <v>137.6</v>
+        <v>137.2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>56.3</v>
       </c>
       <c r="D25" t="n">
-        <v>35</v>
+        <v>32.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>21.2</v>
       </c>
       <c r="F25" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>40.4</v>
       </c>
       <c r="K25" t="n">
-        <v>96.7</v>
+        <v>75.7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N25" t="n">
+        <v>29</v>
       </c>
       <c r="O25" t="n">
-        <v>35.1</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>21.6</v>
       </c>
       <c r="V25" t="n">
-        <v>13.6</v>
+        <v>10.7</v>
       </c>
       <c r="W25" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="X25" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA25" t="n">
-        <v>17.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0</v>
+        <v>0.9</v>
       </c>
       <c r="AC25" t="n">
         <v>5.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>221.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.94</v>
+        <v>7.43</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2918,10 +2939,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>138.76</v>
+        <v>143.61</v>
       </c>
       <c r="AL25" t="n">
-        <v>5.67</v>
+        <v>0.06</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2929,61 +2950,100 @@
       <c r="AN25" t="n">
         <v>142</v>
       </c>
+      <c r="AP25" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL25" s="1" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="B26" t="n">
-        <v>132.5</v>
+        <v>157.5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>59.6</v>
       </c>
       <c r="D26" t="n">
-        <v>33.6</v>
+        <v>35</v>
+      </c>
+      <c r="E26" t="n">
+        <v>30.6</v>
       </c>
       <c r="F26" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>38.9</v>
       </c>
       <c r="K26" t="n">
-        <v>97.8</v>
+        <v>74.3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>33.4</v>
       </c>
       <c r="O26" t="n">
-        <v>31.6</v>
+        <v>37.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>21.1</v>
       </c>
       <c r="V26" t="n">
-        <v>14.8</v>
+        <v>13</v>
       </c>
       <c r="W26" t="n">
-        <v>24.7</v>
+        <v>26.3</v>
       </c>
       <c r="X26" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA26" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.6</v>
+        <v>-2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
-        <v>224.78</v>
+        <v>229.69</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>-2.53</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -2992,10 +3052,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>143.55</v>
+        <v>136.96</v>
       </c>
       <c r="AL26" t="n">
-        <v>4.79</v>
+        <v>-6.65</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3003,94 +3063,100 @@
       <c r="AN26" t="n">
         <v>142</v>
       </c>
+      <c r="AP26" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>16.96</v>
+      </c>
       <c r="BL26" s="1" t="n">
-        <v>46235</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
       <c r="B27" t="n">
-        <v>137.2</v>
+        <v>159.6</v>
       </c>
       <c r="C27" t="n">
-        <v>56.3</v>
+        <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="E27" t="n">
-        <v>21.2</v>
+        <v>31.1</v>
       </c>
       <c r="F27" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="H27" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="I27" t="n">
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="J27" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="K27" t="n">
-        <v>75.7</v>
+        <v>75.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>29</v>
+        <v>34.3</v>
       </c>
       <c r="O27" t="n">
-        <v>32.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="V27" t="n">
-        <v>10.7</v>
+        <v>17.5</v>
       </c>
       <c r="W27" t="n">
-        <v>24.3</v>
+        <v>22.5</v>
       </c>
       <c r="X27" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z27" t="n">
         <v>15</v>
       </c>
       <c r="AA27" t="n">
-        <v>15.4</v>
+        <v>13.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.9</v>
+        <v>-2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>232.22</v>
+        <v>228.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>7.43</v>
+        <v>-1.14</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3099,10 +3165,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>143.61</v>
+        <v>133.01</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.06</v>
+        <v>-3.95</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3111,72 +3177,72 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>89.31999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>18.02</v>
+        <v>15.95</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B28" t="n">
-        <v>157.5</v>
+        <v>160.4</v>
       </c>
       <c r="C28" t="n">
-        <v>59.6</v>
+        <v>62.6</v>
       </c>
       <c r="D28" t="n">
         <v>35</v>
       </c>
       <c r="E28" t="n">
-        <v>30.6</v>
+        <v>32.2</v>
       </c>
       <c r="F28" t="n">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="H28" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="I28" t="n">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="J28" t="n">
-        <v>38.9</v>
+        <v>41.1</v>
       </c>
       <c r="K28" t="n">
-        <v>74.3</v>
+        <v>75.7</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="N28" t="n">
-        <v>33.4</v>
+        <v>32.6</v>
       </c>
       <c r="O28" t="n">
-        <v>37.1</v>
+        <v>38</v>
       </c>
       <c r="Q28" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T28" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="V28" t="n">
-        <v>13</v>
+        <v>16.4</v>
       </c>
       <c r="W28" t="n">
-        <v>26.3</v>
+        <v>22.8</v>
       </c>
       <c r="X28" t="n">
         <v>19.6</v>
@@ -3188,22 +3254,22 @@
         <v>16</v>
       </c>
       <c r="AA28" t="n">
-        <v>15.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>-2.1</v>
+        <v>-3.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="AF28" t="n">
-        <v>229.69</v>
+        <v>225.08</v>
       </c>
       <c r="AG28" t="n">
-        <v>-2.53</v>
+        <v>-3.5</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3212,10 +3278,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>136.96</v>
+        <v>135.24</v>
       </c>
       <c r="AL28" t="n">
-        <v>-6.65</v>
+        <v>2.23</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3224,99 +3290,99 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>86.59</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS28" t="n">
-        <v>16.96</v>
+        <v>15.4</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B29" t="n">
-        <v>159.6</v>
+        <v>161.7</v>
       </c>
       <c r="C29" t="n">
-        <v>63</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E29" t="n">
-        <v>31.1</v>
+        <v>27.3</v>
       </c>
       <c r="F29" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="H29" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="I29" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="J29" t="n">
-        <v>40.5</v>
+        <v>42.6</v>
       </c>
       <c r="K29" t="n">
-        <v>75.2</v>
+        <v>77</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="N29" t="n">
-        <v>34.3</v>
+        <v>31.5</v>
       </c>
       <c r="O29" t="n">
-        <v>38.2</v>
+        <v>37.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T29" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="V29" t="n">
-        <v>17.5</v>
+        <v>12.7</v>
       </c>
       <c r="W29" t="n">
-        <v>22.5</v>
+        <v>27</v>
       </c>
       <c r="X29" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA29" t="n">
-        <v>13.5</v>
+        <v>11.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>-2.2</v>
+        <v>-5.2</v>
       </c>
       <c r="AC29" t="n">
         <v>4.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>228.57</v>
+        <v>225</v>
       </c>
       <c r="AG29" t="n">
-        <v>-1.14</v>
+        <v>-0.08</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3325,10 +3391,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>133.01</v>
+        <v>134.62</v>
       </c>
       <c r="AL29" t="n">
-        <v>-3.95</v>
+        <v>-0.62</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3337,99 +3403,60 @@
         <v>142</v>
       </c>
       <c r="AP29" t="n">
-        <v>84.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>15.95</v>
+        <v>13.86</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B30" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="C30" t="n">
-        <v>62.6</v>
+        <v>151.5</v>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
-      </c>
-      <c r="E30" t="n">
-        <v>32.2</v>
+        <v>35.1</v>
       </c>
       <c r="F30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H30" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="I30" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M30" t="n">
         <v>5.4</v>
       </c>
-      <c r="N30" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="O30" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>20.9</v>
-      </c>
       <c r="V30" t="n">
-        <v>16.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>22.8</v>
+        <v>19.4</v>
       </c>
       <c r="X30" t="n">
-        <v>19.6</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z30" t="n">
         <v>13</v>
       </c>
-      <c r="Z30" t="n">
-        <v>16</v>
-      </c>
       <c r="AA30" t="n">
-        <v>14.1</v>
+        <v>9</v>
       </c>
       <c r="AB30" t="n">
-        <v>-3.1</v>
+        <v>-4.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.6</v>
+        <v>-1.4</v>
       </c>
       <c r="AF30" t="n">
-        <v>225.08</v>
+        <v>221.37</v>
       </c>
       <c r="AG30" t="n">
-        <v>-3.5</v>
+        <v>0.05</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3438,10 +3465,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>135.24</v>
+        <v>135.21</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.23</v>
+        <v>0.59</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3449,100 +3476,61 @@
       <c r="AN30" t="n">
         <v>142</v>
       </c>
-      <c r="AP30" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>15.4</v>
-      </c>
       <c r="BL30" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="B31" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C31" t="n">
-        <v>71.09999999999999</v>
+        <v>145.2</v>
       </c>
       <c r="D31" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E31" t="n">
-        <v>27.3</v>
+        <v>33.5</v>
       </c>
       <c r="F31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H31" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>42.6</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>77</v>
-      </c>
-      <c r="M31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N31" t="n">
-        <v>31.5</v>
+        <v>100.3</v>
       </c>
       <c r="O31" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>21</v>
-      </c>
-      <c r="R31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S31" t="n">
-        <v>6</v>
-      </c>
-      <c r="T31" t="n">
-        <v>21</v>
+        <v>35.5</v>
       </c>
       <c r="V31" t="n">
-        <v>12.7</v>
+        <v>7.1</v>
       </c>
       <c r="W31" t="n">
-        <v>27</v>
+        <v>19.2</v>
       </c>
       <c r="X31" t="n">
-        <v>19.9</v>
+        <v>13.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA31" t="n">
-        <v>11.4</v>
+        <v>10</v>
       </c>
       <c r="AB31" t="n">
-        <v>-5.2</v>
+        <v>-5.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.3</v>
+        <v>-1.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>225</v>
+        <v>224.37</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.08</v>
+        <v>3</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3551,10 +3539,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>134.62</v>
+        <v>135.61</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.62</v>
+        <v>0.4</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3562,61 +3550,61 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
-      <c r="AP31" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL31" s="1" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B32" t="n">
-        <v>151.5</v>
+        <v>146.3</v>
       </c>
       <c r="D32" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="O32" t="n">
         <v>35.1</v>
       </c>
-      <c r="F32" t="n">
-        <v>5.4</v>
-      </c>
       <c r="V32" t="n">
-        <v>8.699999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="W32" t="n">
-        <v>19.4</v>
+        <v>16.4</v>
       </c>
       <c r="X32" t="n">
-        <v>14</v>
+        <v>10.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="n">
         <v>9</v>
       </c>
       <c r="AB32" t="n">
-        <v>-4.7</v>
+        <v>-6.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.9</v>
+        <v>-0.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>-1.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AF32" t="n">
-        <v>221.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.05</v>
+        <v>1.56</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3625,10 +3613,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>135.21</v>
+        <v>135.28</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.59</v>
+        <v>-0.33</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3637,60 +3625,93 @@
         <v>142</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="B33" t="n">
-        <v>145.2</v>
+        <v>182.8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>86.8</v>
       </c>
       <c r="D33" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>33</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N33" t="n">
         <v>33.5</v>
       </c>
-      <c r="F33" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>100.3</v>
-      </c>
       <c r="O33" t="n">
-        <v>35.5</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="n">
+        <v>22.4</v>
       </c>
       <c r="V33" t="n">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="W33" t="n">
-        <v>19.2</v>
+        <v>15</v>
       </c>
       <c r="X33" t="n">
-        <v>13.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA33" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>-5.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>-1.5</v>
+        <v>-5.1</v>
       </c>
       <c r="AF33" t="n">
-        <v>224.37</v>
+        <v>218.63</v>
       </c>
       <c r="AG33" t="n">
-        <v>3</v>
+        <v>-7.3</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3699,10 +3720,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>135.61</v>
+        <v>126.27</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.4</v>
+        <v>-9.01</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3710,61 +3731,100 @@
       <c r="AN33" t="n">
         <v>142</v>
       </c>
+      <c r="AP33" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL33" s="1" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="B34" t="n">
-        <v>146.3</v>
+        <v>181.8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>86.5</v>
       </c>
       <c r="D34" t="n">
-        <v>33.4</v>
+        <v>31.4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>34.2</v>
       </c>
       <c r="F34" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>41.9</v>
       </c>
       <c r="K34" t="n">
-        <v>98.2</v>
+        <v>76.8</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>35.7</v>
       </c>
       <c r="O34" t="n">
-        <v>35.1</v>
+        <v>39.8</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>23</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>23</v>
       </c>
       <c r="V34" t="n">
-        <v>4.9</v>
+        <v>7.1</v>
       </c>
       <c r="W34" t="n">
-        <v>16.4</v>
+        <v>14.8</v>
       </c>
       <c r="X34" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="Y34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z34" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA34" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB34" t="n">
-        <v>-6.4</v>
+        <v>-4.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>-3.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>225.93</v>
+        <v>216.39</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.56</v>
+        <v>-2.23</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3773,10 +3833,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>135.28</v>
+        <v>123.32</v>
       </c>
       <c r="AL34" t="n">
-        <v>-0.33</v>
+        <v>-2.95</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3784,94 +3844,100 @@
       <c r="AN34" t="n">
         <v>142</v>
       </c>
+      <c r="AP34" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>13.91</v>
+      </c>
       <c r="BL34" s="1" t="n">
-        <v>46243</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B35" t="n">
-        <v>182.8</v>
+        <v>183</v>
       </c>
       <c r="C35" t="n">
-        <v>86.8</v>
+        <v>84.7</v>
       </c>
       <c r="D35" t="n">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="E35" t="n">
-        <v>33</v>
+        <v>33.7</v>
       </c>
       <c r="F35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4</v>
+      </c>
+      <c r="N35" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="O35" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V35" t="n">
         <v>5.7</v>
       </c>
-      <c r="H35" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="I35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N35" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S35" t="n">
-        <v>15</v>
-      </c>
-      <c r="T35" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="V35" t="n">
-        <v>9.1</v>
-      </c>
       <c r="W35" t="n">
-        <v>15</v>
+        <v>16.1</v>
       </c>
       <c r="X35" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AB35" t="n">
-        <v>-10.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>-5.1</v>
+        <v>1.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>218.63</v>
+        <v>217.16</v>
       </c>
       <c r="AG35" t="n">
-        <v>-7.3</v>
+        <v>0.76</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3880,10 +3946,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>126.27</v>
+        <v>117.87</v>
       </c>
       <c r="AL35" t="n">
-        <v>-9.01</v>
+        <v>-5.45</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3892,99 +3958,66 @@
         <v>142</v>
       </c>
       <c r="AP35" t="n">
-        <v>82.66</v>
+        <v>78.56</v>
       </c>
       <c r="AS35" t="n">
-        <v>14.7</v>
+        <v>13.45</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B36" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="C36" t="n">
-        <v>86.5</v>
+        <v>163.8</v>
       </c>
       <c r="D36" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E36" t="n">
-        <v>34.2</v>
+        <v>29</v>
       </c>
       <c r="F36" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H36" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J36" t="n">
-        <v>41.9</v>
+        <v>6.5</v>
       </c>
       <c r="K36" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="M36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N36" t="n">
-        <v>35.7</v>
+        <v>101.2</v>
       </c>
       <c r="O36" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>23</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S36" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>23</v>
+        <v>40.2</v>
       </c>
       <c r="V36" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="W36" t="n">
-        <v>14.8</v>
+        <v>17.2</v>
       </c>
       <c r="X36" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z36" t="n">
         <v>12</v>
       </c>
       <c r="AA36" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB36" t="n">
-        <v>-4.5</v>
+        <v>1.2</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>-1.4</v>
+        <v>2.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>216.39</v>
+        <v>220.31</v>
       </c>
       <c r="AG36" t="n">
-        <v>-2.23</v>
+        <v>3.16</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -3993,10 +4026,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>123.32</v>
+        <v>116.52</v>
       </c>
       <c r="AL36" t="n">
-        <v>-2.95</v>
+        <v>-1.35</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4004,100 +4037,61 @@
       <c r="AN36" t="n">
         <v>142</v>
       </c>
-      <c r="AP36" t="n">
-        <v>79.08</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>13.91</v>
-      </c>
       <c r="BL36" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B37" t="n">
-        <v>183</v>
-      </c>
-      <c r="C37" t="n">
-        <v>84.7</v>
+        <v>155.9</v>
       </c>
       <c r="D37" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E37" t="n">
-        <v>33.7</v>
+        <v>28</v>
       </c>
       <c r="F37" t="n">
-        <v>7</v>
-      </c>
-      <c r="H37" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I37" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J37" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K37" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M37" t="n">
-        <v>4</v>
-      </c>
-      <c r="N37" t="n">
-        <v>36.7</v>
+        <v>99.3</v>
       </c>
       <c r="O37" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S37" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T37" t="n">
-        <v>23.6</v>
+        <v>38.5</v>
       </c>
       <c r="V37" t="n">
-        <v>5.7</v>
+        <v>8.9</v>
       </c>
       <c r="W37" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="X37" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z37" t="n">
         <v>13</v>
       </c>
       <c r="AA37" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>217.16</v>
+        <v>221.99</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4106,10 +4100,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>117.87</v>
+        <v>116.37</v>
       </c>
       <c r="AL37" t="n">
-        <v>-5.45</v>
+        <v>-0.15</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4117,67 +4111,61 @@
       <c r="AN37" t="n">
         <v>142</v>
       </c>
-      <c r="AP37" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL37" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="B38" t="n">
-        <v>163.8</v>
+        <v>141.3</v>
       </c>
       <c r="D38" t="n">
-        <v>29</v>
+        <v>26.3</v>
       </c>
       <c r="F38" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K38" t="n">
-        <v>101.2</v>
+        <v>97.8</v>
       </c>
       <c r="O38" t="n">
-        <v>40.2</v>
+        <v>39.8</v>
       </c>
       <c r="V38" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W38" t="n">
-        <v>17.2</v>
+        <v>17.7</v>
       </c>
       <c r="X38" t="n">
-        <v>11.8</v>
+        <v>13.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z38" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA38" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="AF38" t="n">
-        <v>220.31</v>
+        <v>225.14</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4185,12 +4173,6 @@
       <c r="AI38" t="n">
         <v>235</v>
       </c>
-      <c r="AK38" t="n">
-        <v>116.52</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>-1.35</v>
-      </c>
       <c r="AM38" t="n">
         <v>110</v>
       </c>
@@ -4198,60 +4180,54 @@
         <v>142</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="B39" t="n">
-        <v>155.9</v>
+        <v>131.5</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>27.3</v>
       </c>
       <c r="F39" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K39" t="n">
-        <v>99.3</v>
+        <v>97</v>
       </c>
       <c r="O39" t="n">
-        <v>38.5</v>
+        <v>35.7</v>
       </c>
       <c r="V39" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W39" t="n">
-        <v>15.8</v>
+        <v>13.9</v>
       </c>
       <c r="X39" t="n">
-        <v>12.4</v>
+        <v>11.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z39" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA39" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.4</v>
+        <v>-3.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>221.99</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.67</v>
+        <v>-0.4</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4259,12 +4235,6 @@
       <c r="AI39" t="n">
         <v>235</v>
       </c>
-      <c r="AK39" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM39" t="n">
         <v>110</v>
       </c>
@@ -4272,60 +4242,93 @@
         <v>142</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="B40" t="n">
-        <v>141.3</v>
+        <v>153</v>
+      </c>
+      <c r="C40" t="n">
+        <v>71.8</v>
       </c>
       <c r="D40" t="n">
-        <v>26.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E40" t="n">
+        <v>24.7</v>
       </c>
       <c r="F40" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H40" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>41.1</v>
       </c>
       <c r="K40" t="n">
-        <v>97.8</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N40" t="n">
+        <v>33.5</v>
       </c>
       <c r="O40" t="n">
-        <v>39.8</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>23.2</v>
       </c>
       <c r="V40" t="n">
-        <v>9.5</v>
+        <v>11.2</v>
       </c>
       <c r="W40" t="n">
-        <v>17.7</v>
+        <v>13</v>
       </c>
       <c r="X40" t="n">
-        <v>13.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z40" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.2</v>
+        <v>-6.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.9</v>
+        <v>-0.6</v>
       </c>
       <c r="AF40" t="n">
-        <v>225.14</v>
+        <v>229.96</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.15</v>
+        <v>-0.02</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4333,61 +4336,112 @@
       <c r="AI40" t="n">
         <v>235</v>
       </c>
+      <c r="AK40" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM40" t="n">
         <v>110</v>
       </c>
       <c r="AN40" t="n">
         <v>142</v>
       </c>
+      <c r="AP40" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL40" s="1" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46250</v>
+        <v>46252</v>
       </c>
       <c r="B41" t="n">
-        <v>131.5</v>
+        <v>165.8</v>
+      </c>
+      <c r="C41" t="n">
+        <v>77.3</v>
       </c>
       <c r="D41" t="n">
-        <v>27.3</v>
+        <v>29.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>27.7</v>
       </c>
       <c r="F41" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J41" t="n">
+        <v>41.6</v>
       </c>
       <c r="K41" t="n">
-        <v>97</v>
+        <v>76.59999999999999</v>
+      </c>
+      <c r="M41" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N41" t="n">
+        <v>35.1</v>
       </c>
       <c r="O41" t="n">
-        <v>35.7</v>
+        <v>39.8</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S41" t="n">
+        <v>7</v>
+      </c>
+      <c r="T41" t="n">
+        <v>23.8</v>
       </c>
       <c r="V41" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="W41" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="X41" t="n">
-        <v>11.4</v>
+        <v>13.4</v>
       </c>
       <c r="Y41" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z41" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AA41" t="n">
-        <v>15</v>
+        <v>10.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>-3.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.8</v>
+        <v>9.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.4</v>
+        <v>4.4</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>227.01</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>-2.95</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4395,100 +4449,112 @@
       <c r="AI41" t="n">
         <v>235</v>
       </c>
+      <c r="AK41" t="n">
+        <v>128.15</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.01</v>
+      </c>
       <c r="AM41" t="n">
         <v>110</v>
       </c>
       <c r="AN41" t="n">
         <v>142</v>
       </c>
+      <c r="AP41" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>14.52</v>
+      </c>
       <c r="BL41" s="1" t="n">
-        <v>46250</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B42" t="n">
-        <v>153</v>
+        <v>158.1</v>
       </c>
       <c r="C42" t="n">
-        <v>71.8</v>
+        <v>73.7</v>
       </c>
       <c r="D42" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="E42" t="n">
-        <v>24.7</v>
+        <v>26</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H42" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I42" t="n">
-        <v>10.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="K42" t="n">
-        <v>75.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N42" t="n">
-        <v>33.5</v>
+        <v>35.3</v>
       </c>
       <c r="O42" t="n">
-        <v>38.3</v>
+        <v>40.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="R42" t="n">
         <v>2.5</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T42" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="V42" t="n">
-        <v>11.2</v>
+        <v>8.9</v>
       </c>
       <c r="W42" t="n">
-        <v>13</v>
+        <v>19.3</v>
       </c>
       <c r="X42" t="n">
-        <v>12.1</v>
+        <v>14.1</v>
       </c>
       <c r="Y42" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Z42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA42" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AB42" t="n">
-        <v>-6.6</v>
+        <v>4.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.6</v>
+        <v>6.5</v>
       </c>
       <c r="AF42" t="n">
-        <v>229.96</v>
+        <v>228.35</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.02</v>
+        <v>1.33</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4497,10 +4563,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>128.14</v>
+        <v>128.86</v>
       </c>
       <c r="AL42" t="n">
-        <v>11.77</v>
+        <v>0.71</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4509,99 +4575,99 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>87.47</v>
+        <v>82.37</v>
       </c>
       <c r="AS42" t="n">
-        <v>14.8</v>
+        <v>14.22</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B43" t="n">
-        <v>165.8</v>
+        <v>154.9</v>
       </c>
       <c r="C43" t="n">
-        <v>77.3</v>
+        <v>70.2</v>
       </c>
       <c r="D43" t="n">
-        <v>29.3</v>
+        <v>31.5</v>
       </c>
       <c r="E43" t="n">
         <v>27.7</v>
       </c>
       <c r="F43" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="H43" t="n">
         <v>24.1</v>
       </c>
       <c r="I43" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="J43" t="n">
-        <v>41.6</v>
+        <v>40.3</v>
       </c>
       <c r="K43" t="n">
-        <v>76.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="M43" t="n">
-        <v>4.7</v>
+        <v>6.1</v>
       </c>
       <c r="N43" t="n">
-        <v>35.1</v>
+        <v>32.9</v>
       </c>
       <c r="O43" t="n">
-        <v>39.8</v>
+        <v>39</v>
       </c>
       <c r="Q43" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="R43" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T43" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V43" t="n">
-        <v>9.4</v>
+        <v>6.3</v>
       </c>
       <c r="W43" t="n">
-        <v>17.4</v>
+        <v>25.2</v>
       </c>
       <c r="X43" t="n">
-        <v>13.4</v>
+        <v>15.8</v>
       </c>
       <c r="Y43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z43" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AA43" t="n">
-        <v>10.1</v>
+        <v>12.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.7</v>
+        <v>2.9</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>227.01</v>
+        <v>231.16</v>
       </c>
       <c r="AG43" t="n">
-        <v>-2.95</v>
+        <v>2.81</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4610,10 +4676,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>128.15</v>
+        <v>130.88</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.01</v>
+        <v>2.02</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4622,99 +4688,66 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>83.41</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS43" t="n">
-        <v>14.52</v>
+        <v>13.1</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B44" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="C44" t="n">
-        <v>73.7</v>
+        <v>152.2</v>
       </c>
       <c r="D44" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F44" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I44" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J44" t="n">
-        <v>40.9</v>
+        <v>3.5</v>
       </c>
       <c r="K44" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M44" t="n">
-        <v>5</v>
-      </c>
-      <c r="N44" t="n">
-        <v>35.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S44" t="n">
-        <v>7</v>
-      </c>
-      <c r="T44" t="n">
-        <v>23.6</v>
+        <v>34.4</v>
       </c>
       <c r="V44" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W44" t="n">
-        <v>19.3</v>
+        <v>25.5</v>
       </c>
       <c r="X44" t="n">
-        <v>14.1</v>
+        <v>17.5</v>
       </c>
       <c r="Y44" t="n">
         <v>6</v>
       </c>
       <c r="Z44" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="AF44" t="n">
-        <v>228.35</v>
+        <v>228.13</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.33</v>
+        <v>-3.03</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4722,112 +4755,67 @@
       <c r="AI44" t="n">
         <v>235</v>
       </c>
-      <c r="AK44" t="n">
-        <v>128.86</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0.71</v>
-      </c>
       <c r="AM44" t="n">
         <v>110</v>
       </c>
       <c r="AN44" t="n">
         <v>142</v>
       </c>
-      <c r="AP44" t="n">
-        <v>82.37</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>14.22</v>
-      </c>
       <c r="BL44" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B45" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C45" t="n">
-        <v>70.2</v>
+        <v>143.9</v>
       </c>
       <c r="D45" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E45" t="n">
-        <v>27.7</v>
+        <v>30.8</v>
       </c>
       <c r="F45" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H45" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J45" t="n">
-        <v>40.3</v>
+        <v>2.5</v>
       </c>
       <c r="K45" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M45" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>32.9</v>
+        <v>99.2</v>
       </c>
       <c r="O45" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R45" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S45" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T45" t="n">
-        <v>23.7</v>
+        <v>35.2</v>
       </c>
       <c r="V45" t="n">
-        <v>6.3</v>
+        <v>10.7</v>
       </c>
       <c r="W45" t="n">
-        <v>25.2</v>
+        <v>17.6</v>
       </c>
       <c r="X45" t="n">
-        <v>15.8</v>
+        <v>14.2</v>
       </c>
       <c r="Y45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z45" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA45" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="AF45" t="n">
-        <v>231.16</v>
+        <v>229.16</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.81</v>
+        <v>1.03</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4835,79 +4823,100 @@
       <c r="AI45" t="n">
         <v>235</v>
       </c>
-      <c r="AK45" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM45" t="n">
         <v>110</v>
       </c>
       <c r="AN45" t="n">
         <v>142</v>
       </c>
-      <c r="AP45" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL45" s="1" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B46" t="n">
-        <v>152.2</v>
+        <v>163.2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>73.7</v>
       </c>
       <c r="D46" t="n">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="E46" t="n">
+        <v>28.2</v>
       </c>
       <c r="F46" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J46" t="n">
+        <v>40.1</v>
       </c>
       <c r="K46" t="n">
-        <v>98.40000000000001</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N46" t="n">
+        <v>32.9</v>
       </c>
       <c r="O46" t="n">
-        <v>34.4</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S46" t="n">
+        <v>6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>23.5</v>
       </c>
       <c r="V46" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W46" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AC46" t="n">
         <v>9.5</v>
       </c>
-      <c r="W46" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X46" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD46" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AF46" t="n">
-        <v>228.13</v>
+        <v>228.55</v>
       </c>
       <c r="AG46" t="n">
-        <v>-3.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4915,67 +4924,112 @@
       <c r="AI46" t="n">
         <v>235</v>
       </c>
+      <c r="AK46" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM46" t="n">
         <v>110</v>
       </c>
       <c r="AN46" t="n">
         <v>142</v>
       </c>
+      <c r="AP46" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL46" s="1" t="n">
-        <v>46255</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B47" t="n">
-        <v>143.9</v>
+        <v>174.4</v>
+      </c>
+      <c r="C47" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="D47" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E47" t="n">
         <v>30.8</v>
       </c>
       <c r="F47" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
+      </c>
+      <c r="H47" t="n">
+        <v>24</v>
+      </c>
+      <c r="I47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J47" t="n">
+        <v>39.5</v>
       </c>
       <c r="K47" t="n">
-        <v>99.2</v>
+        <v>74</v>
+      </c>
+      <c r="M47" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N47" t="n">
+        <v>35.8</v>
       </c>
       <c r="O47" t="n">
-        <v>35.2</v>
+        <v>42.6</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T47" t="n">
+        <v>23.1</v>
       </c>
       <c r="V47" t="n">
-        <v>10.7</v>
+        <v>12.8</v>
       </c>
       <c r="W47" t="n">
-        <v>17.6</v>
+        <v>22.1</v>
       </c>
       <c r="X47" t="n">
-        <v>14.2</v>
+        <v>17.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z47" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA47" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.8</v>
+        <v>0.3</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD47" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>229.16</v>
+        <v>219.99</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.03</v>
+        <v>-8.56</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -4983,100 +5037,112 @@
       <c r="AI47" t="n">
         <v>235</v>
       </c>
+      <c r="AK47" t="n">
+        <v>125.61</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>-1.45</v>
+      </c>
       <c r="AM47" t="n">
         <v>110</v>
       </c>
       <c r="AN47" t="n">
         <v>142</v>
       </c>
+      <c r="AP47" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>12.96</v>
+      </c>
       <c r="BL47" s="1" t="n">
-        <v>46256</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B48" t="n">
         <v>163.2</v>
       </c>
       <c r="C48" t="n">
-        <v>73.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>30</v>
+        <v>32.9</v>
       </c>
       <c r="E48" t="n">
-        <v>28.2</v>
+        <v>26</v>
       </c>
       <c r="F48" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
       <c r="H48" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="I48" t="n">
-        <v>11.4</v>
+        <v>7.4</v>
       </c>
       <c r="J48" t="n">
         <v>40.1</v>
       </c>
       <c r="K48" t="n">
-        <v>75.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="M48" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N48" t="n">
-        <v>32.9</v>
+        <v>34.3</v>
       </c>
       <c r="O48" t="n">
-        <v>39.7</v>
+        <v>41.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R48" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T48" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V48" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="W48" t="n">
-        <v>20.1</v>
+        <v>23.3</v>
       </c>
       <c r="X48" t="n">
-        <v>14.8</v>
+        <v>16.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA48" t="n">
-        <v>9.300000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.9</v>
+        <v>2.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AF48" t="n">
-        <v>228.55</v>
+        <v>219.22</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.61</v>
+        <v>-0.77</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5085,10 +5151,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>127.06</v>
+        <v>124.36</v>
       </c>
       <c r="AL48" t="n">
-        <v>-3.82</v>
+        <v>-1.25</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5097,99 +5163,99 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>82.81</v>
+        <v>76.81</v>
       </c>
       <c r="AS48" t="n">
-        <v>12.9</v>
+        <v>12.38</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46257</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B49" t="n">
-        <v>174.4</v>
+        <v>152.7</v>
       </c>
       <c r="C49" t="n">
-        <v>75.40000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D49" t="n">
-        <v>32.1</v>
+        <v>32.7</v>
       </c>
       <c r="E49" t="n">
-        <v>30.8</v>
+        <v>24.6</v>
       </c>
       <c r="F49" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I49" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K49" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M49" t="n">
         <v>6.6</v>
       </c>
-      <c r="H49" t="n">
-        <v>24</v>
-      </c>
-      <c r="I49" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="K49" t="n">
-        <v>74</v>
-      </c>
-      <c r="M49" t="n">
-        <v>6.8</v>
-      </c>
       <c r="N49" t="n">
-        <v>35.8</v>
+        <v>33.5</v>
       </c>
       <c r="O49" t="n">
-        <v>42.6</v>
+        <v>40.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R49" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="S49" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="T49" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V49" t="n">
-        <v>12.8</v>
+        <v>11.5</v>
       </c>
       <c r="W49" t="n">
-        <v>22.1</v>
+        <v>27.3</v>
       </c>
       <c r="X49" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z49" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA49" t="n">
-        <v>10.1</v>
+        <v>14</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC49" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>219.99</v>
+        <v>220.73</v>
       </c>
       <c r="AG49" t="n">
-        <v>-8.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5198,10 +5264,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>125.61</v>
+        <v>120.93</v>
       </c>
       <c r="AL49" t="n">
-        <v>-1.45</v>
+        <v>-3.43</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5210,99 +5276,99 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>77.83</v>
+        <v>77.87</v>
       </c>
       <c r="AS49" t="n">
-        <v>12.96</v>
+        <v>13.26</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B50" t="n">
-        <v>163.2</v>
+        <v>150.7</v>
       </c>
       <c r="C50" t="n">
-        <v>70.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="D50" t="n">
-        <v>32.9</v>
+        <v>33.7</v>
       </c>
       <c r="E50" t="n">
-        <v>26</v>
+        <v>27.1</v>
       </c>
       <c r="F50" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="H50" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I50" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J50" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="K50" t="n">
-        <v>71.3</v>
+        <v>70.5</v>
       </c>
       <c r="M50" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="N50" t="n">
-        <v>34.3</v>
+        <v>33</v>
       </c>
       <c r="O50" t="n">
-        <v>41.5</v>
+        <v>38.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R50" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="S50" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="T50" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V50" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="W50" t="n">
-        <v>23.3</v>
+        <v>28.9</v>
       </c>
       <c r="X50" t="n">
-        <v>16.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>12.2</v>
+        <v>13.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.5</v>
+        <v>10.8</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="AF50" t="n">
-        <v>219.22</v>
+        <v>220.58</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.77</v>
+        <v>-0.15</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5311,10 +5377,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>124.36</v>
+        <v>120.28</v>
       </c>
       <c r="AL50" t="n">
-        <v>-1.25</v>
+        <v>-0.65</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5323,99 +5389,54 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>76.81</v>
+        <v>77.22</v>
       </c>
       <c r="AS50" t="n">
-        <v>12.38</v>
+        <v>13.79</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B51" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="C51" t="n">
-        <v>62.6</v>
+        <v>138.2</v>
       </c>
       <c r="D51" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E51" t="n">
-        <v>24.6</v>
+        <v>33.6</v>
       </c>
       <c r="F51" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H51" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I51" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="K51" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="M51" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N51" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="O51" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R51" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S51" t="n">
-        <v>4</v>
-      </c>
-      <c r="T51" t="n">
-        <v>23.2</v>
+        <v>6.1</v>
       </c>
       <c r="V51" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="W51" t="n">
-        <v>27.3</v>
+        <v>23.4</v>
       </c>
       <c r="X51" t="n">
         <v>19.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z51" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA51" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="AC51" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>220.73</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5423,112 +5444,61 @@
       <c r="AI51" t="n">
         <v>235</v>
       </c>
-      <c r="AK51" t="n">
-        <v>120.93</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>-3.43</v>
-      </c>
       <c r="AM51" t="n">
         <v>110</v>
       </c>
       <c r="AN51" t="n">
         <v>142</v>
       </c>
-      <c r="AP51" t="n">
-        <v>77.87</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>13.26</v>
-      </c>
       <c r="BL51" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B52" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C52" t="n">
-        <v>64.8</v>
+        <v>126.5</v>
       </c>
       <c r="D52" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E52" t="n">
-        <v>27.1</v>
+        <v>33.2</v>
       </c>
       <c r="F52" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H52" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I52" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J52" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K52" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M52" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N52" t="n">
-        <v>33</v>
-      </c>
-      <c r="O52" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R52" t="n">
         <v>3.4</v>
       </c>
-      <c r="S52" t="n">
-        <v>3</v>
-      </c>
-      <c r="T52" t="n">
-        <v>23.2</v>
-      </c>
       <c r="V52" t="n">
-        <v>14.5</v>
+        <v>12.6</v>
       </c>
       <c r="W52" t="n">
-        <v>28.9</v>
+        <v>22.3</v>
       </c>
       <c r="X52" t="n">
-        <v>21.7</v>
+        <v>17.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z52" t="n">
         <v>18</v>
       </c>
       <c r="AA52" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>10.8</v>
+        <v>6.7</v>
       </c>
       <c r="AD52" t="n">
-        <v>6.7</v>
+        <v>3.4</v>
       </c>
       <c r="AF52" t="n">
-        <v>220.58</v>
+        <v>229.48</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.15</v>
+        <v>6.05</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5536,67 +5506,100 @@
       <c r="AI52" t="n">
         <v>235</v>
       </c>
-      <c r="AK52" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM52" t="n">
         <v>110</v>
       </c>
       <c r="AN52" t="n">
         <v>142</v>
       </c>
-      <c r="AP52" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL52" s="1" t="n">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B53" t="n">
-        <v>138.2</v>
+        <v>129.4</v>
+      </c>
+      <c r="C53" t="n">
+        <v>50.6</v>
       </c>
       <c r="D53" t="n">
-        <v>33.6</v>
+        <v>31.5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>19.4</v>
       </c>
       <c r="F53" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
+      </c>
+      <c r="H53" t="n">
+        <v>24</v>
+      </c>
+      <c r="I53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K53" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M53" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N53" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O53" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>21.4</v>
       </c>
       <c r="V53" t="n">
-        <v>15.5</v>
+        <v>14.3</v>
       </c>
       <c r="W53" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="X53" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z53" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA53" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB53" t="n">
         <v>0.4</v>
       </c>
       <c r="AC53" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="AD53" t="n">
-        <v>4.5</v>
+        <v>4</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0.02</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5604,61 +5607,112 @@
       <c r="AI53" t="n">
         <v>235</v>
       </c>
+      <c r="AK53" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM53" t="n">
         <v>110</v>
       </c>
       <c r="AN53" t="n">
         <v>142</v>
       </c>
+      <c r="AP53" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL53" s="1" t="n">
-        <v>46262</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B54" t="n">
-        <v>126.5</v>
+        <v>142.9</v>
+      </c>
+      <c r="C54" t="n">
+        <v>52.7</v>
       </c>
       <c r="D54" t="n">
-        <v>33.2</v>
+        <v>34.7</v>
+      </c>
+      <c r="E54" t="n">
+        <v>24.8</v>
       </c>
       <c r="F54" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>22</v>
+      </c>
+      <c r="I54" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J54" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="K54" t="n">
+        <v>70</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N54" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O54" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>19.7</v>
       </c>
       <c r="V54" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="W54" t="n">
-        <v>22.3</v>
+        <v>25.8</v>
       </c>
       <c r="X54" t="n">
-        <v>17.4</v>
+        <v>18.9</v>
       </c>
       <c r="Y54" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA54" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AC54" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AF54" t="n">
-        <v>229.48</v>
+        <v>238.69</v>
       </c>
       <c r="AG54" t="n">
-        <v>6.05</v>
+        <v>-2.8</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5666,100 +5720,112 @@
       <c r="AI54" t="n">
         <v>235</v>
       </c>
+      <c r="AK54" t="n">
+        <v>134.59</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>6.22</v>
+      </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
       <c r="AN54" t="n">
         <v>142</v>
       </c>
+      <c r="AP54" t="n">
+        <v>89.05</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>17.06</v>
+      </c>
       <c r="BL54" s="1" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="B55" t="n">
-        <v>129.4</v>
+        <v>148.1</v>
       </c>
       <c r="C55" t="n">
-        <v>50.6</v>
+        <v>51.9</v>
       </c>
       <c r="D55" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E55" t="n">
         <v>31.5</v>
       </c>
-      <c r="E55" t="n">
-        <v>19.4</v>
-      </c>
       <c r="F55" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="H55" t="n">
-        <v>24</v>
+        <v>21.8</v>
       </c>
       <c r="I55" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="J55" t="n">
-        <v>38.9</v>
+        <v>39.6</v>
       </c>
       <c r="K55" t="n">
-        <v>73.3</v>
+        <v>71</v>
       </c>
       <c r="M55" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="N55" t="n">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="O55" t="n">
-        <v>38</v>
+        <v>33.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="R55" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="V55" t="n">
-        <v>14.3</v>
+        <v>13.1</v>
       </c>
       <c r="W55" t="n">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="X55" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="Y55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z55" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA55" t="n">
-        <v>16.1</v>
+        <v>15.5</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.4</v>
+        <v>-1</v>
       </c>
       <c r="AC55" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AD55" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="AF55" t="n">
-        <v>229.5</v>
+        <v>233.48</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.02</v>
+        <v>-4.86</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5768,10 +5834,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>128.37</v>
+        <v>136.6</v>
       </c>
       <c r="AL55" t="n">
-        <v>8.09</v>
+        <v>2.01</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5780,99 +5846,81 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>91.59999999999999</v>
+        <v>86.25</v>
       </c>
       <c r="AS55" t="n">
-        <v>15.97</v>
+        <v>17.13</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46264</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B56" t="n">
-        <v>142.9</v>
+        <v>143.4</v>
       </c>
       <c r="C56" t="n">
-        <v>52.7</v>
+        <v>50.9</v>
       </c>
       <c r="D56" t="n">
-        <v>34.7</v>
+        <v>35.7</v>
       </c>
       <c r="E56" t="n">
-        <v>24.8</v>
+        <v>26.2</v>
       </c>
       <c r="F56" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="H56" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
       <c r="I56" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>38.2</v>
+        <v>39.9</v>
       </c>
       <c r="K56" t="n">
-        <v>70</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="N56" t="n">
-        <v>31.9</v>
+        <v>31.2</v>
       </c>
       <c r="O56" t="n">
-        <v>35.8</v>
+        <v>33.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>19.7</v>
+        <v>21.6</v>
       </c>
       <c r="R56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V56" t="n">
-        <v>12</v>
-      </c>
-      <c r="W56" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="X56" t="n">
-        <v>18.9</v>
+        <v>21.6</v>
       </c>
       <c r="Y56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z56" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AA56" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>2.9</v>
+        <v>17.9</v>
       </c>
       <c r="AF56" t="n">
-        <v>238.69</v>
+        <v>235.13</v>
       </c>
       <c r="AG56" t="n">
-        <v>-2.8</v>
+        <v>1.66</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5881,10 +5929,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>134.59</v>
+        <v>135.66</v>
       </c>
       <c r="AL56" t="n">
-        <v>6.22</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5893,81 +5941,81 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>89.05</v>
+        <v>88.27</v>
       </c>
       <c r="AS56" t="n">
-        <v>17.06</v>
+        <v>17.6</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B57" t="n">
-        <v>148.1</v>
+        <v>144.9</v>
       </c>
       <c r="C57" t="n">
-        <v>51.9</v>
+        <v>53</v>
       </c>
       <c r="D57" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
       <c r="E57" t="n">
-        <v>31.5</v>
+        <v>26</v>
       </c>
       <c r="F57" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="H57" t="n">
-        <v>21.8</v>
+        <v>24</v>
       </c>
       <c r="I57" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J57" t="n">
-        <v>39.6</v>
+        <v>40.3</v>
       </c>
       <c r="K57" t="n">
-        <v>71</v>
+        <v>73.7</v>
       </c>
       <c r="M57" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="N57" t="n">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="O57" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="R57" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="Y57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA57" t="n">
-        <v>15.5</v>
+        <v>16.3</v>
       </c>
       <c r="AF57" t="n">
-        <v>233.48</v>
+        <v>234.87</v>
       </c>
       <c r="AG57" t="n">
-        <v>-4.86</v>
+        <v>-0.26</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5976,10 +6024,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>136.6</v>
+        <v>136.33</v>
       </c>
       <c r="AL57" t="n">
-        <v>2.01</v>
+        <v>0.67</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -5988,81 +6036,42 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>86.25</v>
+        <v>87.09</v>
       </c>
       <c r="AS57" t="n">
-        <v>17.13</v>
+        <v>17.31</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B58" t="n">
-        <v>143.4</v>
-      </c>
-      <c r="C58" t="n">
-        <v>50.9</v>
+        <v>132.2</v>
       </c>
       <c r="D58" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="E58" t="n">
-        <v>26.2</v>
+        <v>35.6</v>
       </c>
       <c r="F58" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H58" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="I58" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J58" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K58" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2</v>
-      </c>
-      <c r="N58" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="O58" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>21.6</v>
+        <v>4</v>
       </c>
       <c r="Y58" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z58" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA58" t="n">
-        <v>17.9</v>
+        <v>13</v>
       </c>
       <c r="AF58" t="n">
-        <v>235.13</v>
+        <v>234.78</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.66</v>
+        <v>-0.09</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6070,94 +6079,43 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
-      <c r="AK58" t="n">
-        <v>135.66</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
-      <c r="AP58" t="n">
-        <v>88.27</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>17.6</v>
-      </c>
       <c r="BL58" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="B59" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C59" t="n">
-        <v>53</v>
+        <v>137.1</v>
       </c>
       <c r="D59" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="E59" t="n">
-        <v>26</v>
+        <v>35.1</v>
       </c>
       <c r="F59" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H59" t="n">
-        <v>24</v>
-      </c>
-      <c r="I59" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J59" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K59" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N59" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O59" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>21</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>21</v>
+        <v>3.3</v>
       </c>
       <c r="Y59" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z59" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA59" t="n">
-        <v>16.3</v>
+        <v>10.5</v>
       </c>
       <c r="AF59" t="n">
-        <v>234.87</v>
+        <v>229.75</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.26</v>
+        <v>-5.03</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6165,55 +6123,82 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
-      <c r="AK59" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
-      <c r="AP59" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL59" s="1" t="n">
-        <v>46268</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46269</v>
+        <v>46271</v>
       </c>
       <c r="B60" t="n">
-        <v>132.2</v>
+        <v>166.2</v>
+      </c>
+      <c r="C60" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>35.6</v>
+        <v>32.7</v>
+      </c>
+      <c r="E60" t="n">
+        <v>28.1</v>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>3.3</v>
+      </c>
+      <c r="H60" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9</v>
+      </c>
+      <c r="J60" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N60" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O60" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R60" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>23.7</v>
       </c>
       <c r="Y60" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z60" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AA60" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF60" t="n">
-        <v>234.78</v>
+        <v>222.86</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.09</v>
+        <v>-6.9</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6221,43 +6206,55 @@
       <c r="AI60" t="n">
         <v>235</v>
       </c>
+      <c r="AK60" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM60" t="n">
         <v>110</v>
       </c>
       <c r="AN60" t="n">
         <v>142</v>
       </c>
+      <c r="AP60" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL60" s="1" t="n">
-        <v>46269</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B61" t="n">
-        <v>137.1</v>
+        <v>152.4</v>
       </c>
       <c r="D61" t="n">
-        <v>35.1</v>
+        <v>35.7</v>
       </c>
       <c r="F61" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Y61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z61" t="n">
         <v>14</v>
       </c>
       <c r="AA61" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="AF61" t="n">
-        <v>229.75</v>
+        <v>218.37</v>
       </c>
       <c r="AG61" t="n">
-        <v>-5.03</v>
+        <v>-4.49</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6272,36 +6269,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="B62" t="n">
-        <v>140.4</v>
+        <v>135.8</v>
       </c>
       <c r="D62" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="F62" t="n">
         <v>3.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z62" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AA62" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>222.86</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>-6.9</v>
+        <v>13.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6316,7 +6307,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,61 +628,61 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B2" t="n">
-        <v>157.5</v>
+        <v>148.5</v>
       </c>
       <c r="C2" t="n">
-        <v>76.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D2" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="E2" t="n">
-        <v>36.9</v>
+        <v>34.3</v>
       </c>
       <c r="F2" t="n">
         <v>7.4</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="O2" t="n">
-        <v>38</v>
+        <v>39.8</v>
       </c>
       <c r="V2" t="n">
-        <v>6.7</v>
+        <v>11.2</v>
       </c>
       <c r="W2" t="n">
-        <v>20.8</v>
+        <v>21.7</v>
       </c>
       <c r="X2" t="n">
-        <v>13.8</v>
+        <v>16.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2.3</v>
+        <v>-1.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.1</v>
+        <v>1.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>226.95</v>
+        <v>223.11</v>
       </c>
       <c r="AG2" t="n">
-        <v>-2.97</v>
+        <v>-3.83</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -691,10 +691,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>128.4</v>
+        <v>124.76</v>
       </c>
       <c r="AL2" t="n">
-        <v>-4.61</v>
+        <v>-3.64</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -703,66 +703,60 @@
         <v>142</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B3" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="C3" t="n">
-        <v>70.5</v>
+        <v>72.8</v>
       </c>
       <c r="D3" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="E3" t="n">
-        <v>34.3</v>
+        <v>31.4</v>
       </c>
       <c r="F3" t="n">
         <v>7.4</v>
       </c>
       <c r="K3" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>39.8</v>
+        <v>40.2</v>
       </c>
       <c r="V3" t="n">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="W3" t="n">
-        <v>21.7</v>
+        <v>16.8</v>
       </c>
       <c r="X3" t="n">
-        <v>16.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y3" t="n">
         <v>7</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.9</v>
+        <v>0.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>223.11</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-3.83</v>
+        <v>4.8</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -771,10 +765,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>124.76</v>
+        <v>127.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3.64</v>
+        <v>2.44</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -783,60 +777,93 @@
         <v>142</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B4" t="n">
-        <v>147.5</v>
+        <v>183.5</v>
       </c>
       <c r="C4" t="n">
-        <v>72.8</v>
+        <v>84.5</v>
       </c>
       <c r="D4" t="n">
-        <v>26.7</v>
+        <v>31.5</v>
       </c>
       <c r="E4" t="n">
-        <v>31.4</v>
+        <v>34.6</v>
       </c>
       <c r="F4" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>41.5</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>76.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>37.7</v>
       </c>
       <c r="O4" t="n">
-        <v>40.2</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>23</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S4" t="n">
+        <v>18</v>
+      </c>
+      <c r="T4" t="n">
+        <v>23</v>
       </c>
       <c r="V4" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>16.8</v>
+        <v>20</v>
       </c>
       <c r="X4" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>220.36</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-3.75</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -845,10 +872,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>127.2</v>
+        <v>127.13</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -856,94 +883,100 @@
       <c r="AN4" t="n">
         <v>142</v>
       </c>
+      <c r="AP4" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL4" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B5" t="n">
-        <v>183.5</v>
+        <v>180.5</v>
       </c>
       <c r="C5" t="n">
-        <v>84.5</v>
+        <v>79.2</v>
       </c>
       <c r="D5" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="E5" t="n">
         <v>34.6</v>
       </c>
       <c r="F5" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="H5" t="n">
         <v>23.9</v>
       </c>
       <c r="I5" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="J5" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="K5" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
         <v>37.7</v>
       </c>
       <c r="O5" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="T5" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V5" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W5" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="X5" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>220.36</v>
+        <v>219.64</v>
       </c>
       <c r="AG5" t="n">
-        <v>-3.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -952,10 +985,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>127.13</v>
+        <v>126.03</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -964,99 +997,99 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>76.90000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>14.17</v>
+        <v>14.55</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B6" t="n">
-        <v>180.5</v>
+        <v>168.1</v>
       </c>
       <c r="C6" t="n">
-        <v>79.2</v>
+        <v>69.7</v>
       </c>
       <c r="D6" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E6" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F6" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I6" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="J6" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="K6" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O6" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S6" t="n">
         <v>17.6</v>
       </c>
       <c r="T6" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="V6" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W6" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="X6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA6" t="n">
         <v>14.9</v>
       </c>
-      <c r="Y6" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>11.9</v>
-      </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>219.64</v>
+        <v>224.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.72</v>
+        <v>5.29</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1065,10 +1098,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>126.03</v>
+        <v>129.28</v>
       </c>
       <c r="AL6" t="n">
-        <v>-1.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1077,99 +1110,99 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>82.95</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>14.55</v>
+        <v>15.25</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B7" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C7" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D7" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E7" t="n">
         <v>30.4</v>
       </c>
-      <c r="E7" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H7" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I7" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J7" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K7" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O7" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S7" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T7" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="V7" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="W7" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X7" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y7" t="n">
         <v>17</v>
       </c>
-      <c r="Y7" t="n">
-        <v>11</v>
-      </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>14.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1178,10 +1211,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1190,99 +1223,66 @@
         <v>142</v>
       </c>
       <c r="AP7" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B8" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C8" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D8" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K8" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N8" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>15</v>
-      </c>
-      <c r="T8" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
       </c>
       <c r="V8" t="n">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="W8" t="n">
-        <v>26</v>
+        <v>36.1</v>
       </c>
       <c r="X8" t="n">
-        <v>18.1</v>
+        <v>26.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC8" t="n">
         <v>6.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1291,10 +1291,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1302,67 +1302,61 @@
       <c r="AN8" t="n">
         <v>142</v>
       </c>
-      <c r="AP8" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL8" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B9" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D9" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F9" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O9" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
       <c r="W9" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="X9" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1371,10 +1365,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1383,60 +1377,93 @@
         <v>142</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B10" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>67</v>
       </c>
       <c r="D10" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>31.5</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>41.1</v>
       </c>
       <c r="K10" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>35</v>
       </c>
       <c r="O10" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>20.5</v>
       </c>
       <c r="V10" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W10" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X10" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1445,10 +1472,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL10" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1456,94 +1483,100 @@
       <c r="AN10" t="n">
         <v>142</v>
       </c>
+      <c r="AP10" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL10" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B11" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C11" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E11" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H11" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I11" t="n">
         <v>11.4</v>
       </c>
       <c r="J11" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K11" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O11" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T11" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V11" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W11" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X11" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
         <v>9</v>
       </c>
       <c r="Z11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1552,10 +1585,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL11" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1564,99 +1597,99 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS11" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B12" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C12" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D12" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F12" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H12" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I12" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA12" t="n">
         <v>11.4</v>
       </c>
-      <c r="J12" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>76</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>14</v>
-      </c>
-      <c r="T12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB12" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF12" t="n">
         <v>220.92</v>
       </c>
       <c r="AG12" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1665,10 +1698,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1677,99 +1710,99 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS12" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B13" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C13" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E13" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F13" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H13" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I13" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J13" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K13" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O13" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD13" t="n">
         <v>0.5</v>
       </c>
-      <c r="S13" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W13" t="n">
-        <v>13</v>
-      </c>
-      <c r="X13" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF13" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1778,10 +1811,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1790,99 +1823,99 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B14" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C14" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D14" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E14" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F14" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H14" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I14" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J14" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K14" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N14" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O14" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T14" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W14" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X14" t="n">
         <v>12.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z14" t="n">
         <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF14" t="n">
         <v>216.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1891,10 +1924,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL14" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1903,99 +1936,66 @@
         <v>142</v>
       </c>
       <c r="AP14" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS14" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B15" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D15" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E15" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F15" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K15" t="n">
-        <v>75</v>
-      </c>
-      <c r="M15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N15" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V15" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X15" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2004,10 +2004,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2015,67 +2015,61 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
-      <c r="AP15" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL15" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B16" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D16" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
         <v>6.8</v>
       </c>
       <c r="K16" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O16" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
         <v>13.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2084,10 +2078,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2096,60 +2090,93 @@
         <v>142</v>
       </c>
       <c r="BL16" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B17" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>60</v>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E17" t="n">
+        <v>25.9</v>
       </c>
       <c r="F17" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>24</v>
+      </c>
+      <c r="I17" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>38.8</v>
       </c>
       <c r="K17" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>36.7</v>
       </c>
       <c r="O17" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>21.7</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W17" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X17" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG17" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2158,10 +2185,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2169,94 +2196,67 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
+      <c r="AP17" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL17" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B18" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
-      </c>
-      <c r="E18" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H18" t="n">
-        <v>24</v>
-      </c>
-      <c r="I18" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K18" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O18" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V18" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X18" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB18" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF18" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2265,10 +2265,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2276,67 +2276,94 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
-      <c r="AP18" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL18" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B19" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>63.7</v>
       </c>
       <c r="D19" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>36.4</v>
       </c>
       <c r="F19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>39.9</v>
       </c>
       <c r="K19" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>35.9</v>
       </c>
       <c r="O19" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>20.3</v>
       </c>
       <c r="V19" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W19" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X19" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG19" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2345,10 +2372,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2356,94 +2383,100 @@
       <c r="AN19" t="n">
         <v>142</v>
       </c>
+      <c r="AP19" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL19" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B20" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C20" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E20" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F20" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H20" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I20" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J20" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K20" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N20" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O20" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T20" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V20" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W20" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X20" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA20" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2452,10 +2485,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL20" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2464,99 +2497,99 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B21" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C21" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D21" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E21" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F21" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H21" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I21" t="n">
         <v>11.3</v>
       </c>
       <c r="J21" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K21" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N21" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O21" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V21" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W21" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X21" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA21" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2565,10 +2598,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL21" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2577,99 +2610,66 @@
         <v>142</v>
       </c>
       <c r="AP21" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B22" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C22" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D22" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I22" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K22" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N22" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O22" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>9</v>
-      </c>
-      <c r="T22" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V22" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W22" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X22" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB22" t="n">
         <v>-0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2678,10 +2678,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2689,67 +2689,61 @@
       <c r="AN22" t="n">
         <v>142</v>
       </c>
-      <c r="AP22" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL22" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B23" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F23" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O23" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V23" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X23" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y23" t="n">
         <v>14</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2758,10 +2752,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL23" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2770,60 +2764,93 @@
         <v>142</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B24" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>56.3</v>
       </c>
       <c r="D24" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>21.2</v>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>40.4</v>
       </c>
       <c r="K24" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>29</v>
       </c>
       <c r="O24" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>21.6</v>
       </c>
       <c r="V24" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W24" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X24" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z24" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG24" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2832,10 +2859,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL24" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2843,52 +2870,58 @@
       <c r="AN24" t="n">
         <v>142</v>
       </c>
+      <c r="AP24" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL24" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B25" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C25" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D25" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F25" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H25" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I25" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J25" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K25" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O25" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R25" t="n">
         <v>1.3</v>
@@ -2897,40 +2930,40 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V25" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W25" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X25" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA25" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG25" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2939,10 +2972,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2951,99 +2984,99 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS25" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B26" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C26" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D26" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E26" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F26" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H26" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I26" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J26" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K26" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O26" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V26" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W26" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X26" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG26" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3052,10 +3085,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL26" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3064,99 +3097,99 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS26" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B27" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C27" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D27" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F27" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H27" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I27" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J27" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K27" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N27" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O27" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q27" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T27" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V27" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W27" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X27" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA27" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF27" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG27" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3165,10 +3198,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL27" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3177,99 +3210,99 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B28" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C28" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E28" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H28" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I28" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J28" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K28" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M28" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N28" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O28" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V28" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W28" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X28" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA28" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF28" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG28" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3278,10 +3311,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3290,99 +3323,60 @@
         <v>142</v>
       </c>
       <c r="AP28" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B29" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C29" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D29" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E29" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H29" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J29" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K29" t="n">
-        <v>77</v>
-      </c>
-      <c r="M29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N29" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>21</v>
-      </c>
-      <c r="R29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S29" t="n">
-        <v>6</v>
-      </c>
-      <c r="T29" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V29" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X29" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y29" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA29" t="n">
         <v>9</v>
       </c>
-      <c r="Z29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB29" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3391,10 +3385,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL29" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3402,61 +3396,61 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
-      <c r="AP29" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL29" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B30" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D30" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F30" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>35.5</v>
       </c>
       <c r="V30" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W30" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X30" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z30" t="n">
         <v>13</v>
       </c>
       <c r="AA30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB30" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF30" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3465,10 +3459,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3477,60 +3471,60 @@
         <v>142</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B31" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D31" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K31" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O31" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V31" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W31" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X31" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB31" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG31" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3539,10 +3533,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3551,60 +3545,93 @@
         <v>142</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B32" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>86.8</v>
       </c>
       <c r="D32" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>33</v>
       </c>
       <c r="F32" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>41.1</v>
       </c>
       <c r="K32" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N32" t="n">
+        <v>33.5</v>
       </c>
       <c r="O32" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="n">
+        <v>22.4</v>
       </c>
       <c r="V32" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W32" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X32" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z32" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA32" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3613,10 +3640,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL32" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3624,94 +3651,100 @@
       <c r="AN32" t="n">
         <v>142</v>
       </c>
+      <c r="AP32" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL32" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B33" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C33" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D33" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E33" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F33" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H33" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I33" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J33" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K33" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M33" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O33" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R33" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T33" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V33" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W33" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X33" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z33" t="n">
         <v>12</v>
       </c>
       <c r="AA33" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB33" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG33" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3720,10 +3753,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL33" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3732,99 +3765,99 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS33" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B34" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C34" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D34" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E34" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F34" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I34" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J34" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K34" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O34" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R34" t="n">
         <v>1.8</v>
       </c>
       <c r="S34" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T34" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V34" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W34" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X34" t="n">
         <v>10.9</v>
       </c>
       <c r="Y34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB34" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD34" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF34" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG34" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3833,10 +3866,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL34" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3845,99 +3878,66 @@
         <v>142</v>
       </c>
       <c r="AP34" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS34" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B35" t="n">
-        <v>183</v>
-      </c>
-      <c r="C35" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D35" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E35" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
-      </c>
-      <c r="H35" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I35" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K35" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4</v>
-      </c>
-      <c r="N35" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O35" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S35" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T35" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V35" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W35" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X35" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y35" t="n">
         <v>8</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA35" t="n">
         <v>10</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3946,10 +3946,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL35" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3957,67 +3957,61 @@
       <c r="AN35" t="n">
         <v>142</v>
       </c>
-      <c r="AP35" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL35" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B36" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D36" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F36" t="n">
         <v>6.5</v>
       </c>
       <c r="K36" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O36" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V36" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W36" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X36" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA36" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4026,10 +4020,10 @@
         <v>235</v>
       </c>
       <c r="AK36" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL36" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM36" t="n">
         <v>110</v>
@@ -4038,60 +4032,60 @@
         <v>142</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B37" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D37" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F37" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K37" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O37" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V37" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W37" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X37" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA37" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF37" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4099,12 +4093,6 @@
       <c r="AI37" t="n">
         <v>235</v>
       </c>
-      <c r="AK37" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM37" t="n">
         <v>110</v>
       </c>
@@ -4112,60 +4100,54 @@
         <v>142</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B38" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D38" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F38" t="n">
         <v>5.5</v>
       </c>
       <c r="K38" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O38" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V38" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W38" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X38" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA38" t="n">
         <v>15</v>
       </c>
-      <c r="AA38" t="n">
-        <v>14</v>
-      </c>
       <c r="AB38" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4180,54 +4162,93 @@
         <v>142</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B39" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C39" t="n">
+        <v>71.8</v>
       </c>
       <c r="D39" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E39" t="n">
+        <v>24.7</v>
       </c>
       <c r="F39" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J39" t="n">
+        <v>41.1</v>
       </c>
       <c r="K39" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>33.5</v>
       </c>
       <c r="O39" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>23.2</v>
       </c>
       <c r="V39" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W39" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X39" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y39" t="n">
         <v>12</v>
       </c>
       <c r="Z39" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA39" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4235,100 +4256,112 @@
       <c r="AI39" t="n">
         <v>235</v>
       </c>
+      <c r="AK39" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM39" t="n">
         <v>110</v>
       </c>
       <c r="AN39" t="n">
         <v>142</v>
       </c>
+      <c r="AP39" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL39" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B40" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C40" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D40" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E40" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H40" t="n">
         <v>24.1</v>
       </c>
       <c r="I40" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J40" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K40" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N40" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O40" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R40" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T40" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V40" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W40" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X40" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z40" t="n">
         <v>13</v>
       </c>
-      <c r="X40" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>14</v>
-      </c>
       <c r="AA40" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC40" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4337,10 +4370,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL40" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4349,99 +4382,99 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS40" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B41" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C41" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D41" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E41" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F41" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H41" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I41" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K41" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N41" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O41" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R41" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S41" t="n">
         <v>7</v>
       </c>
       <c r="T41" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V41" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W41" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X41" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z41" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA41" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG41" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4450,10 +4483,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4462,99 +4495,99 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS41" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B42" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C42" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D42" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E42" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F42" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H42" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I42" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J42" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K42" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M42" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N42" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O42" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R42" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T42" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V42" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W42" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X42" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z42" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA42" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4563,10 +4596,10 @@
         <v>235</v>
       </c>
       <c r="AK42" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM42" t="n">
         <v>110</v>
@@ -4575,99 +4608,66 @@
         <v>142</v>
       </c>
       <c r="AP42" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS42" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B43" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C43" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D43" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E43" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F43" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H43" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J43" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K43" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M43" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T43" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V43" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W43" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X43" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z43" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA43" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC43" t="n">
         <v>8.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4675,79 +4675,67 @@
       <c r="AI43" t="n">
         <v>235</v>
       </c>
-      <c r="AK43" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM43" t="n">
         <v>110</v>
       </c>
       <c r="AN43" t="n">
         <v>142</v>
       </c>
-      <c r="AP43" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL43" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B44" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D44" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F44" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K44" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O44" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V44" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W44" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X44" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z44" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA44" t="n">
         <v>9</v>
       </c>
       <c r="AB44" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF44" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG44" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4762,60 +4750,93 @@
         <v>142</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B45" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>73.7</v>
       </c>
       <c r="D45" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E45" t="n">
+        <v>28.2</v>
       </c>
       <c r="F45" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H45" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J45" t="n">
+        <v>40.1</v>
       </c>
       <c r="K45" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M45" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N45" t="n">
+        <v>32.9</v>
       </c>
       <c r="O45" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S45" t="n">
+        <v>6</v>
+      </c>
+      <c r="T45" t="n">
+        <v>23.5</v>
       </c>
       <c r="V45" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W45" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X45" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y45" t="n">
         <v>4</v>
       </c>
       <c r="Z45" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA45" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF45" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4823,100 +4844,112 @@
       <c r="AI45" t="n">
         <v>235</v>
       </c>
+      <c r="AK45" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM45" t="n">
         <v>110</v>
       </c>
       <c r="AN45" t="n">
         <v>142</v>
       </c>
+      <c r="AP45" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL45" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B46" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C46" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E46" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F46" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H46" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I46" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J46" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K46" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M46" t="n">
         <v>6.8</v>
       </c>
       <c r="N46" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O46" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q46" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R46" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T46" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V46" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W46" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X46" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z46" t="n">
         <v>13</v>
       </c>
       <c r="AA46" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC46" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB46" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD46" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF46" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG46" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4925,10 +4958,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL46" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4937,99 +4970,99 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS46" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B47" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C47" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E47" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F47" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H47" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I47" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J47" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K47" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M47" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N47" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O47" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q47" t="n">
         <v>23.1</v>
       </c>
       <c r="R47" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S47" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T47" t="n">
         <v>23.1</v>
       </c>
       <c r="V47" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W47" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X47" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA47" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC47" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG47" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5038,10 +5071,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL47" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5050,99 +5083,99 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS47" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B48" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C48" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D48" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E48" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F48" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H48" t="n">
         <v>23.8</v>
       </c>
       <c r="I48" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J48" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K48" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M48" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N48" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O48" t="n">
         <v>40.1</v>
       </c>
-      <c r="K48" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M48" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N48" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O48" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q48" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R48" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S48" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T48" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X48" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC48" t="n">
         <v>9.6</v>
       </c>
-      <c r="W48" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD48" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF48" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5151,10 +5184,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL48" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5163,75 +5196,75 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS48" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B49" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C49" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D49" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E49" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F49" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H49" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I49" t="n">
         <v>7.2</v>
       </c>
       <c r="J49" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K49" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M49" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N49" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O49" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q49" t="n">
         <v>23.2</v>
       </c>
       <c r="R49" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
         <v>23.2</v>
       </c>
       <c r="V49" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W49" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X49" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y49" t="n">
         <v>10</v>
@@ -5240,22 +5273,22 @@
         <v>18</v>
       </c>
       <c r="AA49" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5264,10 +5297,10 @@
         <v>235</v>
       </c>
       <c r="AK49" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL49" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM49" t="n">
         <v>110</v>
@@ -5276,99 +5309,54 @@
         <v>142</v>
       </c>
       <c r="AP49" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS49" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B50" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C50" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D50" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E50" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F50" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H50" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W50" t="n">
         <v>23.4</v>
       </c>
-      <c r="I50" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J50" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K50" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M50" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N50" t="n">
-        <v>33</v>
-      </c>
-      <c r="O50" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3</v>
-      </c>
-      <c r="T50" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V50" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W50" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X50" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA50" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5376,67 +5364,61 @@
       <c r="AI50" t="n">
         <v>235</v>
       </c>
-      <c r="AK50" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM50" t="n">
         <v>110</v>
       </c>
       <c r="AN50" t="n">
         <v>142</v>
       </c>
-      <c r="AP50" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL50" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B51" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D51" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F51" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V51" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W51" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X51" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z51" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA51" t="n">
         <v>13</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD51" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5451,54 +5433,93 @@
         <v>142</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B52" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C52" t="n">
+        <v>50.6</v>
       </c>
       <c r="D52" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>19.4</v>
       </c>
       <c r="F52" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H52" t="n">
+        <v>24</v>
+      </c>
+      <c r="I52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K52" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M52" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N52" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O52" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>21.4</v>
       </c>
       <c r="V52" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W52" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X52" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y52" t="n">
         <v>8</v>
       </c>
       <c r="Z52" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC52" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF52" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG52" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5506,100 +5527,112 @@
       <c r="AI52" t="n">
         <v>235</v>
       </c>
+      <c r="AK52" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM52" t="n">
         <v>110</v>
       </c>
       <c r="AN52" t="n">
         <v>142</v>
       </c>
+      <c r="AP52" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL52" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B53" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C53" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D53" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E53" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F53" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H53" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I53" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J53" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K53" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M53" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N53" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O53" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R53" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V53" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W53" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X53" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA53" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD53" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF53" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5608,10 +5641,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL53" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5620,99 +5653,99 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS53" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B54" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C54" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D54" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E54" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F54" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H54" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I54" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J54" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K54" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M54" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N54" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O54" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R54" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V54" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W54" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X54" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z54" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA54" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC54" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG54" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5721,10 +5754,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL54" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5733,99 +5766,99 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS54" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B55" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C55" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D55" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E55" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F55" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H55" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I55" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K55" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O55" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R55" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V55" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W55" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X55" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z55" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA55" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB55" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC55" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF55" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG55" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5834,10 +5867,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL55" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5846,57 +5879,57 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS55" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B56" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C56" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D56" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E56" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F56" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H56" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I56" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J56" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K56" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N56" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O56" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5905,22 +5938,22 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="Y56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z56" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA56" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AF56" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5929,10 +5962,10 @@
         <v>235</v>
       </c>
       <c r="AK56" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL56" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM56" t="n">
         <v>110</v>
@@ -5941,81 +5974,42 @@
         <v>142</v>
       </c>
       <c r="AP56" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS56" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B57" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C57" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D57" t="n">
         <v>35.6</v>
       </c>
-      <c r="E57" t="n">
-        <v>26</v>
-      </c>
       <c r="F57" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H57" t="n">
-        <v>24</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J57" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K57" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N57" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O57" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>21</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y57" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z57" t="n">
         <v>19</v>
       </c>
       <c r="AA57" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AF57" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6023,55 +6017,43 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
-      <c r="AK57" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
       </c>
-      <c r="AP57" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL57" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B58" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D58" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Y58" t="n">
         <v>7</v>
       </c>
       <c r="Z58" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA58" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AF58" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6086,36 +6068,75 @@
         <v>142</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B59" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C59" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E59" t="n">
+        <v>28.1</v>
       </c>
       <c r="F59" t="n">
         <v>3.3</v>
       </c>
+      <c r="H59" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>9</v>
+      </c>
+      <c r="J59" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N59" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O59" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R59" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>23.7</v>
+      </c>
       <c r="Y59" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z59" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA59" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF59" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG59" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6123,82 +6144,94 @@
       <c r="AI59" t="n">
         <v>235</v>
       </c>
+      <c r="AK59" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM59" t="n">
         <v>110</v>
       </c>
       <c r="AN59" t="n">
         <v>142</v>
       </c>
+      <c r="AP59" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL59" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B60" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C60" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E60" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F60" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H60" t="n">
         <v>23.4</v>
       </c>
       <c r="I60" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K60" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M60" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N60" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O60" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R60" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z60" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA60" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AF60" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG60" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6207,10 +6240,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL60" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6219,42 +6252,36 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS60" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B61" t="n">
-        <v>152.4</v>
+        <v>135.8</v>
       </c>
       <c r="D61" t="n">
-        <v>35.7</v>
+        <v>34.6</v>
       </c>
       <c r="F61" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z61" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA61" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>218.37</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>-4.49</v>
+        <v>13.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6269,30 +6296,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B62" t="n">
         <v>135.8</v>
       </c>
       <c r="D62" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="F62" t="n">
         <v>3.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA62" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6307,7 +6334,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,61 +628,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B2" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="C2" t="n">
-        <v>70.5</v>
+        <v>72.8</v>
       </c>
       <c r="D2" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="n">
-        <v>34.3</v>
+        <v>31.4</v>
       </c>
       <c r="F2" t="n">
         <v>7.4</v>
       </c>
       <c r="K2" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>39.8</v>
+        <v>40.2</v>
       </c>
       <c r="V2" t="n">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="W2" t="n">
-        <v>21.7</v>
+        <v>16.8</v>
       </c>
       <c r="X2" t="n">
-        <v>16.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y2" t="n">
         <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1.9</v>
+        <v>0.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>223.11</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-3.83</v>
+        <v>4.8</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -691,10 +685,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>124.76</v>
+        <v>127.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>-3.64</v>
+        <v>2.44</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -703,60 +697,93 @@
         <v>142</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B3" t="n">
-        <v>147.5</v>
+        <v>183.5</v>
       </c>
       <c r="C3" t="n">
-        <v>72.8</v>
+        <v>84.5</v>
       </c>
       <c r="D3" t="n">
-        <v>26.7</v>
+        <v>31.5</v>
       </c>
       <c r="E3" t="n">
-        <v>31.4</v>
+        <v>34.6</v>
       </c>
       <c r="F3" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>41.5</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>76.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>40.2</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>23</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S3" t="n">
+        <v>18</v>
+      </c>
+      <c r="T3" t="n">
+        <v>23</v>
       </c>
       <c r="V3" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="W3" t="n">
-        <v>16.8</v>
+        <v>20</v>
       </c>
       <c r="X3" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>220.36</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-3.75</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -765,10 +792,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>127.2</v>
+        <v>127.13</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -776,94 +803,100 @@
       <c r="AN3" t="n">
         <v>142</v>
       </c>
+      <c r="AP3" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL3" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B4" t="n">
-        <v>183.5</v>
+        <v>180.5</v>
       </c>
       <c r="C4" t="n">
-        <v>84.5</v>
+        <v>79.2</v>
       </c>
       <c r="D4" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="E4" t="n">
         <v>34.6</v>
       </c>
       <c r="F4" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="H4" t="n">
         <v>23.9</v>
       </c>
       <c r="I4" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="J4" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="K4" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>37.7</v>
       </c>
       <c r="O4" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="T4" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V4" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W4" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="X4" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>220.36</v>
+        <v>219.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -872,10 +905,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>127.13</v>
+        <v>126.03</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -884,99 +917,99 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>76.90000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.17</v>
+        <v>14.55</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B5" t="n">
-        <v>180.5</v>
+        <v>168.1</v>
       </c>
       <c r="C5" t="n">
-        <v>79.2</v>
+        <v>69.7</v>
       </c>
       <c r="D5" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E5" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F5" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H5" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I5" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="J5" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="K5" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O5" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
         <v>17.6</v>
       </c>
       <c r="T5" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="V5" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W5" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA5" t="n">
         <v>14.9</v>
       </c>
-      <c r="Y5" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>11.9</v>
-      </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>219.64</v>
+        <v>224.93</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.72</v>
+        <v>5.29</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -985,10 +1018,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>126.03</v>
+        <v>129.28</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -997,99 +1030,99 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>82.95</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>14.55</v>
+        <v>15.25</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B6" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C6" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D6" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E6" t="n">
         <v>30.4</v>
       </c>
-      <c r="E6" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H6" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I6" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J6" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K6" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O6" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S6" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T6" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="V6" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="W6" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y6" t="n">
         <v>17</v>
       </c>
-      <c r="Y6" t="n">
-        <v>11</v>
-      </c>
       <c r="Z6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
-        <v>14.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG6" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1098,10 +1131,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1110,99 +1143,66 @@
         <v>142</v>
       </c>
       <c r="AP6" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B7" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D7" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K7" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
       </c>
       <c r="V7" t="n">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="W7" t="n">
-        <v>26</v>
+        <v>36.1</v>
       </c>
       <c r="X7" t="n">
-        <v>18.1</v>
+        <v>26.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC7" t="n">
         <v>6.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1211,10 +1211,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1222,67 +1222,61 @@
       <c r="AN7" t="n">
         <v>142</v>
       </c>
-      <c r="AP7" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL7" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B8" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D8" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F8" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O8" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V8" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
       <c r="W8" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="X8" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA8" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1291,10 +1285,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1303,60 +1297,93 @@
         <v>142</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B9" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>67</v>
       </c>
       <c r="D9" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>31.5</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>41.1</v>
       </c>
       <c r="K9" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>35</v>
       </c>
       <c r="O9" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>20.5</v>
       </c>
       <c r="V9" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W9" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X9" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG9" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1365,10 +1392,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1376,94 +1403,100 @@
       <c r="AN9" t="n">
         <v>142</v>
       </c>
+      <c r="AP9" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL9" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B10" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C10" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E10" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H10" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I10" t="n">
         <v>11.4</v>
       </c>
       <c r="J10" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K10" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O10" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T10" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V10" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W10" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X10" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
         <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1472,10 +1505,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL10" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1484,99 +1517,99 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS10" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B11" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C11" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D11" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F11" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA11" t="n">
         <v>11.4</v>
       </c>
-      <c r="J11" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>76</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N11" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>14</v>
-      </c>
-      <c r="T11" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB11" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF11" t="n">
         <v>220.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1585,10 +1618,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL11" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1597,99 +1630,99 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS11" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B12" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C12" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E12" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F12" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H12" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I12" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J12" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K12" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O12" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD12" t="n">
         <v>0.5</v>
       </c>
-      <c r="S12" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>13</v>
-      </c>
-      <c r="X12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF12" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1698,10 +1731,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1710,99 +1743,99 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B13" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C13" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D13" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E13" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F13" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H13" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I13" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J13" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K13" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O13" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T13" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V13" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W13" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X13" t="n">
         <v>12.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
         <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF13" t="n">
         <v>216.02</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1811,10 +1844,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL13" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1823,99 +1856,66 @@
         <v>142</v>
       </c>
       <c r="AP13" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS13" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B14" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C14" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D14" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E14" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F14" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K14" t="n">
-        <v>75</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N14" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V14" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X14" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1924,10 +1924,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1935,67 +1935,61 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
-      <c r="AP14" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL14" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B15" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D15" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F15" t="n">
         <v>6.8</v>
       </c>
       <c r="K15" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O15" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X15" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA15" t="n">
         <v>13.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2004,10 +1998,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2016,60 +2010,93 @@
         <v>142</v>
       </c>
       <c r="BL15" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B16" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25.9</v>
       </c>
       <c r="F16" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>24</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>38.8</v>
       </c>
       <c r="K16" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>36.7</v>
       </c>
       <c r="O16" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>21.7</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W16" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X16" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG16" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2078,10 +2105,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2089,94 +2116,67 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
+      <c r="AP16" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL16" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B17" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
-      </c>
-      <c r="E17" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>24</v>
-      </c>
-      <c r="I17" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K17" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O17" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V17" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X17" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB17" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2185,10 +2185,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2196,67 +2196,94 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
-      <c r="AP17" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL17" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B18" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>63.7</v>
       </c>
       <c r="D18" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>36.4</v>
       </c>
       <c r="F18" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>39.9</v>
       </c>
       <c r="K18" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>35.9</v>
       </c>
       <c r="O18" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>20.3</v>
       </c>
       <c r="V18" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W18" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X18" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG18" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2265,10 +2292,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2276,94 +2303,100 @@
       <c r="AN18" t="n">
         <v>142</v>
       </c>
+      <c r="AP18" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL18" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B19" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C19" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E19" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F19" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H19" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I19" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J19" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K19" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N19" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O19" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V19" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W19" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X19" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2372,10 +2405,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL19" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2384,99 +2417,99 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B20" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C20" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D20" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E20" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F20" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H20" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I20" t="n">
         <v>11.3</v>
       </c>
       <c r="J20" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K20" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N20" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O20" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W20" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X20" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG20" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2485,10 +2518,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL20" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2497,99 +2530,66 @@
         <v>142</v>
       </c>
       <c r="AP20" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B21" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C21" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D21" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H21" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I21" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K21" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N21" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O21" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>9</v>
-      </c>
-      <c r="T21" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V21" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W21" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X21" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB21" t="n">
         <v>-0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2598,10 +2598,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2609,67 +2609,61 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
-      <c r="AP21" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL21" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B22" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F22" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O22" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V22" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W22" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X22" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y22" t="n">
         <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA22" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2678,10 +2672,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL22" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2690,60 +2684,93 @@
         <v>142</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B23" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>56.3</v>
       </c>
       <c r="D23" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>21.2</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>40.4</v>
       </c>
       <c r="K23" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>29</v>
       </c>
       <c r="O23" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>21.6</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W23" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X23" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z23" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF23" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG23" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2752,10 +2779,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL23" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2763,52 +2790,58 @@
       <c r="AN23" t="n">
         <v>142</v>
       </c>
+      <c r="AP23" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL23" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B24" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C24" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D24" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E24" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F24" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H24" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I24" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J24" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K24" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O24" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R24" t="n">
         <v>1.3</v>
@@ -2817,40 +2850,40 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V24" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W24" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X24" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA24" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG24" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2859,10 +2892,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2871,99 +2904,99 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS24" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B25" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C25" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D25" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E25" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F25" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H25" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I25" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J25" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K25" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O25" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V25" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W25" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X25" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA25" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -2972,10 +3005,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL25" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -2984,99 +3017,99 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS25" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B26" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C26" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D26" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E26" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F26" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H26" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I26" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J26" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K26" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N26" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O26" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q26" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V26" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W26" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X26" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA26" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF26" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG26" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3085,10 +3118,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL26" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3097,99 +3130,99 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B27" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C27" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E27" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H27" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I27" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J27" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K27" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M27" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N27" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O27" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R27" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T27" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V27" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W27" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X27" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA27" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG27" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3198,10 +3231,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3210,99 +3243,60 @@
         <v>142</v>
       </c>
       <c r="AP27" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B28" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C28" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D28" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E28" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H28" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K28" t="n">
-        <v>77</v>
-      </c>
-      <c r="M28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N28" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>21</v>
-      </c>
-      <c r="R28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V28" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X28" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA28" t="n">
         <v>9</v>
       </c>
-      <c r="Z28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB28" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF28" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3311,10 +3305,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3322,61 +3316,61 @@
       <c r="AN28" t="n">
         <v>142</v>
       </c>
-      <c r="AP28" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL28" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B29" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D29" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F29" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>35.5</v>
       </c>
       <c r="V29" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W29" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X29" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z29" t="n">
         <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB29" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3385,10 +3379,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3397,60 +3391,60 @@
         <v>142</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B30" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D30" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K30" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O30" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V30" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W30" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X30" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB30" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF30" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG30" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3459,10 +3453,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3471,60 +3465,93 @@
         <v>142</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B31" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C31" t="n">
+        <v>86.8</v>
       </c>
       <c r="D31" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>33</v>
       </c>
       <c r="F31" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>41.1</v>
       </c>
       <c r="K31" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N31" t="n">
+        <v>33.5</v>
       </c>
       <c r="O31" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="n">
+        <v>22.4</v>
       </c>
       <c r="V31" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W31" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X31" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA31" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF31" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3533,10 +3560,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3544,94 +3571,100 @@
       <c r="AN31" t="n">
         <v>142</v>
       </c>
+      <c r="AP31" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL31" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B32" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C32" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D32" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E32" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F32" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H32" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I32" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J32" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K32" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M32" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O32" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R32" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T32" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V32" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W32" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X32" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z32" t="n">
         <v>12</v>
       </c>
       <c r="AA32" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB32" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG32" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3640,10 +3673,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL32" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3652,99 +3685,99 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS32" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B33" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C33" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D33" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E33" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F33" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I33" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J33" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K33" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O33" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R33" t="n">
         <v>1.8</v>
       </c>
       <c r="S33" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T33" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V33" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W33" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X33" t="n">
         <v>10.9</v>
       </c>
       <c r="Y33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB33" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD33" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF33" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG33" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3753,10 +3786,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL33" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3765,99 +3798,66 @@
         <v>142</v>
       </c>
       <c r="AP33" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS33" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B34" t="n">
-        <v>183</v>
-      </c>
-      <c r="C34" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D34" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E34" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
-      </c>
-      <c r="H34" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J34" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K34" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M34" t="n">
-        <v>4</v>
-      </c>
-      <c r="N34" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O34" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S34" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T34" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V34" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W34" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X34" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y34" t="n">
         <v>8</v>
       </c>
       <c r="Z34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA34" t="n">
         <v>10</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3866,10 +3866,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL34" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3877,67 +3877,61 @@
       <c r="AN34" t="n">
         <v>142</v>
       </c>
-      <c r="AP34" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL34" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B35" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F35" t="n">
         <v>6.5</v>
       </c>
       <c r="K35" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O35" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V35" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W35" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X35" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF35" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3946,10 +3940,10 @@
         <v>235</v>
       </c>
       <c r="AK35" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL35" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
@@ -3958,60 +3952,60 @@
         <v>142</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B36" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D36" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F36" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K36" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O36" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V36" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W36" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X36" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z36" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC36" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF36" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4019,12 +4013,6 @@
       <c r="AI36" t="n">
         <v>235</v>
       </c>
-      <c r="AK36" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM36" t="n">
         <v>110</v>
       </c>
@@ -4032,60 +4020,54 @@
         <v>142</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B37" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D37" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F37" t="n">
         <v>5.5</v>
       </c>
       <c r="K37" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O37" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V37" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W37" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X37" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z37" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA37" t="n">
         <v>15</v>
       </c>
-      <c r="AA37" t="n">
-        <v>14</v>
-      </c>
       <c r="AB37" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4100,54 +4082,93 @@
         <v>142</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B38" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C38" t="n">
+        <v>71.8</v>
       </c>
       <c r="D38" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>24.7</v>
       </c>
       <c r="F38" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J38" t="n">
+        <v>41.1</v>
       </c>
       <c r="K38" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>33.5</v>
       </c>
       <c r="O38" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>23.2</v>
       </c>
       <c r="V38" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W38" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X38" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y38" t="n">
         <v>12</v>
       </c>
       <c r="Z38" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA38" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4155,100 +4176,112 @@
       <c r="AI38" t="n">
         <v>235</v>
       </c>
+      <c r="AK38" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM38" t="n">
         <v>110</v>
       </c>
       <c r="AN38" t="n">
         <v>142</v>
       </c>
+      <c r="AP38" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL38" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B39" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C39" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D39" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E39" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H39" t="n">
         <v>24.1</v>
       </c>
       <c r="I39" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J39" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K39" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N39" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O39" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T39" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V39" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W39" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X39" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z39" t="n">
         <v>13</v>
       </c>
-      <c r="X39" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>14</v>
-      </c>
       <c r="AA39" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF39" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4257,10 +4290,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL39" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4269,99 +4302,99 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS39" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B40" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C40" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D40" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E40" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F40" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H40" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I40" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K40" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O40" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R40" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S40" t="n">
         <v>7</v>
       </c>
       <c r="T40" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V40" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W40" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X40" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA40" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF40" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG40" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4370,10 +4403,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4382,99 +4415,99 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS40" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B41" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C41" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D41" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E41" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F41" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H41" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I41" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J41" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K41" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M41" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N41" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O41" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R41" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T41" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V41" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W41" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X41" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z41" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF41" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4483,10 +4516,10 @@
         <v>235</v>
       </c>
       <c r="AK41" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
@@ -4495,99 +4528,66 @@
         <v>142</v>
       </c>
       <c r="AP41" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS41" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B42" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C42" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D42" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E42" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H42" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J42" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K42" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M42" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S42" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T42" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V42" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W42" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X42" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z42" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA42" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC42" t="n">
         <v>8.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4595,79 +4595,67 @@
       <c r="AI42" t="n">
         <v>235</v>
       </c>
-      <c r="AK42" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM42" t="n">
         <v>110</v>
       </c>
       <c r="AN42" t="n">
         <v>142</v>
       </c>
-      <c r="AP42" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL42" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B43" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D43" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F43" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K43" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O43" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V43" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W43" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X43" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z43" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA43" t="n">
         <v>9</v>
       </c>
       <c r="AB43" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF43" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG43" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4682,60 +4670,93 @@
         <v>142</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B44" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>73.7</v>
       </c>
       <c r="D44" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E44" t="n">
+        <v>28.2</v>
       </c>
       <c r="F44" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H44" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>40.1</v>
       </c>
       <c r="K44" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N44" t="n">
+        <v>32.9</v>
       </c>
       <c r="O44" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>6</v>
+      </c>
+      <c r="T44" t="n">
+        <v>23.5</v>
       </c>
       <c r="V44" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W44" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X44" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y44" t="n">
         <v>4</v>
       </c>
       <c r="Z44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA44" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4743,100 +4764,112 @@
       <c r="AI44" t="n">
         <v>235</v>
       </c>
+      <c r="AK44" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM44" t="n">
         <v>110</v>
       </c>
       <c r="AN44" t="n">
         <v>142</v>
       </c>
+      <c r="AP44" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL44" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B45" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C45" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E45" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F45" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H45" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I45" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J45" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K45" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M45" t="n">
         <v>6.8</v>
       </c>
       <c r="N45" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O45" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R45" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T45" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V45" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W45" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X45" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z45" t="n">
         <v>13</v>
       </c>
       <c r="AA45" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC45" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB45" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD45" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF45" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG45" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4845,10 +4878,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL45" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4857,99 +4890,99 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS45" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B46" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C46" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E46" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F46" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H46" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I46" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J46" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K46" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M46" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N46" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O46" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q46" t="n">
         <v>23.1</v>
       </c>
       <c r="R46" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S46" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T46" t="n">
         <v>23.1</v>
       </c>
       <c r="V46" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W46" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X46" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA46" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG46" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4958,10 +4991,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL46" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -4970,99 +5003,99 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS46" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B47" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C47" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D47" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E47" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F47" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H47" t="n">
         <v>23.8</v>
       </c>
       <c r="I47" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J47" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K47" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M47" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N47" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O47" t="n">
         <v>40.1</v>
       </c>
-      <c r="K47" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M47" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O47" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q47" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R47" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S47" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V47" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W47" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X47" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC47" t="n">
         <v>9.6</v>
       </c>
-      <c r="W47" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X47" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD47" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF47" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5071,10 +5104,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL47" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5083,75 +5116,75 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS47" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B48" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C48" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D48" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E48" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F48" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H48" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I48" t="n">
         <v>7.2</v>
       </c>
       <c r="J48" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K48" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M48" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N48" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O48" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q48" t="n">
         <v>23.2</v>
       </c>
       <c r="R48" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T48" t="n">
         <v>23.2</v>
       </c>
       <c r="V48" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W48" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X48" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y48" t="n">
         <v>10</v>
@@ -5160,22 +5193,22 @@
         <v>18</v>
       </c>
       <c r="AA48" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF48" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5184,10 +5217,10 @@
         <v>235</v>
       </c>
       <c r="AK48" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL48" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM48" t="n">
         <v>110</v>
@@ -5196,99 +5229,54 @@
         <v>142</v>
       </c>
       <c r="AP48" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS48" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B49" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C49" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D49" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E49" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H49" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W49" t="n">
         <v>23.4</v>
       </c>
-      <c r="I49" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J49" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K49" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M49" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N49" t="n">
-        <v>33</v>
-      </c>
-      <c r="O49" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3</v>
-      </c>
-      <c r="T49" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V49" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X49" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z49" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA49" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC49" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5296,67 +5284,61 @@
       <c r="AI49" t="n">
         <v>235</v>
       </c>
-      <c r="AK49" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM49" t="n">
         <v>110</v>
       </c>
       <c r="AN49" t="n">
         <v>142</v>
       </c>
-      <c r="AP49" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL49" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B50" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D50" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F50" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V50" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W50" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X50" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA50" t="n">
         <v>13</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD50" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5371,54 +5353,93 @@
         <v>142</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B51" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C51" t="n">
+        <v>50.6</v>
       </c>
       <c r="D51" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>19.4</v>
       </c>
       <c r="F51" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H51" t="n">
+        <v>24</v>
+      </c>
+      <c r="I51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K51" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N51" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>21.4</v>
       </c>
       <c r="V51" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W51" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X51" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y51" t="n">
         <v>8</v>
       </c>
       <c r="Z51" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA51" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF51" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5426,100 +5447,112 @@
       <c r="AI51" t="n">
         <v>235</v>
       </c>
+      <c r="AK51" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM51" t="n">
         <v>110</v>
       </c>
       <c r="AN51" t="n">
         <v>142</v>
       </c>
+      <c r="AP51" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL51" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B52" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C52" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D52" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E52" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F52" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H52" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I52" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J52" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K52" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M52" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N52" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O52" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R52" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V52" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W52" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X52" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y52" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z52" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA52" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC52" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD52" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5528,10 +5561,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL52" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5540,99 +5573,99 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS52" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B53" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C53" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D53" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E53" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F53" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H53" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I53" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J53" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K53" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M53" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N53" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O53" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R53" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V53" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W53" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X53" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y53" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z53" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA53" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB53" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC53" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF53" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG53" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5641,10 +5674,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL53" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5653,99 +5686,99 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS53" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B54" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C54" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D54" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E54" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F54" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H54" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I54" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K54" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N54" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O54" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R54" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V54" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W54" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X54" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z54" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA54" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB54" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC54" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF54" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG54" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5754,10 +5787,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL54" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5766,57 +5799,57 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS54" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B55" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C55" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D55" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E55" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F55" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H55" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I55" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J55" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K55" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N55" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O55" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -5825,40 +5858,40 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V55" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W55" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X55" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z55" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA55" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB55" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC55" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5867,10 +5900,10 @@
         <v>235</v>
       </c>
       <c r="AK55" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL55" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
@@ -5879,81 +5912,42 @@
         <v>142</v>
       </c>
       <c r="AP55" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS55" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B56" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C56" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D56" t="n">
         <v>35.6</v>
       </c>
-      <c r="E56" t="n">
-        <v>26</v>
-      </c>
       <c r="F56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H56" t="n">
-        <v>24</v>
-      </c>
-      <c r="I56" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J56" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K56" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N56" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O56" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>21</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y56" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z56" t="n">
         <v>19</v>
       </c>
       <c r="AA56" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AF56" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5961,55 +5955,43 @@
       <c r="AI56" t="n">
         <v>235</v>
       </c>
-      <c r="AK56" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
       <c r="AN56" t="n">
         <v>142</v>
       </c>
-      <c r="AP56" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL56" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B57" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D57" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Y57" t="n">
         <v>7</v>
       </c>
       <c r="Z57" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA57" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AF57" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6024,36 +6006,75 @@
         <v>142</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B58" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E58" t="n">
+        <v>28.1</v>
       </c>
       <c r="F58" t="n">
         <v>3.3</v>
       </c>
+      <c r="H58" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9</v>
+      </c>
+      <c r="J58" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N58" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O58" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>23.7</v>
+      </c>
       <c r="Y58" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z58" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA58" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF58" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG58" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6061,82 +6082,94 @@
       <c r="AI58" t="n">
         <v>235</v>
       </c>
+      <c r="AK58" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM58" t="n">
         <v>110</v>
       </c>
       <c r="AN58" t="n">
         <v>142</v>
       </c>
+      <c r="AP58" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL58" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B59" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C59" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E59" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F59" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H59" t="n">
         <v>23.4</v>
       </c>
       <c r="I59" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K59" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M59" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N59" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O59" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R59" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z59" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA59" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AF59" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG59" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6145,10 +6178,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL59" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6157,81 +6190,81 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS59" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B60" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C60" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D60" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E60" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F60" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H60" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I60" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J60" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K60" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N60" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O60" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R60" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T60" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="Y60" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z60" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA60" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AF60" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG60" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6240,10 +6273,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL60" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6252,36 +6285,36 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS60" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B61" t="n">
         <v>135.8</v>
       </c>
       <c r="D61" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="F61" t="n">
         <v>3.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z61" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA61" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6296,30 +6329,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B62" t="n">
-        <v>135.8</v>
+        <v>131.7</v>
       </c>
       <c r="D62" t="n">
-        <v>34.2</v>
+        <v>33.2</v>
       </c>
       <c r="F62" t="n">
         <v>3.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z62" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA62" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6334,7 +6367,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,55 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B2" t="n">
-        <v>147.5</v>
+        <v>183.5</v>
       </c>
       <c r="C2" t="n">
-        <v>72.8</v>
+        <v>84.5</v>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>31.5</v>
       </c>
       <c r="E2" t="n">
-        <v>31.4</v>
+        <v>34.6</v>
       </c>
       <c r="F2" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>41.5</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>76.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>37.7</v>
       </c>
       <c r="O2" t="n">
-        <v>40.2</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>23</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>18</v>
+      </c>
+      <c r="T2" t="n">
+        <v>23</v>
       </c>
       <c r="V2" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="W2" t="n">
-        <v>16.8</v>
+        <v>20</v>
       </c>
       <c r="X2" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>220.36</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-3.75</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -685,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>127.2</v>
+        <v>127.13</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -696,94 +729,100 @@
       <c r="AN2" t="n">
         <v>142</v>
       </c>
+      <c r="AP2" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>14.17</v>
+      </c>
       <c r="BL2" s="1" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B3" t="n">
-        <v>183.5</v>
+        <v>180.5</v>
       </c>
       <c r="C3" t="n">
-        <v>84.5</v>
+        <v>79.2</v>
       </c>
       <c r="D3" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="E3" t="n">
         <v>34.6</v>
       </c>
       <c r="F3" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="H3" t="n">
         <v>23.9</v>
       </c>
       <c r="I3" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="J3" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="K3" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
         <v>37.7</v>
       </c>
       <c r="O3" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="T3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V3" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="X3" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>220.36</v>
+        <v>219.64</v>
       </c>
       <c r="AG3" t="n">
-        <v>-3.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -792,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>127.13</v>
+        <v>126.03</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -804,99 +843,99 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>76.90000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.17</v>
+        <v>14.55</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B4" t="n">
-        <v>180.5</v>
+        <v>168.1</v>
       </c>
       <c r="C4" t="n">
-        <v>79.2</v>
+        <v>69.7</v>
       </c>
       <c r="D4" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E4" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F4" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H4" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I4" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="J4" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="K4" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O4" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
         <v>17.6</v>
       </c>
       <c r="T4" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="V4" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W4" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="X4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA4" t="n">
         <v>14.9</v>
       </c>
-      <c r="Y4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>11.9</v>
-      </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>219.64</v>
+        <v>224.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.72</v>
+        <v>5.29</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -905,10 +944,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>126.03</v>
+        <v>129.28</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -917,99 +956,99 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>82.95</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.55</v>
+        <v>15.25</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B5" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C5" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E5" t="n">
         <v>30.4</v>
       </c>
-      <c r="E5" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H5" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I5" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J5" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K5" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O5" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S5" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T5" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="V5" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="W5" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X5" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y5" t="n">
         <v>17</v>
       </c>
-      <c r="Y5" t="n">
-        <v>11</v>
-      </c>
       <c r="Z5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1018,10 +1057,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1030,99 +1069,66 @@
         <v>142</v>
       </c>
       <c r="AP5" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B6" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C6" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D6" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N6" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>15</v>
-      </c>
-      <c r="T6" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
       </c>
       <c r="V6" t="n">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="W6" t="n">
-        <v>26</v>
+        <v>36.1</v>
       </c>
       <c r="X6" t="n">
-        <v>18.1</v>
+        <v>26.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC6" t="n">
         <v>6.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1131,10 +1137,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1142,67 +1148,61 @@
       <c r="AN6" t="n">
         <v>142</v>
       </c>
-      <c r="AP6" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL6" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B7" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D7" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F7" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O7" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V7" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
       <c r="W7" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="X7" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1211,10 +1211,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1223,60 +1223,93 @@
         <v>142</v>
       </c>
       <c r="BL7" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B8" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>31.5</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>41.1</v>
       </c>
       <c r="K8" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>35</v>
       </c>
       <c r="O8" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>20.5</v>
       </c>
       <c r="V8" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W8" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X8" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG8" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1285,10 +1318,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL8" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1296,94 +1329,100 @@
       <c r="AN8" t="n">
         <v>142</v>
       </c>
+      <c r="AP8" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL8" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B9" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E9" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F9" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H9" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I9" t="n">
         <v>11.4</v>
       </c>
       <c r="J9" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K9" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O9" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T9" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V9" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W9" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X9" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y9" t="n">
         <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG9" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1392,10 +1431,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL9" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1404,99 +1443,99 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B10" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C10" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D10" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H10" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>13</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA10" t="n">
         <v>11.4</v>
       </c>
-      <c r="J10" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>76</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N10" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>14</v>
-      </c>
-      <c r="T10" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB10" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF10" t="n">
         <v>220.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1505,10 +1544,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL10" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1517,99 +1556,99 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS10" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B11" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C11" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E11" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F11" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H11" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I11" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J11" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K11" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O11" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD11" t="n">
         <v>0.5</v>
       </c>
-      <c r="S11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF11" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1618,10 +1657,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL11" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1630,99 +1669,99 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B12" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C12" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D12" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E12" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F12" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H12" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I12" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J12" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K12" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N12" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O12" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S12" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T12" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V12" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W12" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X12" t="n">
         <v>12.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="n">
         <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF12" t="n">
         <v>216.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1731,10 +1770,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL12" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1743,99 +1782,66 @@
         <v>142</v>
       </c>
       <c r="AP12" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS12" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL12" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B13" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D13" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E13" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F13" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K13" t="n">
-        <v>75</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N13" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V13" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X13" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1844,10 +1850,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1855,67 +1861,61 @@
       <c r="AN13" t="n">
         <v>142</v>
       </c>
-      <c r="AP13" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL13" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B14" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D14" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F14" t="n">
         <v>6.8</v>
       </c>
       <c r="K14" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O14" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
         <v>13.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1924,10 +1924,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1936,60 +1936,93 @@
         <v>142</v>
       </c>
       <c r="BL14" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B15" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E15" t="n">
+        <v>25.9</v>
       </c>
       <c r="F15" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>24</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>38.8</v>
       </c>
       <c r="K15" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>36.7</v>
       </c>
       <c r="O15" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>21.7</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W15" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X15" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -1998,10 +2031,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2009,94 +2042,67 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
+      <c r="AP15" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL15" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B16" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
-      </c>
-      <c r="E16" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>24</v>
-      </c>
-      <c r="I16" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K16" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O16" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V16" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X16" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB16" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF16" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2105,10 +2111,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2116,67 +2122,94 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
-      <c r="AP16" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL16" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B17" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>63.7</v>
       </c>
       <c r="D17" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>36.4</v>
       </c>
       <c r="F17" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>39.9</v>
       </c>
       <c r="K17" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>35.9</v>
       </c>
       <c r="O17" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>20.3</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W17" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X17" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG17" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2185,10 +2218,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2196,94 +2229,100 @@
       <c r="AN17" t="n">
         <v>142</v>
       </c>
+      <c r="AP17" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL17" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B18" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C18" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E18" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F18" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H18" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I18" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J18" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K18" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N18" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O18" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V18" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W18" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X18" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2292,10 +2331,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL18" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2304,99 +2343,99 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B19" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C19" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D19" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E19" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F19" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H19" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I19" t="n">
         <v>11.3</v>
       </c>
       <c r="J19" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K19" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N19" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O19" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V19" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X19" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2405,10 +2444,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL19" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2417,99 +2456,66 @@
         <v>142</v>
       </c>
       <c r="AP19" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL19" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B20" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D20" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I20" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K20" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N20" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O20" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>9</v>
-      </c>
-      <c r="T20" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V20" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W20" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X20" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB20" t="n">
         <v>-0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2518,10 +2524,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2529,67 +2535,61 @@
       <c r="AN20" t="n">
         <v>142</v>
       </c>
-      <c r="AP20" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL20" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B21" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F21" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O21" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V21" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W21" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X21" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y21" t="n">
         <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA21" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2598,10 +2598,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2610,60 +2610,93 @@
         <v>142</v>
       </c>
       <c r="BL21" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B22" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>56.3</v>
       </c>
       <c r="D22" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>21.2</v>
       </c>
       <c r="F22" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>40.4</v>
       </c>
       <c r="K22" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>29</v>
       </c>
       <c r="O22" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>21.6</v>
       </c>
       <c r="V22" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W22" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X22" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF22" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2672,10 +2705,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL22" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2683,52 +2716,58 @@
       <c r="AN22" t="n">
         <v>142</v>
       </c>
+      <c r="AP22" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL22" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B23" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C23" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D23" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F23" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H23" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I23" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J23" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K23" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O23" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R23" t="n">
         <v>1.3</v>
@@ -2737,40 +2776,40 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V23" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W23" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X23" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA23" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG23" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2779,10 +2818,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2791,99 +2830,99 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS23" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B24" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C24" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D24" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E24" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F24" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I24" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J24" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K24" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O24" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W24" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X24" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG24" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2892,10 +2931,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL24" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2904,99 +2943,99 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS24" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B25" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C25" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D25" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F25" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H25" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I25" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J25" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K25" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N25" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O25" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q25" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T25" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V25" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W25" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X25" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA25" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF25" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG25" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3005,10 +3044,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL25" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3017,99 +3056,99 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS25" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B26" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C26" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E26" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H26" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I26" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J26" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K26" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M26" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N26" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O26" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R26" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T26" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V26" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W26" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X26" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA26" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG26" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3118,10 +3157,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3130,99 +3169,60 @@
         <v>142</v>
       </c>
       <c r="AP26" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL26" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B27" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C27" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D27" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E27" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K27" t="n">
-        <v>77</v>
-      </c>
-      <c r="M27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N27" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>21</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S27" t="n">
-        <v>6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V27" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X27" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y27" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA27" t="n">
         <v>9</v>
       </c>
-      <c r="Z27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB27" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3231,10 +3231,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3242,61 +3242,61 @@
       <c r="AN27" t="n">
         <v>142</v>
       </c>
-      <c r="AP27" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL27" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B28" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D28" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F28" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>35.5</v>
       </c>
       <c r="V28" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W28" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z28" t="n">
         <v>13</v>
       </c>
       <c r="AA28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB28" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3305,10 +3305,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3317,60 +3317,60 @@
         <v>142</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B29" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D29" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K29" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O29" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V29" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W29" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X29" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB29" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF29" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3379,10 +3379,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3391,60 +3391,93 @@
         <v>142</v>
       </c>
       <c r="BL29" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B30" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>86.8</v>
       </c>
       <c r="D30" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>33</v>
       </c>
       <c r="F30" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>41.1</v>
       </c>
       <c r="K30" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N30" t="n">
+        <v>33.5</v>
       </c>
       <c r="O30" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="n">
+        <v>22.4</v>
       </c>
       <c r="V30" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W30" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X30" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA30" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF30" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3453,10 +3486,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3464,94 +3497,100 @@
       <c r="AN30" t="n">
         <v>142</v>
       </c>
+      <c r="AP30" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL30" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B31" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C31" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D31" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E31" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F31" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H31" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I31" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J31" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K31" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M31" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O31" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R31" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T31" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V31" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W31" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X31" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z31" t="n">
         <v>12</v>
       </c>
       <c r="AA31" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB31" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG31" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3560,10 +3599,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL31" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3572,99 +3611,99 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS31" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B32" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C32" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D32" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E32" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F32" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I32" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J32" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K32" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O32" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R32" t="n">
         <v>1.8</v>
       </c>
       <c r="S32" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T32" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V32" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W32" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X32" t="n">
         <v>10.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA32" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB32" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD32" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF32" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG32" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3673,10 +3712,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL32" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3685,99 +3724,66 @@
         <v>142</v>
       </c>
       <c r="AP32" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS32" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL32" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B33" t="n">
-        <v>183</v>
-      </c>
-      <c r="C33" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D33" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E33" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
-      </c>
-      <c r="H33" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I33" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J33" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K33" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M33" t="n">
-        <v>4</v>
-      </c>
-      <c r="N33" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O33" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S33" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T33" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V33" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W33" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X33" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y33" t="n">
         <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA33" t="n">
         <v>10</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3786,10 +3792,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL33" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3797,67 +3803,61 @@
       <c r="AN33" t="n">
         <v>142</v>
       </c>
-      <c r="AP33" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL33" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B34" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F34" t="n">
         <v>6.5</v>
       </c>
       <c r="K34" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O34" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V34" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W34" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X34" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF34" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3866,10 +3866,10 @@
         <v>235</v>
       </c>
       <c r="AK34" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL34" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM34" t="n">
         <v>110</v>
@@ -3878,60 +3878,60 @@
         <v>142</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B35" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D35" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F35" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K35" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O35" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V35" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W35" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X35" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA35" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF35" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3939,12 +3939,6 @@
       <c r="AI35" t="n">
         <v>235</v>
       </c>
-      <c r="AK35" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM35" t="n">
         <v>110</v>
       </c>
@@ -3952,60 +3946,54 @@
         <v>142</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B36" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D36" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F36" t="n">
         <v>5.5</v>
       </c>
       <c r="K36" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O36" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V36" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W36" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X36" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z36" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA36" t="n">
         <v>15</v>
       </c>
-      <c r="AA36" t="n">
-        <v>14</v>
-      </c>
       <c r="AB36" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4020,54 +4008,93 @@
         <v>142</v>
       </c>
       <c r="BL36" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B37" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C37" t="n">
+        <v>71.8</v>
       </c>
       <c r="D37" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E37" t="n">
+        <v>24.7</v>
       </c>
       <c r="F37" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J37" t="n">
+        <v>41.1</v>
       </c>
       <c r="K37" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>33.5</v>
       </c>
       <c r="O37" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>23.2</v>
       </c>
       <c r="V37" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W37" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X37" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y37" t="n">
         <v>12</v>
       </c>
       <c r="Z37" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA37" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4075,100 +4102,112 @@
       <c r="AI37" t="n">
         <v>235</v>
       </c>
+      <c r="AK37" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM37" t="n">
         <v>110</v>
       </c>
       <c r="AN37" t="n">
         <v>142</v>
       </c>
+      <c r="AP37" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL37" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B38" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C38" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D38" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E38" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H38" t="n">
         <v>24.1</v>
       </c>
       <c r="I38" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J38" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K38" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N38" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O38" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T38" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V38" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W38" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X38" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z38" t="n">
         <v>13</v>
       </c>
-      <c r="X38" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>14</v>
-      </c>
       <c r="AA38" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF38" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4177,10 +4216,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL38" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4189,99 +4228,99 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS38" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B39" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C39" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D39" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E39" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F39" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H39" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I39" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K39" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O39" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R39" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S39" t="n">
         <v>7</v>
       </c>
       <c r="T39" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V39" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W39" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X39" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA39" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG39" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4290,10 +4329,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4302,99 +4341,99 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS39" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B40" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C40" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D40" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E40" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F40" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H40" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I40" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J40" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K40" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N40" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O40" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q40" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R40" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T40" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V40" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W40" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X40" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z40" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA40" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4403,10 +4442,10 @@
         <v>235</v>
       </c>
       <c r="AK40" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM40" t="n">
         <v>110</v>
@@ -4415,99 +4454,66 @@
         <v>142</v>
       </c>
       <c r="AP40" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS40" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL40" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B41" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C41" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D41" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E41" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H41" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J41" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K41" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M41" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S41" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T41" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V41" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W41" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X41" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z41" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA41" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC41" t="n">
         <v>8.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF41" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4515,79 +4521,67 @@
       <c r="AI41" t="n">
         <v>235</v>
       </c>
-      <c r="AK41" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM41" t="n">
         <v>110</v>
       </c>
       <c r="AN41" t="n">
         <v>142</v>
       </c>
-      <c r="AP41" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL41" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B42" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D42" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F42" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K42" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O42" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V42" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W42" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X42" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z42" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA42" t="n">
         <v>9</v>
       </c>
       <c r="AB42" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF42" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG42" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4602,60 +4596,93 @@
         <v>142</v>
       </c>
       <c r="BL42" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B43" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>73.7</v>
       </c>
       <c r="D43" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E43" t="n">
+        <v>28.2</v>
       </c>
       <c r="F43" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H43" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J43" t="n">
+        <v>40.1</v>
       </c>
       <c r="K43" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M43" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N43" t="n">
+        <v>32.9</v>
       </c>
       <c r="O43" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="n">
+        <v>23.5</v>
       </c>
       <c r="V43" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W43" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X43" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y43" t="n">
         <v>4</v>
       </c>
       <c r="Z43" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA43" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB43" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF43" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4663,100 +4690,112 @@
       <c r="AI43" t="n">
         <v>235</v>
       </c>
+      <c r="AK43" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM43" t="n">
         <v>110</v>
       </c>
       <c r="AN43" t="n">
         <v>142</v>
       </c>
+      <c r="AP43" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL43" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B44" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C44" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E44" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F44" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H44" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I44" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J44" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K44" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M44" t="n">
         <v>6.8</v>
       </c>
       <c r="N44" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O44" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q44" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R44" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T44" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V44" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W44" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X44" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z44" t="n">
         <v>13</v>
       </c>
       <c r="AA44" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC44" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB44" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD44" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF44" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG44" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4765,10 +4804,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL44" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4777,99 +4816,99 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS44" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B45" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C45" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E45" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F45" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H45" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I45" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J45" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K45" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M45" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N45" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O45" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q45" t="n">
         <v>23.1</v>
       </c>
       <c r="R45" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S45" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T45" t="n">
         <v>23.1</v>
       </c>
       <c r="V45" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W45" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X45" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA45" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG45" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4878,10 +4917,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL45" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4890,99 +4929,99 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS45" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B46" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C46" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D46" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E46" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F46" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H46" t="n">
         <v>23.8</v>
       </c>
       <c r="I46" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J46" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K46" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M46" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N46" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O46" t="n">
         <v>40.1</v>
       </c>
-      <c r="K46" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M46" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N46" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O46" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q46" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R46" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S46" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W46" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X46" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC46" t="n">
         <v>9.6</v>
       </c>
-      <c r="W46" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X46" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD46" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF46" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG46" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -4991,10 +5030,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL46" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5003,75 +5042,75 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS46" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B47" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C47" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D47" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E47" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F47" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H47" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I47" t="n">
         <v>7.2</v>
       </c>
       <c r="J47" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K47" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M47" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N47" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O47" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q47" t="n">
         <v>23.2</v>
       </c>
       <c r="R47" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
         <v>23.2</v>
       </c>
       <c r="V47" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W47" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X47" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y47" t="n">
         <v>10</v>
@@ -5080,22 +5119,22 @@
         <v>18</v>
       </c>
       <c r="AA47" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF47" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5104,10 +5143,10 @@
         <v>235</v>
       </c>
       <c r="AK47" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL47" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM47" t="n">
         <v>110</v>
@@ -5116,99 +5155,54 @@
         <v>142</v>
       </c>
       <c r="AP47" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS47" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL47" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B48" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C48" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D48" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E48" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F48" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H48" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W48" t="n">
         <v>23.4</v>
       </c>
-      <c r="I48" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J48" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K48" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M48" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N48" t="n">
-        <v>33</v>
-      </c>
-      <c r="O48" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R48" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V48" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W48" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X48" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z48" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA48" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC48" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5216,67 +5210,61 @@
       <c r="AI48" t="n">
         <v>235</v>
       </c>
-      <c r="AK48" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM48" t="n">
         <v>110</v>
       </c>
       <c r="AN48" t="n">
         <v>142</v>
       </c>
-      <c r="AP48" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL48" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B49" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D49" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F49" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V49" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W49" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X49" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA49" t="n">
         <v>13</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD49" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5291,54 +5279,93 @@
         <v>142</v>
       </c>
       <c r="BL49" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B50" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C50" t="n">
+        <v>50.6</v>
       </c>
       <c r="D50" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>19.4</v>
       </c>
       <c r="F50" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H50" t="n">
+        <v>24</v>
+      </c>
+      <c r="I50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K50" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N50" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O50" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>21.4</v>
       </c>
       <c r="V50" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W50" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X50" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y50" t="n">
         <v>8</v>
       </c>
       <c r="Z50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF50" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG50" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5346,100 +5373,112 @@
       <c r="AI50" t="n">
         <v>235</v>
       </c>
+      <c r="AK50" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM50" t="n">
         <v>110</v>
       </c>
       <c r="AN50" t="n">
         <v>142</v>
       </c>
+      <c r="AP50" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL50" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B51" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C51" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D51" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E51" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F51" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I51" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J51" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K51" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M51" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N51" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O51" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R51" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V51" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W51" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X51" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y51" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA51" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC51" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD51" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5448,10 +5487,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL51" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5460,99 +5499,99 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS51" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B52" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C52" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D52" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E52" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F52" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H52" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I52" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J52" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K52" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M52" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N52" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O52" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R52" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V52" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W52" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X52" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z52" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA52" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC52" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF52" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG52" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5561,10 +5600,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL52" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5573,99 +5612,99 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS52" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B53" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C53" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D53" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E53" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F53" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H53" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I53" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K53" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N53" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O53" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R53" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V53" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W53" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X53" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z53" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA53" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC53" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF53" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG53" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5674,10 +5713,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL53" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5686,57 +5725,57 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS53" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B54" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C54" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D54" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E54" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F54" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H54" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I54" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J54" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K54" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N54" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O54" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -5745,40 +5784,40 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V54" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W54" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X54" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA54" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC54" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF54" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5787,10 +5826,10 @@
         <v>235</v>
       </c>
       <c r="AK54" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL54" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM54" t="n">
         <v>110</v>
@@ -5799,99 +5838,60 @@
         <v>142</v>
       </c>
       <c r="AP54" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS54" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL54" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B55" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C55" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D55" t="n">
         <v>35.6</v>
       </c>
-      <c r="E55" t="n">
-        <v>26</v>
-      </c>
       <c r="F55" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H55" t="n">
-        <v>24</v>
-      </c>
-      <c r="I55" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J55" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K55" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N55" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O55" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>21</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V55" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="W55" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="X55" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y55" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z55" t="n">
         <v>19</v>
       </c>
       <c r="AA55" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AB55" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC55" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AF55" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5899,55 +5899,43 @@
       <c r="AI55" t="n">
         <v>235</v>
       </c>
-      <c r="AK55" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
         <v>142</v>
       </c>
-      <c r="AP55" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL55" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B56" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D56" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Y56" t="n">
         <v>7</v>
       </c>
       <c r="Z56" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA56" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AF56" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5962,36 +5950,75 @@
         <v>142</v>
       </c>
       <c r="BL56" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B57" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C57" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E57" t="n">
+        <v>28.1</v>
       </c>
       <c r="F57" t="n">
         <v>3.3</v>
       </c>
+      <c r="H57" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9</v>
+      </c>
+      <c r="J57" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N57" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O57" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R57" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>23.7</v>
+      </c>
       <c r="Y57" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z57" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA57" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF57" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG57" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -5999,82 +6026,94 @@
       <c r="AI57" t="n">
         <v>235</v>
       </c>
+      <c r="AK57" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM57" t="n">
         <v>110</v>
       </c>
       <c r="AN57" t="n">
         <v>142</v>
       </c>
+      <c r="AP57" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL57" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B58" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C58" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E58" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F58" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H58" t="n">
         <v>23.4</v>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K58" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M58" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N58" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O58" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R58" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z58" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA58" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AF58" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG58" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6083,10 +6122,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL58" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6095,81 +6134,81 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS58" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B59" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C59" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D59" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E59" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F59" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H59" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I59" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J59" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K59" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N59" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O59" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R59" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T59" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="Y59" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z59" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA59" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AF59" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG59" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6178,10 +6217,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL59" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6190,81 +6229,81 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS59" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B60" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C60" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D60" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E60" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F60" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H60" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I60" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J60" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K60" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N60" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O60" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q60" t="n">
         <v>21.7</v>
       </c>
       <c r="R60" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S60" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
         <v>21.7</v>
       </c>
       <c r="Y60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA60" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AF60" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6273,10 +6312,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL60" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6285,36 +6324,36 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS60" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B61" t="n">
-        <v>135.8</v>
+        <v>131.7</v>
       </c>
       <c r="D61" t="n">
-        <v>34.2</v>
+        <v>33.2</v>
       </c>
       <c r="F61" t="n">
         <v>3.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6329,30 +6368,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B62" t="n">
-        <v>131.7</v>
+        <v>133.9</v>
       </c>
       <c r="D62" t="n">
-        <v>33.2</v>
+        <v>34.7</v>
       </c>
       <c r="F62" t="n">
         <v>3.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z62" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA62" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6367,7 +6406,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/carga_datos.xlsx
+++ b/public/data/carga_datos.xlsx
@@ -628,88 +628,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B2" t="n">
-        <v>183.5</v>
+        <v>180.5</v>
       </c>
       <c r="C2" t="n">
-        <v>84.5</v>
+        <v>79.2</v>
       </c>
       <c r="D2" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="E2" t="n">
         <v>34.6</v>
       </c>
       <c r="F2" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="H2" t="n">
         <v>23.9</v>
       </c>
       <c r="I2" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="J2" t="n">
-        <v>41.5</v>
+        <v>41.9</v>
       </c>
       <c r="K2" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
         <v>37.7</v>
       </c>
       <c r="O2" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="T2" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V2" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W2" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="X2" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.7</v>
+        <v>11.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>220.36</v>
+        <v>219.64</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AH2" t="n">
         <v>215</v>
@@ -718,10 +718,10 @@
         <v>235</v>
       </c>
       <c r="AK2" t="n">
-        <v>127.13</v>
+        <v>126.03</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -730,99 +730,99 @@
         <v>142</v>
       </c>
       <c r="AP2" t="n">
-        <v>76.90000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.17</v>
+        <v>14.55</v>
       </c>
       <c r="BL2" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B3" t="n">
-        <v>180.5</v>
+        <v>168.1</v>
       </c>
       <c r="C3" t="n">
-        <v>79.2</v>
+        <v>69.7</v>
       </c>
       <c r="D3" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E3" t="n">
-        <v>34.6</v>
+        <v>33.9</v>
       </c>
       <c r="F3" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H3" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I3" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="J3" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="K3" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="O3" t="n">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
         <v>17.6</v>
       </c>
       <c r="T3" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W3" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Y3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>11.9</v>
-      </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>219.64</v>
+        <v>224.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.72</v>
+        <v>5.29</v>
       </c>
       <c r="AH3" t="n">
         <v>215</v>
@@ -831,10 +831,10 @@
         <v>235</v>
       </c>
       <c r="AK3" t="n">
-        <v>126.03</v>
+        <v>129.28</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.1</v>
+        <v>3.25</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -843,99 +843,99 @@
         <v>142</v>
       </c>
       <c r="AP3" t="n">
-        <v>82.95</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>14.55</v>
+        <v>15.25</v>
       </c>
       <c r="BL3" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B4" t="n">
-        <v>168.1</v>
+        <v>158.9</v>
       </c>
       <c r="C4" t="n">
-        <v>69.7</v>
+        <v>58.8</v>
       </c>
       <c r="D4" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E4" t="n">
         <v>30.4</v>
       </c>
-      <c r="E4" t="n">
-        <v>33.9</v>
-      </c>
       <c r="F4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H4" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="I4" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J4" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="K4" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="O4" t="n">
-        <v>43.1</v>
+        <v>41.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="S4" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="T4" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="V4" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="W4" t="n">
-        <v>22.9</v>
+        <v>26</v>
       </c>
       <c r="X4" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y4" t="n">
         <v>17</v>
       </c>
-      <c r="Y4" t="n">
-        <v>11</v>
-      </c>
       <c r="Z4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>14.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>224.93</v>
+        <v>232.31</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.29</v>
+        <v>9.67</v>
       </c>
       <c r="AH4" t="n">
         <v>215</v>
@@ -944,10 +944,10 @@
         <v>235</v>
       </c>
       <c r="AK4" t="n">
-        <v>129.28</v>
+        <v>134.44</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.25</v>
+        <v>5.16</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -956,99 +956,66 @@
         <v>142</v>
       </c>
       <c r="AP4" t="n">
-        <v>87.43000000000001</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.25</v>
+        <v>17.07</v>
       </c>
       <c r="BL4" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B5" t="n">
-        <v>158.9</v>
-      </c>
-      <c r="C5" t="n">
-        <v>58.8</v>
+        <v>136.7</v>
       </c>
       <c r="D5" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="F5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H5" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>41</v>
+        <v>7.5</v>
       </c>
       <c r="K5" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N5" t="n">
-        <v>37.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>15</v>
-      </c>
-      <c r="T5" t="n">
-        <v>21.5</v>
+        <v>39.2</v>
       </c>
       <c r="V5" t="n">
-        <v>10.1</v>
+        <v>17.1</v>
       </c>
       <c r="W5" t="n">
-        <v>26</v>
+        <v>36.1</v>
       </c>
       <c r="X5" t="n">
-        <v>18.1</v>
+        <v>26.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC5" t="n">
         <v>6.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>232.31</v>
+        <v>235.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>9.67</v>
+        <v>3.09</v>
       </c>
       <c r="AH5" t="n">
         <v>215</v>
@@ -1057,10 +1024,10 @@
         <v>235</v>
       </c>
       <c r="AK5" t="n">
-        <v>134.44</v>
+        <v>137.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.16</v>
+        <v>3.06</v>
       </c>
       <c r="AM5" t="n">
         <v>110</v>
@@ -1068,67 +1035,61 @@
       <c r="AN5" t="n">
         <v>142</v>
       </c>
-      <c r="AP5" t="n">
-        <v>91.73999999999999</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>17.07</v>
-      </c>
       <c r="BL5" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B6" t="n">
-        <v>136.7</v>
+        <v>138.5</v>
       </c>
       <c r="D6" t="n">
-        <v>30.7</v>
+        <v>31.7</v>
       </c>
       <c r="F6" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>92.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V6" t="n">
-        <v>17.1</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="X6" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>235.4</v>
+        <v>231.99</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.09</v>
+        <v>-3.41</v>
       </c>
       <c r="AH6" t="n">
         <v>215</v>
@@ -1137,10 +1098,10 @@
         <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>137.5</v>
+        <v>136.12</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.06</v>
+        <v>-1.38</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1149,60 +1110,93 @@
         <v>142</v>
       </c>
       <c r="BL6" s="1" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B7" t="n">
-        <v>138.5</v>
+        <v>161.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>67</v>
       </c>
       <c r="D7" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>31.5</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>7.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41.1</v>
       </c>
       <c r="K7" t="n">
-        <v>91</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>35</v>
       </c>
       <c r="O7" t="n">
-        <v>37.8</v>
+        <v>37.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>20.5</v>
       </c>
       <c r="V7" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="W7" t="n">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="X7" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.7</v>
+        <v>-0.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>231.99</v>
+        <v>225.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>-3.41</v>
+        <v>-6.48</v>
       </c>
       <c r="AH7" t="n">
         <v>215</v>
@@ -1211,10 +1205,10 @@
         <v>235</v>
       </c>
       <c r="AK7" t="n">
-        <v>136.12</v>
+        <v>133.83</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
@@ -1222,94 +1216,100 @@
       <c r="AN7" t="n">
         <v>142</v>
       </c>
+      <c r="AP7" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>15.73</v>
+      </c>
       <c r="BL7" s="1" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B8" t="n">
-        <v>161.1</v>
+        <v>176.4</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>31.9</v>
+        <v>32.7</v>
       </c>
       <c r="E8" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H8" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="I8" t="n">
         <v>11.4</v>
       </c>
       <c r="J8" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K8" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="O8" t="n">
-        <v>37.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T8" t="n">
-        <v>20.5</v>
+        <v>22.3</v>
       </c>
       <c r="V8" t="n">
-        <v>14.1</v>
+        <v>11.5</v>
       </c>
       <c r="W8" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="X8" t="n">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
         <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>225.51</v>
+        <v>220.92</v>
       </c>
       <c r="AG8" t="n">
-        <v>-6.48</v>
+        <v>-4.59</v>
       </c>
       <c r="AH8" t="n">
         <v>215</v>
@@ -1318,10 +1318,10 @@
         <v>235</v>
       </c>
       <c r="AK8" t="n">
-        <v>133.83</v>
+        <v>131.85</v>
       </c>
       <c r="AL8" t="n">
-        <v>-2.29</v>
+        <v>-1.98</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -1330,99 +1330,99 @@
         <v>142</v>
       </c>
       <c r="AP8" t="n">
-        <v>82.93000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AS8" t="n">
-        <v>15.73</v>
+        <v>15.49</v>
       </c>
       <c r="BL8" s="1" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B9" t="n">
-        <v>176.4</v>
+        <v>181</v>
       </c>
       <c r="C9" t="n">
-        <v>77.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D9" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="F9" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H9" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>13</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA9" t="n">
         <v>11.4</v>
       </c>
-      <c r="J9" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>76</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N9" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>14</v>
-      </c>
-      <c r="T9" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>11.6</v>
-      </c>
       <c r="AB9" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AF9" t="n">
         <v>220.92</v>
       </c>
       <c r="AG9" t="n">
-        <v>-4.59</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
         <v>215</v>
@@ -1431,10 +1431,10 @@
         <v>235</v>
       </c>
       <c r="AK9" t="n">
-        <v>131.85</v>
+        <v>130.06</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.98</v>
+        <v>-1.79</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
@@ -1443,99 +1443,99 @@
         <v>142</v>
       </c>
       <c r="AP9" t="n">
-        <v>79.75</v>
+        <v>79.94</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.49</v>
+        <v>14.93</v>
       </c>
       <c r="BL9" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B10" t="n">
-        <v>181</v>
+        <v>179.6</v>
       </c>
       <c r="C10" t="n">
-        <v>80.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>30.3</v>
       </c>
       <c r="E10" t="n">
-        <v>35.1</v>
+        <v>31.1</v>
       </c>
       <c r="F10" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="H10" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="I10" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J10" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K10" t="n">
-        <v>75.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="O10" t="n">
-        <v>39.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD10" t="n">
         <v>0.5</v>
       </c>
-      <c r="S10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-0.9</v>
-      </c>
       <c r="AF10" t="n">
-        <v>220.92</v>
+        <v>216.02</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AH10" t="n">
         <v>215</v>
@@ -1544,10 +1544,10 @@
         <v>235</v>
       </c>
       <c r="AK10" t="n">
-        <v>130.06</v>
+        <v>127.85</v>
       </c>
       <c r="AL10" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -1556,99 +1556,99 @@
         <v>142</v>
       </c>
       <c r="AP10" t="n">
-        <v>79.94</v>
+        <v>82.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>14.93</v>
+        <v>15.16</v>
       </c>
       <c r="BL10" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B11" t="n">
-        <v>179.6</v>
+        <v>170.4</v>
       </c>
       <c r="C11" t="n">
-        <v>81.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D11" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="E11" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="F11" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H11" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="I11" t="n">
-        <v>10.8</v>
+        <v>11.2</v>
       </c>
       <c r="J11" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="K11" t="n">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N11" t="n">
-        <v>37.1</v>
+        <v>36.6</v>
       </c>
       <c r="O11" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S11" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="T11" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="V11" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="W11" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="X11" t="n">
         <v>12.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
         <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.1</v>
+        <v>12.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="AF11" t="n">
         <v>216.02</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>215</v>
@@ -1657,10 +1657,10 @@
         <v>235</v>
       </c>
       <c r="AK11" t="n">
-        <v>127.85</v>
+        <v>128.54</v>
       </c>
       <c r="AL11" t="n">
-        <v>-2.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -1669,99 +1669,66 @@
         <v>142</v>
       </c>
       <c r="AP11" t="n">
-        <v>82.2</v>
+        <v>84.73</v>
       </c>
       <c r="AS11" t="n">
-        <v>15.16</v>
+        <v>15.34</v>
       </c>
       <c r="BL11" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B12" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="C12" t="n">
-        <v>78.5</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E12" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="F12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>41.4</v>
+        <v>6.8</v>
       </c>
       <c r="K12" t="n">
-        <v>75</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N12" t="n">
-        <v>36.6</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>23.3</v>
+        <v>39.2</v>
       </c>
       <c r="V12" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>15.7</v>
+        <v>20.9</v>
       </c>
       <c r="X12" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>216.02</v>
+        <v>224.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH12" t="n">
         <v>215</v>
@@ -1770,10 +1737,10 @@
         <v>235</v>
       </c>
       <c r="AK12" t="n">
-        <v>128.54</v>
+        <v>130.92</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
@@ -1781,67 +1748,61 @@
       <c r="AN12" t="n">
         <v>142</v>
       </c>
-      <c r="AP12" t="n">
-        <v>84.73</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>15.34</v>
-      </c>
       <c r="BL12" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B13" t="n">
-        <v>156</v>
+        <v>147.8</v>
       </c>
       <c r="D13" t="n">
-        <v>30.1</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
         <v>6.8</v>
       </c>
       <c r="K13" t="n">
-        <v>95.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="O13" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA13" t="n">
         <v>13.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>224.53</v>
+        <v>230.27</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.32</v>
+        <v>5.74</v>
       </c>
       <c r="AH13" t="n">
         <v>215</v>
@@ -1850,10 +1811,10 @@
         <v>235</v>
       </c>
       <c r="AK13" t="n">
-        <v>130.92</v>
+        <v>132.76</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AM13" t="n">
         <v>110</v>
@@ -1862,60 +1823,93 @@
         <v>142</v>
       </c>
       <c r="BL13" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B14" t="n">
-        <v>147.8</v>
+        <v>149.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>60</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E14" t="n">
+        <v>25.9</v>
       </c>
       <c r="F14" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>24</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>38.8</v>
       </c>
       <c r="K14" t="n">
-        <v>96.5</v>
+        <v>74.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>36.7</v>
       </c>
       <c r="O14" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>21.7</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="W14" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="X14" t="n">
-        <v>15.2</v>
+        <v>17.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.5</v>
+        <v>15.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>230.27</v>
+        <v>237.43</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.74</v>
+        <v>7.16</v>
       </c>
       <c r="AH14" t="n">
         <v>215</v>
@@ -1924,10 +1918,10 @@
         <v>235</v>
       </c>
       <c r="AK14" t="n">
-        <v>132.76</v>
+        <v>134.95</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -1935,94 +1929,67 @@
       <c r="AN14" t="n">
         <v>142</v>
       </c>
+      <c r="AP14" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>16.95</v>
+      </c>
       <c r="BL14" s="1" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B15" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>60</v>
+        <v>143.9</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
-      </c>
-      <c r="E15" t="n">
-        <v>25.9</v>
+        <v>32.9</v>
       </c>
       <c r="F15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H15" t="n">
-        <v>24</v>
-      </c>
-      <c r="I15" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="K15" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>36.7</v>
+        <v>96.2</v>
       </c>
       <c r="O15" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>21.7</v>
+        <v>37.9</v>
       </c>
       <c r="V15" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="W15" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="X15" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="n">
-        <v>15.7</v>
+        <v>16</v>
       </c>
       <c r="AB15" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>237.43</v>
+        <v>236.14</v>
       </c>
       <c r="AG15" t="n">
-        <v>7.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AH15" t="n">
         <v>215</v>
@@ -2031,10 +1998,10 @@
         <v>235</v>
       </c>
       <c r="AK15" t="n">
-        <v>134.95</v>
+        <v>136.28</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -2042,67 +2009,94 @@
       <c r="AN15" t="n">
         <v>142</v>
       </c>
-      <c r="AP15" t="n">
-        <v>91.28</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>16.95</v>
-      </c>
       <c r="BL15" s="1" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B16" t="n">
-        <v>143.9</v>
+        <v>166.4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>63.7</v>
       </c>
       <c r="D16" t="n">
-        <v>32.9</v>
+        <v>34.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>36.4</v>
       </c>
       <c r="F16" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>39.9</v>
       </c>
       <c r="K16" t="n">
-        <v>96.2</v>
+        <v>75.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>35.9</v>
       </c>
       <c r="O16" t="n">
-        <v>37.9</v>
+        <v>39</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>20.3</v>
       </c>
       <c r="V16" t="n">
-        <v>10</v>
+        <v>11.9</v>
       </c>
       <c r="W16" t="n">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="X16" t="n">
-        <v>17.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>-1.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>236.14</v>
+        <v>236.13</v>
       </c>
       <c r="AG16" t="n">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="AH16" t="n">
         <v>215</v>
@@ -2111,10 +2105,10 @@
         <v>235</v>
       </c>
       <c r="AK16" t="n">
-        <v>136.28</v>
+        <v>134.54</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AM16" t="n">
         <v>110</v>
@@ -2122,94 +2116,100 @@
       <c r="AN16" t="n">
         <v>142</v>
       </c>
+      <c r="AP16" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>16.28</v>
+      </c>
       <c r="BL16" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B17" t="n">
-        <v>166.4</v>
+        <v>172.9</v>
       </c>
       <c r="C17" t="n">
-        <v>63.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="E17" t="n">
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="F17" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H17" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="I17" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="J17" t="n">
-        <v>39.9</v>
+        <v>41.7</v>
       </c>
       <c r="K17" t="n">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N17" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="O17" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="V17" t="n">
-        <v>11.9</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
-        <v>27</v>
+        <v>18.7</v>
       </c>
       <c r="X17" t="n">
-        <v>19.4</v>
+        <v>16.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>-3.5</v>
+        <v>-4.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>236.13</v>
+        <v>218.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH17" t="n">
         <v>215</v>
@@ -2218,10 +2218,10 @@
         <v>235</v>
       </c>
       <c r="AK17" t="n">
-        <v>134.54</v>
+        <v>130.39</v>
       </c>
       <c r="AL17" t="n">
-        <v>-1.74</v>
+        <v>-4.15</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -2230,99 +2230,99 @@
         <v>142</v>
       </c>
       <c r="AP17" t="n">
-        <v>82.27</v>
+        <v>78.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>16.28</v>
+        <v>15.79</v>
       </c>
       <c r="BL17" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B18" t="n">
-        <v>172.9</v>
+        <v>157.5</v>
       </c>
       <c r="C18" t="n">
-        <v>67.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="D18" t="n">
-        <v>34.9</v>
+        <v>33.2</v>
       </c>
       <c r="E18" t="n">
-        <v>35.2</v>
+        <v>27.7</v>
       </c>
       <c r="F18" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="H18" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="I18" t="n">
         <v>11.3</v>
       </c>
       <c r="J18" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K18" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="N18" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="O18" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="n">
-        <v>19</v>
+        <v>21.6</v>
       </c>
       <c r="V18" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
       <c r="W18" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="X18" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>218.6</v>
+        <v>218.84</v>
       </c>
       <c r="AG18" t="n">
-        <v>-9.380000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH18" t="n">
         <v>215</v>
@@ -2331,10 +2331,10 @@
         <v>235</v>
       </c>
       <c r="AK18" t="n">
-        <v>130.39</v>
+        <v>133.09</v>
       </c>
       <c r="AL18" t="n">
-        <v>-4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -2343,99 +2343,66 @@
         <v>142</v>
       </c>
       <c r="AP18" t="n">
-        <v>78.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>15.79</v>
+        <v>15.63</v>
       </c>
       <c r="BL18" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B19" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C19" t="n">
-        <v>68.5</v>
+        <v>137.6</v>
       </c>
       <c r="D19" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>27.7</v>
+        <v>35</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H19" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I19" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>41.4</v>
+        <v>6.5</v>
       </c>
       <c r="K19" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N19" t="n">
-        <v>34.9</v>
+        <v>96.7</v>
       </c>
       <c r="O19" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>9</v>
-      </c>
-      <c r="T19" t="n">
-        <v>21.6</v>
+        <v>35.1</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="W19" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X19" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="n">
-        <v>13.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB19" t="n">
         <v>-0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>218.84</v>
+        <v>221.78</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.25</v>
+        <v>2.94</v>
       </c>
       <c r="AH19" t="n">
         <v>215</v>
@@ -2444,10 +2411,10 @@
         <v>235</v>
       </c>
       <c r="AK19" t="n">
-        <v>133.09</v>
+        <v>138.76</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.7</v>
+        <v>5.67</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -2455,67 +2422,61 @@
       <c r="AN19" t="n">
         <v>142</v>
       </c>
-      <c r="AP19" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>15.63</v>
-      </c>
       <c r="BL19" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B20" t="n">
-        <v>137.6</v>
+        <v>132.5</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>33.6</v>
       </c>
       <c r="F20" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O20" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="V20" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="W20" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="Y20" t="n">
         <v>14</v>
       </c>
       <c r="Z20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>221.78</v>
+        <v>224.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="n">
         <v>215</v>
@@ -2524,10 +2485,10 @@
         <v>235</v>
       </c>
       <c r="AK20" t="n">
-        <v>138.76</v>
+        <v>143.55</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.67</v>
+        <v>4.79</v>
       </c>
       <c r="AM20" t="n">
         <v>110</v>
@@ -2536,60 +2497,93 @@
         <v>142</v>
       </c>
       <c r="BL20" s="1" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B21" t="n">
-        <v>132.5</v>
+        <v>137.2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>56.3</v>
       </c>
       <c r="D21" t="n">
-        <v>33.6</v>
+        <v>32.1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>21.2</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>40.4</v>
       </c>
       <c r="K21" t="n">
-        <v>97.8</v>
+        <v>75.7</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N21" t="n">
+        <v>29</v>
       </c>
       <c r="O21" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>21.6</v>
       </c>
       <c r="V21" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="W21" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="X21" t="n">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA21" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>224.78</v>
+        <v>232.22</v>
       </c>
       <c r="AG21" t="n">
-        <v>3</v>
+        <v>7.43</v>
       </c>
       <c r="AH21" t="n">
         <v>215</v>
@@ -2598,10 +2592,10 @@
         <v>235</v>
       </c>
       <c r="AK21" t="n">
-        <v>143.55</v>
+        <v>143.61</v>
       </c>
       <c r="AL21" t="n">
-        <v>4.79</v>
+        <v>0.06</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
@@ -2609,52 +2603,58 @@
       <c r="AN21" t="n">
         <v>142</v>
       </c>
+      <c r="AP21" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>18.02</v>
+      </c>
       <c r="BL21" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B22" t="n">
-        <v>137.2</v>
+        <v>157.5</v>
       </c>
       <c r="C22" t="n">
-        <v>56.3</v>
+        <v>59.6</v>
       </c>
       <c r="D22" t="n">
-        <v>32.1</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
-        <v>21.2</v>
+        <v>30.6</v>
       </c>
       <c r="F22" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="H22" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="I22" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="J22" t="n">
-        <v>40.4</v>
+        <v>38.9</v>
       </c>
       <c r="K22" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
       <c r="O22" t="n">
-        <v>32.6</v>
+        <v>37.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="R22" t="n">
         <v>1.3</v>
@@ -2663,40 +2663,40 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="V22" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="W22" t="n">
-        <v>24.3</v>
+        <v>26.3</v>
       </c>
       <c r="X22" t="n">
-        <v>17.5</v>
+        <v>19.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA22" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>232.22</v>
+        <v>229.69</v>
       </c>
       <c r="AG22" t="n">
-        <v>7.43</v>
+        <v>-2.53</v>
       </c>
       <c r="AH22" t="n">
         <v>215</v>
@@ -2705,10 +2705,10 @@
         <v>235</v>
       </c>
       <c r="AK22" t="n">
-        <v>143.61</v>
+        <v>136.96</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
@@ -2717,99 +2717,99 @@
         <v>142</v>
       </c>
       <c r="AP22" t="n">
-        <v>89.31999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AS22" t="n">
-        <v>18.02</v>
+        <v>16.96</v>
       </c>
       <c r="BL22" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B23" t="n">
-        <v>157.5</v>
+        <v>159.6</v>
       </c>
       <c r="C23" t="n">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>34.5</v>
       </c>
       <c r="E23" t="n">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="F23" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="H23" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="I23" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J23" t="n">
-        <v>38.9</v>
+        <v>40.5</v>
       </c>
       <c r="K23" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>33.4</v>
+        <v>34.3</v>
       </c>
       <c r="O23" t="n">
-        <v>37.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V23" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="W23" t="n">
-        <v>26.3</v>
+        <v>22.5</v>
       </c>
       <c r="X23" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AF23" t="n">
-        <v>229.69</v>
+        <v>228.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>-2.53</v>
+        <v>-1.14</v>
       </c>
       <c r="AH23" t="n">
         <v>215</v>
@@ -2818,10 +2818,10 @@
         <v>235</v>
       </c>
       <c r="AK23" t="n">
-        <v>136.96</v>
+        <v>133.01</v>
       </c>
       <c r="AL23" t="n">
-        <v>-6.65</v>
+        <v>-3.95</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -2830,99 +2830,99 @@
         <v>142</v>
       </c>
       <c r="AP23" t="n">
-        <v>86.59</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AS23" t="n">
-        <v>16.96</v>
+        <v>15.95</v>
       </c>
       <c r="BL23" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B24" t="n">
-        <v>159.6</v>
+        <v>160.4</v>
       </c>
       <c r="C24" t="n">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D24" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E24" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
       <c r="F24" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="H24" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="I24" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J24" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="K24" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="N24" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="O24" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="Q24" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V24" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="W24" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="X24" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA24" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>-2.2</v>
+        <v>-3.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AF24" t="n">
-        <v>228.57</v>
+        <v>225.08</v>
       </c>
       <c r="AG24" t="n">
-        <v>-1.14</v>
+        <v>-3.5</v>
       </c>
       <c r="AH24" t="n">
         <v>215</v>
@@ -2931,10 +2931,10 @@
         <v>235</v>
       </c>
       <c r="AK24" t="n">
-        <v>133.01</v>
+        <v>135.24</v>
       </c>
       <c r="AL24" t="n">
-        <v>-3.95</v>
+        <v>2.23</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -2943,99 +2943,99 @@
         <v>142</v>
       </c>
       <c r="AP24" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AS24" t="n">
-        <v>15.95</v>
+        <v>15.4</v>
       </c>
       <c r="BL24" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B25" t="n">
-        <v>160.4</v>
+        <v>161.7</v>
       </c>
       <c r="C25" t="n">
-        <v>62.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="E25" t="n">
-        <v>32.2</v>
+        <v>27.3</v>
       </c>
       <c r="F25" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H25" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="I25" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J25" t="n">
-        <v>41.1</v>
+        <v>42.6</v>
       </c>
       <c r="K25" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="N25" t="n">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O25" t="n">
-        <v>38</v>
+        <v>37.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="R25" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T25" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V25" t="n">
-        <v>16.4</v>
+        <v>12.7</v>
       </c>
       <c r="W25" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="X25" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA25" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>-3.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AF25" t="n">
-        <v>225.08</v>
+        <v>225</v>
       </c>
       <c r="AG25" t="n">
-        <v>-3.5</v>
+        <v>-0.08</v>
       </c>
       <c r="AH25" t="n">
         <v>215</v>
@@ -3044,10 +3044,10 @@
         <v>235</v>
       </c>
       <c r="AK25" t="n">
-        <v>135.24</v>
+        <v>134.62</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.23</v>
+        <v>-0.62</v>
       </c>
       <c r="AM25" t="n">
         <v>110</v>
@@ -3056,99 +3056,60 @@
         <v>142</v>
       </c>
       <c r="AP25" t="n">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>15.4</v>
+        <v>13.86</v>
       </c>
       <c r="BL25" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B26" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="C26" t="n">
-        <v>71.09999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="D26" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E26" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="F26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K26" t="n">
-        <v>77</v>
-      </c>
-      <c r="M26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>21</v>
-      </c>
-      <c r="R26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S26" t="n">
-        <v>6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="V26" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>27</v>
+        <v>19.4</v>
       </c>
       <c r="X26" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="Y26" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA26" t="n">
         <v>9</v>
       </c>
-      <c r="Z26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AB26" t="n">
-        <v>-5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>225</v>
+        <v>221.37</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="AH26" t="n">
         <v>215</v>
@@ -3157,10 +3118,10 @@
         <v>235</v>
       </c>
       <c r="AK26" t="n">
-        <v>134.62</v>
+        <v>135.21</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.62</v>
+        <v>0.59</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -3168,61 +3129,61 @@
       <c r="AN26" t="n">
         <v>142</v>
       </c>
-      <c r="AP26" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>13.86</v>
-      </c>
       <c r="BL26" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B27" t="n">
-        <v>151.5</v>
+        <v>145.2</v>
       </c>
       <c r="D27" t="n">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="F27" t="n">
-        <v>5.4</v>
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>35.5</v>
       </c>
       <c r="V27" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W27" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="X27" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z27" t="n">
         <v>13</v>
       </c>
       <c r="AA27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB27" t="n">
-        <v>-4.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>221.37</v>
+        <v>224.37</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="AH27" t="n">
         <v>215</v>
@@ -3231,10 +3192,10 @@
         <v>235</v>
       </c>
       <c r="AK27" t="n">
-        <v>135.21</v>
+        <v>135.61</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AM27" t="n">
         <v>110</v>
@@ -3243,60 +3204,60 @@
         <v>142</v>
       </c>
       <c r="BL27" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B28" t="n">
-        <v>145.2</v>
+        <v>146.3</v>
       </c>
       <c r="D28" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K28" t="n">
-        <v>100.3</v>
+        <v>98.2</v>
       </c>
       <c r="O28" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="V28" t="n">
-        <v>7.1</v>
+        <v>4.9</v>
       </c>
       <c r="W28" t="n">
-        <v>19.2</v>
+        <v>16.4</v>
       </c>
       <c r="X28" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB28" t="n">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>-1.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AF28" t="n">
-        <v>224.37</v>
+        <v>225.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AH28" t="n">
         <v>215</v>
@@ -3305,10 +3266,10 @@
         <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>135.61</v>
+        <v>135.28</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
@@ -3317,60 +3278,93 @@
         <v>142</v>
       </c>
       <c r="BL28" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B29" t="n">
-        <v>146.3</v>
+        <v>182.8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>86.8</v>
       </c>
       <c r="D29" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>33</v>
       </c>
       <c r="F29" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>41.1</v>
       </c>
       <c r="K29" t="n">
-        <v>98.2</v>
+        <v>74.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N29" t="n">
+        <v>33.5</v>
       </c>
       <c r="O29" t="n">
-        <v>35.1</v>
+        <v>38.4</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="n">
+        <v>22.4</v>
       </c>
       <c r="V29" t="n">
-        <v>4.9</v>
+        <v>9.1</v>
       </c>
       <c r="W29" t="n">
-        <v>16.4</v>
+        <v>15</v>
       </c>
       <c r="X29" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA29" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>-6.4</v>
+        <v>-10.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>225.93</v>
+        <v>218.63</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.56</v>
+        <v>-7.3</v>
       </c>
       <c r="AH29" t="n">
         <v>215</v>
@@ -3379,10 +3373,10 @@
         <v>235</v>
       </c>
       <c r="AK29" t="n">
-        <v>135.28</v>
+        <v>126.27</v>
       </c>
       <c r="AL29" t="n">
-        <v>-0.33</v>
+        <v>-9.01</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
@@ -3390,94 +3384,100 @@
       <c r="AN29" t="n">
         <v>142</v>
       </c>
+      <c r="AP29" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>14.7</v>
+      </c>
       <c r="BL29" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B30" t="n">
-        <v>182.8</v>
+        <v>181.8</v>
       </c>
       <c r="C30" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="D30" t="n">
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="E30" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="F30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H30" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="I30" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="J30" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="K30" t="n">
-        <v>74.2</v>
+        <v>76.8</v>
       </c>
       <c r="M30" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>33.5</v>
+        <v>35.7</v>
       </c>
       <c r="O30" t="n">
-        <v>38.4</v>
+        <v>39.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="R30" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="T30" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="V30" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="W30" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="X30" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
         <v>12</v>
       </c>
       <c r="AA30" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB30" t="n">
-        <v>-10.5</v>
+        <v>-4.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AF30" t="n">
-        <v>218.63</v>
+        <v>216.39</v>
       </c>
       <c r="AG30" t="n">
-        <v>-7.3</v>
+        <v>-2.23</v>
       </c>
       <c r="AH30" t="n">
         <v>215</v>
@@ -3486,10 +3486,10 @@
         <v>235</v>
       </c>
       <c r="AK30" t="n">
-        <v>126.27</v>
+        <v>123.32</v>
       </c>
       <c r="AL30" t="n">
-        <v>-9.01</v>
+        <v>-2.95</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
@@ -3498,99 +3498,99 @@
         <v>142</v>
       </c>
       <c r="AP30" t="n">
-        <v>82.66</v>
+        <v>79.08</v>
       </c>
       <c r="AS30" t="n">
-        <v>14.7</v>
+        <v>13.91</v>
       </c>
       <c r="BL30" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B31" t="n">
-        <v>181.8</v>
+        <v>183</v>
       </c>
       <c r="C31" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="D31" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="E31" t="n">
-        <v>34.2</v>
+        <v>33.7</v>
       </c>
       <c r="F31" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="I31" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="J31" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="K31" t="n">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>35.7</v>
+        <v>36.7</v>
       </c>
       <c r="O31" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="R31" t="n">
         <v>1.8</v>
       </c>
       <c r="S31" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="T31" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="V31" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="W31" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="X31" t="n">
         <v>10.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA31" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB31" t="n">
-        <v>-4.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD31" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="AF31" t="n">
-        <v>216.39</v>
+        <v>217.16</v>
       </c>
       <c r="AG31" t="n">
-        <v>-2.23</v>
+        <v>0.76</v>
       </c>
       <c r="AH31" t="n">
         <v>215</v>
@@ -3599,10 +3599,10 @@
         <v>235</v>
       </c>
       <c r="AK31" t="n">
-        <v>123.32</v>
+        <v>117.87</v>
       </c>
       <c r="AL31" t="n">
-        <v>-2.95</v>
+        <v>-5.45</v>
       </c>
       <c r="AM31" t="n">
         <v>110</v>
@@ -3611,99 +3611,66 @@
         <v>142</v>
       </c>
       <c r="AP31" t="n">
-        <v>79.08</v>
+        <v>78.56</v>
       </c>
       <c r="AS31" t="n">
-        <v>13.91</v>
+        <v>13.45</v>
       </c>
       <c r="BL31" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B32" t="n">
-        <v>183</v>
-      </c>
-      <c r="C32" t="n">
-        <v>84.7</v>
+        <v>163.8</v>
       </c>
       <c r="D32" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E32" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
-      </c>
-      <c r="H32" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I32" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J32" t="n">
-        <v>42.3</v>
+        <v>6.5</v>
       </c>
       <c r="K32" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M32" t="n">
-        <v>4</v>
-      </c>
-      <c r="N32" t="n">
-        <v>36.7</v>
+        <v>101.2</v>
       </c>
       <c r="O32" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S32" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T32" t="n">
-        <v>23.6</v>
+        <v>40.2</v>
       </c>
       <c r="V32" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W32" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X32" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y32" t="n">
         <v>8</v>
       </c>
       <c r="Z32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA32" t="n">
         <v>10</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>217.16</v>
+        <v>220.31</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.76</v>
+        <v>3.16</v>
       </c>
       <c r="AH32" t="n">
         <v>215</v>
@@ -3712,10 +3679,10 @@
         <v>235</v>
       </c>
       <c r="AK32" t="n">
-        <v>117.87</v>
+        <v>116.52</v>
       </c>
       <c r="AL32" t="n">
-        <v>-5.45</v>
+        <v>-1.35</v>
       </c>
       <c r="AM32" t="n">
         <v>110</v>
@@ -3723,67 +3690,61 @@
       <c r="AN32" t="n">
         <v>142</v>
       </c>
-      <c r="AP32" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>13.45</v>
-      </c>
       <c r="BL32" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B33" t="n">
-        <v>163.8</v>
+        <v>155.9</v>
       </c>
       <c r="D33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F33" t="n">
         <v>6.5</v>
       </c>
       <c r="K33" t="n">
-        <v>101.2</v>
+        <v>99.3</v>
       </c>
       <c r="O33" t="n">
-        <v>40.2</v>
+        <v>38.5</v>
       </c>
       <c r="V33" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="W33" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
       </c>
       <c r="X33" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF33" t="n">
-        <v>220.31</v>
+        <v>221.99</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="AH33" t="n">
         <v>215</v>
@@ -3792,10 +3753,10 @@
         <v>235</v>
       </c>
       <c r="AK33" t="n">
-        <v>116.52</v>
+        <v>116.37</v>
       </c>
       <c r="AL33" t="n">
-        <v>-1.35</v>
+        <v>-0.15</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -3804,60 +3765,60 @@
         <v>142</v>
       </c>
       <c r="BL33" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B34" t="n">
-        <v>155.9</v>
+        <v>141.3</v>
       </c>
       <c r="D34" t="n">
-        <v>28</v>
+        <v>26.3</v>
       </c>
       <c r="F34" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="K34" t="n">
-        <v>99.3</v>
+        <v>97.8</v>
       </c>
       <c r="O34" t="n">
-        <v>38.5</v>
+        <v>39.8</v>
       </c>
       <c r="V34" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W34" t="n">
-        <v>15.8</v>
+        <v>17.7</v>
       </c>
       <c r="X34" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z34" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AF34" t="n">
-        <v>221.99</v>
+        <v>225.14</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="AH34" t="n">
         <v>215</v>
@@ -3865,12 +3826,6 @@
       <c r="AI34" t="n">
         <v>235</v>
       </c>
-      <c r="AK34" t="n">
-        <v>116.37</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AM34" t="n">
         <v>110</v>
       </c>
@@ -3878,60 +3833,54 @@
         <v>142</v>
       </c>
       <c r="BL34" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B35" t="n">
-        <v>141.3</v>
+        <v>131.5</v>
       </c>
       <c r="D35" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="F35" t="n">
         <v>5.5</v>
       </c>
       <c r="K35" t="n">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="O35" t="n">
-        <v>39.8</v>
+        <v>35.7</v>
       </c>
       <c r="V35" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
-        <v>17.7</v>
+        <v>13.9</v>
       </c>
       <c r="X35" t="n">
-        <v>13.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z35" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA35" t="n">
         <v>15</v>
       </c>
-      <c r="AA35" t="n">
-        <v>14</v>
-      </c>
       <c r="AB35" t="n">
-        <v>0.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>225.14</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>3.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AH35" t="n">
         <v>215</v>
@@ -3946,54 +3895,93 @@
         <v>142</v>
       </c>
       <c r="BL35" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B36" t="n">
-        <v>131.5</v>
+        <v>153</v>
+      </c>
+      <c r="C36" t="n">
+        <v>71.8</v>
       </c>
       <c r="D36" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>24.7</v>
       </c>
       <c r="F36" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>41.1</v>
       </c>
       <c r="K36" t="n">
-        <v>97</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N36" t="n">
+        <v>33.5</v>
       </c>
       <c r="O36" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>23.2</v>
       </c>
       <c r="V36" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="W36" t="n">
-        <v>13.9</v>
+        <v>13</v>
       </c>
       <c r="X36" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y36" t="n">
         <v>12</v>
       </c>
       <c r="Z36" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AA36" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>-3.6</v>
+        <v>-6.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AH36" t="n">
         <v>215</v>
@@ -4001,100 +3989,112 @@
       <c r="AI36" t="n">
         <v>235</v>
       </c>
+      <c r="AK36" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>11.77</v>
+      </c>
       <c r="AM36" t="n">
         <v>110</v>
       </c>
       <c r="AN36" t="n">
         <v>142</v>
       </c>
+      <c r="AP36" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>14.8</v>
+      </c>
       <c r="BL36" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B37" t="n">
-        <v>153</v>
+        <v>165.8</v>
       </c>
       <c r="C37" t="n">
-        <v>71.8</v>
+        <v>77.3</v>
       </c>
       <c r="D37" t="n">
-        <v>28.6</v>
+        <v>29.3</v>
       </c>
       <c r="E37" t="n">
-        <v>24.7</v>
+        <v>27.7</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H37" t="n">
         <v>24.1</v>
       </c>
       <c r="I37" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="J37" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K37" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="N37" t="n">
-        <v>33.5</v>
+        <v>35.1</v>
       </c>
       <c r="O37" t="n">
-        <v>38.3</v>
+        <v>39.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="R37" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T37" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V37" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="W37" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X37" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z37" t="n">
         <v>13</v>
       </c>
-      <c r="X37" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>14</v>
-      </c>
       <c r="AA37" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>-6.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.3</v>
+        <v>9.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.6</v>
+        <v>4.4</v>
       </c>
       <c r="AF37" t="n">
-        <v>229.96</v>
+        <v>227.01</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="AH37" t="n">
         <v>215</v>
@@ -4103,10 +4103,10 @@
         <v>235</v>
       </c>
       <c r="AK37" t="n">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="AL37" t="n">
-        <v>11.77</v>
+        <v>0.01</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -4115,99 +4115,99 @@
         <v>142</v>
       </c>
       <c r="AP37" t="n">
-        <v>87.47</v>
+        <v>83.41</v>
       </c>
       <c r="AS37" t="n">
-        <v>14.8</v>
+        <v>14.52</v>
       </c>
       <c r="BL37" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B38" t="n">
-        <v>165.8</v>
+        <v>158.1</v>
       </c>
       <c r="C38" t="n">
-        <v>77.3</v>
+        <v>73.7</v>
       </c>
       <c r="D38" t="n">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
       <c r="E38" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="F38" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="H38" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="I38" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="K38" t="n">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="O38" t="n">
-        <v>39.8</v>
+        <v>40.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S38" t="n">
         <v>7</v>
       </c>
       <c r="T38" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V38" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="W38" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="X38" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z38" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA38" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.7</v>
+        <v>4.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>227.01</v>
+        <v>228.35</v>
       </c>
       <c r="AG38" t="n">
-        <v>-2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
         <v>215</v>
@@ -4216,10 +4216,10 @@
         <v>235</v>
       </c>
       <c r="AK38" t="n">
-        <v>128.15</v>
+        <v>128.86</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.01</v>
+        <v>0.71</v>
       </c>
       <c r="AM38" t="n">
         <v>110</v>
@@ -4228,99 +4228,99 @@
         <v>142</v>
       </c>
       <c r="AP38" t="n">
-        <v>83.41</v>
+        <v>82.37</v>
       </c>
       <c r="AS38" t="n">
-        <v>14.52</v>
+        <v>14.22</v>
       </c>
       <c r="BL38" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B39" t="n">
-        <v>158.1</v>
+        <v>154.9</v>
       </c>
       <c r="C39" t="n">
-        <v>73.7</v>
+        <v>70.2</v>
       </c>
       <c r="D39" t="n">
-        <v>30.3</v>
+        <v>31.5</v>
       </c>
       <c r="E39" t="n">
-        <v>26</v>
+        <v>27.7</v>
       </c>
       <c r="F39" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="H39" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I39" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J39" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="K39" t="n">
-        <v>74.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N39" t="n">
-        <v>35.3</v>
+        <v>32.9</v>
       </c>
       <c r="O39" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
       <c r="Q39" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="T39" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V39" t="n">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="W39" t="n">
-        <v>19.3</v>
+        <v>25.2</v>
       </c>
       <c r="X39" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z39" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA39" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AB39" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>228.35</v>
+        <v>231.16</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.33</v>
+        <v>2.81</v>
       </c>
       <c r="AH39" t="n">
         <v>215</v>
@@ -4329,10 +4329,10 @@
         <v>235</v>
       </c>
       <c r="AK39" t="n">
-        <v>128.86</v>
+        <v>130.88</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.71</v>
+        <v>2.02</v>
       </c>
       <c r="AM39" t="n">
         <v>110</v>
@@ -4341,99 +4341,66 @@
         <v>142</v>
       </c>
       <c r="AP39" t="n">
-        <v>82.37</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="AS39" t="n">
-        <v>14.22</v>
+        <v>13.1</v>
       </c>
       <c r="BL39" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B40" t="n">
-        <v>154.9</v>
-      </c>
-      <c r="C40" t="n">
-        <v>70.2</v>
+        <v>152.2</v>
       </c>
       <c r="D40" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E40" t="n">
-        <v>27.7</v>
+        <v>31</v>
       </c>
       <c r="F40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H40" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J40" t="n">
-        <v>40.3</v>
+        <v>3.5</v>
       </c>
       <c r="K40" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="M40" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N40" t="n">
-        <v>32.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="R40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S40" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T40" t="n">
-        <v>23.7</v>
+        <v>34.4</v>
       </c>
       <c r="V40" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="W40" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="X40" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z40" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AA40" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AC40" t="n">
         <v>8.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>231.16</v>
+        <v>228.13</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.81</v>
+        <v>-3.03</v>
       </c>
       <c r="AH40" t="n">
         <v>215</v>
@@ -4441,79 +4408,67 @@
       <c r="AI40" t="n">
         <v>235</v>
       </c>
-      <c r="AK40" t="n">
-        <v>130.88</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AM40" t="n">
         <v>110</v>
       </c>
       <c r="AN40" t="n">
         <v>142</v>
       </c>
-      <c r="AP40" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>13.1</v>
-      </c>
       <c r="BL40" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B41" t="n">
-        <v>152.2</v>
+        <v>143.9</v>
       </c>
       <c r="D41" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F41" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K41" t="n">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="O41" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="V41" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="W41" t="n">
-        <v>25.5</v>
+        <v>17.6</v>
       </c>
       <c r="X41" t="n">
-        <v>17.5</v>
+        <v>14.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z41" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA41" t="n">
         <v>9</v>
       </c>
       <c r="AB41" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AF41" t="n">
-        <v>228.13</v>
+        <v>229.16</v>
       </c>
       <c r="AG41" t="n">
-        <v>-3.03</v>
+        <v>1.03</v>
       </c>
       <c r="AH41" t="n">
         <v>215</v>
@@ -4528,60 +4483,93 @@
         <v>142</v>
       </c>
       <c r="BL41" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B42" t="n">
-        <v>143.9</v>
+        <v>163.2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>73.7</v>
       </c>
       <c r="D42" t="n">
-        <v>30.8</v>
+        <v>30</v>
+      </c>
+      <c r="E42" t="n">
+        <v>28.2</v>
       </c>
       <c r="F42" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>40.1</v>
       </c>
       <c r="K42" t="n">
-        <v>99.2</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M42" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N42" t="n">
+        <v>32.9</v>
       </c>
       <c r="O42" t="n">
-        <v>35.2</v>
+        <v>39.7</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6</v>
+      </c>
+      <c r="T42" t="n">
+        <v>23.5</v>
       </c>
       <c r="V42" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="W42" t="n">
-        <v>17.6</v>
+        <v>20.1</v>
       </c>
       <c r="X42" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="Y42" t="n">
         <v>4</v>
       </c>
       <c r="Z42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA42" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB42" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>229.16</v>
+        <v>228.55</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.03</v>
+        <v>-0.61</v>
       </c>
       <c r="AH42" t="n">
         <v>215</v>
@@ -4589,100 +4577,112 @@
       <c r="AI42" t="n">
         <v>235</v>
       </c>
+      <c r="AK42" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>-3.82</v>
+      </c>
       <c r="AM42" t="n">
         <v>110</v>
       </c>
       <c r="AN42" t="n">
         <v>142</v>
       </c>
+      <c r="AP42" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>12.9</v>
+      </c>
       <c r="BL42" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B43" t="n">
-        <v>163.2</v>
+        <v>174.4</v>
       </c>
       <c r="C43" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>32.1</v>
       </c>
       <c r="E43" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="F43" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H43" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="I43" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="J43" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="K43" t="n">
-        <v>75.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="M43" t="n">
         <v>6.8</v>
       </c>
       <c r="N43" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
       <c r="O43" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="R43" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T43" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="V43" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="W43" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="X43" t="n">
-        <v>14.8</v>
+        <v>17.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z43" t="n">
         <v>13</v>
       </c>
       <c r="AA43" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC43" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AB43" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AD43" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF43" t="n">
-        <v>228.55</v>
+        <v>219.99</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.61</v>
+        <v>-8.56</v>
       </c>
       <c r="AH43" t="n">
         <v>215</v>
@@ -4691,10 +4691,10 @@
         <v>235</v>
       </c>
       <c r="AK43" t="n">
-        <v>127.06</v>
+        <v>125.61</v>
       </c>
       <c r="AL43" t="n">
-        <v>-3.82</v>
+        <v>-1.45</v>
       </c>
       <c r="AM43" t="n">
         <v>110</v>
@@ -4703,99 +4703,99 @@
         <v>142</v>
       </c>
       <c r="AP43" t="n">
-        <v>82.81</v>
+        <v>77.83</v>
       </c>
       <c r="AS43" t="n">
-        <v>12.9</v>
+        <v>12.96</v>
       </c>
       <c r="BL43" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B44" t="n">
-        <v>174.4</v>
+        <v>163.2</v>
       </c>
       <c r="C44" t="n">
-        <v>75.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="E44" t="n">
-        <v>30.8</v>
+        <v>26</v>
       </c>
       <c r="F44" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H44" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="I44" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="J44" t="n">
-        <v>39.5</v>
+        <v>40.1</v>
       </c>
       <c r="K44" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="M44" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="N44" t="n">
-        <v>35.8</v>
+        <v>34.3</v>
       </c>
       <c r="O44" t="n">
-        <v>42.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q44" t="n">
         <v>23.1</v>
       </c>
       <c r="R44" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S44" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="T44" t="n">
         <v>23.1</v>
       </c>
       <c r="V44" t="n">
-        <v>12.8</v>
+        <v>9.6</v>
       </c>
       <c r="W44" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="X44" t="n">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA44" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>219.99</v>
+        <v>219.22</v>
       </c>
       <c r="AG44" t="n">
-        <v>-8.56</v>
+        <v>-0.77</v>
       </c>
       <c r="AH44" t="n">
         <v>215</v>
@@ -4804,10 +4804,10 @@
         <v>235</v>
       </c>
       <c r="AK44" t="n">
-        <v>125.61</v>
+        <v>124.36</v>
       </c>
       <c r="AL44" t="n">
-        <v>-1.45</v>
+        <v>-1.25</v>
       </c>
       <c r="AM44" t="n">
         <v>110</v>
@@ -4816,99 +4816,99 @@
         <v>142</v>
       </c>
       <c r="AP44" t="n">
-        <v>77.83</v>
+        <v>76.81</v>
       </c>
       <c r="AS44" t="n">
-        <v>12.96</v>
+        <v>12.38</v>
       </c>
       <c r="BL44" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B45" t="n">
-        <v>163.2</v>
+        <v>152.7</v>
       </c>
       <c r="C45" t="n">
-        <v>70.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="D45" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="E45" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="F45" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="H45" t="n">
         <v>23.8</v>
       </c>
       <c r="I45" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J45" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K45" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M45" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N45" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="O45" t="n">
         <v>40.1</v>
       </c>
-      <c r="K45" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="M45" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N45" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="O45" t="n">
-        <v>41.5</v>
-      </c>
       <c r="Q45" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="R45" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S45" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V45" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W45" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="X45" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC45" t="n">
         <v>9.6</v>
       </c>
-      <c r="W45" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="X45" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AD45" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AF45" t="n">
-        <v>219.22</v>
+        <v>220.73</v>
       </c>
       <c r="AG45" t="n">
-        <v>-0.77</v>
+        <v>1.5</v>
       </c>
       <c r="AH45" t="n">
         <v>215</v>
@@ -4917,10 +4917,10 @@
         <v>235</v>
       </c>
       <c r="AK45" t="n">
-        <v>124.36</v>
+        <v>120.93</v>
       </c>
       <c r="AL45" t="n">
-        <v>-1.25</v>
+        <v>-3.43</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
@@ -4929,75 +4929,75 @@
         <v>142</v>
       </c>
       <c r="AP45" t="n">
-        <v>76.81</v>
+        <v>77.87</v>
       </c>
       <c r="AS45" t="n">
-        <v>12.38</v>
+        <v>13.26</v>
       </c>
       <c r="BL45" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B46" t="n">
-        <v>152.7</v>
+        <v>150.7</v>
       </c>
       <c r="C46" t="n">
-        <v>62.6</v>
+        <v>64.8</v>
       </c>
       <c r="D46" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
       <c r="E46" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
       </c>
       <c r="F46" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="H46" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="I46" t="n">
         <v>7.2</v>
       </c>
       <c r="J46" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="K46" t="n">
-        <v>69.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="M46" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="N46" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="O46" t="n">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q46" t="n">
         <v>23.2</v>
       </c>
       <c r="R46" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T46" t="n">
         <v>23.2</v>
       </c>
       <c r="V46" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="W46" t="n">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="X46" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y46" t="n">
         <v>10</v>
@@ -5006,22 +5006,22 @@
         <v>18</v>
       </c>
       <c r="AA46" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="AF46" t="n">
-        <v>220.73</v>
+        <v>220.58</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.5</v>
+        <v>-0.15</v>
       </c>
       <c r="AH46" t="n">
         <v>215</v>
@@ -5030,10 +5030,10 @@
         <v>235</v>
       </c>
       <c r="AK46" t="n">
-        <v>120.93</v>
+        <v>120.28</v>
       </c>
       <c r="AL46" t="n">
-        <v>-3.43</v>
+        <v>-0.65</v>
       </c>
       <c r="AM46" t="n">
         <v>110</v>
@@ -5042,99 +5042,54 @@
         <v>142</v>
       </c>
       <c r="AP46" t="n">
-        <v>77.87</v>
+        <v>77.22</v>
       </c>
       <c r="AS46" t="n">
-        <v>13.26</v>
+        <v>13.79</v>
       </c>
       <c r="BL46" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B47" t="n">
-        <v>150.7</v>
-      </c>
-      <c r="C47" t="n">
-        <v>64.8</v>
+        <v>138.2</v>
       </c>
       <c r="D47" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E47" t="n">
-        <v>27.1</v>
+        <v>33.6</v>
       </c>
       <c r="F47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H47" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="W47" t="n">
         <v>23.4</v>
       </c>
-      <c r="I47" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J47" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="K47" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="M47" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N47" t="n">
-        <v>33</v>
-      </c>
-      <c r="O47" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="R47" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3</v>
-      </c>
-      <c r="T47" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V47" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="W47" t="n">
-        <v>28.9</v>
-      </c>
       <c r="X47" t="n">
-        <v>21.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z47" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA47" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC47" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>220.58</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>-0.15</v>
+        <v>4.5</v>
       </c>
       <c r="AH47" t="n">
         <v>215</v>
@@ -5142,67 +5097,61 @@
       <c r="AI47" t="n">
         <v>235</v>
       </c>
-      <c r="AK47" t="n">
-        <v>120.28</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>-0.65</v>
-      </c>
       <c r="AM47" t="n">
         <v>110</v>
       </c>
       <c r="AN47" t="n">
         <v>142</v>
       </c>
-      <c r="AP47" t="n">
-        <v>77.22</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>13.79</v>
-      </c>
       <c r="BL47" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B48" t="n">
-        <v>138.2</v>
+        <v>126.5</v>
       </c>
       <c r="D48" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="F48" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="V48" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="W48" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="X48" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA48" t="n">
         <v>13</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD48" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>229.48</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>6.05</v>
       </c>
       <c r="AH48" t="n">
         <v>215</v>
@@ -5217,54 +5166,93 @@
         <v>142</v>
       </c>
       <c r="BL48" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B49" t="n">
-        <v>126.5</v>
+        <v>129.4</v>
+      </c>
+      <c r="C49" t="n">
+        <v>50.6</v>
       </c>
       <c r="D49" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>19.4</v>
       </c>
       <c r="F49" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
+      </c>
+      <c r="H49" t="n">
+        <v>24</v>
+      </c>
+      <c r="I49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J49" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K49" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N49" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O49" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>21.4</v>
       </c>
       <c r="V49" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="W49" t="n">
-        <v>22.3</v>
+        <v>23.9</v>
       </c>
       <c r="X49" t="n">
-        <v>17.4</v>
+        <v>19.1</v>
       </c>
       <c r="Y49" t="n">
         <v>8</v>
       </c>
       <c r="Z49" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AC49" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AF49" t="n">
-        <v>229.48</v>
+        <v>229.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>6.05</v>
+        <v>0.02</v>
       </c>
       <c r="AH49" t="n">
         <v>215</v>
@@ -5272,100 +5260,112 @@
       <c r="AI49" t="n">
         <v>235</v>
       </c>
+      <c r="AK49" t="n">
+        <v>128.37</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>8.09</v>
+      </c>
       <c r="AM49" t="n">
         <v>110</v>
       </c>
       <c r="AN49" t="n">
         <v>142</v>
       </c>
+      <c r="AP49" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>15.97</v>
+      </c>
       <c r="BL49" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B50" t="n">
-        <v>129.4</v>
+        <v>142.9</v>
       </c>
       <c r="C50" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="D50" t="n">
-        <v>31.5</v>
+        <v>34.7</v>
       </c>
       <c r="E50" t="n">
-        <v>19.4</v>
+        <v>24.8</v>
       </c>
       <c r="F50" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H50" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I50" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="J50" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="K50" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="M50" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N50" t="n">
-        <v>33.3</v>
+        <v>31.9</v>
       </c>
       <c r="O50" t="n">
-        <v>38</v>
+        <v>35.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="R50" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="V50" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="W50" t="n">
-        <v>23.9</v>
+        <v>25.8</v>
       </c>
       <c r="X50" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y50" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA50" t="n">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AC50" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD50" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>229.5</v>
+        <v>238.69</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.02</v>
+        <v>-2.8</v>
       </c>
       <c r="AH50" t="n">
         <v>215</v>
@@ -5374,10 +5374,10 @@
         <v>235</v>
       </c>
       <c r="AK50" t="n">
-        <v>128.37</v>
+        <v>134.59</v>
       </c>
       <c r="AL50" t="n">
-        <v>8.09</v>
+        <v>6.22</v>
       </c>
       <c r="AM50" t="n">
         <v>110</v>
@@ -5386,99 +5386,99 @@
         <v>142</v>
       </c>
       <c r="AP50" t="n">
-        <v>91.59999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="AS50" t="n">
-        <v>15.97</v>
+        <v>17.06</v>
       </c>
       <c r="BL50" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B51" t="n">
-        <v>142.9</v>
+        <v>148.1</v>
       </c>
       <c r="C51" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="D51" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="E51" t="n">
-        <v>24.8</v>
+        <v>31.5</v>
       </c>
       <c r="F51" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H51" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="I51" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J51" t="n">
-        <v>38.2</v>
+        <v>39.6</v>
       </c>
       <c r="K51" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M51" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N51" t="n">
-        <v>31.9</v>
+        <v>30.8</v>
       </c>
       <c r="O51" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="R51" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>19.7</v>
+        <v>20.7</v>
       </c>
       <c r="V51" t="n">
-        <v>12</v>
+        <v>13.1</v>
       </c>
       <c r="W51" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="X51" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="Y51" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z51" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA51" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="AC51" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AF51" t="n">
-        <v>238.69</v>
+        <v>233.48</v>
       </c>
       <c r="AG51" t="n">
-        <v>-2.8</v>
+        <v>-4.86</v>
       </c>
       <c r="AH51" t="n">
         <v>215</v>
@@ -5487,10 +5487,10 @@
         <v>235</v>
       </c>
       <c r="AK51" t="n">
-        <v>134.59</v>
+        <v>136.6</v>
       </c>
       <c r="AL51" t="n">
-        <v>6.22</v>
+        <v>2.01</v>
       </c>
       <c r="AM51" t="n">
         <v>110</v>
@@ -5499,99 +5499,99 @@
         <v>142</v>
       </c>
       <c r="AP51" t="n">
-        <v>89.05</v>
+        <v>86.25</v>
       </c>
       <c r="AS51" t="n">
-        <v>17.06</v>
+        <v>17.13</v>
       </c>
       <c r="BL51" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B52" t="n">
-        <v>148.1</v>
+        <v>143.4</v>
       </c>
       <c r="C52" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="D52" t="n">
-        <v>35.4</v>
+        <v>35.7</v>
       </c>
       <c r="E52" t="n">
-        <v>31.5</v>
+        <v>26.2</v>
       </c>
       <c r="F52" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H52" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="I52" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="K52" t="n">
-        <v>71</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="N52" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="O52" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="R52" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="V52" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W52" t="n">
-        <v>25.5</v>
+        <v>28.3</v>
       </c>
       <c r="X52" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="Y52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z52" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA52" t="n">
-        <v>15.5</v>
+        <v>17.9</v>
       </c>
       <c r="AB52" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AC52" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AF52" t="n">
-        <v>233.48</v>
+        <v>235.13</v>
       </c>
       <c r="AG52" t="n">
-        <v>-4.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH52" t="n">
         <v>215</v>
@@ -5600,10 +5600,10 @@
         <v>235</v>
       </c>
       <c r="AK52" t="n">
-        <v>136.6</v>
+        <v>135.66</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AM52" t="n">
         <v>110</v>
@@ -5612,57 +5612,57 @@
         <v>142</v>
       </c>
       <c r="AP52" t="n">
-        <v>86.25</v>
+        <v>88.27</v>
       </c>
       <c r="AS52" t="n">
-        <v>17.13</v>
+        <v>17.6</v>
       </c>
       <c r="BL52" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B53" t="n">
-        <v>143.4</v>
+        <v>144.9</v>
       </c>
       <c r="C53" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="D53" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="E53" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="F53" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="H53" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="I53" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J53" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="K53" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="N53" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="O53" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -5671,40 +5671,40 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="V53" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="W53" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="X53" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Y53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z53" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA53" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="AB53" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AF53" t="n">
-        <v>235.13</v>
+        <v>234.87</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.66</v>
+        <v>-0.26</v>
       </c>
       <c r="AH53" t="n">
         <v>215</v>
@@ -5713,10 +5713,10 @@
         <v>235</v>
       </c>
       <c r="AK53" t="n">
-        <v>135.66</v>
+        <v>136.33</v>
       </c>
       <c r="AL53" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="AM53" t="n">
         <v>110</v>
@@ -5725,99 +5725,60 @@
         <v>142</v>
       </c>
       <c r="AP53" t="n">
-        <v>88.27</v>
+        <v>87.09</v>
       </c>
       <c r="AS53" t="n">
-        <v>17.6</v>
+        <v>17.31</v>
       </c>
       <c r="BL53" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B54" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="C54" t="n">
-        <v>53</v>
+        <v>132.2</v>
       </c>
       <c r="D54" t="n">
         <v>35.6</v>
       </c>
-      <c r="E54" t="n">
-        <v>26</v>
-      </c>
       <c r="F54" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H54" t="n">
-        <v>24</v>
-      </c>
-      <c r="I54" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J54" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="K54" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N54" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="O54" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>21</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>14.4</v>
+        <v>11.6</v>
       </c>
       <c r="W54" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="X54" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="Y54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z54" t="n">
         <v>19</v>
       </c>
       <c r="AA54" t="n">
-        <v>16.3</v>
+        <v>13</v>
       </c>
       <c r="AB54" t="n">
-        <v>-1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AC54" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AF54" t="n">
-        <v>234.87</v>
+        <v>234.78</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="AH54" t="n">
         <v>215</v>
@@ -5825,73 +5786,61 @@
       <c r="AI54" t="n">
         <v>235</v>
       </c>
-      <c r="AK54" t="n">
-        <v>136.33</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AM54" t="n">
         <v>110</v>
       </c>
       <c r="AN54" t="n">
         <v>142</v>
       </c>
-      <c r="AP54" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>17.31</v>
-      </c>
       <c r="BL54" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B55" t="n">
-        <v>132.2</v>
+        <v>137.1</v>
       </c>
       <c r="D55" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="V55" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="W55" t="n">
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="X55" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y55" t="n">
         <v>7</v>
       </c>
       <c r="Z55" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA55" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.9</v>
+        <v>-5.3</v>
       </c>
       <c r="AC55" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD55" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF55" t="n">
-        <v>234.78</v>
+        <v>229.75</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AH55" t="n">
         <v>215</v>
@@ -5906,36 +5855,75 @@
         <v>142</v>
       </c>
       <c r="BL55" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B56" t="n">
-        <v>137.1</v>
+        <v>166.2</v>
+      </c>
+      <c r="C56" t="n">
+        <v>72.40000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>35.1</v>
+        <v>32.7</v>
+      </c>
+      <c r="E56" t="n">
+        <v>28.1</v>
       </c>
       <c r="F56" t="n">
         <v>3.3</v>
       </c>
+      <c r="H56" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9</v>
+      </c>
+      <c r="J56" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N56" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="O56" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>23.7</v>
+      </c>
       <c r="Y56" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z56" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA56" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF56" t="n">
-        <v>229.75</v>
+        <v>222.86</v>
       </c>
       <c r="AG56" t="n">
-        <v>-5.03</v>
+        <v>-6.9</v>
       </c>
       <c r="AH56" t="n">
         <v>215</v>
@@ -5943,82 +5931,94 @@
       <c r="AI56" t="n">
         <v>235</v>
       </c>
+      <c r="AK56" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="AM56" t="n">
         <v>110</v>
       </c>
       <c r="AN56" t="n">
         <v>142</v>
       </c>
+      <c r="AP56" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>15.01</v>
+      </c>
       <c r="BL56" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B57" t="n">
-        <v>166.2</v>
+        <v>166.3</v>
       </c>
       <c r="C57" t="n">
-        <v>72.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="E57" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="F57" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H57" t="n">
         <v>23.4</v>
       </c>
       <c r="I57" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>42.1</v>
+        <v>41.2</v>
       </c>
       <c r="K57" t="n">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="M57" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="N57" t="n">
-        <v>33.7</v>
+        <v>35.4</v>
       </c>
       <c r="O57" t="n">
-        <v>39.3</v>
+        <v>42.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R57" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Y57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z57" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA57" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AF57" t="n">
-        <v>222.86</v>
+        <v>218.37</v>
       </c>
       <c r="AG57" t="n">
-        <v>-6.9</v>
+        <v>-4.49</v>
       </c>
       <c r="AH57" t="n">
         <v>215</v>
@@ -6027,10 +6027,10 @@
         <v>235</v>
       </c>
       <c r="AK57" t="n">
-        <v>135.42</v>
+        <v>131.24</v>
       </c>
       <c r="AL57" t="n">
-        <v>-0.91</v>
+        <v>-4.18</v>
       </c>
       <c r="AM57" t="n">
         <v>110</v>
@@ -6039,81 +6039,81 @@
         <v>142</v>
       </c>
       <c r="AP57" t="n">
-        <v>81.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="AS57" t="n">
-        <v>15.01</v>
+        <v>12.97</v>
       </c>
       <c r="BL57" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B58" t="n">
-        <v>166.3</v>
+        <v>154.1</v>
       </c>
       <c r="C58" t="n">
-        <v>74.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="D58" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="E58" t="n">
-        <v>28.8</v>
+        <v>25.2</v>
       </c>
       <c r="F58" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H58" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I58" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J58" t="n">
-        <v>41.2</v>
+        <v>38.5</v>
       </c>
       <c r="K58" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="N58" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
       <c r="O58" t="n">
-        <v>42.6</v>
+        <v>40.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="R58" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T58" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="Y58" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z58" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AA58" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AF58" t="n">
-        <v>218.37</v>
+        <v>218.04</v>
       </c>
       <c r="AG58" t="n">
-        <v>-4.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AH58" t="n">
         <v>215</v>
@@ -6122,10 +6122,10 @@
         <v>235</v>
       </c>
       <c r="AK58" t="n">
-        <v>131.24</v>
+        <v>129.21</v>
       </c>
       <c r="AL58" t="n">
-        <v>-4.18</v>
+        <v>-2.03</v>
       </c>
       <c r="AM58" t="n">
         <v>110</v>
@@ -6134,81 +6134,81 @@
         <v>142</v>
       </c>
       <c r="AP58" t="n">
-        <v>79.98999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AS58" t="n">
-        <v>12.97</v>
+        <v>15.23</v>
       </c>
       <c r="BL58" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B59" t="n">
-        <v>154.1</v>
+        <v>148.8</v>
       </c>
       <c r="C59" t="n">
-        <v>65</v>
+        <v>57.6</v>
       </c>
       <c r="D59" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="E59" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="F59" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H59" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="I59" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J59" t="n">
-        <v>38.5</v>
+        <v>41.6</v>
       </c>
       <c r="K59" t="n">
-        <v>70.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="M59" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="N59" t="n">
-        <v>32.3</v>
+        <v>35</v>
       </c>
       <c r="O59" t="n">
-        <v>40.3</v>
+        <v>42.4</v>
       </c>
       <c r="Q59" t="n">
         <v>21.7</v>
       </c>
       <c r="R59" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S59" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
         <v>21.7</v>
       </c>
       <c r="Y59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z59" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA59" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="AF59" t="n">
-        <v>218.04</v>
+        <v>220.84</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH59" t="n">
         <v>215</v>
@@ -6217,10 +6217,10 @@
         <v>235</v>
       </c>
       <c r="AK59" t="n">
-        <v>129.21</v>
+        <v>129.07</v>
       </c>
       <c r="AL59" t="n">
-        <v>-2.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AM59" t="n">
         <v>110</v>
@@ -6229,81 +6229,81 @@
         <v>142</v>
       </c>
       <c r="AP59" t="n">
-        <v>82.90000000000001</v>
+        <v>85.52</v>
       </c>
       <c r="AS59" t="n">
-        <v>15.23</v>
+        <v>15.82</v>
       </c>
       <c r="BL59" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B60" t="n">
-        <v>148.8</v>
+        <v>146.8</v>
       </c>
       <c r="C60" t="n">
-        <v>57.6</v>
+        <v>52.8</v>
       </c>
       <c r="D60" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="E60" t="n">
-        <v>26.3</v>
+        <v>28.9</v>
       </c>
       <c r="F60" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="H60" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="I60" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J60" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="K60" t="n">
-        <v>74.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="N60" t="n">
-        <v>35</v>
+        <v>33.1</v>
       </c>
       <c r="O60" t="n">
-        <v>42.4</v>
+        <v>38.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="R60" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="Y60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA60" t="n">
-        <v>15.6</v>
+        <v>16.1</v>
       </c>
       <c r="AF60" t="n">
-        <v>220.84</v>
+        <v>225.87</v>
       </c>
       <c r="AG60" t="n">
-        <v>2.8</v>
+        <v>5.03</v>
       </c>
       <c r="AH60" t="n">
         <v>215</v>
@@ -6312,10 +6312,10 @@
         <v>235</v>
       </c>
       <c r="AK60" t="n">
-        <v>129.07</v>
+        <v>130.73</v>
       </c>
       <c r="AL60" t="n">
-        <v>-0.14</v>
+        <v>1.66</v>
       </c>
       <c r="AM60" t="n">
         <v>110</v>
@@ -6324,36 +6324,36 @@
         <v>142</v>
       </c>
       <c r="AP60" t="n">
-        <v>85.52</v>
+        <v>88.2</v>
       </c>
       <c r="AS60" t="n">
-        <v>15.82</v>
+        <v>15.76</v>
       </c>
       <c r="BL60" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B61" t="n">
-        <v>131.7</v>
+        <v>133.9</v>
       </c>
       <c r="D61" t="n">
-        <v>33.2</v>
+        <v>34.7</v>
       </c>
       <c r="F61" t="n">
         <v>3.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z61" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA61" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH61" t="n">
         <v>215</v>
@@ -6368,30 +6368,30 @@
         <v>142</v>
       </c>
       <c r="BL61" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B62" t="n">
-        <v>133.9</v>
+        <v>137.5</v>
       </c>
       <c r="D62" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
       <c r="F62" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z62" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA62" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AH62" t="n">
         <v>215</v>
@@ -6406,7 +6406,7 @@
         <v>142</v>
       </c>
       <c r="BL62" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
   </sheetData>
